--- a/database/catalogos/catalogo_maestro.xlsx
+++ b/database/catalogos/catalogo_maestro.xlsx
@@ -1,45 +1,39 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr codeName="ThisWorkbook"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/fernandaromeroplacencia/Downloads/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{60301EF5-5AAA-934F-B1C8-0B20C46B948D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="600" windowWidth="28800" windowHeight="15900" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView activeTab="4" autoFilterDateGrouping="true" firstSheet="0" minimized="false" showHorizontalScroll="true" showSheetTabs="true" showVerticalScroll="true" tabRatio="600" visibility="visible"/>
   </bookViews>
   <sheets>
-    <sheet name="categorias" sheetId="1" r:id="rId1"/>
-    <sheet name="productos" sheetId="2" r:id="rId2"/>
-    <sheet name="extras" sheetId="3" r:id="rId3"/>
-    <sheet name="grupos_opciones" sheetId="4" r:id="rId4"/>
-    <sheet name="opciones" sheetId="5" r:id="rId5"/>
-    <sheet name="producto_grupo_opcion" sheetId="6" r:id="rId6"/>
-    <sheet name="componentes_preparacion" sheetId="8" r:id="rId7"/>
-    <sheet name="menu_dia_opciones" sheetId="9" r:id="rId8"/>
-    <sheet name="readme" sheetId="10" r:id="rId9"/>
+    <sheet name="categorias" sheetId="1" r:id="rId4"/>
+    <sheet name="productos" sheetId="2" r:id="rId5"/>
+    <sheet name="extras" sheetId="3" r:id="rId6"/>
+    <sheet name="grupos_opciones" sheetId="4" r:id="rId7"/>
+    <sheet name="opciones" sheetId="5" r:id="rId8"/>
+    <sheet name="producto_grupo_opcion" sheetId="6" r:id="rId9"/>
+    <sheet name="componentes_preparacion" sheetId="7" r:id="rId10"/>
+    <sheet name="menu_dia_opciones" sheetId="8" r:id="rId11"/>
+    <sheet name="readme" sheetId="9" r:id="rId12"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">categorias!$A$1:$E$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">componentes_preparacion!$A$1:$G$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">extras!$A$1:$F$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">grupos_opciones!$A$1:$K$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">menu_dia_opciones!$A$1:$F$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">opciones!$A$1:$H$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">producto_grupo_opcion!$A$1:$G$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">productos!$A$1:$P$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">readme!$A$1:$B$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'categorias'!$A$1:$E$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'productos'!$A$1:$P$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'extras'!$A$1:$F$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'grupos_opciones'!$A$1:$K$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'opciones'!$A$1:$H$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'producto_grupo_opcion'!$A$1:$G$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'componentes_preparacion'!$A$1:$G$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'menu_dia_opciones'!$A$1:$F$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'readme'!$A$1:$B$1</definedName>
   </definedNames>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="999999" calcMode="auto" calcCompleted="1" fullCalcOnLoad="0" forceFullCalc="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1120" uniqueCount="563">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="565">
   <si>
     <t>slug</t>
   </si>
@@ -137,6 +131,12 @@
     <t>Chilaquiles</t>
   </si>
   <si>
+    <t>media_orden_chilaquiles</t>
+  </si>
+  <si>
+    <t>Media orden chilaquiles</t>
+  </si>
+  <si>
     <t>capuccino</t>
   </si>
   <si>
@@ -251,6 +251,30 @@
     <t>Pechuga empanizada</t>
   </si>
   <si>
+    <t>bistec_asado</t>
+  </si>
+  <si>
+    <t>Bistec asado</t>
+  </si>
+  <si>
+    <t>bistec_empanizado</t>
+  </si>
+  <si>
+    <t>Bistec empanizado</t>
+  </si>
+  <si>
+    <t>costilla_asada</t>
+  </si>
+  <si>
+    <t>Costilla asada</t>
+  </si>
+  <si>
+    <t>arrachera</t>
+  </si>
+  <si>
+    <t>Arachera</t>
+  </si>
+  <si>
     <t>comida_dia</t>
   </si>
   <si>
@@ -407,6 +431,12 @@
     <t>Desechable grande</t>
   </si>
   <si>
+    <t>otro</t>
+  </si>
+  <si>
+    <t>Otro</t>
+  </si>
+  <si>
     <t>permite_cantidad</t>
   </si>
   <si>
@@ -518,18 +548,6 @@
     <t>Pollo desmenuzado</t>
   </si>
   <si>
-    <t>bistec_asado</t>
-  </si>
-  <si>
-    <t>Bistec asado</t>
-  </si>
-  <si>
-    <t>bistec_empanizado</t>
-  </si>
-  <si>
-    <t>Bistec empanizado</t>
-  </si>
-  <si>
     <t>frijoles</t>
   </si>
   <si>
@@ -584,9 +602,6 @@
     <t>Chistorra</t>
   </si>
   <si>
-    <t>arrachera</t>
-  </si>
-  <si>
     <t>Arrachera</t>
   </si>
   <si>
@@ -776,6 +791,12 @@
     <t>Chimichurri</t>
   </si>
   <si>
+    <t>guarnicion</t>
+  </si>
+  <si>
+    <t>Guarnicion</t>
+  </si>
+  <si>
     <t>grupo_slug</t>
   </si>
   <si>
@@ -1427,6 +1448,42 @@
     <t>Huevo Chorizo</t>
   </si>
   <si>
+    <t>guarnicion_sin_nada</t>
+  </si>
+  <si>
+    <t>Guarnicion: Sin guarnicion</t>
+  </si>
+  <si>
+    <t>Sin Guarnicion</t>
+  </si>
+  <si>
+    <t>guarnicion_pure_papa</t>
+  </si>
+  <si>
+    <t>Guarnicion: Pure Papa</t>
+  </si>
+  <si>
+    <t>Guarnicion Pure Papa</t>
+  </si>
+  <si>
+    <t>guarnicion_papas_francesa</t>
+  </si>
+  <si>
+    <t>Guarnicion: Papas a la francesa</t>
+  </si>
+  <si>
+    <t>Guarnicion Papas Francesa</t>
+  </si>
+  <si>
+    <t>guarnicion_ensalda</t>
+  </si>
+  <si>
+    <t>Guarnicion: Ensalada</t>
+  </si>
+  <si>
+    <t>Guarnicion Ensalda</t>
+  </si>
+  <si>
     <t>producto_sku</t>
   </si>
   <si>
@@ -1445,6 +1502,9 @@
     <t>CHILAQUILES</t>
   </si>
   <si>
+    <t>MEDIA ORDEN CHILAQUILES</t>
+  </si>
+  <si>
     <t>solo</t>
   </si>
   <si>
@@ -1505,6 +1565,18 @@
     <t>PECHUGA EMPANIZADA</t>
   </si>
   <si>
+    <t>BISTEC ASADO</t>
+  </si>
+  <si>
+    <t>BISTEC EMPANIZADO</t>
+  </si>
+  <si>
+    <t>COSTILLA ASADA</t>
+  </si>
+  <si>
+    <t>ARRACHERA</t>
+  </si>
+  <si>
     <t>comida</t>
   </si>
   <si>
@@ -1619,6 +1691,9 @@
     <t>Orden recomendado</t>
   </si>
   <si>
+    <t>1) categorias, 2) productos, 3) extras, 4) grupos_opciones, 5) opciones, 6) producto_grupo_opcion, 7) componentes_preparacion, 8) menu_dia_opciones.</t>
+  </si>
+  <si>
     <t>Claves estables</t>
   </si>
   <si>
@@ -1653,105 +1728,31 @@
   </si>
   <si>
     <t>php artisan pos:generar-catalogo-maestro-template --force</t>
-  </si>
-  <si>
-    <t>media_orden_chilaquiles</t>
-  </si>
-  <si>
-    <t>Media orden chilaquiles</t>
-  </si>
-  <si>
-    <t>guarnicion</t>
-  </si>
-  <si>
-    <t>guarnicion_pure_papa</t>
-  </si>
-  <si>
-    <t>guarnicion_papas_francesa</t>
-  </si>
-  <si>
-    <t>guarnicion_ensalda</t>
-  </si>
-  <si>
-    <t>Guarnicion: Pure Papa</t>
-  </si>
-  <si>
-    <t>Guarnicion: Papas a la francesa</t>
-  </si>
-  <si>
-    <t>Guarnicion: Ensalada</t>
-  </si>
-  <si>
-    <t>Guarnicion Pure Papa</t>
-  </si>
-  <si>
-    <t>Guarnicion Papas Francesa</t>
-  </si>
-  <si>
-    <t>Guarnicion Ensalda</t>
-  </si>
-  <si>
-    <t>costilla_asada</t>
-  </si>
-  <si>
-    <t>Costilla asada</t>
-  </si>
-  <si>
-    <t>Arachera</t>
-  </si>
-  <si>
-    <t>Sin Guarnicion</t>
-  </si>
-  <si>
-    <t>guarnicion_sin_nada</t>
-  </si>
-  <si>
-    <t>Guarnicion: Sin guarnicion</t>
-  </si>
-  <si>
-    <t>BISTEC ASADO</t>
-  </si>
-  <si>
-    <t>BISTEC EMPANIZADO</t>
-  </si>
-  <si>
-    <t>COSTILLA ASADA</t>
-  </si>
-  <si>
-    <t>ARRACHERA</t>
-  </si>
-  <si>
-    <t>MEDIA ORDEN CHILAQUILES</t>
-  </si>
-  <si>
-    <t>1) categorias, 2) productos, 3) extras, 4) grupos_opciones, 5) opciones, 6) producto_grupo_opcion, 7) componentes_preparacion, 8) menu_dia_opciones.</t>
-  </si>
-  <si>
-    <t>Guarnicion</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="2">
     <font>
+      <b val="0"/>
+      <i val="0"/>
+      <strike val="0"/>
+      <u val="none"/>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
     </font>
     <font>
-      <b/>
+      <b val="1"/>
+      <i val="0"/>
+      <strike val="0"/>
+      <u val="none"/>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
     </font>
   </fonts>
   <fills count="3">
@@ -1781,32 +1782,24 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="6">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="0" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0"/>
+    <xf xfId="0" fontId="1" numFmtId="0" fillId="2" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="0"/>
+    <xf xfId="0" fontId="1" numFmtId="0" fillId="2" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="1">
+      <alignment vertical="bottom" textRotation="0" wrapText="true" shrinkToFit="false"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment wrapText="1"/>
+    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="0" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="1">
+      <alignment vertical="bottom" textRotation="0" wrapText="true" shrinkToFit="false"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="0" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0"/>
+    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="0" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="1">
+      <alignment vertical="bottom" textRotation="0" wrapText="true" shrinkToFit="false"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium9"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <tableStyles defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotTableStyle1"/>
 </styleSheet>
 </file>
 
@@ -2096,18 +2089,21 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr filterMode="1">
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+  </sheetPr>
   <dimension ref="A1:E6"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="14.4" defaultColWidth="8.83203125" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col min="1" max="1" width="12.6640625" customWidth="1"/>
-    <col min="2" max="2" width="13" customWidth="1"/>
-    <col min="3" max="3" width="8.1640625" customWidth="1"/>
-    <col min="4" max="4" width="10.5" customWidth="1"/>
-    <col min="5" max="5" width="9.33203125" customWidth="1"/>
+    <col min="1" max="1" width="12.6640625" customWidth="true" style="0"/>
+    <col min="2" max="2" width="13" customWidth="true" style="0"/>
+    <col min="3" max="3" width="8.1640625" customWidth="true" style="0"/>
+    <col min="4" max="4" width="10.5" customWidth="true" style="0"/>
+    <col min="5" max="5" width="9.33203125" customWidth="true" style="0"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:5">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2124,7 +2120,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:5">
       <c r="A2" t="s">
         <v>5</v>
       </c>
@@ -2141,7 +2137,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:5">
       <c r="A3" t="s">
         <v>8</v>
       </c>
@@ -2158,7 +2154,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:5">
       <c r="A4" t="s">
         <v>11</v>
       </c>
@@ -2175,7 +2171,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:5">
       <c r="A5" t="s">
         <v>13</v>
       </c>
@@ -2192,7 +2188,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:5">
       <c r="A6" t="s">
         <v>15</v>
       </c>
@@ -2210,35 +2206,40 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E1" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:E1"/>
+  <printOptions gridLines="false" gridLinesSet="true"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait"/>
+  <pageSetup paperSize="1" orientation="portrait" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:P52"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr filterMode="1">
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+  </sheetPr>
+  <dimension ref="A1:P53"/>
+  <sheetFormatPr defaultRowHeight="14.4" defaultColWidth="8.83203125" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col min="1" max="1" width="26.83203125" customWidth="1"/>
-    <col min="2" max="2" width="25.83203125" customWidth="1"/>
-    <col min="3" max="3" width="19.83203125" customWidth="1"/>
-    <col min="4" max="4" width="10.5" customWidth="1"/>
-    <col min="5" max="5" width="9.33203125" customWidth="1"/>
-    <col min="6" max="6" width="10.5" customWidth="1"/>
-    <col min="7" max="7" width="17.5" customWidth="1"/>
-    <col min="8" max="8" width="22.33203125" customWidth="1"/>
-    <col min="9" max="9" width="19.83203125" customWidth="1"/>
-    <col min="10" max="10" width="25.6640625" customWidth="1"/>
-    <col min="11" max="11" width="23.5" customWidth="1"/>
-    <col min="12" max="12" width="17.5" customWidth="1"/>
-    <col min="13" max="13" width="15.1640625" customWidth="1"/>
-    <col min="14" max="15" width="14" customWidth="1"/>
-    <col min="16" max="16" width="9.33203125" customWidth="1"/>
+    <col min="1" max="1" width="26.83203125" customWidth="true" style="0"/>
+    <col min="2" max="2" width="25.83203125" customWidth="true" style="0"/>
+    <col min="3" max="3" width="19.83203125" customWidth="true" style="0"/>
+    <col min="4" max="4" width="10.5" customWidth="true" style="0"/>
+    <col min="5" max="5" width="9.33203125" customWidth="true" style="0"/>
+    <col min="6" max="6" width="10.5" customWidth="true" style="0"/>
+    <col min="7" max="7" width="17.5" customWidth="true" style="0"/>
+    <col min="8" max="8" width="22.33203125" customWidth="true" style="0"/>
+    <col min="9" max="9" width="19.83203125" customWidth="true" style="0"/>
+    <col min="10" max="10" width="25.6640625" customWidth="true" style="0"/>
+    <col min="11" max="11" width="23.5" customWidth="true" style="0"/>
+    <col min="12" max="12" width="17.5" customWidth="true" style="0"/>
+    <col min="13" max="13" width="15.1640625" customWidth="true" style="0"/>
+    <col min="14" max="14" width="14" customWidth="true" style="0"/>
+    <col min="15" max="15" width="14" customWidth="true" style="0"/>
+    <col min="16" max="16" width="9.33203125" customWidth="true" style="0"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:16">
       <c r="A1" s="1" t="s">
         <v>17</v>
       </c>
@@ -2288,7 +2289,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:16">
       <c r="A2" t="s">
         <v>30</v>
       </c>
@@ -2338,12 +2339,12 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:16">
       <c r="A3" s="4" t="s">
-        <v>538</v>
+        <v>32</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>539</v>
+        <v>33</v>
       </c>
       <c r="C3" s="4" t="s">
         <v>5</v>
@@ -2388,12 +2389,12 @@
         <v>20</v>
       </c>
     </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:16">
       <c r="A4" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B4" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="C4" t="s">
         <v>8</v>
@@ -2438,12 +2439,12 @@
         <v>30</v>
       </c>
     </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:16">
       <c r="A5" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B5" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="C5" t="s">
         <v>5</v>
@@ -2488,12 +2489,12 @@
         <v>40</v>
       </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:16">
       <c r="A6" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B6" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C6" t="s">
         <v>5</v>
@@ -2538,12 +2539,12 @@
         <v>50</v>
       </c>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:16">
       <c r="A7" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B7" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="C7" t="s">
         <v>5</v>
@@ -2588,12 +2589,12 @@
         <v>60</v>
       </c>
     </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:16">
       <c r="A8" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B8" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="C8" t="s">
         <v>5</v>
@@ -2638,12 +2639,12 @@
         <v>70</v>
       </c>
     </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:16">
       <c r="A9" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B9" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="C9" t="s">
         <v>5</v>
@@ -2688,12 +2689,12 @@
         <v>80</v>
       </c>
     </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:16">
       <c r="A10" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="B10" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="C10" t="s">
         <v>5</v>
@@ -2738,12 +2739,12 @@
         <v>90</v>
       </c>
     </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:16">
       <c r="A11" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="B11" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="C11" t="s">
         <v>5</v>
@@ -2788,12 +2789,12 @@
         <v>100</v>
       </c>
     </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:16">
       <c r="A12" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="B12" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="C12" t="s">
         <v>5</v>
@@ -2838,12 +2839,12 @@
         <v>110</v>
       </c>
     </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:16">
       <c r="A13" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="B13" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="C13" t="s">
         <v>5</v>
@@ -2888,12 +2889,12 @@
         <v>120</v>
       </c>
     </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:16">
       <c r="A14" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="B14" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="C14" t="s">
         <v>5</v>
@@ -2938,12 +2939,12 @@
         <v>130</v>
       </c>
     </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:16">
       <c r="A15" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="B15" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="C15" t="s">
         <v>5</v>
@@ -2988,12 +2989,12 @@
         <v>140</v>
       </c>
     </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:16">
       <c r="A16" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B16" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C16" t="s">
         <v>5</v>
@@ -3038,12 +3039,12 @@
         <v>150</v>
       </c>
     </row>
-    <row r="17" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:16">
       <c r="A17" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="B17" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="C17" t="s">
         <v>5</v>
@@ -3088,12 +3089,12 @@
         <v>160</v>
       </c>
     </row>
-    <row r="18" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:16">
       <c r="A18" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="B18" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="C18" t="s">
         <v>5</v>
@@ -3138,12 +3139,12 @@
         <v>170</v>
       </c>
     </row>
-    <row r="19" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:16">
       <c r="A19" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="B19" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="C19" t="s">
         <v>5</v>
@@ -3188,12 +3189,12 @@
         <v>180</v>
       </c>
     </row>
-    <row r="20" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:16">
       <c r="A20" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="B20" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="C20" t="s">
         <v>5</v>
@@ -3238,12 +3239,12 @@
         <v>190</v>
       </c>
     </row>
-    <row r="21" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:16">
       <c r="A21" s="4" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="B21" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="C21" t="s">
         <v>5</v>
@@ -3288,12 +3289,12 @@
         <v>200</v>
       </c>
     </row>
-    <row r="22" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:16">
       <c r="A22" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="B22" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="C22" t="s">
         <v>5</v>
@@ -3338,12 +3339,12 @@
         <v>210</v>
       </c>
     </row>
-    <row r="23" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:16">
       <c r="A23" s="4" t="s">
-        <v>159</v>
+        <v>72</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>160</v>
+        <v>73</v>
       </c>
       <c r="C23" t="s">
         <v>5</v>
@@ -3388,12 +3389,12 @@
         <v>220</v>
       </c>
     </row>
-    <row r="24" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:16">
       <c r="A24" s="4" t="s">
-        <v>161</v>
+        <v>74</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>162</v>
+        <v>75</v>
       </c>
       <c r="C24" t="s">
         <v>5</v>
@@ -3438,12 +3439,12 @@
         <v>230</v>
       </c>
     </row>
-    <row r="25" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:16">
       <c r="A25" s="4" t="s">
-        <v>550</v>
+        <v>76</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>551</v>
+        <v>77</v>
       </c>
       <c r="C25" t="s">
         <v>5</v>
@@ -3488,12 +3489,12 @@
         <v>240</v>
       </c>
     </row>
-    <row r="26" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:16">
       <c r="A26" s="4" t="s">
-        <v>181</v>
+        <v>78</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>552</v>
+        <v>79</v>
       </c>
       <c r="C26" t="s">
         <v>5</v>
@@ -3538,12 +3539,12 @@
         <v>250</v>
       </c>
     </row>
-    <row r="27" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:16">
       <c r="A27" t="s">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="B27" t="s">
-        <v>71</v>
+        <v>81</v>
       </c>
       <c r="C27" t="s">
         <v>11</v>
@@ -3588,12 +3589,12 @@
         <v>260</v>
       </c>
     </row>
-    <row r="28" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:16">
       <c r="A28" t="s">
-        <v>72</v>
+        <v>82</v>
       </c>
       <c r="B28" t="s">
-        <v>73</v>
+        <v>83</v>
       </c>
       <c r="C28" t="s">
         <v>11</v>
@@ -3638,12 +3639,12 @@
         <v>270</v>
       </c>
     </row>
-    <row r="29" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:16">
       <c r="A29" t="s">
-        <v>74</v>
+        <v>84</v>
       </c>
       <c r="B29" t="s">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="C29" t="s">
         <v>11</v>
@@ -3688,12 +3689,12 @@
         <v>280</v>
       </c>
     </row>
-    <row r="30" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:16">
       <c r="A30" t="s">
-        <v>76</v>
+        <v>86</v>
       </c>
       <c r="B30" t="s">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="C30" t="s">
         <v>11</v>
@@ -3738,12 +3739,12 @@
         <v>290</v>
       </c>
     </row>
-    <row r="31" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:16">
       <c r="A31" t="s">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="B31" t="s">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="C31" t="s">
         <v>11</v>
@@ -3788,12 +3789,12 @@
         <v>300</v>
       </c>
     </row>
-    <row r="32" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:16">
       <c r="A32" t="s">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="B32" t="s">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="C32" t="s">
         <v>5</v>
@@ -3838,12 +3839,12 @@
         <v>310</v>
       </c>
     </row>
-    <row r="33" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:16">
       <c r="A33" t="s">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="B33" t="s">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="C33" t="s">
         <v>5</v>
@@ -3888,12 +3889,12 @@
         <v>320</v>
       </c>
     </row>
-    <row r="34" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:16">
       <c r="A34" t="s">
-        <v>84</v>
+        <v>94</v>
       </c>
       <c r="B34" t="s">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="C34" t="s">
         <v>5</v>
@@ -3938,12 +3939,12 @@
         <v>330</v>
       </c>
     </row>
-    <row r="35" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:16">
       <c r="A35" t="s">
-        <v>86</v>
+        <v>96</v>
       </c>
       <c r="B35" t="s">
-        <v>87</v>
+        <v>97</v>
       </c>
       <c r="C35" t="s">
         <v>5</v>
@@ -3988,12 +3989,12 @@
         <v>340</v>
       </c>
     </row>
-    <row r="36" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:16">
       <c r="A36" t="s">
-        <v>88</v>
+        <v>98</v>
       </c>
       <c r="B36" t="s">
-        <v>89</v>
+        <v>99</v>
       </c>
       <c r="C36" t="s">
         <v>5</v>
@@ -4038,12 +4039,12 @@
         <v>350</v>
       </c>
     </row>
-    <row r="37" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:16">
       <c r="A37" t="s">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="B37" t="s">
-        <v>91</v>
+        <v>101</v>
       </c>
       <c r="C37" t="s">
         <v>5</v>
@@ -4088,12 +4089,12 @@
         <v>360</v>
       </c>
     </row>
-    <row r="38" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:16">
       <c r="A38" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="B38" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C38" t="s">
         <v>5</v>
@@ -4138,12 +4139,12 @@
         <v>370</v>
       </c>
     </row>
-    <row r="39" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:16">
       <c r="A39" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="B39" t="s">
-        <v>95</v>
+        <v>105</v>
       </c>
       <c r="C39" t="s">
         <v>8</v>
@@ -4188,12 +4189,12 @@
         <v>380</v>
       </c>
     </row>
-    <row r="40" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:16">
       <c r="A40" t="s">
-        <v>96</v>
+        <v>106</v>
       </c>
       <c r="B40" t="s">
-        <v>97</v>
+        <v>107</v>
       </c>
       <c r="C40" t="s">
         <v>8</v>
@@ -4238,12 +4239,12 @@
         <v>390</v>
       </c>
     </row>
-    <row r="41" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:16">
       <c r="A41" t="s">
-        <v>98</v>
+        <v>108</v>
       </c>
       <c r="B41" t="s">
-        <v>99</v>
+        <v>109</v>
       </c>
       <c r="C41" t="s">
         <v>8</v>
@@ -4288,12 +4289,12 @@
         <v>400</v>
       </c>
     </row>
-    <row r="42" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:16">
       <c r="A42" t="s">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="B42" t="s">
-        <v>101</v>
+        <v>111</v>
       </c>
       <c r="C42" t="s">
         <v>8</v>
@@ -4338,12 +4339,12 @@
         <v>410</v>
       </c>
     </row>
-    <row r="43" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:16">
       <c r="A43" t="s">
-        <v>102</v>
+        <v>112</v>
       </c>
       <c r="B43" t="s">
-        <v>103</v>
+        <v>113</v>
       </c>
       <c r="C43" t="s">
         <v>8</v>
@@ -4388,12 +4389,12 @@
         <v>420</v>
       </c>
     </row>
-    <row r="44" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:16">
       <c r="A44" t="s">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="B44" t="s">
-        <v>105</v>
+        <v>115</v>
       </c>
       <c r="C44" t="s">
         <v>8</v>
@@ -4438,12 +4439,12 @@
         <v>430</v>
       </c>
     </row>
-    <row r="45" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:16">
       <c r="A45" t="s">
-        <v>106</v>
+        <v>116</v>
       </c>
       <c r="B45" t="s">
-        <v>107</v>
+        <v>117</v>
       </c>
       <c r="C45" t="s">
         <v>8</v>
@@ -4488,12 +4489,12 @@
         <v>440</v>
       </c>
     </row>
-    <row r="46" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:16">
       <c r="A46" t="s">
-        <v>108</v>
+        <v>118</v>
       </c>
       <c r="B46" t="s">
-        <v>109</v>
+        <v>119</v>
       </c>
       <c r="C46" t="s">
         <v>8</v>
@@ -4538,12 +4539,12 @@
         <v>450</v>
       </c>
     </row>
-    <row r="47" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:16">
       <c r="A47" t="s">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="B47" t="s">
-        <v>111</v>
+        <v>121</v>
       </c>
       <c r="C47" t="s">
         <v>13</v>
@@ -4588,12 +4589,12 @@
         <v>460</v>
       </c>
     </row>
-    <row r="48" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:16">
       <c r="A48" t="s">
-        <v>112</v>
+        <v>122</v>
       </c>
       <c r="B48" t="s">
-        <v>113</v>
+        <v>123</v>
       </c>
       <c r="C48" t="s">
         <v>13</v>
@@ -4638,12 +4639,12 @@
         <v>470</v>
       </c>
     </row>
-    <row r="49" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:16">
       <c r="A49" t="s">
-        <v>114</v>
+        <v>124</v>
       </c>
       <c r="B49" t="s">
-        <v>115</v>
+        <v>125</v>
       </c>
       <c r="C49" t="s">
         <v>5</v>
@@ -4688,12 +4689,12 @@
         <v>480</v>
       </c>
     </row>
-    <row r="50" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:16">
       <c r="A50" t="s">
-        <v>116</v>
+        <v>126</v>
       </c>
       <c r="B50" t="s">
-        <v>117</v>
+        <v>127</v>
       </c>
       <c r="C50" t="s">
         <v>11</v>
@@ -4738,12 +4739,12 @@
         <v>490</v>
       </c>
     </row>
-    <row r="51" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:16">
       <c r="A51" t="s">
-        <v>118</v>
+        <v>128</v>
       </c>
       <c r="B51" t="s">
-        <v>119</v>
+        <v>129</v>
       </c>
       <c r="C51" t="s">
         <v>15</v>
@@ -4788,12 +4789,12 @@
         <v>500</v>
       </c>
     </row>
-    <row r="52" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:16">
       <c r="A52" t="s">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="B52" t="s">
-        <v>121</v>
+        <v>131</v>
       </c>
       <c r="C52" t="s">
         <v>15</v>
@@ -4838,25 +4839,81 @@
         <v>510</v>
       </c>
     </row>
+    <row r="53" spans="1:16">
+      <c r="A53" t="s">
+        <v>132</v>
+      </c>
+      <c r="B53" t="s">
+        <v>133</v>
+      </c>
+      <c r="C53" t="s">
+        <v>5</v>
+      </c>
+      <c r="D53">
+        <v>0</v>
+      </c>
+      <c r="E53">
+        <v>0</v>
+      </c>
+      <c r="F53">
+        <v>1</v>
+      </c>
+      <c r="G53">
+        <v>1</v>
+      </c>
+      <c r="H53">
+        <v>0</v>
+      </c>
+      <c r="I53">
+        <v>0</v>
+      </c>
+      <c r="J53">
+        <v>0</v>
+      </c>
+      <c r="K53">
+        <v>0</v>
+      </c>
+      <c r="L53">
+        <v>0</v>
+      </c>
+      <c r="M53">
+        <v>0</v>
+      </c>
+      <c r="N53">
+        <v>0</v>
+      </c>
+      <c r="O53">
+        <v>0</v>
+      </c>
+      <c r="P53">
+        <v>520</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:P1" xr:uid="{00000000-0009-0000-0000-000001000000}"/>
+  <autoFilter ref="A1:P1"/>
+  <printOptions gridLines="false" gridLinesSet="true"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait"/>
+  <pageSetup paperSize="1" orientation="portrait" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr filterMode="1">
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+  </sheetPr>
   <dimension ref="A1:F37"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="14.4" defaultColWidth="8.83203125" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col min="1" max="2" width="14" customWidth="1"/>
-    <col min="3" max="4" width="10.5" customWidth="1"/>
-    <col min="5" max="5" width="22.33203125" customWidth="1"/>
-    <col min="6" max="6" width="9.33203125" customWidth="1"/>
+    <col min="1" max="1" width="14" customWidth="true" style="0"/>
+    <col min="2" max="2" width="14" customWidth="true" style="0"/>
+    <col min="3" max="3" width="10.5" customWidth="true" style="0"/>
+    <col min="4" max="4" width="10.5" customWidth="true" style="0"/>
+    <col min="5" max="5" width="22.33203125" customWidth="true" style="0"/>
+    <col min="6" max="6" width="9.33203125" customWidth="true" style="0"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:6">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -4870,18 +4927,18 @@
         <v>3</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>122</v>
+        <v>134</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:6">
       <c r="A2" t="s">
-        <v>123</v>
+        <v>135</v>
       </c>
       <c r="B2" t="s">
-        <v>124</v>
+        <v>136</v>
       </c>
       <c r="C2">
         <v>10</v>
@@ -4896,12 +4953,12 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:6">
       <c r="A3" t="s">
-        <v>125</v>
+        <v>137</v>
       </c>
       <c r="B3" t="s">
-        <v>126</v>
+        <v>138</v>
       </c>
       <c r="C3">
         <v>10</v>
@@ -4916,12 +4973,12 @@
         <v>20</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:6">
       <c r="A4" t="s">
-        <v>127</v>
+        <v>139</v>
       </c>
       <c r="B4" t="s">
-        <v>128</v>
+        <v>140</v>
       </c>
       <c r="C4">
         <v>10</v>
@@ -4936,12 +4993,12 @@
         <v>30</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:6">
       <c r="A5" t="s">
-        <v>129</v>
+        <v>141</v>
       </c>
       <c r="B5" t="s">
-        <v>130</v>
+        <v>142</v>
       </c>
       <c r="C5">
         <v>10</v>
@@ -4956,12 +5013,12 @@
         <v>40</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:6">
       <c r="A6" t="s">
-        <v>131</v>
+        <v>143</v>
       </c>
       <c r="B6" t="s">
-        <v>132</v>
+        <v>144</v>
       </c>
       <c r="C6">
         <v>10</v>
@@ -4976,12 +5033,12 @@
         <v>50</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:6">
       <c r="A7" t="s">
-        <v>133</v>
+        <v>145</v>
       </c>
       <c r="B7" t="s">
-        <v>134</v>
+        <v>146</v>
       </c>
       <c r="C7">
         <v>10</v>
@@ -4996,12 +5053,12 @@
         <v>60</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:6">
       <c r="A8" t="s">
-        <v>135</v>
+        <v>147</v>
       </c>
       <c r="B8" t="s">
-        <v>136</v>
+        <v>148</v>
       </c>
       <c r="C8">
         <v>15</v>
@@ -5016,12 +5073,12 @@
         <v>70</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:6">
       <c r="A9" t="s">
-        <v>137</v>
+        <v>149</v>
       </c>
       <c r="B9" t="s">
-        <v>138</v>
+        <v>150</v>
       </c>
       <c r="C9">
         <v>10</v>
@@ -5036,12 +5093,12 @@
         <v>80</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:6">
       <c r="A10" t="s">
-        <v>139</v>
+        <v>151</v>
       </c>
       <c r="B10" t="s">
-        <v>140</v>
+        <v>152</v>
       </c>
       <c r="C10">
         <v>10</v>
@@ -5056,12 +5113,12 @@
         <v>90</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:6">
       <c r="A11" t="s">
-        <v>141</v>
+        <v>153</v>
       </c>
       <c r="B11" t="s">
-        <v>142</v>
+        <v>154</v>
       </c>
       <c r="C11">
         <v>5</v>
@@ -5076,12 +5133,12 @@
         <v>100</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:6">
       <c r="A12" t="s">
-        <v>143</v>
+        <v>155</v>
       </c>
       <c r="B12" t="s">
-        <v>144</v>
+        <v>156</v>
       </c>
       <c r="C12">
         <v>5</v>
@@ -5096,12 +5153,12 @@
         <v>110</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:6">
       <c r="A13" t="s">
-        <v>145</v>
+        <v>157</v>
       </c>
       <c r="B13" t="s">
-        <v>146</v>
+        <v>158</v>
       </c>
       <c r="C13">
         <v>5</v>
@@ -5116,12 +5173,12 @@
         <v>120</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:6">
       <c r="A14" t="s">
-        <v>147</v>
+        <v>159</v>
       </c>
       <c r="B14" t="s">
-        <v>148</v>
+        <v>160</v>
       </c>
       <c r="C14">
         <v>5</v>
@@ -5136,12 +5193,12 @@
         <v>130</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:6">
       <c r="A15" t="s">
-        <v>149</v>
+        <v>161</v>
       </c>
       <c r="B15" t="s">
-        <v>150</v>
+        <v>162</v>
       </c>
       <c r="C15">
         <v>5</v>
@@ -5156,12 +5213,12 @@
         <v>140</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:6">
       <c r="A16" t="s">
-        <v>151</v>
+        <v>163</v>
       </c>
       <c r="B16" t="s">
-        <v>152</v>
+        <v>164</v>
       </c>
       <c r="C16">
         <v>10</v>
@@ -5176,12 +5233,12 @@
         <v>150</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:6">
       <c r="A17" t="s">
-        <v>153</v>
+        <v>165</v>
       </c>
       <c r="B17" t="s">
-        <v>154</v>
+        <v>166</v>
       </c>
       <c r="C17">
         <v>10</v>
@@ -5196,12 +5253,12 @@
         <v>160</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:6">
       <c r="A18" t="s">
-        <v>155</v>
+        <v>167</v>
       </c>
       <c r="B18" t="s">
-        <v>156</v>
+        <v>168</v>
       </c>
       <c r="C18">
         <v>10</v>
@@ -5216,12 +5273,12 @@
         <v>170</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:6">
       <c r="A19" t="s">
-        <v>157</v>
+        <v>169</v>
       </c>
       <c r="B19" t="s">
-        <v>158</v>
+        <v>170</v>
       </c>
       <c r="C19">
         <v>10</v>
@@ -5236,12 +5293,12 @@
         <v>180</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:6">
       <c r="A20" t="s">
-        <v>88</v>
+        <v>98</v>
       </c>
       <c r="B20" t="s">
-        <v>89</v>
+        <v>99</v>
       </c>
       <c r="C20">
         <v>15</v>
@@ -5256,12 +5313,12 @@
         <v>190</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:6">
       <c r="A21" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="B21" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="C21">
         <v>25</v>
@@ -5276,12 +5333,12 @@
         <v>200</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:6">
       <c r="A22" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="B22" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="C22">
         <v>30</v>
@@ -5296,12 +5353,12 @@
         <v>210</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:6">
       <c r="A23" t="s">
-        <v>159</v>
+        <v>72</v>
       </c>
       <c r="B23" t="s">
-        <v>160</v>
+        <v>73</v>
       </c>
       <c r="C23">
         <v>30</v>
@@ -5316,12 +5373,12 @@
         <v>220</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:6">
       <c r="A24" t="s">
-        <v>161</v>
+        <v>74</v>
       </c>
       <c r="B24" t="s">
-        <v>162</v>
+        <v>75</v>
       </c>
       <c r="C24">
         <v>35</v>
@@ -5336,12 +5393,12 @@
         <v>230</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:6">
       <c r="A25" t="s">
-        <v>163</v>
+        <v>171</v>
       </c>
       <c r="B25" t="s">
-        <v>164</v>
+        <v>172</v>
       </c>
       <c r="C25">
         <v>10</v>
@@ -5356,12 +5413,12 @@
         <v>240</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:6">
       <c r="A26" t="s">
-        <v>165</v>
+        <v>173</v>
       </c>
       <c r="B26" t="s">
-        <v>166</v>
+        <v>174</v>
       </c>
       <c r="C26">
         <v>15</v>
@@ -5376,12 +5433,12 @@
         <v>250</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:6">
       <c r="A27" t="s">
-        <v>167</v>
+        <v>175</v>
       </c>
       <c r="B27" t="s">
-        <v>168</v>
+        <v>176</v>
       </c>
       <c r="C27">
         <v>10</v>
@@ -5396,12 +5453,12 @@
         <v>260</v>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:6">
       <c r="A28" t="s">
-        <v>169</v>
+        <v>177</v>
       </c>
       <c r="B28" t="s">
-        <v>170</v>
+        <v>178</v>
       </c>
       <c r="C28">
         <v>10</v>
@@ -5416,12 +5473,12 @@
         <v>270</v>
       </c>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:6">
       <c r="A29" t="s">
-        <v>171</v>
+        <v>179</v>
       </c>
       <c r="B29" t="s">
-        <v>172</v>
+        <v>180</v>
       </c>
       <c r="C29">
         <v>5</v>
@@ -5436,12 +5493,12 @@
         <v>280</v>
       </c>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:6">
       <c r="A30" t="s">
-        <v>173</v>
+        <v>181</v>
       </c>
       <c r="B30" t="s">
-        <v>174</v>
+        <v>182</v>
       </c>
       <c r="C30">
         <v>5</v>
@@ -5456,12 +5513,12 @@
         <v>290</v>
       </c>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:6">
       <c r="A31" t="s">
-        <v>175</v>
+        <v>183</v>
       </c>
       <c r="B31" t="s">
-        <v>176</v>
+        <v>184</v>
       </c>
       <c r="C31">
         <v>35</v>
@@ -5476,12 +5533,12 @@
         <v>300</v>
       </c>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:6">
       <c r="A32" t="s">
-        <v>177</v>
+        <v>185</v>
       </c>
       <c r="B32" t="s">
-        <v>178</v>
+        <v>186</v>
       </c>
       <c r="C32">
         <v>25</v>
@@ -5496,12 +5553,12 @@
         <v>310</v>
       </c>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:6">
       <c r="A33" t="s">
-        <v>179</v>
+        <v>187</v>
       </c>
       <c r="B33" t="s">
-        <v>180</v>
+        <v>188</v>
       </c>
       <c r="C33">
         <v>15</v>
@@ -5516,12 +5573,12 @@
         <v>320</v>
       </c>
     </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:6">
       <c r="A34" t="s">
-        <v>181</v>
+        <v>78</v>
       </c>
       <c r="B34" t="s">
-        <v>182</v>
+        <v>189</v>
       </c>
       <c r="C34">
         <v>40</v>
@@ -5536,12 +5593,12 @@
         <v>330</v>
       </c>
     </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:6">
       <c r="A35" t="s">
-        <v>183</v>
+        <v>190</v>
       </c>
       <c r="B35" t="s">
-        <v>184</v>
+        <v>191</v>
       </c>
       <c r="C35">
         <v>35</v>
@@ -5556,12 +5613,12 @@
         <v>340</v>
       </c>
     </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:6">
       <c r="A36" t="s">
-        <v>185</v>
+        <v>192</v>
       </c>
       <c r="B36" t="s">
-        <v>186</v>
+        <v>193</v>
       </c>
       <c r="C36">
         <v>15</v>
@@ -5576,12 +5633,12 @@
         <v>350</v>
       </c>
     </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:6">
       <c r="A37" t="s">
-        <v>187</v>
+        <v>194</v>
       </c>
       <c r="B37" t="s">
-        <v>188</v>
+        <v>195</v>
       </c>
       <c r="C37">
         <v>7</v>
@@ -5597,30 +5654,35 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F1" xr:uid="{00000000-0009-0000-0000-000002000000}"/>
+  <autoFilter ref="A1:F1"/>
+  <printOptions gridLines="false" gridLinesSet="true"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait"/>
+  <pageSetup paperSize="1" orientation="portrait" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr filterMode="1">
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+  </sheetPr>
   <dimension ref="A1:K25"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="14.4" defaultColWidth="8.83203125" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col min="1" max="1" width="15.33203125" customWidth="1"/>
-    <col min="2" max="2" width="15" customWidth="1"/>
-    <col min="3" max="3" width="18.6640625" customWidth="1"/>
-    <col min="4" max="4" width="16.33203125" customWidth="1"/>
-    <col min="5" max="5" width="12.83203125" customWidth="1"/>
-    <col min="6" max="6" width="10.5" customWidth="1"/>
-    <col min="7" max="7" width="17.5" customWidth="1"/>
-    <col min="8" max="9" width="21" customWidth="1"/>
-    <col min="10" max="10" width="19.83203125" customWidth="1"/>
-    <col min="11" max="11" width="22.33203125" customWidth="1"/>
+    <col min="1" max="1" width="15.33203125" customWidth="true" style="0"/>
+    <col min="2" max="2" width="15" customWidth="true" style="0"/>
+    <col min="3" max="3" width="18.6640625" customWidth="true" style="0"/>
+    <col min="4" max="4" width="16.33203125" customWidth="true" style="0"/>
+    <col min="5" max="5" width="12.83203125" customWidth="true" style="0"/>
+    <col min="6" max="6" width="10.5" customWidth="true" style="0"/>
+    <col min="7" max="7" width="17.5" customWidth="true" style="0"/>
+    <col min="8" max="8" width="21" customWidth="true" style="0"/>
+    <col min="9" max="9" width="21" customWidth="true" style="0"/>
+    <col min="10" max="10" width="19.83203125" customWidth="true" style="0"/>
+    <col min="11" max="11" width="22.33203125" customWidth="true" style="0"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:11">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -5631,39 +5693,39 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>189</v>
+        <v>196</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>190</v>
+        <v>197</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>3</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>191</v>
+        <v>198</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>192</v>
+        <v>199</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>193</v>
+        <v>200</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>194</v>
+        <v>201</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.2">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11">
       <c r="A2" t="s">
-        <v>196</v>
+        <v>203</v>
       </c>
       <c r="B2" t="s">
-        <v>197</v>
+        <v>204</v>
       </c>
       <c r="C2" t="s">
-        <v>198</v>
+        <v>205</v>
       </c>
       <c r="D2">
         <v>1</v>
@@ -5678,7 +5740,7 @@
         <v>5</v>
       </c>
       <c r="H2" t="s">
-        <v>199</v>
+        <v>206</v>
       </c>
       <c r="I2" t="s">
         <v>7</v>
@@ -5690,15 +5752,15 @@
         <v>-100</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:11">
       <c r="A3" t="s">
-        <v>200</v>
+        <v>207</v>
       </c>
       <c r="B3" t="s">
-        <v>201</v>
+        <v>208</v>
       </c>
       <c r="C3" t="s">
-        <v>202</v>
+        <v>209</v>
       </c>
       <c r="D3">
         <v>0</v>
@@ -5713,7 +5775,7 @@
         <v>15</v>
       </c>
       <c r="H3" t="s">
-        <v>199</v>
+        <v>206</v>
       </c>
       <c r="I3" t="s">
         <v>7</v>
@@ -5725,15 +5787,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:11">
       <c r="A4" t="s">
-        <v>203</v>
+        <v>210</v>
       </c>
       <c r="B4" t="s">
-        <v>204</v>
+        <v>211</v>
       </c>
       <c r="C4" t="s">
-        <v>198</v>
+        <v>205</v>
       </c>
       <c r="D4">
         <v>1</v>
@@ -5748,7 +5810,7 @@
         <v>20</v>
       </c>
       <c r="H4" t="s">
-        <v>199</v>
+        <v>206</v>
       </c>
       <c r="I4" t="s">
         <v>7</v>
@@ -5760,15 +5822,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:11">
       <c r="A5" t="s">
+        <v>212</v>
+      </c>
+      <c r="B5" t="s">
+        <v>213</v>
+      </c>
+      <c r="C5" t="s">
         <v>205</v>
-      </c>
-      <c r="B5" t="s">
-        <v>206</v>
-      </c>
-      <c r="C5" t="s">
-        <v>198</v>
       </c>
       <c r="D5">
         <v>1</v>
@@ -5783,7 +5845,7 @@
         <v>25</v>
       </c>
       <c r="H5" t="s">
-        <v>199</v>
+        <v>206</v>
       </c>
       <c r="I5" t="s">
         <v>7</v>
@@ -5795,15 +5857,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:11">
       <c r="A6" t="s">
-        <v>207</v>
+        <v>214</v>
       </c>
       <c r="B6" t="s">
-        <v>208</v>
+        <v>215</v>
       </c>
       <c r="C6" t="s">
-        <v>202</v>
+        <v>209</v>
       </c>
       <c r="D6">
         <v>0</v>
@@ -5818,7 +5880,7 @@
         <v>30</v>
       </c>
       <c r="H6" t="s">
-        <v>199</v>
+        <v>206</v>
       </c>
       <c r="I6" t="s">
         <v>7</v>
@@ -5830,15 +5892,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:11">
       <c r="A7" t="s">
-        <v>209</v>
+        <v>216</v>
       </c>
       <c r="B7" t="s">
-        <v>210</v>
+        <v>217</v>
       </c>
       <c r="C7" t="s">
-        <v>198</v>
+        <v>205</v>
       </c>
       <c r="D7">
         <v>1</v>
@@ -5853,7 +5915,7 @@
         <v>35</v>
       </c>
       <c r="H7" t="s">
-        <v>199</v>
+        <v>206</v>
       </c>
       <c r="I7" t="s">
         <v>7</v>
@@ -5865,15 +5927,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:11">
       <c r="A8" t="s">
-        <v>211</v>
+        <v>218</v>
       </c>
       <c r="B8" t="s">
-        <v>212</v>
+        <v>219</v>
       </c>
       <c r="C8" t="s">
-        <v>198</v>
+        <v>205</v>
       </c>
       <c r="D8">
         <v>1</v>
@@ -5888,7 +5950,7 @@
         <v>45</v>
       </c>
       <c r="H8" t="s">
-        <v>199</v>
+        <v>206</v>
       </c>
       <c r="I8" t="s">
         <v>7</v>
@@ -5900,15 +5962,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:11">
       <c r="A9" t="s">
-        <v>213</v>
+        <v>220</v>
       </c>
       <c r="B9" t="s">
-        <v>214</v>
+        <v>221</v>
       </c>
       <c r="C9" t="s">
-        <v>198</v>
+        <v>205</v>
       </c>
       <c r="D9">
         <v>1</v>
@@ -5923,7 +5985,7 @@
         <v>50</v>
       </c>
       <c r="H9" t="s">
-        <v>199</v>
+        <v>206</v>
       </c>
       <c r="I9" t="s">
         <v>7</v>
@@ -5935,15 +5997,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:11">
       <c r="A10" t="s">
-        <v>215</v>
+        <v>222</v>
       </c>
       <c r="B10" t="s">
-        <v>216</v>
+        <v>223</v>
       </c>
       <c r="C10" t="s">
-        <v>198</v>
+        <v>205</v>
       </c>
       <c r="D10">
         <v>1</v>
@@ -5958,7 +6020,7 @@
         <v>55</v>
       </c>
       <c r="H10" t="s">
-        <v>199</v>
+        <v>206</v>
       </c>
       <c r="I10" t="s">
         <v>10</v>
@@ -5970,15 +6032,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:11">
       <c r="A11" t="s">
-        <v>217</v>
+        <v>224</v>
       </c>
       <c r="B11" t="s">
-        <v>218</v>
+        <v>225</v>
       </c>
       <c r="C11" t="s">
-        <v>198</v>
+        <v>205</v>
       </c>
       <c r="D11">
         <v>1</v>
@@ -5993,7 +6055,7 @@
         <v>60</v>
       </c>
       <c r="H11" t="s">
-        <v>199</v>
+        <v>206</v>
       </c>
       <c r="I11" t="s">
         <v>10</v>
@@ -6005,15 +6067,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:11">
       <c r="A12" t="s">
-        <v>219</v>
+        <v>226</v>
       </c>
       <c r="B12" t="s">
-        <v>220</v>
+        <v>227</v>
       </c>
       <c r="C12" t="s">
-        <v>198</v>
+        <v>205</v>
       </c>
       <c r="D12">
         <v>1</v>
@@ -6028,7 +6090,7 @@
         <v>65</v>
       </c>
       <c r="H12" t="s">
-        <v>199</v>
+        <v>206</v>
       </c>
       <c r="I12" t="s">
         <v>10</v>
@@ -6040,15 +6102,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:11">
       <c r="A13" t="s">
-        <v>221</v>
+        <v>228</v>
       </c>
       <c r="B13" t="s">
-        <v>222</v>
+        <v>229</v>
       </c>
       <c r="C13" t="s">
-        <v>198</v>
+        <v>205</v>
       </c>
       <c r="D13">
         <v>1</v>
@@ -6063,7 +6125,7 @@
         <v>70</v>
       </c>
       <c r="H13" t="s">
-        <v>199</v>
+        <v>206</v>
       </c>
       <c r="I13" t="s">
         <v>10</v>
@@ -6075,15 +6137,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:11">
       <c r="A14" t="s">
-        <v>223</v>
+        <v>230</v>
       </c>
       <c r="B14" t="s">
-        <v>224</v>
+        <v>231</v>
       </c>
       <c r="C14" t="s">
-        <v>198</v>
+        <v>205</v>
       </c>
       <c r="D14">
         <v>1</v>
@@ -6098,7 +6160,7 @@
         <v>80</v>
       </c>
       <c r="H14" t="s">
-        <v>199</v>
+        <v>206</v>
       </c>
       <c r="I14" t="s">
         <v>10</v>
@@ -6110,15 +6172,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:11">
       <c r="A15" t="s">
-        <v>225</v>
+        <v>232</v>
       </c>
       <c r="B15" t="s">
-        <v>226</v>
+        <v>233</v>
       </c>
       <c r="C15" t="s">
-        <v>198</v>
+        <v>205</v>
       </c>
       <c r="D15">
         <v>1</v>
@@ -6133,7 +6195,7 @@
         <v>90</v>
       </c>
       <c r="H15" t="s">
-        <v>199</v>
+        <v>206</v>
       </c>
       <c r="I15" t="s">
         <v>10</v>
@@ -6145,15 +6207,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:11">
       <c r="A16" t="s">
-        <v>227</v>
+        <v>234</v>
       </c>
       <c r="B16" t="s">
-        <v>228</v>
+        <v>235</v>
       </c>
       <c r="C16" t="s">
-        <v>198</v>
+        <v>205</v>
       </c>
       <c r="D16">
         <v>1</v>
@@ -6168,7 +6230,7 @@
         <v>100</v>
       </c>
       <c r="H16" t="s">
-        <v>199</v>
+        <v>206</v>
       </c>
       <c r="I16" t="s">
         <v>10</v>
@@ -6180,15 +6242,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:11">
       <c r="A17" t="s">
-        <v>229</v>
+        <v>236</v>
       </c>
       <c r="B17" t="s">
-        <v>230</v>
+        <v>237</v>
       </c>
       <c r="C17" t="s">
-        <v>198</v>
+        <v>205</v>
       </c>
       <c r="D17">
         <v>1</v>
@@ -6203,7 +6265,7 @@
         <v>110</v>
       </c>
       <c r="H17" t="s">
-        <v>199</v>
+        <v>206</v>
       </c>
       <c r="I17" t="s">
         <v>10</v>
@@ -6215,15 +6277,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:11">
       <c r="A18" t="s">
-        <v>231</v>
+        <v>238</v>
       </c>
       <c r="B18" t="s">
-        <v>232</v>
+        <v>239</v>
       </c>
       <c r="C18" t="s">
-        <v>198</v>
+        <v>205</v>
       </c>
       <c r="D18">
         <v>1</v>
@@ -6238,7 +6300,7 @@
         <v>120</v>
       </c>
       <c r="H18" t="s">
-        <v>199</v>
+        <v>206</v>
       </c>
       <c r="I18" t="s">
         <v>10</v>
@@ -6250,15 +6312,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:11">
       <c r="A19" t="s">
-        <v>233</v>
+        <v>240</v>
       </c>
       <c r="B19" t="s">
-        <v>234</v>
+        <v>241</v>
       </c>
       <c r="C19" t="s">
-        <v>198</v>
+        <v>205</v>
       </c>
       <c r="D19">
         <v>1</v>
@@ -6273,7 +6335,7 @@
         <v>130</v>
       </c>
       <c r="H19" t="s">
-        <v>199</v>
+        <v>206</v>
       </c>
       <c r="I19" t="s">
         <v>10</v>
@@ -6285,15 +6347,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:11">
       <c r="A20" t="s">
-        <v>235</v>
+        <v>242</v>
       </c>
       <c r="B20" t="s">
-        <v>236</v>
+        <v>243</v>
       </c>
       <c r="C20" t="s">
-        <v>198</v>
+        <v>205</v>
       </c>
       <c r="D20">
         <v>1</v>
@@ -6308,7 +6370,7 @@
         <v>140</v>
       </c>
       <c r="H20" t="s">
-        <v>199</v>
+        <v>206</v>
       </c>
       <c r="I20" t="s">
         <v>7</v>
@@ -6320,15 +6382,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:11">
       <c r="A21" t="s">
-        <v>237</v>
+        <v>244</v>
       </c>
       <c r="B21" t="s">
-        <v>238</v>
+        <v>245</v>
       </c>
       <c r="C21" t="s">
-        <v>198</v>
+        <v>205</v>
       </c>
       <c r="D21">
         <v>1</v>
@@ -6343,7 +6405,7 @@
         <v>150</v>
       </c>
       <c r="H21" t="s">
-        <v>199</v>
+        <v>206</v>
       </c>
       <c r="I21" t="s">
         <v>7</v>
@@ -6355,15 +6417,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:11">
       <c r="A22" t="s">
-        <v>239</v>
+        <v>246</v>
       </c>
       <c r="B22" t="s">
-        <v>240</v>
+        <v>247</v>
       </c>
       <c r="C22" t="s">
-        <v>198</v>
+        <v>205</v>
       </c>
       <c r="D22">
         <v>1</v>
@@ -6378,7 +6440,7 @@
         <v>160</v>
       </c>
       <c r="H22" t="s">
-        <v>199</v>
+        <v>206</v>
       </c>
       <c r="I22" t="s">
         <v>7</v>
@@ -6390,15 +6452,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:11">
       <c r="A23" t="s">
-        <v>241</v>
+        <v>248</v>
       </c>
       <c r="B23" t="s">
-        <v>242</v>
+        <v>249</v>
       </c>
       <c r="C23" t="s">
-        <v>198</v>
+        <v>205</v>
       </c>
       <c r="D23">
         <v>0</v>
@@ -6413,7 +6475,7 @@
         <v>170</v>
       </c>
       <c r="H23" t="s">
-        <v>199</v>
+        <v>206</v>
       </c>
       <c r="I23" t="s">
         <v>7</v>
@@ -6425,15 +6487,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:11">
       <c r="A24" t="s">
-        <v>243</v>
+        <v>250</v>
       </c>
       <c r="B24" t="s">
-        <v>244</v>
+        <v>251</v>
       </c>
       <c r="C24" t="s">
-        <v>198</v>
+        <v>205</v>
       </c>
       <c r="D24">
         <v>0</v>
@@ -6448,7 +6510,7 @@
         <v>180</v>
       </c>
       <c r="H24" t="s">
-        <v>199</v>
+        <v>206</v>
       </c>
       <c r="I24" t="s">
         <v>7</v>
@@ -6460,15 +6522,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:11">
       <c r="A25" s="4" t="s">
-        <v>540</v>
+        <v>252</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>562</v>
+        <v>253</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>198</v>
+        <v>205</v>
       </c>
       <c r="D25">
         <v>1</v>
@@ -6483,7 +6545,7 @@
         <v>190</v>
       </c>
       <c r="H25" s="4" t="s">
-        <v>199</v>
+        <v>206</v>
       </c>
       <c r="I25" t="s">
         <v>7</v>
@@ -6496,30 +6558,34 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K1" xr:uid="{00000000-0009-0000-0000-000003000000}"/>
+  <autoFilter ref="A1:K1"/>
+  <printOptions gridLines="false" gridLinesSet="true"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait"/>
+  <pageSetup paperSize="1" orientation="portrait" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr filterMode="1">
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+  </sheetPr>
   <dimension ref="A1:H90"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="14.4" defaultColWidth="8.83203125" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col min="1" max="1" width="17.6640625" customWidth="1"/>
-    <col min="2" max="2" width="22.1640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="28.83203125" customWidth="1"/>
-    <col min="4" max="4" width="10.5" customWidth="1"/>
-    <col min="5" max="5" width="9.33203125" customWidth="1"/>
-    <col min="6" max="6" width="10.5" customWidth="1"/>
-    <col min="7" max="7" width="9.33203125" customWidth="1"/>
-    <col min="8" max="8" width="17.5" customWidth="1"/>
+    <col min="1" max="1" width="17.6640625" customWidth="true" style="0"/>
+    <col min="2" max="2" width="22.1640625" customWidth="true" style="0"/>
+    <col min="3" max="3" width="28.83203125" customWidth="true" style="0"/>
+    <col min="4" max="4" width="10.5" customWidth="true" style="0"/>
+    <col min="5" max="5" width="9.33203125" customWidth="true" style="0"/>
+    <col min="6" max="6" width="10.5" customWidth="true" style="0"/>
+    <col min="7" max="7" width="9.33203125" customWidth="true" style="0"/>
+    <col min="8" max="8" width="17.5" customWidth="true" style="0"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:8">
       <c r="A1" s="1" t="s">
-        <v>245</v>
+        <v>254</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>0</v>
@@ -6540,18 +6606,18 @@
         <v>4</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>246</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8">
       <c r="A2" t="s">
-        <v>196</v>
+        <v>203</v>
       </c>
       <c r="B2" t="s">
-        <v>247</v>
+        <v>256</v>
       </c>
       <c r="C2" t="s">
-        <v>248</v>
+        <v>257</v>
       </c>
       <c r="D2">
         <v>0</v>
@@ -6566,18 +6632,18 @@
         <v>10</v>
       </c>
       <c r="H2" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8">
       <c r="A3" t="s">
-        <v>196</v>
+        <v>203</v>
       </c>
       <c r="B3" t="s">
-        <v>250</v>
+        <v>259</v>
       </c>
       <c r="C3" t="s">
-        <v>251</v>
+        <v>260</v>
       </c>
       <c r="D3">
         <v>0</v>
@@ -6592,18 +6658,18 @@
         <v>20</v>
       </c>
       <c r="H3" t="s">
-        <v>252</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8">
       <c r="A4" t="s">
-        <v>196</v>
+        <v>203</v>
       </c>
       <c r="B4" t="s">
-        <v>253</v>
+        <v>262</v>
       </c>
       <c r="C4" t="s">
-        <v>254</v>
+        <v>263</v>
       </c>
       <c r="D4">
         <v>0</v>
@@ -6618,18 +6684,18 @@
         <v>30</v>
       </c>
       <c r="H4" t="s">
-        <v>255</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8">
       <c r="A5" t="s">
-        <v>215</v>
+        <v>222</v>
       </c>
       <c r="B5" t="s">
-        <v>256</v>
+        <v>265</v>
       </c>
       <c r="C5" t="s">
-        <v>257</v>
+        <v>266</v>
       </c>
       <c r="D5">
         <v>0</v>
@@ -6644,18 +6710,18 @@
         <v>10</v>
       </c>
       <c r="H5" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8">
       <c r="A6" t="s">
-        <v>215</v>
+        <v>222</v>
       </c>
       <c r="B6" t="s">
-        <v>259</v>
+        <v>268</v>
       </c>
       <c r="C6" t="s">
-        <v>260</v>
+        <v>269</v>
       </c>
       <c r="D6">
         <v>0</v>
@@ -6670,18 +6736,18 @@
         <v>20</v>
       </c>
       <c r="H6" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.2">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8">
       <c r="A7" t="s">
-        <v>200</v>
+        <v>207</v>
       </c>
       <c r="B7" t="s">
-        <v>147</v>
+        <v>159</v>
       </c>
       <c r="C7" t="s">
-        <v>262</v>
+        <v>271</v>
       </c>
       <c r="D7">
         <v>0</v>
@@ -6696,18 +6762,18 @@
         <v>10</v>
       </c>
       <c r="H7" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.2">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8">
       <c r="A8" t="s">
-        <v>200</v>
+        <v>207</v>
       </c>
       <c r="B8" t="s">
-        <v>143</v>
+        <v>155</v>
       </c>
       <c r="C8" t="s">
-        <v>263</v>
+        <v>272</v>
       </c>
       <c r="D8">
         <v>0</v>
@@ -6722,18 +6788,18 @@
         <v>20</v>
       </c>
       <c r="H8" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.2">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8">
       <c r="A9" t="s">
-        <v>200</v>
+        <v>207</v>
       </c>
       <c r="B9" t="s">
-        <v>141</v>
+        <v>153</v>
       </c>
       <c r="C9" t="s">
-        <v>265</v>
+        <v>274</v>
       </c>
       <c r="D9">
         <v>0</v>
@@ -6748,18 +6814,18 @@
         <v>30</v>
       </c>
       <c r="H9" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.2">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8">
       <c r="A10" t="s">
-        <v>200</v>
+        <v>207</v>
       </c>
       <c r="B10" t="s">
-        <v>266</v>
+        <v>275</v>
       </c>
       <c r="C10" t="s">
-        <v>267</v>
+        <v>276</v>
       </c>
       <c r="D10">
         <v>0</v>
@@ -6774,18 +6840,18 @@
         <v>40</v>
       </c>
       <c r="H10" t="s">
-        <v>268</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.2">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8">
       <c r="A11" t="s">
-        <v>200</v>
+        <v>207</v>
       </c>
       <c r="B11" t="s">
-        <v>145</v>
+        <v>157</v>
       </c>
       <c r="C11" t="s">
-        <v>269</v>
+        <v>278</v>
       </c>
       <c r="D11">
         <v>0</v>
@@ -6800,18 +6866,18 @@
         <v>50</v>
       </c>
       <c r="H11" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.2">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8">
       <c r="A12" t="s">
-        <v>203</v>
+        <v>210</v>
       </c>
       <c r="B12" t="s">
-        <v>270</v>
+        <v>279</v>
       </c>
       <c r="C12" t="s">
-        <v>271</v>
+        <v>280</v>
       </c>
       <c r="D12">
         <v>0</v>
@@ -6826,18 +6892,18 @@
         <v>10</v>
       </c>
       <c r="H12" t="s">
-        <v>272</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.2">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8">
       <c r="A13" t="s">
-        <v>203</v>
+        <v>210</v>
       </c>
       <c r="B13" t="s">
-        <v>273</v>
+        <v>282</v>
       </c>
       <c r="C13" t="s">
-        <v>274</v>
+        <v>283</v>
       </c>
       <c r="D13">
         <v>0</v>
@@ -6852,18 +6918,18 @@
         <v>20</v>
       </c>
       <c r="H13" t="s">
-        <v>275</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.2">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8">
       <c r="A14" t="s">
-        <v>203</v>
+        <v>210</v>
       </c>
       <c r="B14" t="s">
-        <v>276</v>
+        <v>285</v>
       </c>
       <c r="C14" t="s">
-        <v>277</v>
+        <v>286</v>
       </c>
       <c r="D14">
         <v>0</v>
@@ -6878,18 +6944,18 @@
         <v>30</v>
       </c>
       <c r="H14" t="s">
-        <v>278</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.2">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8">
       <c r="A15" t="s">
-        <v>205</v>
+        <v>212</v>
       </c>
       <c r="B15" t="s">
-        <v>279</v>
+        <v>288</v>
       </c>
       <c r="C15" t="s">
-        <v>280</v>
+        <v>289</v>
       </c>
       <c r="D15">
         <v>0</v>
@@ -6904,18 +6970,18 @@
         <v>10</v>
       </c>
       <c r="H15" t="s">
-        <v>281</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.2">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8">
       <c r="A16" t="s">
-        <v>205</v>
+        <v>212</v>
       </c>
       <c r="B16" t="s">
-        <v>282</v>
+        <v>291</v>
       </c>
       <c r="C16" t="s">
-        <v>283</v>
+        <v>292</v>
       </c>
       <c r="D16">
         <v>0</v>
@@ -6930,18 +6996,18 @@
         <v>20</v>
       </c>
       <c r="H16" t="s">
-        <v>284</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.2">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8">
       <c r="A17" t="s">
-        <v>207</v>
+        <v>214</v>
       </c>
       <c r="B17" t="s">
-        <v>123</v>
+        <v>135</v>
       </c>
       <c r="C17" t="s">
-        <v>285</v>
+        <v>294</v>
       </c>
       <c r="D17">
         <v>10</v>
@@ -6956,18 +7022,18 @@
         <v>10</v>
       </c>
       <c r="H17" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.2">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8">
       <c r="A18" t="s">
-        <v>207</v>
+        <v>214</v>
       </c>
       <c r="B18" t="s">
-        <v>286</v>
+        <v>295</v>
       </c>
       <c r="C18" t="s">
-        <v>287</v>
+        <v>296</v>
       </c>
       <c r="D18">
         <v>10</v>
@@ -6982,18 +7048,18 @@
         <v>20</v>
       </c>
       <c r="H18" t="s">
-        <v>288</v>
-      </c>
-    </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.2">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8">
       <c r="A19" t="s">
-        <v>207</v>
+        <v>214</v>
       </c>
       <c r="B19" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C19" t="s">
-        <v>289</v>
+        <v>298</v>
       </c>
       <c r="D19">
         <v>25</v>
@@ -7008,18 +7074,18 @@
         <v>30</v>
       </c>
       <c r="H19" t="s">
-        <v>290</v>
-      </c>
-    </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.2">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8">
       <c r="A20" t="s">
-        <v>207</v>
+        <v>214</v>
       </c>
       <c r="B20" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="C20" t="s">
-        <v>291</v>
+        <v>300</v>
       </c>
       <c r="D20">
         <v>30</v>
@@ -7034,18 +7100,18 @@
         <v>40</v>
       </c>
       <c r="H20" t="s">
-        <v>292</v>
-      </c>
-    </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.2">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8">
       <c r="A21" t="s">
-        <v>207</v>
+        <v>214</v>
       </c>
       <c r="B21" t="s">
-        <v>159</v>
+        <v>72</v>
       </c>
       <c r="C21" t="s">
-        <v>293</v>
+        <v>302</v>
       </c>
       <c r="D21">
         <v>30</v>
@@ -7060,18 +7126,18 @@
         <v>50</v>
       </c>
       <c r="H21" t="s">
-        <v>294</v>
-      </c>
-    </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.2">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8">
       <c r="A22" t="s">
-        <v>207</v>
+        <v>214</v>
       </c>
       <c r="B22" t="s">
-        <v>161</v>
+        <v>74</v>
       </c>
       <c r="C22" t="s">
-        <v>295</v>
+        <v>304</v>
       </c>
       <c r="D22">
         <v>35</v>
@@ -7086,18 +7152,18 @@
         <v>60</v>
       </c>
       <c r="H22" t="s">
-        <v>296</v>
-      </c>
-    </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.2">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8">
       <c r="A23" t="s">
-        <v>209</v>
+        <v>216</v>
       </c>
       <c r="B23" t="s">
-        <v>297</v>
+        <v>306</v>
       </c>
       <c r="C23" t="s">
-        <v>298</v>
+        <v>307</v>
       </c>
       <c r="D23">
         <v>0</v>
@@ -7112,18 +7178,18 @@
         <v>10</v>
       </c>
       <c r="H23" t="s">
-        <v>299</v>
-      </c>
-    </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.2">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8">
       <c r="A24" t="s">
-        <v>209</v>
+        <v>216</v>
       </c>
       <c r="B24" t="s">
-        <v>300</v>
+        <v>309</v>
       </c>
       <c r="C24" t="s">
-        <v>301</v>
+        <v>310</v>
       </c>
       <c r="D24">
         <v>0</v>
@@ -7138,18 +7204,18 @@
         <v>20</v>
       </c>
       <c r="H24" t="s">
-        <v>302</v>
-      </c>
-    </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.2">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8">
       <c r="A25" t="s">
-        <v>209</v>
+        <v>216</v>
       </c>
       <c r="B25" t="s">
-        <v>303</v>
+        <v>312</v>
       </c>
       <c r="C25" t="s">
-        <v>304</v>
+        <v>313</v>
       </c>
       <c r="D25">
         <v>0</v>
@@ -7164,18 +7230,18 @@
         <v>30</v>
       </c>
       <c r="H25" t="s">
-        <v>305</v>
-      </c>
-    </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.2">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8">
       <c r="A26" t="s">
-        <v>209</v>
+        <v>216</v>
       </c>
       <c r="B26" t="s">
-        <v>306</v>
+        <v>315</v>
       </c>
       <c r="C26" t="s">
-        <v>307</v>
+        <v>316</v>
       </c>
       <c r="D26">
         <v>0</v>
@@ -7190,18 +7256,18 @@
         <v>40</v>
       </c>
       <c r="H26" t="s">
-        <v>308</v>
-      </c>
-    </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.2">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8">
       <c r="A27" t="s">
-        <v>209</v>
+        <v>216</v>
       </c>
       <c r="B27" t="s">
-        <v>309</v>
+        <v>318</v>
       </c>
       <c r="C27" t="s">
-        <v>310</v>
+        <v>319</v>
       </c>
       <c r="D27">
         <v>0</v>
@@ -7216,18 +7282,18 @@
         <v>50</v>
       </c>
       <c r="H27" t="s">
-        <v>311</v>
-      </c>
-    </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.2">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8">
       <c r="A28" t="s">
-        <v>211</v>
+        <v>218</v>
       </c>
       <c r="B28" t="s">
-        <v>312</v>
+        <v>321</v>
       </c>
       <c r="C28" t="s">
-        <v>313</v>
+        <v>322</v>
       </c>
       <c r="D28">
         <v>0</v>
@@ -7242,18 +7308,18 @@
         <v>10</v>
       </c>
       <c r="H28" t="s">
-        <v>314</v>
-      </c>
-    </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.2">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8">
       <c r="A29" t="s">
-        <v>211</v>
+        <v>218</v>
       </c>
       <c r="B29" t="s">
-        <v>315</v>
+        <v>324</v>
       </c>
       <c r="C29" t="s">
-        <v>316</v>
+        <v>325</v>
       </c>
       <c r="D29">
         <v>0</v>
@@ -7268,18 +7334,18 @@
         <v>20</v>
       </c>
       <c r="H29" t="s">
-        <v>317</v>
-      </c>
-    </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.2">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8">
       <c r="A30" t="s">
-        <v>211</v>
+        <v>218</v>
       </c>
       <c r="B30" t="s">
-        <v>318</v>
+        <v>327</v>
       </c>
       <c r="C30" t="s">
-        <v>319</v>
+        <v>328</v>
       </c>
       <c r="D30">
         <v>0</v>
@@ -7294,18 +7360,18 @@
         <v>30</v>
       </c>
       <c r="H30" t="s">
-        <v>320</v>
-      </c>
-    </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.2">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8">
       <c r="A31" t="s">
-        <v>211</v>
+        <v>218</v>
       </c>
       <c r="B31" t="s">
-        <v>321</v>
+        <v>330</v>
       </c>
       <c r="C31" t="s">
-        <v>322</v>
+        <v>331</v>
       </c>
       <c r="D31">
         <v>0</v>
@@ -7320,18 +7386,18 @@
         <v>40</v>
       </c>
       <c r="H31" t="s">
-        <v>323</v>
-      </c>
-    </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.2">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8">
       <c r="A32" t="s">
-        <v>211</v>
+        <v>218</v>
       </c>
       <c r="B32" t="s">
-        <v>324</v>
+        <v>333</v>
       </c>
       <c r="C32" t="s">
-        <v>325</v>
+        <v>334</v>
       </c>
       <c r="D32">
         <v>0</v>
@@ -7346,18 +7412,18 @@
         <v>50</v>
       </c>
       <c r="H32" t="s">
-        <v>326</v>
-      </c>
-    </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.2">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8">
       <c r="A33" t="s">
-        <v>213</v>
+        <v>220</v>
       </c>
       <c r="B33" t="s">
-        <v>327</v>
+        <v>336</v>
       </c>
       <c r="C33" t="s">
-        <v>328</v>
+        <v>337</v>
       </c>
       <c r="D33">
         <v>0</v>
@@ -7372,18 +7438,18 @@
         <v>10</v>
       </c>
       <c r="H33" t="s">
-        <v>329</v>
-      </c>
-    </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.2">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8">
       <c r="A34" t="s">
-        <v>213</v>
+        <v>220</v>
       </c>
       <c r="B34" t="s">
-        <v>330</v>
+        <v>339</v>
       </c>
       <c r="C34" t="s">
-        <v>331</v>
+        <v>340</v>
       </c>
       <c r="D34">
         <v>5</v>
@@ -7398,18 +7464,18 @@
         <v>20</v>
       </c>
       <c r="H34" t="s">
-        <v>332</v>
-      </c>
-    </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.2">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8">
       <c r="A35" t="s">
-        <v>213</v>
+        <v>220</v>
       </c>
       <c r="B35" t="s">
-        <v>333</v>
+        <v>342</v>
       </c>
       <c r="C35" t="s">
-        <v>334</v>
+        <v>343</v>
       </c>
       <c r="D35">
         <v>10</v>
@@ -7424,18 +7490,18 @@
         <v>30</v>
       </c>
       <c r="H35" t="s">
-        <v>335</v>
-      </c>
-    </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.2">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8">
       <c r="A36" t="s">
-        <v>213</v>
+        <v>220</v>
       </c>
       <c r="B36" t="s">
-        <v>336</v>
+        <v>345</v>
       </c>
       <c r="C36" t="s">
-        <v>337</v>
+        <v>346</v>
       </c>
       <c r="D36">
         <v>10</v>
@@ -7450,18 +7516,18 @@
         <v>40</v>
       </c>
       <c r="H36" t="s">
-        <v>338</v>
-      </c>
-    </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.2">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8">
       <c r="A37" t="s">
-        <v>217</v>
+        <v>224</v>
       </c>
       <c r="B37" t="s">
-        <v>339</v>
+        <v>348</v>
       </c>
       <c r="C37" t="s">
-        <v>340</v>
+        <v>349</v>
       </c>
       <c r="D37">
         <v>0</v>
@@ -7476,18 +7542,18 @@
         <v>10</v>
       </c>
       <c r="H37" t="s">
-        <v>341</v>
-      </c>
-    </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.2">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8">
       <c r="A38" t="s">
-        <v>217</v>
+        <v>224</v>
       </c>
       <c r="B38" t="s">
-        <v>342</v>
+        <v>351</v>
       </c>
       <c r="C38" t="s">
-        <v>343</v>
+        <v>352</v>
       </c>
       <c r="D38">
         <v>5</v>
@@ -7502,18 +7568,18 @@
         <v>20</v>
       </c>
       <c r="H38" t="s">
-        <v>344</v>
-      </c>
-    </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.2">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8">
       <c r="A39" t="s">
-        <v>217</v>
+        <v>224</v>
       </c>
       <c r="B39" t="s">
-        <v>345</v>
+        <v>354</v>
       </c>
       <c r="C39" t="s">
-        <v>346</v>
+        <v>355</v>
       </c>
       <c r="D39">
         <v>5</v>
@@ -7528,18 +7594,18 @@
         <v>30</v>
       </c>
       <c r="H39" t="s">
-        <v>347</v>
-      </c>
-    </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.2">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8">
       <c r="A40" t="s">
-        <v>217</v>
+        <v>224</v>
       </c>
       <c r="B40" t="s">
-        <v>348</v>
+        <v>357</v>
       </c>
       <c r="C40" t="s">
-        <v>349</v>
+        <v>358</v>
       </c>
       <c r="D40">
         <v>5</v>
@@ -7554,18 +7620,18 @@
         <v>40</v>
       </c>
       <c r="H40" t="s">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.2">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8">
       <c r="A41" t="s">
-        <v>217</v>
+        <v>224</v>
       </c>
       <c r="B41" t="s">
-        <v>351</v>
+        <v>360</v>
       </c>
       <c r="C41" t="s">
-        <v>352</v>
+        <v>361</v>
       </c>
       <c r="D41">
         <v>5</v>
@@ -7580,18 +7646,18 @@
         <v>50</v>
       </c>
       <c r="H41" t="s">
-        <v>353</v>
-      </c>
-    </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.2">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8">
       <c r="A42" t="s">
-        <v>219</v>
+        <v>226</v>
       </c>
       <c r="B42" t="s">
-        <v>354</v>
+        <v>363</v>
       </c>
       <c r="C42" t="s">
-        <v>355</v>
+        <v>364</v>
       </c>
       <c r="D42">
         <v>0</v>
@@ -7606,18 +7672,18 @@
         <v>10</v>
       </c>
       <c r="H42" t="s">
-        <v>356</v>
-      </c>
-    </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.2">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8">
       <c r="A43" t="s">
-        <v>219</v>
+        <v>226</v>
       </c>
       <c r="B43" t="s">
-        <v>357</v>
+        <v>366</v>
       </c>
       <c r="C43" t="s">
-        <v>358</v>
+        <v>367</v>
       </c>
       <c r="D43">
         <v>0</v>
@@ -7632,18 +7698,18 @@
         <v>20</v>
       </c>
       <c r="H43" t="s">
-        <v>359</v>
-      </c>
-    </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.2">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8">
       <c r="A44" t="s">
-        <v>219</v>
+        <v>226</v>
       </c>
       <c r="B44" t="s">
-        <v>360</v>
+        <v>369</v>
       </c>
       <c r="C44" t="s">
-        <v>361</v>
+        <v>370</v>
       </c>
       <c r="D44">
         <v>0</v>
@@ -7658,18 +7724,18 @@
         <v>30</v>
       </c>
       <c r="H44" t="s">
-        <v>362</v>
-      </c>
-    </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.2">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8">
       <c r="A45" t="s">
-        <v>219</v>
+        <v>226</v>
       </c>
       <c r="B45" t="s">
-        <v>363</v>
+        <v>372</v>
       </c>
       <c r="C45" t="s">
-        <v>364</v>
+        <v>373</v>
       </c>
       <c r="D45">
         <v>0</v>
@@ -7684,18 +7750,18 @@
         <v>40</v>
       </c>
       <c r="H45" t="s">
-        <v>365</v>
-      </c>
-    </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.2">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8">
       <c r="A46" t="s">
-        <v>221</v>
+        <v>228</v>
       </c>
       <c r="B46" t="s">
-        <v>366</v>
+        <v>375</v>
       </c>
       <c r="C46" t="s">
-        <v>367</v>
+        <v>376</v>
       </c>
       <c r="D46">
         <v>0</v>
@@ -7710,18 +7776,18 @@
         <v>10</v>
       </c>
       <c r="H46" t="s">
-        <v>368</v>
-      </c>
-    </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.2">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8">
       <c r="A47" t="s">
-        <v>221</v>
+        <v>228</v>
       </c>
       <c r="B47" t="s">
-        <v>369</v>
+        <v>378</v>
       </c>
       <c r="C47" t="s">
-        <v>370</v>
+        <v>379</v>
       </c>
       <c r="D47">
         <v>0</v>
@@ -7736,18 +7802,18 @@
         <v>20</v>
       </c>
       <c r="H47" t="s">
-        <v>371</v>
-      </c>
-    </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.2">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8">
       <c r="A48" t="s">
-        <v>221</v>
+        <v>228</v>
       </c>
       <c r="B48" t="s">
-        <v>372</v>
+        <v>381</v>
       </c>
       <c r="C48" t="s">
-        <v>373</v>
+        <v>382</v>
       </c>
       <c r="D48">
         <v>0</v>
@@ -7762,18 +7828,18 @@
         <v>30</v>
       </c>
       <c r="H48" t="s">
-        <v>374</v>
-      </c>
-    </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.2">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="49" spans="1:8">
       <c r="A49" t="s">
-        <v>221</v>
+        <v>228</v>
       </c>
       <c r="B49" t="s">
-        <v>375</v>
+        <v>384</v>
       </c>
       <c r="C49" t="s">
-        <v>376</v>
+        <v>385</v>
       </c>
       <c r="D49">
         <v>0</v>
@@ -7788,18 +7854,18 @@
         <v>40</v>
       </c>
       <c r="H49" t="s">
-        <v>377</v>
-      </c>
-    </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.2">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="50" spans="1:8">
       <c r="A50" t="s">
-        <v>223</v>
+        <v>230</v>
       </c>
       <c r="B50" t="s">
-        <v>378</v>
+        <v>387</v>
       </c>
       <c r="C50" t="s">
-        <v>379</v>
+        <v>388</v>
       </c>
       <c r="D50">
         <v>0</v>
@@ -7814,18 +7880,18 @@
         <v>10</v>
       </c>
       <c r="H50" t="s">
-        <v>380</v>
-      </c>
-    </row>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.2">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="51" spans="1:8">
       <c r="A51" t="s">
-        <v>223</v>
+        <v>230</v>
       </c>
       <c r="B51" t="s">
-        <v>381</v>
+        <v>390</v>
       </c>
       <c r="C51" t="s">
-        <v>382</v>
+        <v>391</v>
       </c>
       <c r="D51">
         <v>0</v>
@@ -7840,18 +7906,18 @@
         <v>20</v>
       </c>
       <c r="H51" t="s">
-        <v>383</v>
-      </c>
-    </row>
-    <row r="52" spans="1:8" x14ac:dyDescent="0.2">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="52" spans="1:8">
       <c r="A52" t="s">
-        <v>223</v>
+        <v>230</v>
       </c>
       <c r="B52" t="s">
-        <v>384</v>
+        <v>393</v>
       </c>
       <c r="C52" t="s">
-        <v>385</v>
+        <v>394</v>
       </c>
       <c r="D52">
         <v>0</v>
@@ -7866,18 +7932,18 @@
         <v>10</v>
       </c>
       <c r="H52" t="s">
-        <v>386</v>
-      </c>
-    </row>
-    <row r="53" spans="1:8" x14ac:dyDescent="0.2">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="53" spans="1:8">
       <c r="A53" t="s">
-        <v>225</v>
+        <v>232</v>
       </c>
       <c r="B53" t="s">
-        <v>387</v>
+        <v>396</v>
       </c>
       <c r="C53" t="s">
-        <v>388</v>
+        <v>397</v>
       </c>
       <c r="D53">
         <v>0</v>
@@ -7892,18 +7958,18 @@
         <v>20</v>
       </c>
       <c r="H53" t="s">
-        <v>389</v>
-      </c>
-    </row>
-    <row r="54" spans="1:8" x14ac:dyDescent="0.2">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="54" spans="1:8">
       <c r="A54" t="s">
-        <v>225</v>
+        <v>232</v>
       </c>
       <c r="B54" t="s">
-        <v>390</v>
+        <v>399</v>
       </c>
       <c r="C54" t="s">
-        <v>391</v>
+        <v>400</v>
       </c>
       <c r="D54">
         <v>0</v>
@@ -7918,18 +7984,18 @@
         <v>30</v>
       </c>
       <c r="H54" t="s">
-        <v>392</v>
-      </c>
-    </row>
-    <row r="55" spans="1:8" x14ac:dyDescent="0.2">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="55" spans="1:8">
       <c r="A55" t="s">
-        <v>225</v>
+        <v>232</v>
       </c>
       <c r="B55" t="s">
-        <v>393</v>
+        <v>402</v>
       </c>
       <c r="C55" t="s">
-        <v>394</v>
+        <v>403</v>
       </c>
       <c r="D55">
         <v>0</v>
@@ -7944,18 +8010,18 @@
         <v>40</v>
       </c>
       <c r="H55" t="s">
-        <v>395</v>
-      </c>
-    </row>
-    <row r="56" spans="1:8" x14ac:dyDescent="0.2">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="56" spans="1:8">
       <c r="A56" t="s">
-        <v>225</v>
+        <v>232</v>
       </c>
       <c r="B56" t="s">
-        <v>396</v>
+        <v>405</v>
       </c>
       <c r="C56" t="s">
-        <v>397</v>
+        <v>406</v>
       </c>
       <c r="D56">
         <v>0</v>
@@ -7970,18 +8036,18 @@
         <v>50</v>
       </c>
       <c r="H56" t="s">
-        <v>398</v>
-      </c>
-    </row>
-    <row r="57" spans="1:8" x14ac:dyDescent="0.2">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="57" spans="1:8">
       <c r="A57" t="s">
-        <v>225</v>
+        <v>232</v>
       </c>
       <c r="B57" t="s">
-        <v>399</v>
+        <v>408</v>
       </c>
       <c r="C57" t="s">
-        <v>400</v>
+        <v>409</v>
       </c>
       <c r="D57">
         <v>0</v>
@@ -7996,18 +8062,18 @@
         <v>60</v>
       </c>
       <c r="H57" t="s">
-        <v>401</v>
-      </c>
-    </row>
-    <row r="58" spans="1:8" x14ac:dyDescent="0.2">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="58" spans="1:8">
       <c r="A58" t="s">
-        <v>227</v>
+        <v>234</v>
       </c>
       <c r="B58" t="s">
-        <v>402</v>
+        <v>411</v>
       </c>
       <c r="C58" t="s">
-        <v>403</v>
+        <v>412</v>
       </c>
       <c r="D58">
         <v>0</v>
@@ -8022,18 +8088,18 @@
         <v>10</v>
       </c>
       <c r="H58" t="s">
-        <v>404</v>
-      </c>
-    </row>
-    <row r="59" spans="1:8" x14ac:dyDescent="0.2">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="59" spans="1:8">
       <c r="A59" t="s">
-        <v>227</v>
+        <v>234</v>
       </c>
       <c r="B59" t="s">
-        <v>405</v>
+        <v>414</v>
       </c>
       <c r="C59" t="s">
-        <v>406</v>
+        <v>415</v>
       </c>
       <c r="D59">
         <v>0</v>
@@ -8048,18 +8114,18 @@
         <v>20</v>
       </c>
       <c r="H59" t="s">
-        <v>407</v>
-      </c>
-    </row>
-    <row r="60" spans="1:8" x14ac:dyDescent="0.2">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="60" spans="1:8">
       <c r="A60" t="s">
-        <v>229</v>
+        <v>236</v>
       </c>
       <c r="B60" t="s">
-        <v>408</v>
+        <v>417</v>
       </c>
       <c r="C60" t="s">
-        <v>409</v>
+        <v>418</v>
       </c>
       <c r="D60">
         <v>0</v>
@@ -8074,18 +8140,18 @@
         <v>10</v>
       </c>
       <c r="H60" t="s">
-        <v>409</v>
-      </c>
-    </row>
-    <row r="61" spans="1:8" x14ac:dyDescent="0.2">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="61" spans="1:8">
       <c r="A61" t="s">
-        <v>229</v>
+        <v>236</v>
       </c>
       <c r="B61" t="s">
-        <v>410</v>
+        <v>419</v>
       </c>
       <c r="C61" t="s">
-        <v>411</v>
+        <v>420</v>
       </c>
       <c r="D61">
         <v>0</v>
@@ -8100,18 +8166,18 @@
         <v>20</v>
       </c>
       <c r="H61" t="s">
-        <v>411</v>
-      </c>
-    </row>
-    <row r="62" spans="1:8" x14ac:dyDescent="0.2">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="62" spans="1:8">
       <c r="A62" t="s">
-        <v>229</v>
+        <v>236</v>
       </c>
       <c r="B62" t="s">
-        <v>412</v>
+        <v>421</v>
       </c>
       <c r="C62" t="s">
-        <v>413</v>
+        <v>422</v>
       </c>
       <c r="D62">
         <v>0</v>
@@ -8126,18 +8192,18 @@
         <v>30</v>
       </c>
       <c r="H62" t="s">
-        <v>413</v>
-      </c>
-    </row>
-    <row r="63" spans="1:8" x14ac:dyDescent="0.2">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="63" spans="1:8">
       <c r="A63" t="s">
-        <v>229</v>
+        <v>236</v>
       </c>
       <c r="B63" t="s">
-        <v>414</v>
+        <v>423</v>
       </c>
       <c r="C63" t="s">
-        <v>415</v>
+        <v>424</v>
       </c>
       <c r="D63">
         <v>0</v>
@@ -8152,18 +8218,18 @@
         <v>40</v>
       </c>
       <c r="H63" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="64" spans="1:8" x14ac:dyDescent="0.2">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="64" spans="1:8">
       <c r="A64" t="s">
-        <v>229</v>
+        <v>236</v>
       </c>
       <c r="B64" t="s">
-        <v>416</v>
+        <v>425</v>
       </c>
       <c r="C64" t="s">
-        <v>417</v>
+        <v>426</v>
       </c>
       <c r="D64">
         <v>0</v>
@@ -8178,18 +8244,18 @@
         <v>50</v>
       </c>
       <c r="H64" t="s">
-        <v>417</v>
-      </c>
-    </row>
-    <row r="65" spans="1:8" x14ac:dyDescent="0.2">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="65" spans="1:8">
       <c r="A65" t="s">
-        <v>229</v>
+        <v>236</v>
       </c>
       <c r="B65" t="s">
-        <v>418</v>
+        <v>427</v>
       </c>
       <c r="C65" t="s">
-        <v>419</v>
+        <v>428</v>
       </c>
       <c r="D65">
         <v>0</v>
@@ -8204,18 +8270,18 @@
         <v>60</v>
       </c>
       <c r="H65" t="s">
-        <v>419</v>
-      </c>
-    </row>
-    <row r="66" spans="1:8" x14ac:dyDescent="0.2">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="66" spans="1:8">
       <c r="A66" t="s">
-        <v>229</v>
+        <v>236</v>
       </c>
       <c r="B66" t="s">
-        <v>420</v>
+        <v>429</v>
       </c>
       <c r="C66" t="s">
-        <v>421</v>
+        <v>430</v>
       </c>
       <c r="D66">
         <v>0</v>
@@ -8230,18 +8296,18 @@
         <v>70</v>
       </c>
       <c r="H66" t="s">
-        <v>421</v>
-      </c>
-    </row>
-    <row r="67" spans="1:8" x14ac:dyDescent="0.2">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="67" spans="1:8">
       <c r="A67" t="s">
-        <v>229</v>
+        <v>236</v>
       </c>
       <c r="B67" t="s">
-        <v>422</v>
+        <v>431</v>
       </c>
       <c r="C67" t="s">
-        <v>423</v>
+        <v>432</v>
       </c>
       <c r="D67">
         <v>0</v>
@@ -8256,18 +8322,18 @@
         <v>80</v>
       </c>
       <c r="H67" t="s">
-        <v>423</v>
-      </c>
-    </row>
-    <row r="68" spans="1:8" x14ac:dyDescent="0.2">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="68" spans="1:8">
       <c r="A68" t="s">
-        <v>231</v>
+        <v>238</v>
       </c>
       <c r="B68" t="s">
-        <v>424</v>
+        <v>433</v>
       </c>
       <c r="C68" t="s">
-        <v>425</v>
+        <v>434</v>
       </c>
       <c r="D68">
         <v>0</v>
@@ -8282,18 +8348,18 @@
         <v>10</v>
       </c>
       <c r="H68" t="s">
-        <v>425</v>
-      </c>
-    </row>
-    <row r="69" spans="1:8" x14ac:dyDescent="0.2">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="69" spans="1:8">
       <c r="A69" t="s">
-        <v>231</v>
+        <v>238</v>
       </c>
       <c r="B69" t="s">
-        <v>426</v>
+        <v>435</v>
       </c>
       <c r="C69" t="s">
-        <v>427</v>
+        <v>436</v>
       </c>
       <c r="D69">
         <v>0</v>
@@ -8308,18 +8374,18 @@
         <v>20</v>
       </c>
       <c r="H69" t="s">
-        <v>427</v>
-      </c>
-    </row>
-    <row r="70" spans="1:8" x14ac:dyDescent="0.2">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="70" spans="1:8">
       <c r="A70" t="s">
-        <v>231</v>
+        <v>238</v>
       </c>
       <c r="B70" t="s">
-        <v>428</v>
+        <v>437</v>
       </c>
       <c r="C70" t="s">
-        <v>429</v>
+        <v>438</v>
       </c>
       <c r="D70">
         <v>0</v>
@@ -8334,18 +8400,18 @@
         <v>30</v>
       </c>
       <c r="H70" t="s">
-        <v>429</v>
-      </c>
-    </row>
-    <row r="71" spans="1:8" x14ac:dyDescent="0.2">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="71" spans="1:8">
       <c r="A71" t="s">
-        <v>233</v>
+        <v>240</v>
       </c>
       <c r="B71" t="s">
-        <v>233</v>
+        <v>240</v>
       </c>
       <c r="C71" t="s">
-        <v>234</v>
+        <v>241</v>
       </c>
       <c r="D71">
         <v>0</v>
@@ -8360,18 +8426,18 @@
         <v>10</v>
       </c>
       <c r="H71" t="s">
-        <v>234</v>
-      </c>
-    </row>
-    <row r="72" spans="1:8" x14ac:dyDescent="0.2">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="72" spans="1:8">
       <c r="A72" t="s">
-        <v>235</v>
+        <v>242</v>
       </c>
       <c r="B72" t="s">
-        <v>181</v>
+        <v>78</v>
       </c>
       <c r="C72" t="s">
-        <v>430</v>
+        <v>439</v>
       </c>
       <c r="D72">
         <v>35</v>
@@ -8386,18 +8452,18 @@
         <v>10</v>
       </c>
       <c r="H72" t="s">
-        <v>431</v>
-      </c>
-    </row>
-    <row r="73" spans="1:8" x14ac:dyDescent="0.2">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="73" spans="1:8">
       <c r="A73" t="s">
-        <v>235</v>
+        <v>242</v>
       </c>
       <c r="B73" t="s">
-        <v>179</v>
+        <v>187</v>
       </c>
       <c r="C73" t="s">
-        <v>432</v>
+        <v>441</v>
       </c>
       <c r="D73">
         <v>35</v>
@@ -8412,18 +8478,18 @@
         <v>20</v>
       </c>
       <c r="H73" t="s">
-        <v>433</v>
-      </c>
-    </row>
-    <row r="74" spans="1:8" x14ac:dyDescent="0.2">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="74" spans="1:8">
       <c r="A74" t="s">
-        <v>235</v>
+        <v>242</v>
       </c>
       <c r="B74" t="s">
-        <v>175</v>
+        <v>183</v>
       </c>
       <c r="C74" t="s">
-        <v>434</v>
+        <v>443</v>
       </c>
       <c r="D74">
         <v>35</v>
@@ -8438,18 +8504,18 @@
         <v>30</v>
       </c>
       <c r="H74" t="s">
-        <v>435</v>
-      </c>
-    </row>
-    <row r="75" spans="1:8" x14ac:dyDescent="0.2">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="75" spans="1:8">
       <c r="A75" t="s">
-        <v>235</v>
+        <v>242</v>
       </c>
       <c r="B75" t="s">
-        <v>183</v>
+        <v>190</v>
       </c>
       <c r="C75" t="s">
-        <v>436</v>
+        <v>445</v>
       </c>
       <c r="D75">
         <v>35</v>
@@ -8464,18 +8530,18 @@
         <v>40</v>
       </c>
       <c r="H75" t="s">
-        <v>437</v>
-      </c>
-    </row>
-    <row r="76" spans="1:8" x14ac:dyDescent="0.2">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="76" spans="1:8">
       <c r="A76" t="s">
-        <v>235</v>
+        <v>242</v>
       </c>
       <c r="B76" t="s">
-        <v>185</v>
+        <v>192</v>
       </c>
       <c r="C76" t="s">
-        <v>438</v>
+        <v>447</v>
       </c>
       <c r="D76">
         <v>35</v>
@@ -8490,18 +8556,18 @@
         <v>50</v>
       </c>
       <c r="H76" t="s">
-        <v>439</v>
-      </c>
-    </row>
-    <row r="77" spans="1:8" x14ac:dyDescent="0.2">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="77" spans="1:8">
       <c r="A77" t="s">
-        <v>235</v>
+        <v>242</v>
       </c>
       <c r="B77" t="s">
-        <v>177</v>
+        <v>185</v>
       </c>
       <c r="C77" t="s">
-        <v>440</v>
+        <v>449</v>
       </c>
       <c r="D77">
         <v>55</v>
@@ -8516,18 +8582,18 @@
         <v>60</v>
       </c>
       <c r="H77" t="s">
-        <v>441</v>
-      </c>
-    </row>
-    <row r="78" spans="1:8" x14ac:dyDescent="0.2">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="78" spans="1:8">
       <c r="A78" t="s">
-        <v>235</v>
+        <v>242</v>
       </c>
       <c r="B78" t="s">
-        <v>442</v>
+        <v>451</v>
       </c>
       <c r="C78" t="s">
-        <v>443</v>
+        <v>452</v>
       </c>
       <c r="D78">
         <v>40</v>
@@ -8542,18 +8608,18 @@
         <v>70</v>
       </c>
       <c r="H78" t="s">
-        <v>444</v>
-      </c>
-    </row>
-    <row r="79" spans="1:8" x14ac:dyDescent="0.2">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="79" spans="1:8">
       <c r="A79" t="s">
-        <v>237</v>
+        <v>244</v>
       </c>
       <c r="B79" t="s">
-        <v>445</v>
+        <v>454</v>
       </c>
       <c r="C79" t="s">
-        <v>446</v>
+        <v>455</v>
       </c>
       <c r="D79">
         <v>0</v>
@@ -8568,18 +8634,18 @@
         <v>10</v>
       </c>
       <c r="H79" t="s">
-        <v>447</v>
-      </c>
-    </row>
-    <row r="80" spans="1:8" x14ac:dyDescent="0.2">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="80" spans="1:8">
       <c r="A80" t="s">
-        <v>237</v>
+        <v>244</v>
       </c>
       <c r="B80" t="s">
-        <v>448</v>
+        <v>457</v>
       </c>
       <c r="C80" t="s">
-        <v>449</v>
+        <v>458</v>
       </c>
       <c r="D80">
         <v>5</v>
@@ -8594,18 +8660,18 @@
         <v>20</v>
       </c>
       <c r="H80" t="s">
-        <v>450</v>
-      </c>
-    </row>
-    <row r="81" spans="1:8" x14ac:dyDescent="0.2">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="81" spans="1:8">
       <c r="A81" t="s">
-        <v>239</v>
+        <v>246</v>
       </c>
       <c r="B81" t="s">
-        <v>451</v>
+        <v>460</v>
       </c>
       <c r="C81" t="s">
-        <v>452</v>
+        <v>461</v>
       </c>
       <c r="D81">
         <v>0</v>
@@ -8620,18 +8686,18 @@
         <v>10</v>
       </c>
       <c r="H81" t="s">
-        <v>452</v>
-      </c>
-    </row>
-    <row r="82" spans="1:8" x14ac:dyDescent="0.2">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="82" spans="1:8">
       <c r="A82" t="s">
-        <v>239</v>
+        <v>246</v>
       </c>
       <c r="B82" t="s">
-        <v>453</v>
+        <v>462</v>
       </c>
       <c r="C82" t="s">
-        <v>454</v>
+        <v>463</v>
       </c>
       <c r="D82">
         <v>0</v>
@@ -8646,18 +8712,18 @@
         <v>20</v>
       </c>
       <c r="H82" t="s">
-        <v>454</v>
-      </c>
-    </row>
-    <row r="83" spans="1:8" x14ac:dyDescent="0.2">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="83" spans="1:8">
       <c r="A83" t="s">
-        <v>239</v>
+        <v>246</v>
       </c>
       <c r="B83" t="s">
-        <v>455</v>
+        <v>464</v>
       </c>
       <c r="C83" t="s">
-        <v>456</v>
+        <v>465</v>
       </c>
       <c r="D83">
         <v>0</v>
@@ -8672,18 +8738,18 @@
         <v>30</v>
       </c>
       <c r="H83" t="s">
-        <v>456</v>
-      </c>
-    </row>
-    <row r="84" spans="1:8" x14ac:dyDescent="0.2">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="84" spans="1:8">
       <c r="A84" t="s">
-        <v>241</v>
+        <v>248</v>
       </c>
       <c r="B84" t="s">
-        <v>457</v>
+        <v>466</v>
       </c>
       <c r="C84" t="s">
-        <v>458</v>
+        <v>467</v>
       </c>
       <c r="D84">
         <v>7</v>
@@ -8698,18 +8764,18 @@
         <v>10</v>
       </c>
       <c r="H84" t="s">
-        <v>458</v>
-      </c>
-    </row>
-    <row r="85" spans="1:8" x14ac:dyDescent="0.2">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="85" spans="1:8">
       <c r="A85" t="s">
-        <v>243</v>
+        <v>250</v>
       </c>
       <c r="B85" t="s">
-        <v>243</v>
+        <v>250</v>
       </c>
       <c r="C85" t="s">
-        <v>244</v>
+        <v>251</v>
       </c>
       <c r="D85">
         <v>0</v>
@@ -8724,18 +8790,18 @@
         <v>10</v>
       </c>
       <c r="H85" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="86" spans="1:8" x14ac:dyDescent="0.2">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="86" spans="1:8">
       <c r="A86" t="s">
-        <v>209</v>
+        <v>216</v>
       </c>
       <c r="B86" t="s">
-        <v>459</v>
+        <v>468</v>
       </c>
       <c r="C86" t="s">
-        <v>460</v>
+        <v>469</v>
       </c>
       <c r="D86">
         <v>0</v>
@@ -8750,18 +8816,18 @@
         <v>60</v>
       </c>
       <c r="H86" t="s">
-        <v>461</v>
-      </c>
-    </row>
-    <row r="87" spans="1:8" x14ac:dyDescent="0.2">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="87" spans="1:8">
       <c r="A87" s="4" t="s">
-        <v>540</v>
+        <v>252</v>
       </c>
       <c r="B87" s="4" t="s">
-        <v>554</v>
+        <v>471</v>
       </c>
       <c r="C87" s="4" t="s">
-        <v>555</v>
+        <v>472</v>
       </c>
       <c r="D87">
         <v>0</v>
@@ -8776,18 +8842,18 @@
         <v>10</v>
       </c>
       <c r="H87" s="4" t="s">
-        <v>553</v>
-      </c>
-    </row>
-    <row r="88" spans="1:8" x14ac:dyDescent="0.2">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="88" spans="1:8">
       <c r="A88" s="4" t="s">
-        <v>540</v>
+        <v>252</v>
       </c>
       <c r="B88" s="4" t="s">
-        <v>541</v>
+        <v>474</v>
       </c>
       <c r="C88" s="4" t="s">
-        <v>544</v>
+        <v>475</v>
       </c>
       <c r="D88">
         <v>0</v>
@@ -8802,18 +8868,18 @@
         <v>20</v>
       </c>
       <c r="H88" s="4" t="s">
-        <v>547</v>
-      </c>
-    </row>
-    <row r="89" spans="1:8" x14ac:dyDescent="0.2">
+        <v>476</v>
+      </c>
+    </row>
+    <row r="89" spans="1:8">
       <c r="A89" s="4" t="s">
-        <v>540</v>
+        <v>252</v>
       </c>
       <c r="B89" s="4" t="s">
-        <v>542</v>
+        <v>477</v>
       </c>
       <c r="C89" s="4" t="s">
-        <v>545</v>
+        <v>478</v>
       </c>
       <c r="D89">
         <v>0</v>
@@ -8828,18 +8894,18 @@
         <v>30</v>
       </c>
       <c r="H89" s="4" t="s">
-        <v>548</v>
-      </c>
-    </row>
-    <row r="90" spans="1:8" x14ac:dyDescent="0.2">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="90" spans="1:8">
       <c r="A90" s="4" t="s">
-        <v>540</v>
+        <v>252</v>
       </c>
       <c r="B90" s="4" t="s">
-        <v>543</v>
+        <v>480</v>
       </c>
       <c r="C90" s="4" t="s">
-        <v>546</v>
+        <v>481</v>
       </c>
       <c r="D90">
         <v>0</v>
@@ -8854,59 +8920,63 @@
         <v>40</v>
       </c>
       <c r="H90" s="4" t="s">
-        <v>549</v>
+        <v>482</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H1" xr:uid="{00000000-0009-0000-0000-000004000000}"/>
+  <autoFilter ref="A1:H1"/>
+  <printOptions gridLines="false" gridLinesSet="true"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait"/>
+  <pageSetup paperSize="1" orientation="portrait" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr filterMode="1">
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+  </sheetPr>
   <dimension ref="A1:G47"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="14.4" defaultColWidth="8.83203125" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col min="1" max="1" width="19.5" customWidth="1"/>
-    <col min="2" max="2" width="15.1640625" customWidth="1"/>
-    <col min="3" max="3" width="16.33203125" customWidth="1"/>
-    <col min="4" max="4" width="12.83203125" customWidth="1"/>
-    <col min="5" max="5" width="21" customWidth="1"/>
-    <col min="6" max="6" width="17.5" customWidth="1"/>
-    <col min="7" max="7" width="10.5" customWidth="1"/>
+    <col min="1" max="1" width="19.5" customWidth="true" style="0"/>
+    <col min="2" max="2" width="15.1640625" customWidth="true" style="0"/>
+    <col min="3" max="3" width="16.33203125" customWidth="true" style="0"/>
+    <col min="4" max="4" width="12.83203125" customWidth="true" style="0"/>
+    <col min="5" max="5" width="21" customWidth="true" style="0"/>
+    <col min="6" max="6" width="17.5" customWidth="true" style="0"/>
+    <col min="7" max="7" width="10.5" customWidth="true" style="0"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:7">
       <c r="A1" s="1" t="s">
-        <v>462</v>
+        <v>483</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>245</v>
+        <v>254</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>189</v>
+        <v>196</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>190</v>
+        <v>197</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>192</v>
+        <v>199</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>191</v>
+        <v>198</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:7">
       <c r="A2" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B2" t="s">
-        <v>209</v>
+        <v>216</v>
       </c>
       <c r="C2">
         <v>1</v>
@@ -8915,7 +8985,7 @@
         <v>0</v>
       </c>
       <c r="E2" t="s">
-        <v>199</v>
+        <v>206</v>
       </c>
       <c r="F2">
         <v>5</v>
@@ -8924,12 +8994,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:7">
       <c r="A3" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B3" t="s">
-        <v>196</v>
+        <v>203</v>
       </c>
       <c r="C3">
         <v>1</v>
@@ -8938,7 +9008,7 @@
         <v>0</v>
       </c>
       <c r="E3" t="s">
-        <v>199</v>
+        <v>206</v>
       </c>
       <c r="F3">
         <v>5</v>
@@ -8947,12 +9017,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:7">
       <c r="A4" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B4" t="s">
-        <v>211</v>
+        <v>218</v>
       </c>
       <c r="C4">
         <v>1</v>
@@ -8961,7 +9031,7 @@
         <v>0</v>
       </c>
       <c r="E4" t="s">
-        <v>199</v>
+        <v>206</v>
       </c>
       <c r="F4">
         <v>5</v>
@@ -8970,12 +9040,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:7">
       <c r="A5" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B5" t="s">
-        <v>200</v>
+        <v>207</v>
       </c>
       <c r="C5">
         <v>0</v>
@@ -8984,7 +9054,7 @@
         <v>1</v>
       </c>
       <c r="E5" t="s">
-        <v>199</v>
+        <v>206</v>
       </c>
       <c r="F5">
         <v>5</v>
@@ -8993,12 +9063,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:7">
       <c r="A6" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="B6" t="s">
-        <v>213</v>
+        <v>220</v>
       </c>
       <c r="C6">
         <v>1</v>
@@ -9007,7 +9077,7 @@
         <v>0</v>
       </c>
       <c r="E6" t="s">
-        <v>199</v>
+        <v>206</v>
       </c>
       <c r="F6">
         <v>5</v>
@@ -9016,12 +9086,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:7">
       <c r="A7" t="s">
         <v>30</v>
       </c>
       <c r="B7" t="s">
-        <v>196</v>
+        <v>203</v>
       </c>
       <c r="C7">
         <v>1</v>
@@ -9030,7 +9100,7 @@
         <v>0</v>
       </c>
       <c r="E7" t="s">
-        <v>199</v>
+        <v>206</v>
       </c>
       <c r="F7">
         <v>5</v>
@@ -9039,12 +9109,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:7">
       <c r="A8" t="s">
         <v>30</v>
       </c>
       <c r="B8" t="s">
-        <v>207</v>
+        <v>214</v>
       </c>
       <c r="C8">
         <v>0</v>
@@ -9053,7 +9123,7 @@
         <v>1</v>
       </c>
       <c r="E8" t="s">
-        <v>199</v>
+        <v>206</v>
       </c>
       <c r="F8">
         <v>10</v>
@@ -9062,12 +9132,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:7">
       <c r="A9" s="4" t="s">
-        <v>538</v>
+        <v>32</v>
       </c>
       <c r="B9" t="s">
-        <v>196</v>
+        <v>203</v>
       </c>
       <c r="C9">
         <v>1</v>
@@ -9076,7 +9146,7 @@
         <v>0</v>
       </c>
       <c r="E9" t="s">
-        <v>199</v>
+        <v>206</v>
       </c>
       <c r="F9">
         <v>5</v>
@@ -9085,12 +9155,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:7">
       <c r="A10" s="4" t="s">
-        <v>538</v>
+        <v>32</v>
       </c>
       <c r="B10" t="s">
-        <v>207</v>
+        <v>214</v>
       </c>
       <c r="C10">
         <v>0</v>
@@ -9099,7 +9169,7 @@
         <v>1</v>
       </c>
       <c r="E10" t="s">
-        <v>199</v>
+        <v>206</v>
       </c>
       <c r="F10">
         <v>10</v>
@@ -9108,12 +9178,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:7">
       <c r="A11" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="B11" t="s">
-        <v>196</v>
+        <v>203</v>
       </c>
       <c r="C11">
         <v>1</v>
@@ -9122,7 +9192,7 @@
         <v>0</v>
       </c>
       <c r="E11" t="s">
-        <v>199</v>
+        <v>206</v>
       </c>
       <c r="F11">
         <v>5</v>
@@ -9131,12 +9201,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:7">
       <c r="A12" t="s">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="B12" t="s">
-        <v>205</v>
+        <v>212</v>
       </c>
       <c r="C12">
         <v>1</v>
@@ -9145,7 +9215,7 @@
         <v>0</v>
       </c>
       <c r="E12" t="s">
-        <v>199</v>
+        <v>206</v>
       </c>
       <c r="F12">
         <v>5</v>
@@ -9154,12 +9224,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:7">
       <c r="A13" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="B13" t="s">
-        <v>203</v>
+        <v>210</v>
       </c>
       <c r="C13">
         <v>1</v>
@@ -9168,7 +9238,7 @@
         <v>0</v>
       </c>
       <c r="E13" t="s">
-        <v>199</v>
+        <v>206</v>
       </c>
       <c r="F13">
         <v>5</v>
@@ -9177,12 +9247,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:7">
       <c r="A14" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B14" t="s">
-        <v>215</v>
+        <v>222</v>
       </c>
       <c r="C14">
         <v>1</v>
@@ -9191,7 +9261,7 @@
         <v>0</v>
       </c>
       <c r="E14" t="s">
-        <v>199</v>
+        <v>206</v>
       </c>
       <c r="F14">
         <v>5</v>
@@ -9200,12 +9270,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:7">
       <c r="A15" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B15" t="s">
-        <v>217</v>
+        <v>224</v>
       </c>
       <c r="C15">
         <v>1</v>
@@ -9214,7 +9284,7 @@
         <v>0</v>
       </c>
       <c r="E15" t="s">
-        <v>199</v>
+        <v>206</v>
       </c>
       <c r="F15">
         <v>10</v>
@@ -9223,12 +9293,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:7">
       <c r="A16" t="s">
-        <v>98</v>
+        <v>108</v>
       </c>
       <c r="B16" t="s">
-        <v>215</v>
+        <v>222</v>
       </c>
       <c r="C16">
         <v>1</v>
@@ -9237,7 +9307,7 @@
         <v>0</v>
       </c>
       <c r="E16" t="s">
-        <v>199</v>
+        <v>206</v>
       </c>
       <c r="F16">
         <v>5</v>
@@ -9246,12 +9316,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:7">
       <c r="A17" t="s">
-        <v>96</v>
+        <v>106</v>
       </c>
       <c r="B17" t="s">
-        <v>219</v>
+        <v>226</v>
       </c>
       <c r="C17">
         <v>1</v>
@@ -9260,7 +9330,7 @@
         <v>0</v>
       </c>
       <c r="E17" t="s">
-        <v>199</v>
+        <v>206</v>
       </c>
       <c r="F17">
         <v>5</v>
@@ -9269,12 +9339,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:7">
       <c r="A18" t="s">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="B18" t="s">
-        <v>221</v>
+        <v>228</v>
       </c>
       <c r="C18">
         <v>1</v>
@@ -9283,7 +9353,7 @@
         <v>0</v>
       </c>
       <c r="E18" t="s">
-        <v>199</v>
+        <v>206</v>
       </c>
       <c r="F18">
         <v>5</v>
@@ -9292,12 +9362,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:7">
       <c r="A19" t="s">
-        <v>102</v>
+        <v>112</v>
       </c>
       <c r="B19" t="s">
-        <v>215</v>
+        <v>222</v>
       </c>
       <c r="C19">
         <v>1</v>
@@ -9306,7 +9376,7 @@
         <v>0</v>
       </c>
       <c r="E19" t="s">
-        <v>199</v>
+        <v>206</v>
       </c>
       <c r="F19">
         <v>5</v>
@@ -9315,12 +9385,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:7">
       <c r="A20" t="s">
-        <v>102</v>
+        <v>112</v>
       </c>
       <c r="B20" t="s">
-        <v>223</v>
+        <v>230</v>
       </c>
       <c r="C20">
         <v>1</v>
@@ -9329,7 +9399,7 @@
         <v>0</v>
       </c>
       <c r="E20" t="s">
-        <v>199</v>
+        <v>206</v>
       </c>
       <c r="F20">
         <v>10</v>
@@ -9338,12 +9408,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:7">
       <c r="A21" t="s">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="B21" t="s">
-        <v>215</v>
+        <v>222</v>
       </c>
       <c r="C21">
         <v>1</v>
@@ -9352,7 +9422,7 @@
         <v>0</v>
       </c>
       <c r="E21" t="s">
-        <v>199</v>
+        <v>206</v>
       </c>
       <c r="F21">
         <v>5</v>
@@ -9361,12 +9431,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:7">
       <c r="A22" t="s">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="B22" t="s">
-        <v>225</v>
+        <v>232</v>
       </c>
       <c r="C22">
         <v>1</v>
@@ -9375,7 +9445,7 @@
         <v>0</v>
       </c>
       <c r="E22" t="s">
-        <v>199</v>
+        <v>206</v>
       </c>
       <c r="F22">
         <v>10</v>
@@ -9384,12 +9454,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:7">
       <c r="A23" t="s">
-        <v>106</v>
+        <v>116</v>
       </c>
       <c r="B23" t="s">
-        <v>227</v>
+        <v>234</v>
       </c>
       <c r="C23">
         <v>1</v>
@@ -9398,7 +9468,7 @@
         <v>0</v>
       </c>
       <c r="E23" t="s">
-        <v>199</v>
+        <v>206</v>
       </c>
       <c r="F23">
         <v>5</v>
@@ -9407,12 +9477,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:7">
       <c r="A24" t="s">
-        <v>108</v>
+        <v>118</v>
       </c>
       <c r="B24" t="s">
-        <v>229</v>
+        <v>236</v>
       </c>
       <c r="C24">
         <v>1</v>
@@ -9421,7 +9491,7 @@
         <v>0</v>
       </c>
       <c r="E24" t="s">
-        <v>199</v>
+        <v>206</v>
       </c>
       <c r="F24">
         <v>5</v>
@@ -9430,12 +9500,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:7">
       <c r="A25" t="s">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="B25" t="s">
-        <v>235</v>
+        <v>242</v>
       </c>
       <c r="C25">
         <v>1</v>
@@ -9444,7 +9514,7 @@
         <v>0</v>
       </c>
       <c r="E25" t="s">
-        <v>199</v>
+        <v>206</v>
       </c>
       <c r="F25">
         <v>5</v>
@@ -9453,12 +9523,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:7">
       <c r="A26" t="s">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="B26" t="s">
-        <v>237</v>
+        <v>244</v>
       </c>
       <c r="C26">
         <v>1</v>
@@ -9467,7 +9537,7 @@
         <v>0</v>
       </c>
       <c r="E26" t="s">
-        <v>199</v>
+        <v>206</v>
       </c>
       <c r="F26">
         <v>10</v>
@@ -9476,12 +9546,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:7">
       <c r="A27" t="s">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="B27" t="s">
-        <v>239</v>
+        <v>246</v>
       </c>
       <c r="C27">
         <v>1</v>
@@ -9490,7 +9560,7 @@
         <v>0</v>
       </c>
       <c r="E27" t="s">
-        <v>199</v>
+        <v>206</v>
       </c>
       <c r="F27">
         <v>15</v>
@@ -9499,12 +9569,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:7">
       <c r="A28" t="s">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="B28" t="s">
-        <v>241</v>
+        <v>248</v>
       </c>
       <c r="C28">
         <v>0</v>
@@ -9513,7 +9583,7 @@
         <v>0</v>
       </c>
       <c r="E28" t="s">
-        <v>199</v>
+        <v>206</v>
       </c>
       <c r="F28">
         <v>20</v>
@@ -9522,12 +9592,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:7">
       <c r="A29" t="s">
-        <v>112</v>
+        <v>122</v>
       </c>
       <c r="B29" t="s">
-        <v>243</v>
+        <v>250</v>
       </c>
       <c r="C29">
         <v>0</v>
@@ -9536,7 +9606,7 @@
         <v>0</v>
       </c>
       <c r="E29" t="s">
-        <v>199</v>
+        <v>206</v>
       </c>
       <c r="F29">
         <v>5</v>
@@ -9545,12 +9615,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:7">
       <c r="A30" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>540</v>
+        <v>252</v>
       </c>
       <c r="C30">
         <v>1</v>
@@ -9559,7 +9629,7 @@
         <v>0</v>
       </c>
       <c r="E30" s="4" t="s">
-        <v>199</v>
+        <v>206</v>
       </c>
       <c r="F30">
         <v>5</v>
@@ -9568,12 +9638,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:7">
       <c r="A31" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>540</v>
+        <v>252</v>
       </c>
       <c r="C31">
         <v>1</v>
@@ -9582,7 +9652,7 @@
         <v>0</v>
       </c>
       <c r="E31" s="4" t="s">
-        <v>199</v>
+        <v>206</v>
       </c>
       <c r="F31">
         <v>10</v>
@@ -9591,12 +9661,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:7">
       <c r="A32" s="4" t="s">
-        <v>159</v>
+        <v>72</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>540</v>
+        <v>252</v>
       </c>
       <c r="C32">
         <v>1</v>
@@ -9605,7 +9675,7 @@
         <v>0</v>
       </c>
       <c r="E32" s="4" t="s">
-        <v>199</v>
+        <v>206</v>
       </c>
       <c r="F32">
         <v>15</v>
@@ -9614,12 +9684,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:7">
       <c r="A33" s="4" t="s">
-        <v>161</v>
+        <v>74</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>540</v>
+        <v>252</v>
       </c>
       <c r="C33">
         <v>1</v>
@@ -9628,7 +9698,7 @@
         <v>0</v>
       </c>
       <c r="E33" s="4" t="s">
-        <v>199</v>
+        <v>206</v>
       </c>
       <c r="F33">
         <v>20</v>
@@ -9637,12 +9707,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:7">
       <c r="A34" s="4" t="s">
-        <v>550</v>
+        <v>76</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>540</v>
+        <v>252</v>
       </c>
       <c r="C34">
         <v>1</v>
@@ -9651,7 +9721,7 @@
         <v>0</v>
       </c>
       <c r="E34" s="4" t="s">
-        <v>199</v>
+        <v>206</v>
       </c>
       <c r="F34">
         <v>25</v>
@@ -9660,12 +9730,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:7">
       <c r="A35" s="4" t="s">
-        <v>181</v>
+        <v>78</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>540</v>
+        <v>252</v>
       </c>
       <c r="C35">
         <v>1</v>
@@ -9674,7 +9744,7 @@
         <v>0</v>
       </c>
       <c r="E35" s="4" t="s">
-        <v>199</v>
+        <v>206</v>
       </c>
       <c r="F35">
         <v>30</v>
@@ -9683,12 +9753,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:7">
       <c r="A46" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B46" t="s">
-        <v>196</v>
+        <v>203</v>
       </c>
       <c r="C46">
         <v>1</v>
@@ -9697,7 +9767,7 @@
         <v>0</v>
       </c>
       <c r="E46" t="s">
-        <v>199</v>
+        <v>206</v>
       </c>
       <c r="F46">
         <v>5</v>
@@ -9706,12 +9776,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:7">
       <c r="A47" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B47" t="s">
-        <v>196</v>
+        <v>203</v>
       </c>
       <c r="C47">
         <v>1</v>
@@ -9720,7 +9790,7 @@
         <v>0</v>
       </c>
       <c r="E47" t="s">
-        <v>199</v>
+        <v>206</v>
       </c>
       <c r="F47">
         <v>5</v>
@@ -9730,41 +9800,45 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G1" xr:uid="{00000000-0009-0000-0000-000005000000}"/>
+  <autoFilter ref="A1:G1"/>
+  <printOptions gridLines="false" gridLinesSet="true"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait"/>
+  <pageSetup paperSize="1" orientation="portrait" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr filterMode="1">
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+  </sheetPr>
   <dimension ref="A1:G52"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="14.4" defaultColWidth="8.83203125" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col min="1" max="1" width="19.6640625" customWidth="1"/>
-    <col min="2" max="2" width="14" customWidth="1"/>
-    <col min="3" max="3" width="8.1640625" customWidth="1"/>
-    <col min="4" max="4" width="23.5" customWidth="1"/>
-    <col min="5" max="5" width="12.83203125" customWidth="1"/>
-    <col min="6" max="6" width="9.33203125" customWidth="1"/>
-    <col min="7" max="7" width="10.5" customWidth="1"/>
+    <col min="1" max="1" width="19.6640625" customWidth="true" style="0"/>
+    <col min="2" max="2" width="14" customWidth="true" style="0"/>
+    <col min="3" max="3" width="8.1640625" customWidth="true" style="0"/>
+    <col min="4" max="4" width="23.5" customWidth="true" style="0"/>
+    <col min="5" max="5" width="12.83203125" customWidth="true" style="0"/>
+    <col min="6" max="6" width="9.33203125" customWidth="true" style="0"/>
+    <col min="7" max="7" width="10.5" customWidth="true" style="0"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:7">
       <c r="A1" s="1" t="s">
-        <v>462</v>
+        <v>483</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>463</v>
+        <v>484</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>464</v>
+        <v>485</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>465</v>
+        <v>486</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>466</v>
+        <v>487</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>4</v>
@@ -9773,18 +9847,18 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:7">
       <c r="A2" t="s">
         <v>30</v>
       </c>
       <c r="B2" t="s">
-        <v>199</v>
+        <v>206</v>
       </c>
       <c r="C2" t="s">
         <v>7</v>
       </c>
       <c r="D2" t="s">
-        <v>467</v>
+        <v>488</v>
       </c>
       <c r="E2">
         <v>1</v>
@@ -9796,18 +9870,18 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:7">
       <c r="A3" s="4" t="s">
-        <v>538</v>
+        <v>32</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>199</v>
+        <v>206</v>
       </c>
       <c r="C3" s="4" t="s">
         <v>7</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>560</v>
+        <v>489</v>
       </c>
       <c r="E3">
         <v>1</v>
@@ -9819,18 +9893,18 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:7">
       <c r="A4" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B4" t="s">
-        <v>468</v>
+        <v>490</v>
       </c>
       <c r="C4" t="s">
         <v>10</v>
       </c>
       <c r="D4" t="s">
-        <v>469</v>
+        <v>491</v>
       </c>
       <c r="E4">
         <v>1</v>
@@ -9842,18 +9916,18 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:7">
       <c r="A5" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B5" t="s">
-        <v>199</v>
+        <v>206</v>
       </c>
       <c r="C5" t="s">
         <v>7</v>
       </c>
       <c r="D5" t="s">
-        <v>470</v>
+        <v>492</v>
       </c>
       <c r="E5">
         <v>1</v>
@@ -9865,18 +9939,18 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:7">
       <c r="A6" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B6" t="s">
-        <v>199</v>
+        <v>206</v>
       </c>
       <c r="C6" t="s">
         <v>7</v>
       </c>
       <c r="D6" t="s">
-        <v>471</v>
+        <v>493</v>
       </c>
       <c r="E6">
         <v>1</v>
@@ -9888,18 +9962,18 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:7">
       <c r="A7" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B7" t="s">
-        <v>199</v>
+        <v>206</v>
       </c>
       <c r="C7" t="s">
         <v>7</v>
       </c>
       <c r="D7" t="s">
-        <v>472</v>
+        <v>494</v>
       </c>
       <c r="E7">
         <v>1</v>
@@ -9911,18 +9985,18 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:7">
       <c r="A8" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B8" t="s">
-        <v>199</v>
+        <v>206</v>
       </c>
       <c r="C8" t="s">
         <v>7</v>
       </c>
       <c r="D8" t="s">
-        <v>473</v>
+        <v>495</v>
       </c>
       <c r="E8">
         <v>1</v>
@@ -9934,18 +10008,18 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:7">
       <c r="A9" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B9" t="s">
-        <v>199</v>
+        <v>206</v>
       </c>
       <c r="C9" t="s">
         <v>7</v>
       </c>
       <c r="D9" t="s">
-        <v>474</v>
+        <v>496</v>
       </c>
       <c r="E9">
         <v>1</v>
@@ -9957,18 +10031,18 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:7">
       <c r="A10" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="B10" t="s">
-        <v>199</v>
+        <v>206</v>
       </c>
       <c r="C10" t="s">
         <v>7</v>
       </c>
       <c r="D10" t="s">
-        <v>475</v>
+        <v>497</v>
       </c>
       <c r="E10">
         <v>1</v>
@@ -9980,18 +10054,18 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:7">
       <c r="A11" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="B11" t="s">
-        <v>199</v>
+        <v>206</v>
       </c>
       <c r="C11" t="s">
         <v>7</v>
       </c>
       <c r="D11" t="s">
-        <v>476</v>
+        <v>498</v>
       </c>
       <c r="E11">
         <v>1</v>
@@ -10003,18 +10077,18 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:7">
       <c r="A12" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="B12" t="s">
-        <v>199</v>
+        <v>206</v>
       </c>
       <c r="C12" t="s">
         <v>7</v>
       </c>
       <c r="D12" t="s">
-        <v>477</v>
+        <v>499</v>
       </c>
       <c r="E12">
         <v>1</v>
@@ -10026,18 +10100,18 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:7">
       <c r="A13" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="B13" t="s">
-        <v>199</v>
+        <v>206</v>
       </c>
       <c r="C13" t="s">
         <v>7</v>
       </c>
       <c r="D13" t="s">
-        <v>478</v>
+        <v>500</v>
       </c>
       <c r="E13">
         <v>1</v>
@@ -10049,18 +10123,18 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:7">
       <c r="A14" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="B14" t="s">
-        <v>199</v>
+        <v>206</v>
       </c>
       <c r="C14" t="s">
         <v>7</v>
       </c>
       <c r="D14" t="s">
-        <v>479</v>
+        <v>501</v>
       </c>
       <c r="E14">
         <v>1</v>
@@ -10072,18 +10146,18 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:7">
       <c r="A15" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="B15" t="s">
-        <v>199</v>
+        <v>206</v>
       </c>
       <c r="C15" t="s">
         <v>7</v>
       </c>
       <c r="D15" t="s">
-        <v>480</v>
+        <v>502</v>
       </c>
       <c r="E15">
         <v>1</v>
@@ -10095,18 +10169,18 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:7">
       <c r="A16" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B16" t="s">
-        <v>199</v>
+        <v>206</v>
       </c>
       <c r="C16" t="s">
         <v>7</v>
       </c>
       <c r="D16" t="s">
-        <v>481</v>
+        <v>503</v>
       </c>
       <c r="E16">
         <v>1</v>
@@ -10118,18 +10192,18 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:7">
       <c r="A17" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="B17" t="s">
-        <v>199</v>
+        <v>206</v>
       </c>
       <c r="C17" t="s">
         <v>7</v>
       </c>
       <c r="D17" t="s">
-        <v>482</v>
+        <v>504</v>
       </c>
       <c r="E17">
         <v>1</v>
@@ -10141,18 +10215,18 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:7">
       <c r="A18" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="B18" t="s">
-        <v>199</v>
+        <v>206</v>
       </c>
       <c r="C18" t="s">
         <v>7</v>
       </c>
       <c r="D18" t="s">
-        <v>483</v>
+        <v>505</v>
       </c>
       <c r="E18">
         <v>1</v>
@@ -10164,18 +10238,18 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:7">
       <c r="A19" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="B19" t="s">
-        <v>199</v>
+        <v>206</v>
       </c>
       <c r="C19" t="s">
         <v>7</v>
       </c>
       <c r="D19" t="s">
-        <v>484</v>
+        <v>506</v>
       </c>
       <c r="E19">
         <v>1</v>
@@ -10187,18 +10261,18 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:7">
       <c r="A20" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="B20" t="s">
-        <v>199</v>
+        <v>206</v>
       </c>
       <c r="C20" t="s">
         <v>7</v>
       </c>
       <c r="D20" t="s">
-        <v>485</v>
+        <v>507</v>
       </c>
       <c r="E20">
         <v>1</v>
@@ -10210,18 +10284,18 @@
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:7">
       <c r="A21" s="4" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="B21" t="s">
-        <v>199</v>
+        <v>206</v>
       </c>
       <c r="C21" t="s">
         <v>7</v>
       </c>
       <c r="D21" t="s">
-        <v>486</v>
+        <v>508</v>
       </c>
       <c r="E21">
         <v>1</v>
@@ -10233,18 +10307,18 @@
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:7">
       <c r="A22" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="B22" t="s">
-        <v>199</v>
+        <v>206</v>
       </c>
       <c r="C22" t="s">
         <v>7</v>
       </c>
       <c r="D22" t="s">
-        <v>487</v>
+        <v>509</v>
       </c>
       <c r="E22">
         <v>1</v>
@@ -10256,18 +10330,18 @@
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:7">
       <c r="A23" s="4" t="s">
-        <v>159</v>
+        <v>72</v>
       </c>
       <c r="B23" t="s">
-        <v>199</v>
+        <v>206</v>
       </c>
       <c r="C23" t="s">
         <v>7</v>
       </c>
       <c r="D23" s="4" t="s">
-        <v>556</v>
+        <v>510</v>
       </c>
       <c r="E23">
         <v>1</v>
@@ -10279,18 +10353,18 @@
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:7">
       <c r="A24" s="4" t="s">
-        <v>161</v>
+        <v>74</v>
       </c>
       <c r="B24" t="s">
-        <v>199</v>
+        <v>206</v>
       </c>
       <c r="C24" t="s">
         <v>7</v>
       </c>
       <c r="D24" s="4" t="s">
-        <v>557</v>
+        <v>511</v>
       </c>
       <c r="E24">
         <v>1</v>
@@ -10302,18 +10376,18 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:7">
       <c r="A25" s="4" t="s">
-        <v>550</v>
+        <v>76</v>
       </c>
       <c r="B25" t="s">
-        <v>199</v>
+        <v>206</v>
       </c>
       <c r="C25" t="s">
         <v>7</v>
       </c>
       <c r="D25" s="4" t="s">
-        <v>558</v>
+        <v>512</v>
       </c>
       <c r="E25">
         <v>1</v>
@@ -10325,18 +10399,18 @@
         <v>1</v>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:7">
       <c r="A26" s="4" t="s">
-        <v>181</v>
+        <v>78</v>
       </c>
       <c r="B26" t="s">
-        <v>199</v>
+        <v>206</v>
       </c>
       <c r="C26" t="s">
         <v>7</v>
       </c>
       <c r="D26" s="4" t="s">
-        <v>559</v>
+        <v>513</v>
       </c>
       <c r="E26">
         <v>1</v>
@@ -10348,18 +10422,18 @@
         <v>1</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:7">
       <c r="A27" t="s">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="B27" t="s">
-        <v>488</v>
+        <v>514</v>
       </c>
       <c r="C27" t="s">
         <v>7</v>
       </c>
       <c r="D27" t="s">
-        <v>489</v>
+        <v>515</v>
       </c>
       <c r="E27">
         <v>1</v>
@@ -10371,18 +10445,18 @@
         <v>1</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:7">
       <c r="A28" t="s">
-        <v>72</v>
+        <v>82</v>
       </c>
       <c r="B28" t="s">
-        <v>468</v>
+        <v>490</v>
       </c>
       <c r="C28" t="s">
         <v>7</v>
       </c>
       <c r="D28" t="s">
-        <v>490</v>
+        <v>516</v>
       </c>
       <c r="E28">
         <v>1</v>
@@ -10394,18 +10468,18 @@
         <v>1</v>
       </c>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:7">
       <c r="A29" t="s">
-        <v>74</v>
+        <v>84</v>
       </c>
       <c r="B29" t="s">
-        <v>468</v>
+        <v>490</v>
       </c>
       <c r="C29" t="s">
         <v>7</v>
       </c>
       <c r="D29" t="s">
-        <v>491</v>
+        <v>517</v>
       </c>
       <c r="E29">
         <v>1</v>
@@ -10417,18 +10491,18 @@
         <v>1</v>
       </c>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:7">
       <c r="A30" t="s">
-        <v>76</v>
+        <v>86</v>
       </c>
       <c r="B30" t="s">
-        <v>468</v>
+        <v>490</v>
       </c>
       <c r="C30" t="s">
         <v>7</v>
       </c>
       <c r="D30" t="s">
-        <v>492</v>
+        <v>518</v>
       </c>
       <c r="E30">
         <v>1</v>
@@ -10440,18 +10514,18 @@
         <v>1</v>
       </c>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:7">
       <c r="A31" t="s">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="B31" t="s">
-        <v>199</v>
+        <v>206</v>
       </c>
       <c r="C31" t="s">
         <v>7</v>
       </c>
       <c r="D31" t="s">
-        <v>493</v>
+        <v>519</v>
       </c>
       <c r="E31">
         <v>1</v>
@@ -10463,18 +10537,18 @@
         <v>1</v>
       </c>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:7">
       <c r="A32" t="s">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="B32" t="s">
-        <v>199</v>
+        <v>206</v>
       </c>
       <c r="C32" t="s">
         <v>7</v>
       </c>
       <c r="D32" t="s">
-        <v>494</v>
+        <v>520</v>
       </c>
       <c r="E32">
         <v>1</v>
@@ -10486,18 +10560,18 @@
         <v>1</v>
       </c>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:7">
       <c r="A33" t="s">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="B33" t="s">
-        <v>199</v>
+        <v>206</v>
       </c>
       <c r="C33" t="s">
         <v>7</v>
       </c>
       <c r="D33" t="s">
-        <v>495</v>
+        <v>521</v>
       </c>
       <c r="E33">
         <v>1</v>
@@ -10509,18 +10583,18 @@
         <v>1</v>
       </c>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:7">
       <c r="A34" t="s">
-        <v>84</v>
+        <v>94</v>
       </c>
       <c r="B34" t="s">
-        <v>199</v>
+        <v>206</v>
       </c>
       <c r="C34" t="s">
         <v>7</v>
       </c>
       <c r="D34" t="s">
-        <v>496</v>
+        <v>522</v>
       </c>
       <c r="E34">
         <v>1</v>
@@ -10532,18 +10606,18 @@
         <v>1</v>
       </c>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:7">
       <c r="A35" t="s">
-        <v>86</v>
+        <v>96</v>
       </c>
       <c r="B35" t="s">
-        <v>199</v>
+        <v>206</v>
       </c>
       <c r="C35" t="s">
         <v>7</v>
       </c>
       <c r="D35" t="s">
-        <v>497</v>
+        <v>523</v>
       </c>
       <c r="E35">
         <v>1</v>
@@ -10555,18 +10629,18 @@
         <v>1</v>
       </c>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:7">
       <c r="A36" t="s">
-        <v>88</v>
+        <v>98</v>
       </c>
       <c r="B36" t="s">
-        <v>468</v>
+        <v>490</v>
       </c>
       <c r="C36" t="s">
         <v>7</v>
       </c>
       <c r="D36" t="s">
-        <v>498</v>
+        <v>524</v>
       </c>
       <c r="E36">
         <v>1</v>
@@ -10578,18 +10652,18 @@
         <v>1</v>
       </c>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:7">
       <c r="A37" t="s">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="B37" t="s">
-        <v>468</v>
+        <v>490</v>
       </c>
       <c r="C37" t="s">
         <v>7</v>
       </c>
       <c r="D37" t="s">
-        <v>499</v>
+        <v>525</v>
       </c>
       <c r="E37">
         <v>1</v>
@@ -10601,18 +10675,18 @@
         <v>1</v>
       </c>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:7">
       <c r="A38" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="B38" t="s">
-        <v>468</v>
+        <v>490</v>
       </c>
       <c r="C38" t="s">
         <v>7</v>
       </c>
       <c r="D38" t="s">
-        <v>500</v>
+        <v>526</v>
       </c>
       <c r="E38">
         <v>1</v>
@@ -10624,18 +10698,18 @@
         <v>1</v>
       </c>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:7">
       <c r="A39" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="B39" t="s">
-        <v>468</v>
+        <v>490</v>
       </c>
       <c r="C39" t="s">
         <v>10</v>
       </c>
       <c r="D39" t="s">
-        <v>501</v>
+        <v>527</v>
       </c>
       <c r="E39">
         <v>1</v>
@@ -10647,18 +10721,18 @@
         <v>1</v>
       </c>
     </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:7">
       <c r="A40" t="s">
-        <v>96</v>
+        <v>106</v>
       </c>
       <c r="B40" t="s">
-        <v>468</v>
+        <v>490</v>
       </c>
       <c r="C40" t="s">
         <v>10</v>
       </c>
       <c r="D40" t="s">
-        <v>502</v>
+        <v>528</v>
       </c>
       <c r="E40">
         <v>1</v>
@@ -10670,18 +10744,18 @@
         <v>1</v>
       </c>
     </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:7">
       <c r="A41" t="s">
-        <v>98</v>
+        <v>108</v>
       </c>
       <c r="B41" t="s">
-        <v>468</v>
+        <v>490</v>
       </c>
       <c r="C41" t="s">
         <v>10</v>
       </c>
       <c r="D41" t="s">
-        <v>503</v>
+        <v>529</v>
       </c>
       <c r="E41">
         <v>1</v>
@@ -10693,18 +10767,18 @@
         <v>1</v>
       </c>
     </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:7">
       <c r="A42" t="s">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="B42" t="s">
-        <v>468</v>
+        <v>490</v>
       </c>
       <c r="C42" t="s">
         <v>10</v>
       </c>
       <c r="D42" t="s">
-        <v>504</v>
+        <v>530</v>
       </c>
       <c r="E42">
         <v>1</v>
@@ -10716,18 +10790,18 @@
         <v>1</v>
       </c>
     </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:7">
       <c r="A43" t="s">
-        <v>102</v>
+        <v>112</v>
       </c>
       <c r="B43" t="s">
-        <v>468</v>
+        <v>490</v>
       </c>
       <c r="C43" t="s">
         <v>10</v>
       </c>
       <c r="D43" t="s">
-        <v>505</v>
+        <v>531</v>
       </c>
       <c r="E43">
         <v>1</v>
@@ -10739,18 +10813,18 @@
         <v>1</v>
       </c>
     </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:7">
       <c r="A44" t="s">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="B44" t="s">
-        <v>468</v>
+        <v>490</v>
       </c>
       <c r="C44" t="s">
         <v>10</v>
       </c>
       <c r="D44" t="s">
-        <v>506</v>
+        <v>532</v>
       </c>
       <c r="E44">
         <v>1</v>
@@ -10762,18 +10836,18 @@
         <v>1</v>
       </c>
     </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:7">
       <c r="A45" t="s">
-        <v>106</v>
+        <v>116</v>
       </c>
       <c r="B45" t="s">
-        <v>468</v>
+        <v>490</v>
       </c>
       <c r="C45" t="s">
         <v>10</v>
       </c>
       <c r="D45" t="s">
-        <v>507</v>
+        <v>533</v>
       </c>
       <c r="E45">
         <v>1</v>
@@ -10785,18 +10859,18 @@
         <v>1</v>
       </c>
     </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:7">
       <c r="A46" t="s">
-        <v>108</v>
+        <v>118</v>
       </c>
       <c r="B46" t="s">
-        <v>468</v>
+        <v>490</v>
       </c>
       <c r="C46" t="s">
         <v>10</v>
       </c>
       <c r="D46" t="s">
-        <v>508</v>
+        <v>534</v>
       </c>
       <c r="E46">
         <v>1</v>
@@ -10808,18 +10882,18 @@
         <v>1</v>
       </c>
     </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:7">
       <c r="A47" t="s">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="B47" t="s">
-        <v>468</v>
+        <v>490</v>
       </c>
       <c r="C47" t="s">
         <v>7</v>
       </c>
       <c r="D47" t="s">
-        <v>509</v>
+        <v>535</v>
       </c>
       <c r="E47">
         <v>1</v>
@@ -10831,18 +10905,18 @@
         <v>1</v>
       </c>
     </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:7">
       <c r="A48" t="s">
-        <v>112</v>
+        <v>122</v>
       </c>
       <c r="B48" t="s">
-        <v>468</v>
+        <v>490</v>
       </c>
       <c r="C48" t="s">
         <v>7</v>
       </c>
       <c r="D48" t="s">
-        <v>510</v>
+        <v>536</v>
       </c>
       <c r="E48">
         <v>1</v>
@@ -10854,18 +10928,18 @@
         <v>1</v>
       </c>
     </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:7">
       <c r="A49" t="s">
-        <v>114</v>
+        <v>124</v>
       </c>
       <c r="B49" t="s">
-        <v>468</v>
+        <v>490</v>
       </c>
       <c r="C49" t="s">
         <v>7</v>
       </c>
       <c r="D49" t="s">
-        <v>511</v>
+        <v>537</v>
       </c>
       <c r="E49">
         <v>1</v>
@@ -10877,18 +10951,18 @@
         <v>1</v>
       </c>
     </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:7">
       <c r="A50" t="s">
-        <v>116</v>
+        <v>126</v>
       </c>
       <c r="B50" t="s">
-        <v>468</v>
+        <v>490</v>
       </c>
       <c r="C50" t="s">
         <v>7</v>
       </c>
       <c r="D50" t="s">
-        <v>512</v>
+        <v>538</v>
       </c>
       <c r="E50">
         <v>1</v>
@@ -10900,18 +10974,18 @@
         <v>1</v>
       </c>
     </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:7">
       <c r="A51" t="s">
-        <v>118</v>
+        <v>128</v>
       </c>
       <c r="B51" t="s">
-        <v>468</v>
+        <v>490</v>
       </c>
       <c r="C51" t="s">
         <v>7</v>
       </c>
       <c r="D51" t="s">
-        <v>513</v>
+        <v>539</v>
       </c>
       <c r="E51">
         <v>1</v>
@@ -10923,18 +10997,18 @@
         <v>1</v>
       </c>
     </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:7">
       <c r="A52" t="s">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="B52" t="s">
-        <v>468</v>
+        <v>490</v>
       </c>
       <c r="C52" t="s">
         <v>7</v>
       </c>
       <c r="D52" t="s">
-        <v>514</v>
+        <v>540</v>
       </c>
       <c r="E52">
         <v>1</v>
@@ -10947,26 +11021,30 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G1" xr:uid="{00000000-0009-0000-0000-000007000000}"/>
+  <autoFilter ref="A1:G1"/>
+  <printOptions gridLines="false" gridLinesSet="true"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait"/>
+  <pageSetup paperSize="1" orientation="portrait" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr filterMode="1">
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+  </sheetPr>
   <dimension ref="A1:F3"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="14.4" defaultColWidth="8.83203125" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col min="1" max="1" width="17.5" customWidth="1"/>
-    <col min="2" max="2" width="24.6640625" customWidth="1"/>
-    <col min="3" max="3" width="21.1640625" customWidth="1"/>
-    <col min="4" max="4" width="9.33203125" customWidth="1"/>
-    <col min="5" max="5" width="10.5" customWidth="1"/>
-    <col min="6" max="6" width="9.33203125" customWidth="1"/>
+    <col min="1" max="1" width="17.5" customWidth="true" style="0"/>
+    <col min="2" max="2" width="24.6640625" customWidth="true" style="0"/>
+    <col min="3" max="3" width="21.1640625" customWidth="true" style="0"/>
+    <col min="4" max="4" width="9.33203125" customWidth="true" style="0"/>
+    <col min="5" max="5" width="10.5" customWidth="true" style="0"/>
+    <col min="6" max="6" width="9.33203125" customWidth="true" style="0"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:6">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -10977,7 +11055,7 @@
         <v>1</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>515</v>
+        <v>541</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>3</v>
@@ -10986,15 +11064,15 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:6">
       <c r="A2" t="s">
-        <v>516</v>
+        <v>542</v>
       </c>
       <c r="B2" t="s">
-        <v>517</v>
+        <v>543</v>
       </c>
       <c r="C2" t="s">
-        <v>518</v>
+        <v>544</v>
       </c>
       <c r="E2">
         <v>1</v>
@@ -11003,15 +11081,15 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:6">
       <c r="A3" t="s">
-        <v>519</v>
+        <v>545</v>
       </c>
       <c r="B3" t="s">
-        <v>517</v>
+        <v>543</v>
       </c>
       <c r="C3" t="s">
-        <v>520</v>
+        <v>546</v>
       </c>
       <c r="E3">
         <v>1</v>
@@ -11021,104 +11099,109 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F1" xr:uid="{00000000-0009-0000-0000-000008000000}"/>
+  <autoFilter ref="A1:F1"/>
+  <printOptions gridLines="false" gridLinesSet="true"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait"/>
+  <pageSetup paperSize="1" orientation="portrait" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr filterMode="1">
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+  </sheetPr>
   <dimension ref="A1:B10"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="14.4" defaultColWidth="8.83203125" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col min="1" max="1" width="21.1640625" style="3" customWidth="1"/>
-    <col min="2" max="2" width="198.1640625" style="3" customWidth="1"/>
+    <col min="1" max="1" width="21.1640625" customWidth="true" style="3"/>
+    <col min="2" max="2" width="198.1640625" customWidth="true" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:2" customHeight="1" ht="16">
       <c r="A1" s="2" t="s">
-        <v>521</v>
+        <v>547</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>522</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+        <v>548</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" customHeight="1" ht="16">
       <c r="A2" s="3" t="s">
-        <v>523</v>
+        <v>549</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>524</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+        <v>550</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" customHeight="1" ht="16">
       <c r="A3" s="3" t="s">
-        <v>525</v>
+        <v>551</v>
       </c>
       <c r="B3" s="5" t="s">
+        <v>552</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" customHeight="1" ht="16">
+      <c r="A4" s="3" t="s">
+        <v>553</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>554</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" customHeight="1" ht="16">
+      <c r="A5" s="3" t="s">
+        <v>555</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>556</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" customHeight="1" ht="16">
+      <c r="A6" s="3" t="s">
+        <v>204</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>557</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" customHeight="1" ht="16">
+      <c r="A7" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>558</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" customHeight="1" ht="16">
+      <c r="A8" s="3" t="s">
+        <v>559</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>560</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" customHeight="1" ht="16">
+      <c r="A9" s="3" t="s">
         <v>561</v>
       </c>
-    </row>
-    <row r="4" spans="1:2" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="3" t="s">
-        <v>526</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>527</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="3" t="s">
-        <v>528</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>529</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="3" t="s">
-        <v>197</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>530</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>531</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="3" t="s">
-        <v>532</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>533</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="3" t="s">
-        <v>534</v>
-      </c>
       <c r="B9" s="3" t="s">
-        <v>535</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+        <v>562</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" customHeight="1" ht="16">
       <c r="A10" s="3" t="s">
-        <v>536</v>
+        <v>563</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>537</v>
+        <v>564</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:B1" xr:uid="{00000000-0009-0000-0000-000009000000}"/>
+  <autoFilter ref="A1:B1"/>
+  <printOptions gridLines="false" gridLinesSet="true"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait"/>
+  <pageSetup paperSize="1" orientation="portrait" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver"/>
 </worksheet>
 </file>
--- a/database/catalogos/catalogo_maestro.xlsx
+++ b/database/catalogos/catalogo_maestro.xlsx
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="565">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="571">
   <si>
     <t>slug</t>
   </si>
@@ -797,6 +797,12 @@
     <t>Guarnicion</t>
   </si>
   <si>
+    <t>bebida_del_paquete</t>
+  </si>
+  <si>
+    <t>Bebida del paquete</t>
+  </si>
+  <si>
     <t>grupo_slug</t>
   </si>
   <si>
@@ -1482,6 +1488,18 @@
   </si>
   <si>
     <t>Guarnicion Ensalda</t>
+  </si>
+  <si>
+    <t>cafe</t>
+  </si>
+  <si>
+    <t>Bebida del paquete: Cafe</t>
+  </si>
+  <si>
+    <t>Cafe</t>
+  </si>
+  <si>
+    <t>Bebida del paquete: Te</t>
   </si>
   <si>
     <t>producto_sku</t>
@@ -5666,7 +5684,7 @@
   <sheetPr filterMode="1">
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:K25"/>
+  <dimension ref="A1:K26"/>
   <sheetFormatPr defaultRowHeight="14.4" defaultColWidth="8.83203125" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="15.33203125" customWidth="true" style="0"/>
@@ -6288,7 +6306,7 @@
         <v>205</v>
       </c>
       <c r="D18">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E18">
         <v>0</v>
@@ -6323,7 +6341,7 @@
         <v>205</v>
       </c>
       <c r="D19">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E19">
         <v>0</v>
@@ -6554,6 +6572,41 @@
         <v>0</v>
       </c>
       <c r="K25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11">
+      <c r="A26" t="s">
+        <v>254</v>
+      </c>
+      <c r="B26" t="s">
+        <v>255</v>
+      </c>
+      <c r="C26" t="s">
+        <v>205</v>
+      </c>
+      <c r="D26">
+        <v>0</v>
+      </c>
+      <c r="E26">
+        <v>0</v>
+      </c>
+      <c r="F26">
+        <v>1</v>
+      </c>
+      <c r="G26">
+        <v>62</v>
+      </c>
+      <c r="H26" t="s">
+        <v>206</v>
+      </c>
+      <c r="I26" t="s">
+        <v>10</v>
+      </c>
+      <c r="J26">
+        <v>0</v>
+      </c>
+      <c r="K26">
         <v>0</v>
       </c>
     </row>
@@ -6570,7 +6623,7 @@
   <sheetPr filterMode="1">
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:H90"/>
+  <dimension ref="A1:H92"/>
   <sheetFormatPr defaultRowHeight="14.4" defaultColWidth="8.83203125" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="17.6640625" customWidth="true" style="0"/>
@@ -6585,7 +6638,7 @@
   <sheetData>
     <row r="1" spans="1:8">
       <c r="A1" s="1" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>0</v>
@@ -6606,7 +6659,7 @@
         <v>4</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
     </row>
     <row r="2" spans="1:8">
@@ -6614,10 +6667,10 @@
         <v>203</v>
       </c>
       <c r="B2" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="C2" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="D2">
         <v>0</v>
@@ -6632,7 +6685,7 @@
         <v>10</v>
       </c>
       <c r="H2" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -6640,10 +6693,10 @@
         <v>203</v>
       </c>
       <c r="B3" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="C3" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="D3">
         <v>0</v>
@@ -6658,7 +6711,7 @@
         <v>20</v>
       </c>
       <c r="H3" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -6666,10 +6719,10 @@
         <v>203</v>
       </c>
       <c r="B4" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="C4" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="D4">
         <v>0</v>
@@ -6684,7 +6737,7 @@
         <v>30</v>
       </c>
       <c r="H4" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -6692,10 +6745,10 @@
         <v>222</v>
       </c>
       <c r="B5" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="C5" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="D5">
         <v>0</v>
@@ -6710,7 +6763,7 @@
         <v>10</v>
       </c>
       <c r="H5" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -6718,10 +6771,10 @@
         <v>222</v>
       </c>
       <c r="B6" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="C6" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="D6">
         <v>0</v>
@@ -6736,7 +6789,7 @@
         <v>20</v>
       </c>
       <c r="H6" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -6747,7 +6800,7 @@
         <v>159</v>
       </c>
       <c r="C7" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="D7">
         <v>0</v>
@@ -6773,7 +6826,7 @@
         <v>155</v>
       </c>
       <c r="C8" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="D8">
         <v>0</v>
@@ -6788,7 +6841,7 @@
         <v>20</v>
       </c>
       <c r="H8" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
     </row>
     <row r="9" spans="1:8">
@@ -6799,7 +6852,7 @@
         <v>153</v>
       </c>
       <c r="C9" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="D9">
         <v>0</v>
@@ -6822,10 +6875,10 @@
         <v>207</v>
       </c>
       <c r="B10" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="C10" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="D10">
         <v>0</v>
@@ -6840,7 +6893,7 @@
         <v>40</v>
       </c>
       <c r="H10" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
     </row>
     <row r="11" spans="1:8">
@@ -6851,7 +6904,7 @@
         <v>157</v>
       </c>
       <c r="C11" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="D11">
         <v>0</v>
@@ -6874,10 +6927,10 @@
         <v>210</v>
       </c>
       <c r="B12" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="C12" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="D12">
         <v>0</v>
@@ -6892,7 +6945,7 @@
         <v>10</v>
       </c>
       <c r="H12" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
     </row>
     <row r="13" spans="1:8">
@@ -6900,10 +6953,10 @@
         <v>210</v>
       </c>
       <c r="B13" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="C13" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="D13">
         <v>0</v>
@@ -6918,7 +6971,7 @@
         <v>20</v>
       </c>
       <c r="H13" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
     </row>
     <row r="14" spans="1:8">
@@ -6926,10 +6979,10 @@
         <v>210</v>
       </c>
       <c r="B14" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="C14" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="D14">
         <v>0</v>
@@ -6944,7 +6997,7 @@
         <v>30</v>
       </c>
       <c r="H14" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
     </row>
     <row r="15" spans="1:8">
@@ -6952,10 +7005,10 @@
         <v>212</v>
       </c>
       <c r="B15" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="C15" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="D15">
         <v>0</v>
@@ -6970,7 +7023,7 @@
         <v>10</v>
       </c>
       <c r="H15" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
     </row>
     <row r="16" spans="1:8">
@@ -6978,10 +7031,10 @@
         <v>212</v>
       </c>
       <c r="B16" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="C16" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="D16">
         <v>0</v>
@@ -6996,7 +7049,7 @@
         <v>20</v>
       </c>
       <c r="H16" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
     </row>
     <row r="17" spans="1:8">
@@ -7007,7 +7060,7 @@
         <v>135</v>
       </c>
       <c r="C17" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="D17">
         <v>10</v>
@@ -7030,10 +7083,10 @@
         <v>214</v>
       </c>
       <c r="B18" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="C18" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="D18">
         <v>10</v>
@@ -7048,7 +7101,7 @@
         <v>20</v>
       </c>
       <c r="H18" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
     </row>
     <row r="19" spans="1:8">
@@ -7059,7 +7112,7 @@
         <v>68</v>
       </c>
       <c r="C19" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="D19">
         <v>25</v>
@@ -7074,7 +7127,7 @@
         <v>30</v>
       </c>
       <c r="H19" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
     </row>
     <row r="20" spans="1:8">
@@ -7085,7 +7138,7 @@
         <v>70</v>
       </c>
       <c r="C20" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="D20">
         <v>30</v>
@@ -7100,7 +7153,7 @@
         <v>40</v>
       </c>
       <c r="H20" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
     </row>
     <row r="21" spans="1:8">
@@ -7111,7 +7164,7 @@
         <v>72</v>
       </c>
       <c r="C21" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="D21">
         <v>30</v>
@@ -7126,7 +7179,7 @@
         <v>50</v>
       </c>
       <c r="H21" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
     </row>
     <row r="22" spans="1:8">
@@ -7137,7 +7190,7 @@
         <v>74</v>
       </c>
       <c r="C22" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="D22">
         <v>35</v>
@@ -7152,7 +7205,7 @@
         <v>60</v>
       </c>
       <c r="H22" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
     </row>
     <row r="23" spans="1:8">
@@ -7160,10 +7213,10 @@
         <v>216</v>
       </c>
       <c r="B23" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="C23" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="D23">
         <v>0</v>
@@ -7178,7 +7231,7 @@
         <v>10</v>
       </c>
       <c r="H23" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
     </row>
     <row r="24" spans="1:8">
@@ -7186,10 +7239,10 @@
         <v>216</v>
       </c>
       <c r="B24" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="C24" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="D24">
         <v>0</v>
@@ -7204,7 +7257,7 @@
         <v>20</v>
       </c>
       <c r="H24" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
     </row>
     <row r="25" spans="1:8">
@@ -7212,10 +7265,10 @@
         <v>216</v>
       </c>
       <c r="B25" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="C25" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="D25">
         <v>0</v>
@@ -7230,7 +7283,7 @@
         <v>30</v>
       </c>
       <c r="H25" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
     </row>
     <row r="26" spans="1:8">
@@ -7238,10 +7291,10 @@
         <v>216</v>
       </c>
       <c r="B26" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="C26" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="D26">
         <v>0</v>
@@ -7256,7 +7309,7 @@
         <v>40</v>
       </c>
       <c r="H26" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
     </row>
     <row r="27" spans="1:8">
@@ -7264,10 +7317,10 @@
         <v>216</v>
       </c>
       <c r="B27" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="C27" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="D27">
         <v>0</v>
@@ -7282,7 +7335,7 @@
         <v>50</v>
       </c>
       <c r="H27" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
     </row>
     <row r="28" spans="1:8">
@@ -7290,10 +7343,10 @@
         <v>218</v>
       </c>
       <c r="B28" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="C28" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="D28">
         <v>0</v>
@@ -7308,7 +7361,7 @@
         <v>10</v>
       </c>
       <c r="H28" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
     </row>
     <row r="29" spans="1:8">
@@ -7316,10 +7369,10 @@
         <v>218</v>
       </c>
       <c r="B29" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="C29" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="D29">
         <v>0</v>
@@ -7334,7 +7387,7 @@
         <v>20</v>
       </c>
       <c r="H29" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
     </row>
     <row r="30" spans="1:8">
@@ -7342,10 +7395,10 @@
         <v>218</v>
       </c>
       <c r="B30" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="C30" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="D30">
         <v>0</v>
@@ -7360,7 +7413,7 @@
         <v>30</v>
       </c>
       <c r="H30" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
     </row>
     <row r="31" spans="1:8">
@@ -7368,10 +7421,10 @@
         <v>218</v>
       </c>
       <c r="B31" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="C31" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="D31">
         <v>0</v>
@@ -7386,7 +7439,7 @@
         <v>40</v>
       </c>
       <c r="H31" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
     </row>
     <row r="32" spans="1:8">
@@ -7394,10 +7447,10 @@
         <v>218</v>
       </c>
       <c r="B32" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="C32" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="D32">
         <v>0</v>
@@ -7412,7 +7465,7 @@
         <v>50</v>
       </c>
       <c r="H32" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
     </row>
     <row r="33" spans="1:8">
@@ -7420,10 +7473,10 @@
         <v>220</v>
       </c>
       <c r="B33" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="C33" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="D33">
         <v>0</v>
@@ -7438,7 +7491,7 @@
         <v>10</v>
       </c>
       <c r="H33" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
     </row>
     <row r="34" spans="1:8">
@@ -7446,10 +7499,10 @@
         <v>220</v>
       </c>
       <c r="B34" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="C34" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="D34">
         <v>5</v>
@@ -7464,7 +7517,7 @@
         <v>20</v>
       </c>
       <c r="H34" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
     </row>
     <row r="35" spans="1:8">
@@ -7472,10 +7525,10 @@
         <v>220</v>
       </c>
       <c r="B35" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="C35" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="D35">
         <v>10</v>
@@ -7490,7 +7543,7 @@
         <v>30</v>
       </c>
       <c r="H35" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
     </row>
     <row r="36" spans="1:8">
@@ -7498,10 +7551,10 @@
         <v>220</v>
       </c>
       <c r="B36" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="C36" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="D36">
         <v>10</v>
@@ -7516,7 +7569,7 @@
         <v>40</v>
       </c>
       <c r="H36" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
     </row>
     <row r="37" spans="1:8">
@@ -7524,10 +7577,10 @@
         <v>224</v>
       </c>
       <c r="B37" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="C37" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="D37">
         <v>0</v>
@@ -7542,7 +7595,7 @@
         <v>10</v>
       </c>
       <c r="H37" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
     </row>
     <row r="38" spans="1:8">
@@ -7550,10 +7603,10 @@
         <v>224</v>
       </c>
       <c r="B38" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="C38" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="D38">
         <v>5</v>
@@ -7568,7 +7621,7 @@
         <v>20</v>
       </c>
       <c r="H38" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
     </row>
     <row r="39" spans="1:8">
@@ -7576,10 +7629,10 @@
         <v>224</v>
       </c>
       <c r="B39" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="C39" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="D39">
         <v>5</v>
@@ -7594,7 +7647,7 @@
         <v>30</v>
       </c>
       <c r="H39" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
     </row>
     <row r="40" spans="1:8">
@@ -7602,10 +7655,10 @@
         <v>224</v>
       </c>
       <c r="B40" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="C40" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="D40">
         <v>5</v>
@@ -7620,7 +7673,7 @@
         <v>40</v>
       </c>
       <c r="H40" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
     </row>
     <row r="41" spans="1:8">
@@ -7628,10 +7681,10 @@
         <v>224</v>
       </c>
       <c r="B41" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="C41" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="D41">
         <v>5</v>
@@ -7646,7 +7699,7 @@
         <v>50</v>
       </c>
       <c r="H41" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
     </row>
     <row r="42" spans="1:8">
@@ -7654,10 +7707,10 @@
         <v>226</v>
       </c>
       <c r="B42" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="C42" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="D42">
         <v>0</v>
@@ -7672,7 +7725,7 @@
         <v>10</v>
       </c>
       <c r="H42" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
     </row>
     <row r="43" spans="1:8">
@@ -7680,10 +7733,10 @@
         <v>226</v>
       </c>
       <c r="B43" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="C43" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="D43">
         <v>0</v>
@@ -7698,7 +7751,7 @@
         <v>20</v>
       </c>
       <c r="H43" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
     </row>
     <row r="44" spans="1:8">
@@ -7706,10 +7759,10 @@
         <v>226</v>
       </c>
       <c r="B44" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="C44" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="D44">
         <v>0</v>
@@ -7724,7 +7777,7 @@
         <v>30</v>
       </c>
       <c r="H44" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
     </row>
     <row r="45" spans="1:8">
@@ -7732,10 +7785,10 @@
         <v>226</v>
       </c>
       <c r="B45" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="C45" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="D45">
         <v>0</v>
@@ -7750,7 +7803,7 @@
         <v>40</v>
       </c>
       <c r="H45" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
     </row>
     <row r="46" spans="1:8">
@@ -7758,10 +7811,10 @@
         <v>228</v>
       </c>
       <c r="B46" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="C46" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="D46">
         <v>0</v>
@@ -7776,7 +7829,7 @@
         <v>10</v>
       </c>
       <c r="H46" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
     </row>
     <row r="47" spans="1:8">
@@ -7784,10 +7837,10 @@
         <v>228</v>
       </c>
       <c r="B47" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="C47" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="D47">
         <v>0</v>
@@ -7802,7 +7855,7 @@
         <v>20</v>
       </c>
       <c r="H47" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
     </row>
     <row r="48" spans="1:8">
@@ -7810,10 +7863,10 @@
         <v>228</v>
       </c>
       <c r="B48" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="C48" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="D48">
         <v>0</v>
@@ -7828,7 +7881,7 @@
         <v>30</v>
       </c>
       <c r="H48" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
     </row>
     <row r="49" spans="1:8">
@@ -7836,10 +7889,10 @@
         <v>228</v>
       </c>
       <c r="B49" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="C49" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="D49">
         <v>0</v>
@@ -7854,7 +7907,7 @@
         <v>40</v>
       </c>
       <c r="H49" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
     </row>
     <row r="50" spans="1:8">
@@ -7862,10 +7915,10 @@
         <v>230</v>
       </c>
       <c r="B50" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="C50" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="D50">
         <v>0</v>
@@ -7880,7 +7933,7 @@
         <v>10</v>
       </c>
       <c r="H50" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
     </row>
     <row r="51" spans="1:8">
@@ -7888,10 +7941,10 @@
         <v>230</v>
       </c>
       <c r="B51" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="C51" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="D51">
         <v>0</v>
@@ -7906,7 +7959,7 @@
         <v>20</v>
       </c>
       <c r="H51" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
     </row>
     <row r="52" spans="1:8">
@@ -7914,10 +7967,10 @@
         <v>230</v>
       </c>
       <c r="B52" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="C52" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="D52">
         <v>0</v>
@@ -7932,7 +7985,7 @@
         <v>10</v>
       </c>
       <c r="H52" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
     </row>
     <row r="53" spans="1:8">
@@ -7940,10 +7993,10 @@
         <v>232</v>
       </c>
       <c r="B53" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="C53" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="D53">
         <v>0</v>
@@ -7958,7 +8011,7 @@
         <v>20</v>
       </c>
       <c r="H53" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
     </row>
     <row r="54" spans="1:8">
@@ -7966,10 +8019,10 @@
         <v>232</v>
       </c>
       <c r="B54" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="C54" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="D54">
         <v>0</v>
@@ -7984,7 +8037,7 @@
         <v>30</v>
       </c>
       <c r="H54" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
     </row>
     <row r="55" spans="1:8">
@@ -7992,10 +8045,10 @@
         <v>232</v>
       </c>
       <c r="B55" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="C55" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="D55">
         <v>0</v>
@@ -8010,7 +8063,7 @@
         <v>40</v>
       </c>
       <c r="H55" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
     </row>
     <row r="56" spans="1:8">
@@ -8018,10 +8071,10 @@
         <v>232</v>
       </c>
       <c r="B56" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="C56" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="D56">
         <v>0</v>
@@ -8036,7 +8089,7 @@
         <v>50</v>
       </c>
       <c r="H56" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
     </row>
     <row r="57" spans="1:8">
@@ -8044,10 +8097,10 @@
         <v>232</v>
       </c>
       <c r="B57" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="C57" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="D57">
         <v>0</v>
@@ -8062,7 +8115,7 @@
         <v>60</v>
       </c>
       <c r="H57" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
     </row>
     <row r="58" spans="1:8">
@@ -8070,10 +8123,10 @@
         <v>234</v>
       </c>
       <c r="B58" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="C58" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="D58">
         <v>0</v>
@@ -8088,7 +8141,7 @@
         <v>10</v>
       </c>
       <c r="H58" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
     </row>
     <row r="59" spans="1:8">
@@ -8096,10 +8149,10 @@
         <v>234</v>
       </c>
       <c r="B59" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="C59" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="D59">
         <v>0</v>
@@ -8114,7 +8167,7 @@
         <v>20</v>
       </c>
       <c r="H59" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
     </row>
     <row r="60" spans="1:8">
@@ -8122,10 +8175,10 @@
         <v>236</v>
       </c>
       <c r="B60" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="C60" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="D60">
         <v>0</v>
@@ -8140,7 +8193,7 @@
         <v>10</v>
       </c>
       <c r="H60" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
     </row>
     <row r="61" spans="1:8">
@@ -8148,10 +8201,10 @@
         <v>236</v>
       </c>
       <c r="B61" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="C61" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="D61">
         <v>0</v>
@@ -8166,7 +8219,7 @@
         <v>20</v>
       </c>
       <c r="H61" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
     </row>
     <row r="62" spans="1:8">
@@ -8174,10 +8227,10 @@
         <v>236</v>
       </c>
       <c r="B62" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="C62" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="D62">
         <v>0</v>
@@ -8192,7 +8245,7 @@
         <v>30</v>
       </c>
       <c r="H62" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
     </row>
     <row r="63" spans="1:8">
@@ -8200,10 +8253,10 @@
         <v>236</v>
       </c>
       <c r="B63" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="C63" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="D63">
         <v>0</v>
@@ -8218,7 +8271,7 @@
         <v>40</v>
       </c>
       <c r="H63" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
     </row>
     <row r="64" spans="1:8">
@@ -8226,10 +8279,10 @@
         <v>236</v>
       </c>
       <c r="B64" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="C64" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="D64">
         <v>0</v>
@@ -8244,7 +8297,7 @@
         <v>50</v>
       </c>
       <c r="H64" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
     </row>
     <row r="65" spans="1:8">
@@ -8252,10 +8305,10 @@
         <v>236</v>
       </c>
       <c r="B65" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="C65" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="D65">
         <v>0</v>
@@ -8270,7 +8323,7 @@
         <v>60</v>
       </c>
       <c r="H65" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
     </row>
     <row r="66" spans="1:8">
@@ -8278,10 +8331,10 @@
         <v>236</v>
       </c>
       <c r="B66" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="C66" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="D66">
         <v>0</v>
@@ -8296,7 +8349,7 @@
         <v>70</v>
       </c>
       <c r="H66" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
     </row>
     <row r="67" spans="1:8">
@@ -8304,10 +8357,10 @@
         <v>236</v>
       </c>
       <c r="B67" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="C67" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="D67">
         <v>0</v>
@@ -8322,7 +8375,7 @@
         <v>80</v>
       </c>
       <c r="H67" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
     </row>
     <row r="68" spans="1:8">
@@ -8330,10 +8383,10 @@
         <v>238</v>
       </c>
       <c r="B68" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="C68" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="D68">
         <v>0</v>
@@ -8348,7 +8401,7 @@
         <v>10</v>
       </c>
       <c r="H68" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
     </row>
     <row r="69" spans="1:8">
@@ -8356,10 +8409,10 @@
         <v>238</v>
       </c>
       <c r="B69" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="C69" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="D69">
         <v>0</v>
@@ -8374,7 +8427,7 @@
         <v>20</v>
       </c>
       <c r="H69" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
     </row>
     <row r="70" spans="1:8">
@@ -8382,10 +8435,10 @@
         <v>238</v>
       </c>
       <c r="B70" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="C70" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="D70">
         <v>0</v>
@@ -8400,7 +8453,7 @@
         <v>30</v>
       </c>
       <c r="H70" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
     </row>
     <row r="71" spans="1:8">
@@ -8437,7 +8490,7 @@
         <v>78</v>
       </c>
       <c r="C72" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="D72">
         <v>35</v>
@@ -8452,7 +8505,7 @@
         <v>10</v>
       </c>
       <c r="H72" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
     </row>
     <row r="73" spans="1:8">
@@ -8463,7 +8516,7 @@
         <v>187</v>
       </c>
       <c r="C73" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="D73">
         <v>35</v>
@@ -8478,7 +8531,7 @@
         <v>20</v>
       </c>
       <c r="H73" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
     </row>
     <row r="74" spans="1:8">
@@ -8489,7 +8542,7 @@
         <v>183</v>
       </c>
       <c r="C74" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="D74">
         <v>35</v>
@@ -8504,7 +8557,7 @@
         <v>30</v>
       </c>
       <c r="H74" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
     </row>
     <row r="75" spans="1:8">
@@ -8515,7 +8568,7 @@
         <v>190</v>
       </c>
       <c r="C75" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="D75">
         <v>35</v>
@@ -8530,7 +8583,7 @@
         <v>40</v>
       </c>
       <c r="H75" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
     </row>
     <row r="76" spans="1:8">
@@ -8541,7 +8594,7 @@
         <v>192</v>
       </c>
       <c r="C76" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="D76">
         <v>35</v>
@@ -8556,7 +8609,7 @@
         <v>50</v>
       </c>
       <c r="H76" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
     </row>
     <row r="77" spans="1:8">
@@ -8567,7 +8620,7 @@
         <v>185</v>
       </c>
       <c r="C77" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="D77">
         <v>55</v>
@@ -8582,7 +8635,7 @@
         <v>60</v>
       </c>
       <c r="H77" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
     </row>
     <row r="78" spans="1:8">
@@ -8590,10 +8643,10 @@
         <v>242</v>
       </c>
       <c r="B78" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="C78" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="D78">
         <v>40</v>
@@ -8608,7 +8661,7 @@
         <v>70</v>
       </c>
       <c r="H78" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
     </row>
     <row r="79" spans="1:8">
@@ -8616,10 +8669,10 @@
         <v>244</v>
       </c>
       <c r="B79" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="C79" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="D79">
         <v>0</v>
@@ -8634,7 +8687,7 @@
         <v>10</v>
       </c>
       <c r="H79" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
     </row>
     <row r="80" spans="1:8">
@@ -8642,10 +8695,10 @@
         <v>244</v>
       </c>
       <c r="B80" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="C80" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="D80">
         <v>5</v>
@@ -8660,7 +8713,7 @@
         <v>20</v>
       </c>
       <c r="H80" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
     </row>
     <row r="81" spans="1:8">
@@ -8668,10 +8721,10 @@
         <v>246</v>
       </c>
       <c r="B81" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="C81" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="D81">
         <v>0</v>
@@ -8686,7 +8739,7 @@
         <v>10</v>
       </c>
       <c r="H81" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
     </row>
     <row r="82" spans="1:8">
@@ -8694,10 +8747,10 @@
         <v>246</v>
       </c>
       <c r="B82" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="C82" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="D82">
         <v>0</v>
@@ -8712,7 +8765,7 @@
         <v>20</v>
       </c>
       <c r="H82" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
     </row>
     <row r="83" spans="1:8">
@@ -8720,10 +8773,10 @@
         <v>246</v>
       </c>
       <c r="B83" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="C83" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="D83">
         <v>0</v>
@@ -8738,7 +8791,7 @@
         <v>30</v>
       </c>
       <c r="H83" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
     </row>
     <row r="84" spans="1:8">
@@ -8746,10 +8799,10 @@
         <v>248</v>
       </c>
       <c r="B84" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="C84" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="D84">
         <v>7</v>
@@ -8764,7 +8817,7 @@
         <v>10</v>
       </c>
       <c r="H84" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
     </row>
     <row r="85" spans="1:8">
@@ -8798,10 +8851,10 @@
         <v>216</v>
       </c>
       <c r="B86" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="C86" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="D86">
         <v>0</v>
@@ -8816,7 +8869,7 @@
         <v>60</v>
       </c>
       <c r="H86" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
     </row>
     <row r="87" spans="1:8">
@@ -8824,10 +8877,10 @@
         <v>252</v>
       </c>
       <c r="B87" s="4" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="C87" s="4" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="D87">
         <v>0</v>
@@ -8842,7 +8895,7 @@
         <v>10</v>
       </c>
       <c r="H87" s="4" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
     </row>
     <row r="88" spans="1:8">
@@ -8850,10 +8903,10 @@
         <v>252</v>
       </c>
       <c r="B88" s="4" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="C88" s="4" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="D88">
         <v>0</v>
@@ -8868,7 +8921,7 @@
         <v>20</v>
       </c>
       <c r="H88" s="4" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
     </row>
     <row r="89" spans="1:8">
@@ -8876,10 +8929,10 @@
         <v>252</v>
       </c>
       <c r="B89" s="4" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="C89" s="4" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="D89">
         <v>0</v>
@@ -8894,7 +8947,7 @@
         <v>30</v>
       </c>
       <c r="H89" s="4" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
     </row>
     <row r="90" spans="1:8">
@@ -8902,10 +8955,10 @@
         <v>252</v>
       </c>
       <c r="B90" s="4" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="C90" s="4" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="D90">
         <v>0</v>
@@ -8920,7 +8973,59 @@
         <v>40</v>
       </c>
       <c r="H90" s="4" t="s">
-        <v>482</v>
+        <v>484</v>
+      </c>
+    </row>
+    <row r="91" spans="1:8">
+      <c r="A91" t="s">
+        <v>254</v>
+      </c>
+      <c r="B91" t="s">
+        <v>485</v>
+      </c>
+      <c r="C91" t="s">
+        <v>486</v>
+      </c>
+      <c r="D91">
+        <v>0</v>
+      </c>
+      <c r="E91">
+        <v>0</v>
+      </c>
+      <c r="F91">
+        <v>1</v>
+      </c>
+      <c r="G91">
+        <v>10</v>
+      </c>
+      <c r="H91" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="92" spans="1:8">
+      <c r="A92" t="s">
+        <v>254</v>
+      </c>
+      <c r="B92" t="s">
+        <v>106</v>
+      </c>
+      <c r="C92" t="s">
+        <v>488</v>
+      </c>
+      <c r="D92">
+        <v>0</v>
+      </c>
+      <c r="E92">
+        <v>0</v>
+      </c>
+      <c r="F92">
+        <v>1</v>
+      </c>
+      <c r="G92">
+        <v>20</v>
+      </c>
+      <c r="H92" t="s">
+        <v>107</v>
       </c>
     </row>
   </sheetData>
@@ -8950,10 +9055,10 @@
   <sheetData>
     <row r="1" spans="1:7">
       <c r="A1" s="1" t="s">
-        <v>483</v>
+        <v>489</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>196</v>
@@ -9826,19 +9931,19 @@
   <sheetData>
     <row r="1" spans="1:7">
       <c r="A1" s="1" t="s">
-        <v>483</v>
+        <v>489</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>484</v>
+        <v>490</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>485</v>
+        <v>491</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>486</v>
+        <v>492</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>487</v>
+        <v>493</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>4</v>
@@ -9858,7 +9963,7 @@
         <v>7</v>
       </c>
       <c r="D2" t="s">
-        <v>488</v>
+        <v>494</v>
       </c>
       <c r="E2">
         <v>1</v>
@@ -9881,7 +9986,7 @@
         <v>7</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>489</v>
+        <v>495</v>
       </c>
       <c r="E3">
         <v>1</v>
@@ -9898,13 +10003,13 @@
         <v>34</v>
       </c>
       <c r="B4" t="s">
-        <v>490</v>
+        <v>496</v>
       </c>
       <c r="C4" t="s">
         <v>10</v>
       </c>
       <c r="D4" t="s">
-        <v>491</v>
+        <v>497</v>
       </c>
       <c r="E4">
         <v>1</v>
@@ -9927,7 +10032,7 @@
         <v>7</v>
       </c>
       <c r="D5" t="s">
-        <v>492</v>
+        <v>498</v>
       </c>
       <c r="E5">
         <v>1</v>
@@ -9950,7 +10055,7 @@
         <v>7</v>
       </c>
       <c r="D6" t="s">
-        <v>493</v>
+        <v>499</v>
       </c>
       <c r="E6">
         <v>1</v>
@@ -9973,7 +10078,7 @@
         <v>7</v>
       </c>
       <c r="D7" t="s">
-        <v>494</v>
+        <v>500</v>
       </c>
       <c r="E7">
         <v>1</v>
@@ -9996,7 +10101,7 @@
         <v>7</v>
       </c>
       <c r="D8" t="s">
-        <v>495</v>
+        <v>501</v>
       </c>
       <c r="E8">
         <v>1</v>
@@ -10019,7 +10124,7 @@
         <v>7</v>
       </c>
       <c r="D9" t="s">
-        <v>496</v>
+        <v>502</v>
       </c>
       <c r="E9">
         <v>1</v>
@@ -10042,7 +10147,7 @@
         <v>7</v>
       </c>
       <c r="D10" t="s">
-        <v>497</v>
+        <v>503</v>
       </c>
       <c r="E10">
         <v>1</v>
@@ -10065,7 +10170,7 @@
         <v>7</v>
       </c>
       <c r="D11" t="s">
-        <v>498</v>
+        <v>504</v>
       </c>
       <c r="E11">
         <v>1</v>
@@ -10088,7 +10193,7 @@
         <v>7</v>
       </c>
       <c r="D12" t="s">
-        <v>499</v>
+        <v>505</v>
       </c>
       <c r="E12">
         <v>1</v>
@@ -10111,7 +10216,7 @@
         <v>7</v>
       </c>
       <c r="D13" t="s">
-        <v>500</v>
+        <v>506</v>
       </c>
       <c r="E13">
         <v>1</v>
@@ -10134,7 +10239,7 @@
         <v>7</v>
       </c>
       <c r="D14" t="s">
-        <v>501</v>
+        <v>507</v>
       </c>
       <c r="E14">
         <v>1</v>
@@ -10157,7 +10262,7 @@
         <v>7</v>
       </c>
       <c r="D15" t="s">
-        <v>502</v>
+        <v>508</v>
       </c>
       <c r="E15">
         <v>1</v>
@@ -10180,7 +10285,7 @@
         <v>7</v>
       </c>
       <c r="D16" t="s">
-        <v>503</v>
+        <v>509</v>
       </c>
       <c r="E16">
         <v>1</v>
@@ -10203,7 +10308,7 @@
         <v>7</v>
       </c>
       <c r="D17" t="s">
-        <v>504</v>
+        <v>510</v>
       </c>
       <c r="E17">
         <v>1</v>
@@ -10226,7 +10331,7 @@
         <v>7</v>
       </c>
       <c r="D18" t="s">
-        <v>505</v>
+        <v>511</v>
       </c>
       <c r="E18">
         <v>1</v>
@@ -10249,7 +10354,7 @@
         <v>7</v>
       </c>
       <c r="D19" t="s">
-        <v>506</v>
+        <v>512</v>
       </c>
       <c r="E19">
         <v>1</v>
@@ -10272,7 +10377,7 @@
         <v>7</v>
       </c>
       <c r="D20" t="s">
-        <v>507</v>
+        <v>513</v>
       </c>
       <c r="E20">
         <v>1</v>
@@ -10295,7 +10400,7 @@
         <v>7</v>
       </c>
       <c r="D21" t="s">
-        <v>508</v>
+        <v>514</v>
       </c>
       <c r="E21">
         <v>1</v>
@@ -10318,7 +10423,7 @@
         <v>7</v>
       </c>
       <c r="D22" t="s">
-        <v>509</v>
+        <v>515</v>
       </c>
       <c r="E22">
         <v>1</v>
@@ -10341,7 +10446,7 @@
         <v>7</v>
       </c>
       <c r="D23" s="4" t="s">
-        <v>510</v>
+        <v>516</v>
       </c>
       <c r="E23">
         <v>1</v>
@@ -10364,7 +10469,7 @@
         <v>7</v>
       </c>
       <c r="D24" s="4" t="s">
-        <v>511</v>
+        <v>517</v>
       </c>
       <c r="E24">
         <v>1</v>
@@ -10387,7 +10492,7 @@
         <v>7</v>
       </c>
       <c r="D25" s="4" t="s">
-        <v>512</v>
+        <v>518</v>
       </c>
       <c r="E25">
         <v>1</v>
@@ -10410,7 +10515,7 @@
         <v>7</v>
       </c>
       <c r="D26" s="4" t="s">
-        <v>513</v>
+        <v>519</v>
       </c>
       <c r="E26">
         <v>1</v>
@@ -10427,13 +10532,13 @@
         <v>80</v>
       </c>
       <c r="B27" t="s">
-        <v>514</v>
+        <v>520</v>
       </c>
       <c r="C27" t="s">
         <v>7</v>
       </c>
       <c r="D27" t="s">
-        <v>515</v>
+        <v>521</v>
       </c>
       <c r="E27">
         <v>1</v>
@@ -10450,13 +10555,13 @@
         <v>82</v>
       </c>
       <c r="B28" t="s">
-        <v>490</v>
+        <v>496</v>
       </c>
       <c r="C28" t="s">
         <v>7</v>
       </c>
       <c r="D28" t="s">
-        <v>516</v>
+        <v>522</v>
       </c>
       <c r="E28">
         <v>1</v>
@@ -10473,13 +10578,13 @@
         <v>84</v>
       </c>
       <c r="B29" t="s">
-        <v>490</v>
+        <v>496</v>
       </c>
       <c r="C29" t="s">
         <v>7</v>
       </c>
       <c r="D29" t="s">
-        <v>517</v>
+        <v>523</v>
       </c>
       <c r="E29">
         <v>1</v>
@@ -10496,13 +10601,13 @@
         <v>86</v>
       </c>
       <c r="B30" t="s">
-        <v>490</v>
+        <v>496</v>
       </c>
       <c r="C30" t="s">
         <v>7</v>
       </c>
       <c r="D30" t="s">
-        <v>518</v>
+        <v>524</v>
       </c>
       <c r="E30">
         <v>1</v>
@@ -10525,7 +10630,7 @@
         <v>7</v>
       </c>
       <c r="D31" t="s">
-        <v>519</v>
+        <v>525</v>
       </c>
       <c r="E31">
         <v>1</v>
@@ -10548,7 +10653,7 @@
         <v>7</v>
       </c>
       <c r="D32" t="s">
-        <v>520</v>
+        <v>526</v>
       </c>
       <c r="E32">
         <v>1</v>
@@ -10571,7 +10676,7 @@
         <v>7</v>
       </c>
       <c r="D33" t="s">
-        <v>521</v>
+        <v>527</v>
       </c>
       <c r="E33">
         <v>1</v>
@@ -10594,7 +10699,7 @@
         <v>7</v>
       </c>
       <c r="D34" t="s">
-        <v>522</v>
+        <v>528</v>
       </c>
       <c r="E34">
         <v>1</v>
@@ -10617,7 +10722,7 @@
         <v>7</v>
       </c>
       <c r="D35" t="s">
-        <v>523</v>
+        <v>529</v>
       </c>
       <c r="E35">
         <v>1</v>
@@ -10634,13 +10739,13 @@
         <v>98</v>
       </c>
       <c r="B36" t="s">
-        <v>490</v>
+        <v>496</v>
       </c>
       <c r="C36" t="s">
         <v>7</v>
       </c>
       <c r="D36" t="s">
-        <v>524</v>
+        <v>530</v>
       </c>
       <c r="E36">
         <v>1</v>
@@ -10657,13 +10762,13 @@
         <v>100</v>
       </c>
       <c r="B37" t="s">
-        <v>490</v>
+        <v>496</v>
       </c>
       <c r="C37" t="s">
         <v>7</v>
       </c>
       <c r="D37" t="s">
-        <v>525</v>
+        <v>531</v>
       </c>
       <c r="E37">
         <v>1</v>
@@ -10680,13 +10785,13 @@
         <v>102</v>
       </c>
       <c r="B38" t="s">
-        <v>490</v>
+        <v>496</v>
       </c>
       <c r="C38" t="s">
         <v>7</v>
       </c>
       <c r="D38" t="s">
-        <v>526</v>
+        <v>532</v>
       </c>
       <c r="E38">
         <v>1</v>
@@ -10703,13 +10808,13 @@
         <v>104</v>
       </c>
       <c r="B39" t="s">
-        <v>490</v>
+        <v>496</v>
       </c>
       <c r="C39" t="s">
         <v>10</v>
       </c>
       <c r="D39" t="s">
-        <v>527</v>
+        <v>533</v>
       </c>
       <c r="E39">
         <v>1</v>
@@ -10726,13 +10831,13 @@
         <v>106</v>
       </c>
       <c r="B40" t="s">
-        <v>490</v>
+        <v>496</v>
       </c>
       <c r="C40" t="s">
         <v>10</v>
       </c>
       <c r="D40" t="s">
-        <v>528</v>
+        <v>534</v>
       </c>
       <c r="E40">
         <v>1</v>
@@ -10749,13 +10854,13 @@
         <v>108</v>
       </c>
       <c r="B41" t="s">
-        <v>490</v>
+        <v>496</v>
       </c>
       <c r="C41" t="s">
         <v>10</v>
       </c>
       <c r="D41" t="s">
-        <v>529</v>
+        <v>535</v>
       </c>
       <c r="E41">
         <v>1</v>
@@ -10772,13 +10877,13 @@
         <v>110</v>
       </c>
       <c r="B42" t="s">
-        <v>490</v>
+        <v>496</v>
       </c>
       <c r="C42" t="s">
         <v>10</v>
       </c>
       <c r="D42" t="s">
-        <v>530</v>
+        <v>536</v>
       </c>
       <c r="E42">
         <v>1</v>
@@ -10795,13 +10900,13 @@
         <v>112</v>
       </c>
       <c r="B43" t="s">
-        <v>490</v>
+        <v>496</v>
       </c>
       <c r="C43" t="s">
         <v>10</v>
       </c>
       <c r="D43" t="s">
-        <v>531</v>
+        <v>537</v>
       </c>
       <c r="E43">
         <v>1</v>
@@ -10818,13 +10923,13 @@
         <v>114</v>
       </c>
       <c r="B44" t="s">
-        <v>490</v>
+        <v>496</v>
       </c>
       <c r="C44" t="s">
         <v>10</v>
       </c>
       <c r="D44" t="s">
-        <v>532</v>
+        <v>538</v>
       </c>
       <c r="E44">
         <v>1</v>
@@ -10841,13 +10946,13 @@
         <v>116</v>
       </c>
       <c r="B45" t="s">
-        <v>490</v>
+        <v>496</v>
       </c>
       <c r="C45" t="s">
         <v>10</v>
       </c>
       <c r="D45" t="s">
-        <v>533</v>
+        <v>539</v>
       </c>
       <c r="E45">
         <v>1</v>
@@ -10864,13 +10969,13 @@
         <v>118</v>
       </c>
       <c r="B46" t="s">
-        <v>490</v>
+        <v>496</v>
       </c>
       <c r="C46" t="s">
         <v>10</v>
       </c>
       <c r="D46" t="s">
-        <v>534</v>
+        <v>540</v>
       </c>
       <c r="E46">
         <v>1</v>
@@ -10887,13 +10992,13 @@
         <v>120</v>
       </c>
       <c r="B47" t="s">
-        <v>490</v>
+        <v>496</v>
       </c>
       <c r="C47" t="s">
         <v>7</v>
       </c>
       <c r="D47" t="s">
-        <v>535</v>
+        <v>541</v>
       </c>
       <c r="E47">
         <v>1</v>
@@ -10910,13 +11015,13 @@
         <v>122</v>
       </c>
       <c r="B48" t="s">
-        <v>490</v>
+        <v>496</v>
       </c>
       <c r="C48" t="s">
         <v>7</v>
       </c>
       <c r="D48" t="s">
-        <v>536</v>
+        <v>542</v>
       </c>
       <c r="E48">
         <v>1</v>
@@ -10933,13 +11038,13 @@
         <v>124</v>
       </c>
       <c r="B49" t="s">
-        <v>490</v>
+        <v>496</v>
       </c>
       <c r="C49" t="s">
         <v>7</v>
       </c>
       <c r="D49" t="s">
-        <v>537</v>
+        <v>543</v>
       </c>
       <c r="E49">
         <v>1</v>
@@ -10956,13 +11061,13 @@
         <v>126</v>
       </c>
       <c r="B50" t="s">
-        <v>490</v>
+        <v>496</v>
       </c>
       <c r="C50" t="s">
         <v>7</v>
       </c>
       <c r="D50" t="s">
-        <v>538</v>
+        <v>544</v>
       </c>
       <c r="E50">
         <v>1</v>
@@ -10979,13 +11084,13 @@
         <v>128</v>
       </c>
       <c r="B51" t="s">
-        <v>490</v>
+        <v>496</v>
       </c>
       <c r="C51" t="s">
         <v>7</v>
       </c>
       <c r="D51" t="s">
-        <v>539</v>
+        <v>545</v>
       </c>
       <c r="E51">
         <v>1</v>
@@ -11002,13 +11107,13 @@
         <v>130</v>
       </c>
       <c r="B52" t="s">
-        <v>490</v>
+        <v>496</v>
       </c>
       <c r="C52" t="s">
         <v>7</v>
       </c>
       <c r="D52" t="s">
-        <v>540</v>
+        <v>546</v>
       </c>
       <c r="E52">
         <v>1</v>
@@ -11055,7 +11160,7 @@
         <v>1</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>541</v>
+        <v>547</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>3</v>
@@ -11066,13 +11171,13 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" t="s">
-        <v>542</v>
+        <v>548</v>
       </c>
       <c r="B2" t="s">
-        <v>543</v>
+        <v>549</v>
       </c>
       <c r="C2" t="s">
-        <v>544</v>
+        <v>550</v>
       </c>
       <c r="E2">
         <v>1</v>
@@ -11083,13 +11188,13 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3" t="s">
-        <v>545</v>
+        <v>551</v>
       </c>
       <c r="B3" t="s">
-        <v>543</v>
+        <v>549</v>
       </c>
       <c r="C3" t="s">
-        <v>546</v>
+        <v>552</v>
       </c>
       <c r="E3">
         <v>1</v>
@@ -11120,42 +11225,42 @@
   <sheetData>
     <row r="1" spans="1:2" customHeight="1" ht="16">
       <c r="A1" s="2" t="s">
-        <v>547</v>
+        <v>553</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>548</v>
+        <v>554</v>
       </c>
     </row>
     <row r="2" spans="1:2" customHeight="1" ht="16">
       <c r="A2" s="3" t="s">
-        <v>549</v>
+        <v>555</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>550</v>
+        <v>556</v>
       </c>
     </row>
     <row r="3" spans="1:2" customHeight="1" ht="16">
       <c r="A3" s="3" t="s">
-        <v>551</v>
+        <v>557</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>552</v>
+        <v>558</v>
       </c>
     </row>
     <row r="4" spans="1:2" customHeight="1" ht="16">
       <c r="A4" s="3" t="s">
-        <v>553</v>
+        <v>559</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>554</v>
+        <v>560</v>
       </c>
     </row>
     <row r="5" spans="1:2" customHeight="1" ht="16">
       <c r="A5" s="3" t="s">
-        <v>555</v>
+        <v>561</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>556</v>
+        <v>562</v>
       </c>
     </row>
     <row r="6" spans="1:2" customHeight="1" ht="16">
@@ -11163,7 +11268,7 @@
         <v>204</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>557</v>
+        <v>563</v>
       </c>
     </row>
     <row r="7" spans="1:2" customHeight="1" ht="16">
@@ -11171,31 +11276,31 @@
         <v>35</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>558</v>
+        <v>564</v>
       </c>
     </row>
     <row r="8" spans="1:2" customHeight="1" ht="16">
       <c r="A8" s="3" t="s">
-        <v>559</v>
+        <v>565</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>560</v>
+        <v>566</v>
       </c>
     </row>
     <row r="9" spans="1:2" customHeight="1" ht="16">
       <c r="A9" s="3" t="s">
-        <v>561</v>
+        <v>567</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>562</v>
+        <v>568</v>
       </c>
     </row>
     <row r="10" spans="1:2" customHeight="1" ht="16">
       <c r="A10" s="3" t="s">
-        <v>563</v>
+        <v>569</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>564</v>
+        <v>570</v>
       </c>
     </row>
   </sheetData>

--- a/database/catalogos/catalogo_maestro.xlsx
+++ b/database/catalogos/catalogo_maestro.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1143" uniqueCount="575">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1193" uniqueCount="604">
   <si>
     <t>slug</t>
   </si>
@@ -349,6 +349,12 @@
     <t>Pastel</t>
   </si>
   <si>
+    <t>espresso</t>
+  </si>
+  <si>
+    <t>Espresso</t>
+  </si>
+  <si>
     <t>cafe_americano</t>
   </si>
   <si>
@@ -433,6 +439,18 @@
     <t>Desechable grande</t>
   </si>
   <si>
+    <t>pozole_chico</t>
+  </si>
+  <si>
+    <t>Pozole chico</t>
+  </si>
+  <si>
+    <t>pozole_grande</t>
+  </si>
+  <si>
+    <t>Pozole grande</t>
+  </si>
+  <si>
     <t>otro</t>
   </si>
   <si>
@@ -805,6 +823,12 @@
     <t>Bebida del paquete</t>
   </si>
   <si>
+    <t>proteina_pozole</t>
+  </si>
+  <si>
+    <t>Proteina Pozole</t>
+  </si>
+  <si>
     <t>grupo_slug</t>
   </si>
   <si>
@@ -907,6 +931,15 @@
     <t>Pastel Fresa</t>
   </si>
   <si>
+    <t>pastel_cajeta</t>
+  </si>
+  <si>
+    <t>Sabor Pastel: Cajeta</t>
+  </si>
+  <si>
+    <t>Pastel Cajeta</t>
+  </si>
+  <si>
     <t>pay_oreo</t>
   </si>
   <si>
@@ -1276,6 +1309,15 @@
     <t>Frappe Chocolate</t>
   </si>
   <si>
+    <t>frappe_vainilla</t>
+  </si>
+  <si>
+    <t>Sabor Frappe: Vainilla</t>
+  </si>
+  <si>
+    <t>Frappe Vainilla</t>
+  </si>
+  <si>
     <t>chamoyada_mango</t>
   </si>
   <si>
@@ -1510,6 +1552,42 @@
     <t>Bebida del paquete: Te</t>
   </si>
   <si>
+    <t>proteina_pozole_sin_proteina</t>
+  </si>
+  <si>
+    <t>Proteina Pozole: Sin Proteina</t>
+  </si>
+  <si>
+    <t>Pozole Sin Proteina</t>
+  </si>
+  <si>
+    <t>proteina_pozole_pollo</t>
+  </si>
+  <si>
+    <t>Proteina Pozole: Pollo</t>
+  </si>
+  <si>
+    <t>Pozole Pollo</t>
+  </si>
+  <si>
+    <t>proteina_pozole_maciza</t>
+  </si>
+  <si>
+    <t>Proteina Pozole: Maciza</t>
+  </si>
+  <si>
+    <t>Pozole Maciza</t>
+  </si>
+  <si>
+    <t>proteina_pozole_surtida</t>
+  </si>
+  <si>
+    <t>Proteina Pozole: Surtida</t>
+  </si>
+  <si>
+    <t>Pozole Surtida</t>
+  </si>
+  <si>
     <t>producto_sku</t>
   </si>
   <si>
@@ -1642,6 +1720,9 @@
     <t>PASTEL</t>
   </si>
   <si>
+    <t>ESPRESSO</t>
+  </si>
+  <si>
     <t>CAFE AMERICANO</t>
   </si>
   <si>
@@ -1682,6 +1763,12 @@
   </si>
   <si>
     <t>DESECHABLE GRANDE</t>
+  </si>
+  <si>
+    <t>POZOLE CHICO</t>
+  </si>
+  <si>
+    <t>POZOLE GRANDE</t>
   </si>
   <si>
     <t>fecha</t>
@@ -1760,7 +1847,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <sz val="11.0"/>
       <color rgb="FF000000"/>
@@ -1781,6 +1868,11 @@
       <sz val="11.0"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
+    </font>
+    <font>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="3">
@@ -1809,7 +1901,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -1817,6 +1909,9 @@
     <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyFont="1"/>
     <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyFont="1"/>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
     <xf borderId="1" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
@@ -3520,7 +3615,7 @@
       <c r="N6" s="2">
         <v>1.0</v>
       </c>
-      <c r="O6" s="4">
+      <c r="O6" s="2">
         <v>0.0</v>
       </c>
       <c r="P6" s="2">
@@ -5128,52 +5223,52 @@
       </c>
     </row>
     <row r="39" ht="14.25" customHeight="1">
-      <c r="A39" s="2" t="s">
+      <c r="A39" s="4" t="s">
         <v>106</v>
       </c>
-      <c r="B39" s="2" t="s">
+      <c r="B39" s="4" t="s">
         <v>107</v>
       </c>
       <c r="C39" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="D39" s="2">
-        <v>35.0</v>
-      </c>
-      <c r="E39" s="2">
-        <v>13.0</v>
-      </c>
-      <c r="F39" s="2">
-        <v>1.0</v>
-      </c>
-      <c r="G39" s="2">
-        <v>1.0</v>
-      </c>
-      <c r="H39" s="2">
-        <v>0.0</v>
-      </c>
-      <c r="I39" s="2">
-        <v>0.0</v>
-      </c>
-      <c r="J39" s="2">
-        <v>0.0</v>
-      </c>
-      <c r="K39" s="2">
-        <v>0.0</v>
-      </c>
-      <c r="L39" s="2">
-        <v>0.0</v>
-      </c>
-      <c r="M39" s="2">
-        <v>1.0</v>
-      </c>
-      <c r="N39" s="2">
-        <v>1.0</v>
-      </c>
-      <c r="O39" s="2">
-        <v>0.0</v>
-      </c>
-      <c r="P39" s="2">
+      <c r="D39" s="4">
+        <v>40.0</v>
+      </c>
+      <c r="E39" s="4">
+        <v>15.0</v>
+      </c>
+      <c r="F39" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="G39" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="H39" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="I39" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="J39" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="K39" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="L39" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="M39" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="N39" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="O39" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="P39" s="4">
         <v>380.0</v>
       </c>
     </row>
@@ -5188,10 +5283,10 @@
         <v>8</v>
       </c>
       <c r="D40" s="2">
-        <v>25.0</v>
+        <v>35.0</v>
       </c>
       <c r="E40" s="2">
-        <v>9.0</v>
+        <v>13.0</v>
       </c>
       <c r="F40" s="2">
         <v>1.0</v>
@@ -5238,10 +5333,10 @@
         <v>8</v>
       </c>
       <c r="D41" s="2">
-        <v>50.0</v>
+        <v>25.0</v>
       </c>
       <c r="E41" s="2">
-        <v>15.0</v>
+        <v>9.0</v>
       </c>
       <c r="F41" s="2">
         <v>1.0</v>
@@ -5288,10 +5383,10 @@
         <v>8</v>
       </c>
       <c r="D42" s="2">
-        <v>65.0</v>
+        <v>50.0</v>
       </c>
       <c r="E42" s="2">
-        <v>27.0</v>
+        <v>15.0</v>
       </c>
       <c r="F42" s="2">
         <v>1.0</v>
@@ -5323,7 +5418,7 @@
       <c r="O42" s="2">
         <v>0.0</v>
       </c>
-      <c r="P42" s="2">
+      <c r="P42" s="4">
         <v>410.0</v>
       </c>
     </row>
@@ -5338,10 +5433,10 @@
         <v>8</v>
       </c>
       <c r="D43" s="2">
-        <v>80.0</v>
+        <v>65.0</v>
       </c>
       <c r="E43" s="2">
-        <v>26.0</v>
+        <v>27.0</v>
       </c>
       <c r="F43" s="2">
         <v>1.0</v>
@@ -5391,7 +5486,7 @@
         <v>80.0</v>
       </c>
       <c r="E44" s="2">
-        <v>36.0</v>
+        <v>26.0</v>
       </c>
       <c r="F44" s="2">
         <v>1.0</v>
@@ -5438,10 +5533,10 @@
         <v>8</v>
       </c>
       <c r="D45" s="2">
-        <v>75.0</v>
+        <v>80.0</v>
       </c>
       <c r="E45" s="2">
-        <v>28.0</v>
+        <v>36.0</v>
       </c>
       <c r="F45" s="2">
         <v>1.0</v>
@@ -5473,7 +5568,7 @@
       <c r="O45" s="2">
         <v>0.0</v>
       </c>
-      <c r="P45" s="2">
+      <c r="P45" s="4">
         <v>440.0</v>
       </c>
     </row>
@@ -5488,10 +5583,10 @@
         <v>8</v>
       </c>
       <c r="D46" s="2">
-        <v>30.0</v>
+        <v>75.0</v>
       </c>
       <c r="E46" s="2">
-        <v>14.0</v>
+        <v>28.0</v>
       </c>
       <c r="F46" s="2">
         <v>1.0</v>
@@ -5515,7 +5610,7 @@
         <v>0.0</v>
       </c>
       <c r="M46" s="2">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="N46" s="2">
         <v>1.0</v>
@@ -5535,13 +5630,13 @@
         <v>123</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="D47" s="2">
-        <v>0.0</v>
-      </c>
-      <c r="E47" s="2">
-        <v>0.0</v>
+        <v>30.0</v>
+      </c>
+      <c r="E47" s="4">
+        <v>15.0</v>
       </c>
       <c r="F47" s="2">
         <v>1.0</v>
@@ -5565,7 +5660,7 @@
         <v>0.0</v>
       </c>
       <c r="M47" s="2">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="N47" s="2">
         <v>1.0</v>
@@ -5588,10 +5683,10 @@
         <v>15</v>
       </c>
       <c r="D48" s="2">
-        <v>90.0</v>
+        <v>0.0</v>
       </c>
       <c r="E48" s="2">
-        <v>50.0</v>
+        <v>0.0</v>
       </c>
       <c r="F48" s="2">
         <v>1.0</v>
@@ -5623,7 +5718,7 @@
       <c r="O48" s="2">
         <v>0.0</v>
       </c>
-      <c r="P48" s="2">
+      <c r="P48" s="4">
         <v>470.0</v>
       </c>
     </row>
@@ -5635,13 +5730,13 @@
         <v>127</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="D49" s="2">
-        <v>20.0</v>
+        <v>90.0</v>
       </c>
       <c r="E49" s="2">
-        <v>11.0</v>
+        <v>50.0</v>
       </c>
       <c r="F49" s="2">
         <v>1.0</v>
@@ -5665,7 +5760,7 @@
         <v>0.0</v>
       </c>
       <c r="M49" s="2">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="N49" s="2">
         <v>1.0</v>
@@ -5685,13 +5780,13 @@
         <v>129</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D50" s="2">
-        <v>40.0</v>
+        <v>20.0</v>
       </c>
       <c r="E50" s="2">
-        <v>25.0</v>
+        <v>11.0</v>
       </c>
       <c r="F50" s="2">
         <v>1.0</v>
@@ -5735,13 +5830,13 @@
         <v>131</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="D51" s="2">
-        <v>5.0</v>
+        <v>40.0</v>
       </c>
       <c r="E51" s="2">
-        <v>5.0</v>
+        <v>25.0</v>
       </c>
       <c r="F51" s="2">
         <v>1.0</v>
@@ -5768,12 +5863,12 @@
         <v>0.0</v>
       </c>
       <c r="N51" s="2">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="O51" s="2">
         <v>0.0</v>
       </c>
-      <c r="P51" s="2">
+      <c r="P51" s="4">
         <v>500.0</v>
       </c>
     </row>
@@ -5788,10 +5883,10 @@
         <v>17</v>
       </c>
       <c r="D52" s="2">
-        <v>10.0</v>
+        <v>5.0</v>
       </c>
       <c r="E52" s="2">
-        <v>10.0</v>
+        <v>5.0</v>
       </c>
       <c r="F52" s="2">
         <v>1.0</v>
@@ -5835,13 +5930,13 @@
         <v>135</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="D53" s="2">
-        <v>0.0</v>
+        <v>10.0</v>
       </c>
       <c r="E53" s="2">
-        <v>0.0</v>
+        <v>10.0</v>
       </c>
       <c r="F53" s="2">
         <v>1.0</v>
@@ -5877,9 +5972,156 @@
         <v>520.0</v>
       </c>
     </row>
-    <row r="54" ht="14.25" customHeight="1"/>
-    <row r="55" ht="14.25" customHeight="1"/>
-    <row r="56" ht="14.25" customHeight="1"/>
+    <row r="54" ht="14.25" customHeight="1">
+      <c r="A54" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="B54" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="C54" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D54" s="4">
+        <v>55.0</v>
+      </c>
+      <c r="E54" s="4">
+        <v>20.0</v>
+      </c>
+      <c r="F54" s="2">
+        <v>1.0</v>
+      </c>
+      <c r="G54" s="2">
+        <v>1.0</v>
+      </c>
+      <c r="H54" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="I54" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="J54" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="K54" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="L54" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="M54" s="2">
+        <v>1.0</v>
+      </c>
+      <c r="N54" s="2">
+        <v>1.0</v>
+      </c>
+      <c r="O54" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="P54" s="4">
+        <v>530.0</v>
+      </c>
+    </row>
+    <row r="55" ht="14.25" customHeight="1">
+      <c r="A55" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="B55" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="C55" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D55" s="4">
+        <v>95.0</v>
+      </c>
+      <c r="E55" s="4">
+        <v>28.0</v>
+      </c>
+      <c r="F55" s="2">
+        <v>1.0</v>
+      </c>
+      <c r="G55" s="2">
+        <v>1.0</v>
+      </c>
+      <c r="H55" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="I55" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="J55" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="K55" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="L55" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="M55" s="2">
+        <v>1.0</v>
+      </c>
+      <c r="N55" s="2">
+        <v>1.0</v>
+      </c>
+      <c r="O55" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="P55" s="2">
+        <v>540.0</v>
+      </c>
+    </row>
+    <row r="56" ht="14.25" customHeight="1">
+      <c r="A56" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="B56" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="C56" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="D56" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="E56" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="F56" s="2">
+        <v>1.0</v>
+      </c>
+      <c r="G56" s="2">
+        <v>1.0</v>
+      </c>
+      <c r="H56" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="I56" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="J56" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="K56" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="L56" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="M56" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="N56" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="O56" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="P56" s="2">
+        <v>550.0</v>
+      </c>
+    </row>
     <row r="57" ht="14.25" customHeight="1"/>
     <row r="58" ht="14.25" customHeight="1"/>
     <row r="59" ht="14.25" customHeight="1"/>
@@ -6077,9 +6319,9 @@
     <row r="251" ht="14.25" customHeight="1"/>
     <row r="252" ht="14.25" customHeight="1"/>
     <row r="253" ht="14.25" customHeight="1"/>
-    <row r="254" ht="15.75" customHeight="1"/>
-    <row r="255" ht="15.75" customHeight="1"/>
-    <row r="256" ht="15.75" customHeight="1"/>
+    <row r="254" ht="14.25" customHeight="1"/>
+    <row r="255" ht="14.25" customHeight="1"/>
+    <row r="256" ht="14.25" customHeight="1"/>
     <row r="257" ht="15.75" customHeight="1"/>
     <row r="258" ht="15.75" customHeight="1"/>
     <row r="259" ht="15.75" customHeight="1"/>
@@ -6824,6 +7066,9 @@
     <row r="998" ht="15.75" customHeight="1"/>
     <row r="999" ht="15.75" customHeight="1"/>
     <row r="1000" ht="15.75" customHeight="1"/>
+    <row r="1001" ht="15.75" customHeight="1"/>
+    <row r="1002" ht="15.75" customHeight="1"/>
+    <row r="1003" ht="15.75" customHeight="1"/>
   </sheetData>
   <autoFilter ref="$A$1:$P$1"/>
   <printOptions/>
@@ -6860,7 +7105,7 @@
         <v>3</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>136</v>
+        <v>142</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>4</v>
@@ -6868,10 +7113,10 @@
     </row>
     <row r="2" ht="14.25" customHeight="1">
       <c r="A2" s="2" t="s">
-        <v>137</v>
+        <v>143</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>138</v>
+        <v>144</v>
       </c>
       <c r="C2" s="2">
         <v>10.0</v>
@@ -6888,10 +7133,10 @@
     </row>
     <row r="3" ht="14.25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>139</v>
+        <v>145</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>140</v>
+        <v>146</v>
       </c>
       <c r="C3" s="2">
         <v>10.0</v>
@@ -6908,10 +7153,10 @@
     </row>
     <row r="4" ht="14.25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>141</v>
+        <v>147</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="C4" s="2">
         <v>10.0</v>
@@ -6928,10 +7173,10 @@
     </row>
     <row r="5" ht="14.25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>143</v>
+        <v>149</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>144</v>
+        <v>150</v>
       </c>
       <c r="C5" s="2">
         <v>10.0</v>
@@ -6948,10 +7193,10 @@
     </row>
     <row r="6" ht="14.25" customHeight="1">
       <c r="A6" s="2" t="s">
-        <v>145</v>
+        <v>151</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>146</v>
+        <v>152</v>
       </c>
       <c r="C6" s="2">
         <v>10.0</v>
@@ -6968,10 +7213,10 @@
     </row>
     <row r="7" ht="14.25" customHeight="1">
       <c r="A7" s="2" t="s">
-        <v>147</v>
+        <v>153</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>148</v>
+        <v>154</v>
       </c>
       <c r="C7" s="2">
         <v>10.0</v>
@@ -6988,10 +7233,10 @@
     </row>
     <row r="8" ht="14.25" customHeight="1">
       <c r="A8" s="2" t="s">
-        <v>149</v>
+        <v>155</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="C8" s="2">
         <v>15.0</v>
@@ -7008,10 +7253,10 @@
     </row>
     <row r="9" ht="14.25" customHeight="1">
       <c r="A9" s="2" t="s">
-        <v>151</v>
+        <v>157</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>152</v>
+        <v>158</v>
       </c>
       <c r="C9" s="2">
         <v>10.0</v>
@@ -7028,10 +7273,10 @@
     </row>
     <row r="10" ht="14.25" customHeight="1">
       <c r="A10" s="2" t="s">
-        <v>153</v>
+        <v>159</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>154</v>
+        <v>160</v>
       </c>
       <c r="C10" s="2">
         <v>10.0</v>
@@ -7048,10 +7293,10 @@
     </row>
     <row r="11" ht="14.25" customHeight="1">
       <c r="A11" s="2" t="s">
-        <v>155</v>
+        <v>161</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>156</v>
+        <v>162</v>
       </c>
       <c r="C11" s="2">
         <v>5.0</v>
@@ -7068,10 +7313,10 @@
     </row>
     <row r="12" ht="14.25" customHeight="1">
       <c r="A12" s="2" t="s">
-        <v>157</v>
+        <v>163</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>158</v>
+        <v>164</v>
       </c>
       <c r="C12" s="2">
         <v>5.0</v>
@@ -7088,10 +7333,10 @@
     </row>
     <row r="13" ht="14.25" customHeight="1">
       <c r="A13" s="2" t="s">
-        <v>159</v>
+        <v>165</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>160</v>
+        <v>166</v>
       </c>
       <c r="C13" s="2">
         <v>5.0</v>
@@ -7108,10 +7353,10 @@
     </row>
     <row r="14" ht="14.25" customHeight="1">
       <c r="A14" s="2" t="s">
-        <v>161</v>
+        <v>167</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>162</v>
+        <v>168</v>
       </c>
       <c r="C14" s="2">
         <v>5.0</v>
@@ -7128,10 +7373,10 @@
     </row>
     <row r="15" ht="14.25" customHeight="1">
       <c r="A15" s="2" t="s">
-        <v>163</v>
+        <v>169</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>164</v>
+        <v>170</v>
       </c>
       <c r="C15" s="2">
         <v>5.0</v>
@@ -7148,10 +7393,10 @@
     </row>
     <row r="16" ht="14.25" customHeight="1">
       <c r="A16" s="2" t="s">
-        <v>165</v>
+        <v>171</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>166</v>
+        <v>172</v>
       </c>
       <c r="C16" s="2">
         <v>10.0</v>
@@ -7168,10 +7413,10 @@
     </row>
     <row r="17" ht="14.25" customHeight="1">
       <c r="A17" s="2" t="s">
-        <v>167</v>
+        <v>173</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>168</v>
+        <v>174</v>
       </c>
       <c r="C17" s="2">
         <v>10.0</v>
@@ -7188,10 +7433,10 @@
     </row>
     <row r="18" ht="14.25" customHeight="1">
       <c r="A18" s="2" t="s">
-        <v>169</v>
+        <v>175</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>170</v>
+        <v>176</v>
       </c>
       <c r="C18" s="2">
         <v>10.0</v>
@@ -7208,10 +7453,10 @@
     </row>
     <row r="19" ht="14.25" customHeight="1">
       <c r="A19" s="2" t="s">
-        <v>171</v>
+        <v>177</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>172</v>
+        <v>178</v>
       </c>
       <c r="C19" s="2">
         <v>10.0</v>
@@ -7328,10 +7573,10 @@
     </row>
     <row r="25" ht="14.25" customHeight="1">
       <c r="A25" s="2" t="s">
-        <v>173</v>
+        <v>179</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>174</v>
+        <v>180</v>
       </c>
       <c r="C25" s="2">
         <v>10.0</v>
@@ -7348,10 +7593,10 @@
     </row>
     <row r="26" ht="14.25" customHeight="1">
       <c r="A26" s="2" t="s">
-        <v>175</v>
+        <v>181</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>176</v>
+        <v>182</v>
       </c>
       <c r="C26" s="2">
         <v>15.0</v>
@@ -7368,10 +7613,10 @@
     </row>
     <row r="27" ht="14.25" customHeight="1">
       <c r="A27" s="2" t="s">
-        <v>177</v>
+        <v>183</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>178</v>
+        <v>184</v>
       </c>
       <c r="C27" s="2">
         <v>10.0</v>
@@ -7388,10 +7633,10 @@
     </row>
     <row r="28" ht="14.25" customHeight="1">
       <c r="A28" s="2" t="s">
-        <v>179</v>
+        <v>185</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>180</v>
+        <v>186</v>
       </c>
       <c r="C28" s="2">
         <v>10.0</v>
@@ -7408,10 +7653,10 @@
     </row>
     <row r="29" ht="14.25" customHeight="1">
       <c r="A29" s="2" t="s">
-        <v>181</v>
+        <v>187</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>182</v>
+        <v>188</v>
       </c>
       <c r="C29" s="2">
         <v>5.0</v>
@@ -7428,10 +7673,10 @@
     </row>
     <row r="30" ht="14.25" customHeight="1">
       <c r="A30" s="2" t="s">
-        <v>183</v>
+        <v>189</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>184</v>
+        <v>190</v>
       </c>
       <c r="C30" s="2">
         <v>5.0</v>
@@ -7448,10 +7693,10 @@
     </row>
     <row r="31" ht="14.25" customHeight="1">
       <c r="A31" s="2" t="s">
-        <v>185</v>
+        <v>191</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>186</v>
+        <v>192</v>
       </c>
       <c r="C31" s="2">
         <v>35.0</v>
@@ -7468,10 +7713,10 @@
     </row>
     <row r="32" ht="14.25" customHeight="1">
       <c r="A32" s="2" t="s">
-        <v>187</v>
+        <v>193</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>188</v>
+        <v>194</v>
       </c>
       <c r="C32" s="2">
         <v>25.0</v>
@@ -7488,10 +7733,10 @@
     </row>
     <row r="33" ht="14.25" customHeight="1">
       <c r="A33" s="2" t="s">
-        <v>189</v>
+        <v>195</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>190</v>
+        <v>196</v>
       </c>
       <c r="C33" s="2">
         <v>15.0</v>
@@ -7511,7 +7756,7 @@
         <v>80</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>191</v>
+        <v>197</v>
       </c>
       <c r="C34" s="2">
         <v>40.0</v>
@@ -7528,10 +7773,10 @@
     </row>
     <row r="35" ht="14.25" customHeight="1">
       <c r="A35" s="2" t="s">
-        <v>192</v>
+        <v>198</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>193</v>
+        <v>199</v>
       </c>
       <c r="C35" s="2">
         <v>35.0</v>
@@ -7548,10 +7793,10 @@
     </row>
     <row r="36" ht="14.25" customHeight="1">
       <c r="A36" s="2" t="s">
-        <v>194</v>
+        <v>200</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>195</v>
+        <v>201</v>
       </c>
       <c r="C36" s="2">
         <v>15.0</v>
@@ -7568,10 +7813,10 @@
     </row>
     <row r="37" ht="14.25" customHeight="1">
       <c r="A37" s="2" t="s">
-        <v>196</v>
+        <v>202</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>197</v>
+        <v>203</v>
       </c>
       <c r="C37" s="2">
         <v>7.0</v>
@@ -8588,39 +8833,39 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>199</v>
+        <v>205</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>3</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>200</v>
+        <v>206</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>201</v>
+        <v>207</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>202</v>
+        <v>208</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>203</v>
+        <v>209</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>204</v>
+        <v>210</v>
       </c>
     </row>
     <row r="2" ht="14.25" customHeight="1">
       <c r="A2" s="2" t="s">
-        <v>205</v>
+        <v>211</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>206</v>
+        <v>212</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>207</v>
+        <v>213</v>
       </c>
       <c r="D2" s="2">
         <v>1.0</v>
@@ -8635,7 +8880,7 @@
         <v>5.0</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>208</v>
+        <v>214</v>
       </c>
       <c r="I2" s="2" t="s">
         <v>7</v>
@@ -8649,13 +8894,13 @@
     </row>
     <row r="3" ht="14.25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>209</v>
+        <v>215</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>210</v>
+        <v>216</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="D3" s="2">
         <v>0.0</v>
@@ -8670,7 +8915,7 @@
         <v>15.0</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>208</v>
+        <v>214</v>
       </c>
       <c r="I3" s="2" t="s">
         <v>7</v>
@@ -8684,13 +8929,13 @@
     </row>
     <row r="4" ht="14.25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>212</v>
+        <v>218</v>
       </c>
       <c r="B4" s="2" t="s">
+        <v>219</v>
+      </c>
+      <c r="C4" s="2" t="s">
         <v>213</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>207</v>
       </c>
       <c r="D4" s="2">
         <v>1.0</v>
@@ -8705,7 +8950,7 @@
         <v>20.0</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>208</v>
+        <v>214</v>
       </c>
       <c r="I4" s="2" t="s">
         <v>7</v>
@@ -8719,13 +8964,13 @@
     </row>
     <row r="5" ht="14.25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>214</v>
+        <v>220</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>215</v>
+        <v>221</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>207</v>
+        <v>213</v>
       </c>
       <c r="D5" s="2">
         <v>1.0</v>
@@ -8740,7 +8985,7 @@
         <v>25.0</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>208</v>
+        <v>214</v>
       </c>
       <c r="I5" s="2" t="s">
         <v>7</v>
@@ -8754,13 +8999,13 @@
     </row>
     <row r="6" ht="14.25" customHeight="1">
       <c r="A6" s="2" t="s">
-        <v>216</v>
+        <v>222</v>
       </c>
       <c r="B6" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="C6" s="2" t="s">
         <v>217</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>211</v>
       </c>
       <c r="D6" s="2">
         <v>0.0</v>
@@ -8775,7 +9020,7 @@
         <v>30.0</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>208</v>
+        <v>214</v>
       </c>
       <c r="I6" s="2" t="s">
         <v>7</v>
@@ -8789,13 +9034,13 @@
     </row>
     <row r="7" ht="14.25" customHeight="1">
       <c r="A7" s="2" t="s">
-        <v>218</v>
+        <v>224</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>219</v>
+        <v>225</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>207</v>
+        <v>213</v>
       </c>
       <c r="D7" s="2">
         <v>1.0</v>
@@ -8810,7 +9055,7 @@
         <v>35.0</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>208</v>
+        <v>214</v>
       </c>
       <c r="I7" s="2" t="s">
         <v>7</v>
@@ -8824,13 +9069,13 @@
     </row>
     <row r="8" ht="14.25" customHeight="1">
       <c r="A8" s="2" t="s">
-        <v>220</v>
+        <v>226</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>221</v>
+        <v>227</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>207</v>
+        <v>213</v>
       </c>
       <c r="D8" s="2">
         <v>1.0</v>
@@ -8845,7 +9090,7 @@
         <v>45.0</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>208</v>
+        <v>214</v>
       </c>
       <c r="I8" s="2" t="s">
         <v>7</v>
@@ -8859,13 +9104,13 @@
     </row>
     <row r="9" ht="14.25" customHeight="1">
       <c r="A9" s="2" t="s">
-        <v>222</v>
+        <v>228</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>223</v>
+        <v>229</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>207</v>
+        <v>213</v>
       </c>
       <c r="D9" s="2">
         <v>1.0</v>
@@ -8880,7 +9125,7 @@
         <v>50.0</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>208</v>
+        <v>214</v>
       </c>
       <c r="I9" s="2" t="s">
         <v>7</v>
@@ -8894,13 +9139,13 @@
     </row>
     <row r="10" ht="14.25" customHeight="1">
       <c r="A10" s="2" t="s">
-        <v>224</v>
+        <v>230</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>225</v>
+        <v>231</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>207</v>
+        <v>213</v>
       </c>
       <c r="D10" s="2">
         <v>1.0</v>
@@ -8915,7 +9160,7 @@
         <v>55.0</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>208</v>
+        <v>214</v>
       </c>
       <c r="I10" s="2" t="s">
         <v>10</v>
@@ -8929,13 +9174,13 @@
     </row>
     <row r="11" ht="14.25" customHeight="1">
       <c r="A11" s="2" t="s">
-        <v>226</v>
+        <v>232</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>227</v>
+        <v>233</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>207</v>
+        <v>213</v>
       </c>
       <c r="D11" s="2">
         <v>1.0</v>
@@ -8950,7 +9195,7 @@
         <v>60.0</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>208</v>
+        <v>214</v>
       </c>
       <c r="I11" s="2" t="s">
         <v>10</v>
@@ -8964,13 +9209,13 @@
     </row>
     <row r="12" ht="14.25" customHeight="1">
       <c r="A12" s="2" t="s">
-        <v>228</v>
+        <v>234</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>229</v>
+        <v>235</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>207</v>
+        <v>213</v>
       </c>
       <c r="D12" s="2">
         <v>1.0</v>
@@ -8985,7 +9230,7 @@
         <v>65.0</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>208</v>
+        <v>214</v>
       </c>
       <c r="I12" s="2" t="s">
         <v>10</v>
@@ -8999,13 +9244,13 @@
     </row>
     <row r="13" ht="14.25" customHeight="1">
       <c r="A13" s="2" t="s">
-        <v>230</v>
+        <v>236</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>231</v>
+        <v>237</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>207</v>
+        <v>213</v>
       </c>
       <c r="D13" s="2">
         <v>1.0</v>
@@ -9020,7 +9265,7 @@
         <v>70.0</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>208</v>
+        <v>214</v>
       </c>
       <c r="I13" s="2" t="s">
         <v>10</v>
@@ -9034,13 +9279,13 @@
     </row>
     <row r="14" ht="14.25" customHeight="1">
       <c r="A14" s="2" t="s">
-        <v>232</v>
+        <v>238</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>233</v>
+        <v>239</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>207</v>
+        <v>213</v>
       </c>
       <c r="D14" s="2">
         <v>1.0</v>
@@ -9055,7 +9300,7 @@
         <v>80.0</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>208</v>
+        <v>214</v>
       </c>
       <c r="I14" s="2" t="s">
         <v>10</v>
@@ -9069,13 +9314,13 @@
     </row>
     <row r="15" ht="14.25" customHeight="1">
       <c r="A15" s="2" t="s">
-        <v>234</v>
+        <v>240</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>235</v>
+        <v>241</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>207</v>
+        <v>213</v>
       </c>
       <c r="D15" s="2">
         <v>1.0</v>
@@ -9090,7 +9335,7 @@
         <v>90.0</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>208</v>
+        <v>214</v>
       </c>
       <c r="I15" s="2" t="s">
         <v>10</v>
@@ -9104,13 +9349,13 @@
     </row>
     <row r="16" ht="14.25" customHeight="1">
       <c r="A16" s="2" t="s">
-        <v>236</v>
+        <v>242</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>237</v>
+        <v>243</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>207</v>
+        <v>213</v>
       </c>
       <c r="D16" s="2">
         <v>1.0</v>
@@ -9125,7 +9370,7 @@
         <v>100.0</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>208</v>
+        <v>214</v>
       </c>
       <c r="I16" s="2" t="s">
         <v>10</v>
@@ -9139,13 +9384,13 @@
     </row>
     <row r="17" ht="14.25" customHeight="1">
       <c r="A17" s="2" t="s">
-        <v>238</v>
+        <v>244</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>239</v>
+        <v>245</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>207</v>
+        <v>213</v>
       </c>
       <c r="D17" s="2">
         <v>1.0</v>
@@ -9160,7 +9405,7 @@
         <v>110.0</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>208</v>
+        <v>214</v>
       </c>
       <c r="I17" s="2" t="s">
         <v>10</v>
@@ -9174,13 +9419,13 @@
     </row>
     <row r="18" ht="14.25" customHeight="1">
       <c r="A18" s="2" t="s">
-        <v>240</v>
+        <v>246</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>241</v>
+        <v>247</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>207</v>
+        <v>213</v>
       </c>
       <c r="D18" s="2">
         <v>0.0</v>
@@ -9195,7 +9440,7 @@
         <v>120.0</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>208</v>
+        <v>214</v>
       </c>
       <c r="I18" s="2" t="s">
         <v>10</v>
@@ -9209,13 +9454,13 @@
     </row>
     <row r="19" ht="14.25" customHeight="1">
       <c r="A19" s="2" t="s">
-        <v>242</v>
+        <v>248</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>243</v>
+        <v>249</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>207</v>
+        <v>213</v>
       </c>
       <c r="D19" s="2">
         <v>0.0</v>
@@ -9230,7 +9475,7 @@
         <v>130.0</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>208</v>
+        <v>214</v>
       </c>
       <c r="I19" s="2" t="s">
         <v>10</v>
@@ -9244,13 +9489,13 @@
     </row>
     <row r="20" ht="14.25" customHeight="1">
       <c r="A20" s="2" t="s">
-        <v>244</v>
+        <v>250</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>245</v>
+        <v>251</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>207</v>
+        <v>213</v>
       </c>
       <c r="D20" s="2">
         <v>1.0</v>
@@ -9265,7 +9510,7 @@
         <v>140.0</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>208</v>
+        <v>214</v>
       </c>
       <c r="I20" s="2" t="s">
         <v>7</v>
@@ -9279,13 +9524,13 @@
     </row>
     <row r="21" ht="14.25" customHeight="1">
       <c r="A21" s="2" t="s">
-        <v>246</v>
+        <v>252</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>247</v>
+        <v>253</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>207</v>
+        <v>213</v>
       </c>
       <c r="D21" s="2">
         <v>1.0</v>
@@ -9300,7 +9545,7 @@
         <v>150.0</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>208</v>
+        <v>214</v>
       </c>
       <c r="I21" s="2" t="s">
         <v>7</v>
@@ -9314,13 +9559,13 @@
     </row>
     <row r="22" ht="14.25" customHeight="1">
       <c r="A22" s="2" t="s">
-        <v>248</v>
+        <v>254</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>249</v>
+        <v>255</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>207</v>
+        <v>213</v>
       </c>
       <c r="D22" s="2">
         <v>1.0</v>
@@ -9335,7 +9580,7 @@
         <v>160.0</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>208</v>
+        <v>214</v>
       </c>
       <c r="I22" s="2" t="s">
         <v>7</v>
@@ -9349,13 +9594,13 @@
     </row>
     <row r="23" ht="14.25" customHeight="1">
       <c r="A23" s="2" t="s">
-        <v>250</v>
+        <v>256</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>251</v>
+        <v>257</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>207</v>
+        <v>213</v>
       </c>
       <c r="D23" s="2">
         <v>0.0</v>
@@ -9370,7 +9615,7 @@
         <v>170.0</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>208</v>
+        <v>214</v>
       </c>
       <c r="I23" s="2" t="s">
         <v>7</v>
@@ -9384,13 +9629,13 @@
     </row>
     <row r="24" ht="14.25" customHeight="1">
       <c r="A24" s="2" t="s">
-        <v>252</v>
+        <v>258</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>253</v>
+        <v>259</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>207</v>
+        <v>213</v>
       </c>
       <c r="D24" s="2">
         <v>0.0</v>
@@ -9405,7 +9650,7 @@
         <v>180.0</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>208</v>
+        <v>214</v>
       </c>
       <c r="I24" s="2" t="s">
         <v>7</v>
@@ -9419,13 +9664,13 @@
     </row>
     <row r="25" ht="14.25" customHeight="1">
       <c r="A25" s="3" t="s">
-        <v>254</v>
+        <v>260</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>255</v>
+        <v>261</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>207</v>
+        <v>213</v>
       </c>
       <c r="D25" s="2">
         <v>1.0</v>
@@ -9440,7 +9685,7 @@
         <v>190.0</v>
       </c>
       <c r="H25" s="3" t="s">
-        <v>208</v>
+        <v>214</v>
       </c>
       <c r="I25" s="2" t="s">
         <v>7</v>
@@ -9454,13 +9699,13 @@
     </row>
     <row r="26" ht="14.25" customHeight="1">
       <c r="A26" s="2" t="s">
-        <v>256</v>
+        <v>262</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>257</v>
+        <v>263</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>207</v>
+        <v>213</v>
       </c>
       <c r="D26" s="2">
         <v>0.0</v>
@@ -9475,7 +9720,7 @@
         <v>62.0</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>208</v>
+        <v>214</v>
       </c>
       <c r="I26" s="2" t="s">
         <v>10</v>
@@ -9487,7 +9732,41 @@
         <v>0.0</v>
       </c>
     </row>
-    <row r="27" ht="14.25" customHeight="1"/>
+    <row r="27" ht="14.25" customHeight="1">
+      <c r="A27" s="5" t="s">
+        <v>264</v>
+      </c>
+      <c r="B27" s="5" t="s">
+        <v>265</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="D27" s="5">
+        <v>1.0</v>
+      </c>
+      <c r="E27" s="5">
+        <v>0.0</v>
+      </c>
+      <c r="F27" s="5">
+        <v>1.0</v>
+      </c>
+      <c r="G27" s="5">
+        <v>200.0</v>
+      </c>
+      <c r="H27" s="5" t="s">
+        <v>214</v>
+      </c>
+      <c r="I27" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="J27" s="5">
+        <v>0.0</v>
+      </c>
+      <c r="K27" s="5">
+        <v>0.0</v>
+      </c>
+    </row>
     <row r="28" ht="14.25" customHeight="1"/>
     <row r="29" ht="14.25" customHeight="1"/>
     <row r="30" ht="14.25" customHeight="1"/>
@@ -10478,7 +10757,7 @@
   <sheetFormatPr customHeight="1" defaultColWidth="14.43" defaultRowHeight="15.0"/>
   <cols>
     <col customWidth="1" min="1" max="1" width="17.71"/>
-    <col customWidth="1" min="2" max="2" width="22.14"/>
+    <col customWidth="1" min="2" max="2" width="26.71"/>
     <col customWidth="1" min="3" max="3" width="28.86"/>
     <col customWidth="1" min="4" max="4" width="10.43"/>
     <col customWidth="1" min="5" max="5" width="9.29"/>
@@ -10489,7 +10768,7 @@
   <sheetData>
     <row r="1" ht="14.25" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>258</v>
+        <v>266</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>0</v>
@@ -10510,18 +10789,18 @@
         <v>4</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>259</v>
+        <v>267</v>
       </c>
     </row>
     <row r="2" ht="14.25" customHeight="1">
       <c r="A2" s="2" t="s">
-        <v>205</v>
+        <v>211</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>260</v>
+        <v>268</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>261</v>
+        <v>269</v>
       </c>
       <c r="D2" s="2">
         <v>0.0</v>
@@ -10536,18 +10815,18 @@
         <v>10.0</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>262</v>
+        <v>270</v>
       </c>
     </row>
     <row r="3" ht="14.25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>205</v>
+        <v>211</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>263</v>
+        <v>271</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>264</v>
+        <v>272</v>
       </c>
       <c r="D3" s="2">
         <v>0.0</v>
@@ -10562,18 +10841,18 @@
         <v>20.0</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>265</v>
+        <v>273</v>
       </c>
     </row>
     <row r="4" ht="14.25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>205</v>
+        <v>211</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>266</v>
+        <v>274</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>267</v>
+        <v>275</v>
       </c>
       <c r="D4" s="2">
         <v>0.0</v>
@@ -10588,18 +10867,18 @@
         <v>30.0</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>268</v>
+        <v>276</v>
       </c>
     </row>
     <row r="5" ht="14.25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>224</v>
+        <v>230</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>269</v>
+        <v>277</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>270</v>
+        <v>278</v>
       </c>
       <c r="D5" s="2">
         <v>0.0</v>
@@ -10614,18 +10893,18 @@
         <v>10.0</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>271</v>
+        <v>279</v>
       </c>
     </row>
     <row r="6" ht="14.25" customHeight="1">
       <c r="A6" s="2" t="s">
-        <v>224</v>
+        <v>230</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>272</v>
+        <v>280</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>273</v>
+        <v>281</v>
       </c>
       <c r="D6" s="2">
         <v>0.0</v>
@@ -10640,18 +10919,18 @@
         <v>20.0</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>274</v>
+        <v>282</v>
       </c>
     </row>
     <row r="7" ht="14.25" customHeight="1">
       <c r="A7" s="2" t="s">
-        <v>209</v>
+        <v>215</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>161</v>
+        <v>167</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>275</v>
+        <v>283</v>
       </c>
       <c r="D7" s="2">
         <v>0.0</v>
@@ -10666,18 +10945,18 @@
         <v>10.0</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>162</v>
+        <v>168</v>
       </c>
     </row>
     <row r="8" ht="14.25" customHeight="1">
       <c r="A8" s="2" t="s">
-        <v>209</v>
+        <v>215</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>157</v>
+        <v>163</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>276</v>
+        <v>284</v>
       </c>
       <c r="D8" s="2">
         <v>0.0</v>
@@ -10692,18 +10971,18 @@
         <v>20.0</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>277</v>
+        <v>285</v>
       </c>
     </row>
     <row r="9" ht="14.25" customHeight="1">
       <c r="A9" s="2" t="s">
-        <v>209</v>
+        <v>215</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>155</v>
+        <v>161</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>278</v>
+        <v>286</v>
       </c>
       <c r="D9" s="2">
         <v>0.0</v>
@@ -10718,18 +10997,18 @@
         <v>30.0</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>156</v>
+        <v>162</v>
       </c>
     </row>
     <row r="10" ht="14.25" customHeight="1">
       <c r="A10" s="2" t="s">
-        <v>209</v>
+        <v>215</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>279</v>
+        <v>287</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>280</v>
+        <v>288</v>
       </c>
       <c r="D10" s="2">
         <v>0.0</v>
@@ -10744,18 +11023,18 @@
         <v>40.0</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>281</v>
+        <v>289</v>
       </c>
     </row>
     <row r="11" ht="14.25" customHeight="1">
       <c r="A11" s="2" t="s">
-        <v>209</v>
+        <v>215</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>159</v>
+        <v>165</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>282</v>
+        <v>290</v>
       </c>
       <c r="D11" s="2">
         <v>0.0</v>
@@ -10770,18 +11049,18 @@
         <v>50.0</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>160</v>
+        <v>166</v>
       </c>
     </row>
     <row r="12" ht="14.25" customHeight="1">
       <c r="A12" s="2" t="s">
-        <v>212</v>
+        <v>218</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>283</v>
+        <v>291</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>284</v>
+        <v>292</v>
       </c>
       <c r="D12" s="2">
         <v>0.0</v>
@@ -10796,18 +11075,18 @@
         <v>10.0</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>285</v>
+        <v>293</v>
       </c>
     </row>
     <row r="13" ht="14.25" customHeight="1">
       <c r="A13" s="2" t="s">
-        <v>212</v>
+        <v>218</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>286</v>
+        <v>294</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>287</v>
+        <v>295</v>
       </c>
       <c r="D13" s="2">
         <v>0.0</v>
@@ -10822,18 +11101,18 @@
         <v>20.0</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>288</v>
+        <v>296</v>
       </c>
     </row>
     <row r="14" ht="14.25" customHeight="1">
       <c r="A14" s="2" t="s">
-        <v>212</v>
+        <v>218</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>289</v>
+        <v>297</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>290</v>
+        <v>298</v>
       </c>
       <c r="D14" s="2">
         <v>0.0</v>
@@ -10841,25 +11120,25 @@
       <c r="E14" s="2">
         <v>0.0</v>
       </c>
-      <c r="F14" s="2">
-        <v>0.0</v>
+      <c r="F14" s="4">
+        <v>1.0</v>
       </c>
       <c r="G14" s="2">
         <v>30.0</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>291</v>
+        <v>299</v>
       </c>
     </row>
     <row r="15" ht="14.25" customHeight="1">
       <c r="A15" s="2" t="s">
-        <v>214</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>292</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>293</v>
+        <v>218</v>
+      </c>
+      <c r="B15" s="4" t="s">
+        <v>300</v>
+      </c>
+      <c r="C15" s="4" t="s">
+        <v>301</v>
       </c>
       <c r="D15" s="2">
         <v>0.0</v>
@@ -10867,25 +11146,25 @@
       <c r="E15" s="2">
         <v>0.0</v>
       </c>
-      <c r="F15" s="2">
-        <v>1.0</v>
-      </c>
-      <c r="G15" s="2">
-        <v>10.0</v>
-      </c>
-      <c r="H15" s="2" t="s">
-        <v>294</v>
+      <c r="F15" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="G15" s="4">
+        <v>40.0</v>
+      </c>
+      <c r="H15" s="4" t="s">
+        <v>302</v>
       </c>
     </row>
     <row r="16" ht="14.25" customHeight="1">
       <c r="A16" s="2" t="s">
-        <v>214</v>
+        <v>220</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>295</v>
+        <v>303</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>296</v>
+        <v>304</v>
       </c>
       <c r="D16" s="2">
         <v>0.0</v>
@@ -10897,203 +11176,203 @@
         <v>1.0</v>
       </c>
       <c r="G16" s="2">
-        <v>20.0</v>
+        <v>10.0</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>297</v>
+        <v>305</v>
       </c>
     </row>
     <row r="17" ht="14.25" customHeight="1">
       <c r="A17" s="2" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>137</v>
+        <v>306</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>298</v>
+        <v>307</v>
       </c>
       <c r="D17" s="2">
-        <v>10.0</v>
+        <v>0.0</v>
       </c>
       <c r="E17" s="2">
-        <v>5.0</v>
+        <v>0.0</v>
       </c>
       <c r="F17" s="2">
         <v>1.0</v>
       </c>
       <c r="G17" s="2">
-        <v>10.0</v>
+        <v>20.0</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>138</v>
+        <v>308</v>
       </c>
     </row>
     <row r="18" ht="14.25" customHeight="1">
       <c r="A18" s="2" t="s">
-        <v>216</v>
+        <v>222</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>299</v>
+        <v>143</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>300</v>
+        <v>309</v>
       </c>
       <c r="D18" s="2">
         <v>10.0</v>
       </c>
       <c r="E18" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="F18" s="2">
+        <v>1.0</v>
+      </c>
+      <c r="G18" s="2">
         <v>10.0</v>
       </c>
-      <c r="F18" s="2">
-        <v>1.0</v>
-      </c>
-      <c r="G18" s="2">
-        <v>20.0</v>
-      </c>
       <c r="H18" s="2" t="s">
-        <v>301</v>
+        <v>144</v>
       </c>
     </row>
     <row r="19" ht="14.25" customHeight="1">
       <c r="A19" s="2" t="s">
-        <v>216</v>
+        <v>222</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>70</v>
+        <v>310</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>302</v>
+        <v>311</v>
       </c>
       <c r="D19" s="2">
-        <v>25.0</v>
+        <v>10.0</v>
       </c>
       <c r="E19" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="F19" s="2">
+        <v>1.0</v>
+      </c>
+      <c r="G19" s="2">
         <v>20.0</v>
       </c>
-      <c r="F19" s="2">
-        <v>1.0</v>
-      </c>
-      <c r="G19" s="2">
-        <v>30.0</v>
-      </c>
       <c r="H19" s="2" t="s">
-        <v>303</v>
+        <v>312</v>
       </c>
     </row>
     <row r="20" ht="14.25" customHeight="1">
       <c r="A20" s="2" t="s">
-        <v>216</v>
+        <v>222</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>304</v>
+        <v>313</v>
       </c>
       <c r="D20" s="2">
+        <v>25.0</v>
+      </c>
+      <c r="E20" s="2">
+        <v>20.0</v>
+      </c>
+      <c r="F20" s="2">
+        <v>1.0</v>
+      </c>
+      <c r="G20" s="2">
         <v>30.0</v>
       </c>
-      <c r="E20" s="2">
-        <v>25.0</v>
-      </c>
-      <c r="F20" s="2">
-        <v>1.0</v>
-      </c>
-      <c r="G20" s="2">
-        <v>40.0</v>
-      </c>
       <c r="H20" s="2" t="s">
-        <v>305</v>
+        <v>314</v>
       </c>
     </row>
     <row r="21" ht="14.25" customHeight="1">
       <c r="A21" s="2" t="s">
-        <v>216</v>
+        <v>222</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>306</v>
+        <v>315</v>
       </c>
       <c r="D21" s="2">
         <v>30.0</v>
       </c>
       <c r="E21" s="2">
-        <v>20.0</v>
+        <v>25.0</v>
       </c>
       <c r="F21" s="2">
         <v>1.0</v>
       </c>
       <c r="G21" s="2">
-        <v>50.0</v>
+        <v>40.0</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>307</v>
+        <v>316</v>
       </c>
     </row>
     <row r="22" ht="14.25" customHeight="1">
       <c r="A22" s="2" t="s">
-        <v>216</v>
+        <v>222</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>308</v>
+        <v>317</v>
       </c>
       <c r="D22" s="2">
-        <v>35.0</v>
+        <v>30.0</v>
       </c>
       <c r="E22" s="2">
-        <v>25.0</v>
+        <v>20.0</v>
       </c>
       <c r="F22" s="2">
         <v>1.0</v>
       </c>
       <c r="G22" s="2">
-        <v>60.0</v>
+        <v>50.0</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>309</v>
+        <v>318</v>
       </c>
     </row>
     <row r="23" ht="14.25" customHeight="1">
       <c r="A23" s="2" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>310</v>
+        <v>76</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>311</v>
+        <v>319</v>
       </c>
       <c r="D23" s="2">
-        <v>0.0</v>
+        <v>35.0</v>
       </c>
       <c r="E23" s="2">
-        <v>0.0</v>
+        <v>25.0</v>
       </c>
       <c r="F23" s="2">
         <v>1.0</v>
       </c>
       <c r="G23" s="2">
-        <v>10.0</v>
+        <v>60.0</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>312</v>
+        <v>320</v>
       </c>
     </row>
     <row r="24" ht="14.25" customHeight="1">
       <c r="A24" s="2" t="s">
-        <v>218</v>
+        <v>224</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>313</v>
+        <v>321</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>314</v>
+        <v>322</v>
       </c>
       <c r="D24" s="2">
         <v>0.0</v>
@@ -11105,21 +11384,21 @@
         <v>1.0</v>
       </c>
       <c r="G24" s="2">
-        <v>20.0</v>
+        <v>10.0</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>315</v>
+        <v>323</v>
       </c>
     </row>
     <row r="25" ht="14.25" customHeight="1">
       <c r="A25" s="2" t="s">
-        <v>218</v>
+        <v>224</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>316</v>
+        <v>324</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>317</v>
+        <v>325</v>
       </c>
       <c r="D25" s="2">
         <v>0.0</v>
@@ -11131,21 +11410,21 @@
         <v>1.0</v>
       </c>
       <c r="G25" s="2">
-        <v>30.0</v>
+        <v>20.0</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>318</v>
+        <v>326</v>
       </c>
     </row>
     <row r="26" ht="14.25" customHeight="1">
       <c r="A26" s="2" t="s">
-        <v>218</v>
+        <v>224</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>319</v>
+        <v>327</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>320</v>
+        <v>328</v>
       </c>
       <c r="D26" s="2">
         <v>0.0</v>
@@ -11157,21 +11436,21 @@
         <v>1.0</v>
       </c>
       <c r="G26" s="2">
-        <v>40.0</v>
+        <v>30.0</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>321</v>
+        <v>329</v>
       </c>
     </row>
     <row r="27" ht="14.25" customHeight="1">
       <c r="A27" s="2" t="s">
-        <v>218</v>
+        <v>224</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>322</v>
+        <v>330</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>323</v>
+        <v>331</v>
       </c>
       <c r="D27" s="2">
         <v>0.0</v>
@@ -11183,21 +11462,21 @@
         <v>1.0</v>
       </c>
       <c r="G27" s="2">
-        <v>50.0</v>
+        <v>40.0</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>324</v>
+        <v>332</v>
       </c>
     </row>
     <row r="28" ht="14.25" customHeight="1">
       <c r="A28" s="2" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>325</v>
+        <v>333</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>326</v>
+        <v>334</v>
       </c>
       <c r="D28" s="2">
         <v>0.0</v>
@@ -11209,21 +11488,21 @@
         <v>1.0</v>
       </c>
       <c r="G28" s="2">
-        <v>10.0</v>
+        <v>50.0</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>327</v>
+        <v>335</v>
       </c>
     </row>
     <row r="29" ht="14.25" customHeight="1">
       <c r="A29" s="2" t="s">
-        <v>220</v>
+        <v>226</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>328</v>
+        <v>336</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>329</v>
+        <v>337</v>
       </c>
       <c r="D29" s="2">
         <v>0.0</v>
@@ -11235,21 +11514,21 @@
         <v>1.0</v>
       </c>
       <c r="G29" s="2">
-        <v>20.0</v>
+        <v>10.0</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>330</v>
+        <v>338</v>
       </c>
     </row>
     <row r="30" ht="14.25" customHeight="1">
       <c r="A30" s="2" t="s">
-        <v>220</v>
+        <v>226</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>331</v>
+        <v>339</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>332</v>
+        <v>340</v>
       </c>
       <c r="D30" s="2">
         <v>0.0</v>
@@ -11261,21 +11540,21 @@
         <v>1.0</v>
       </c>
       <c r="G30" s="2">
-        <v>30.0</v>
+        <v>20.0</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>333</v>
+        <v>341</v>
       </c>
     </row>
     <row r="31" ht="14.25" customHeight="1">
       <c r="A31" s="2" t="s">
-        <v>220</v>
+        <v>226</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>334</v>
+        <v>342</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>335</v>
+        <v>343</v>
       </c>
       <c r="D31" s="2">
         <v>0.0</v>
@@ -11287,21 +11566,21 @@
         <v>1.0</v>
       </c>
       <c r="G31" s="2">
-        <v>40.0</v>
+        <v>30.0</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>336</v>
+        <v>344</v>
       </c>
     </row>
     <row r="32" ht="14.25" customHeight="1">
       <c r="A32" s="2" t="s">
-        <v>220</v>
+        <v>226</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>337</v>
+        <v>345</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>338</v>
+        <v>346</v>
       </c>
       <c r="D32" s="2">
         <v>0.0</v>
@@ -11313,21 +11592,21 @@
         <v>1.0</v>
       </c>
       <c r="G32" s="2">
-        <v>50.0</v>
+        <v>40.0</v>
       </c>
       <c r="H32" s="2" t="s">
-        <v>339</v>
+        <v>347</v>
       </c>
     </row>
     <row r="33" ht="14.25" customHeight="1">
       <c r="A33" s="2" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>340</v>
+        <v>348</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>341</v>
+        <v>349</v>
       </c>
       <c r="D33" s="2">
         <v>0.0</v>
@@ -11339,73 +11618,73 @@
         <v>1.0</v>
       </c>
       <c r="G33" s="2">
-        <v>10.0</v>
+        <v>50.0</v>
       </c>
       <c r="H33" s="2" t="s">
-        <v>342</v>
+        <v>350</v>
       </c>
     </row>
     <row r="34" ht="14.25" customHeight="1">
       <c r="A34" s="2" t="s">
-        <v>222</v>
+        <v>228</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>343</v>
+        <v>351</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>344</v>
+        <v>352</v>
       </c>
       <c r="D34" s="2">
-        <v>5.0</v>
+        <v>0.0</v>
       </c>
       <c r="E34" s="2">
-        <v>5.0</v>
+        <v>0.0</v>
       </c>
       <c r="F34" s="2">
         <v>1.0</v>
       </c>
       <c r="G34" s="2">
-        <v>20.0</v>
+        <v>10.0</v>
       </c>
       <c r="H34" s="2" t="s">
-        <v>345</v>
+        <v>353</v>
       </c>
     </row>
     <row r="35" ht="14.25" customHeight="1">
       <c r="A35" s="2" t="s">
-        <v>222</v>
+        <v>228</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>346</v>
+        <v>354</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>347</v>
+        <v>355</v>
       </c>
       <c r="D35" s="2">
-        <v>10.0</v>
+        <v>5.0</v>
       </c>
       <c r="E35" s="2">
-        <v>10.0</v>
+        <v>5.0</v>
       </c>
       <c r="F35" s="2">
         <v>1.0</v>
       </c>
       <c r="G35" s="2">
-        <v>30.0</v>
+        <v>20.0</v>
       </c>
       <c r="H35" s="2" t="s">
-        <v>348</v>
+        <v>356</v>
       </c>
     </row>
     <row r="36" ht="14.25" customHeight="1">
       <c r="A36" s="2" t="s">
-        <v>222</v>
+        <v>228</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>349</v>
+        <v>357</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>350</v>
+        <v>358</v>
       </c>
       <c r="D36" s="2">
         <v>10.0</v>
@@ -11417,73 +11696,73 @@
         <v>1.0</v>
       </c>
       <c r="G36" s="2">
-        <v>40.0</v>
+        <v>30.0</v>
       </c>
       <c r="H36" s="2" t="s">
-        <v>351</v>
+        <v>359</v>
       </c>
     </row>
     <row r="37" ht="14.25" customHeight="1">
       <c r="A37" s="2" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>352</v>
+        <v>360</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>353</v>
+        <v>361</v>
       </c>
       <c r="D37" s="2">
-        <v>0.0</v>
+        <v>10.0</v>
       </c>
       <c r="E37" s="2">
-        <v>0.0</v>
+        <v>10.0</v>
       </c>
       <c r="F37" s="2">
         <v>1.0</v>
       </c>
       <c r="G37" s="2">
-        <v>10.0</v>
+        <v>40.0</v>
       </c>
       <c r="H37" s="2" t="s">
-        <v>354</v>
+        <v>362</v>
       </c>
     </row>
     <row r="38" ht="14.25" customHeight="1">
       <c r="A38" s="2" t="s">
-        <v>226</v>
+        <v>232</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>355</v>
+        <v>363</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="D38" s="2">
-        <v>5.0</v>
+        <v>0.0</v>
       </c>
       <c r="E38" s="2">
-        <v>5.0</v>
+        <v>0.0</v>
       </c>
       <c r="F38" s="2">
         <v>1.0</v>
       </c>
       <c r="G38" s="2">
-        <v>20.0</v>
+        <v>10.0</v>
       </c>
       <c r="H38" s="2" t="s">
-        <v>357</v>
+        <v>365</v>
       </c>
     </row>
     <row r="39" ht="14.25" customHeight="1">
       <c r="A39" s="2" t="s">
-        <v>226</v>
+        <v>232</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>358</v>
+        <v>366</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>359</v>
+        <v>367</v>
       </c>
       <c r="D39" s="2">
         <v>5.0</v>
@@ -11495,21 +11774,21 @@
         <v>1.0</v>
       </c>
       <c r="G39" s="2">
-        <v>30.0</v>
+        <v>20.0</v>
       </c>
       <c r="H39" s="2" t="s">
-        <v>360</v>
+        <v>368</v>
       </c>
     </row>
     <row r="40" ht="14.25" customHeight="1">
       <c r="A40" s="2" t="s">
-        <v>226</v>
+        <v>232</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>361</v>
+        <v>369</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>362</v>
+        <v>370</v>
       </c>
       <c r="D40" s="2">
         <v>5.0</v>
@@ -11521,21 +11800,21 @@
         <v>1.0</v>
       </c>
       <c r="G40" s="2">
-        <v>40.0</v>
+        <v>30.0</v>
       </c>
       <c r="H40" s="2" t="s">
-        <v>363</v>
+        <v>371</v>
       </c>
     </row>
     <row r="41" ht="14.25" customHeight="1">
       <c r="A41" s="2" t="s">
-        <v>226</v>
+        <v>232</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>364</v>
+        <v>372</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>365</v>
+        <v>373</v>
       </c>
       <c r="D41" s="2">
         <v>5.0</v>
@@ -11547,47 +11826,47 @@
         <v>1.0</v>
       </c>
       <c r="G41" s="2">
-        <v>50.0</v>
+        <v>40.0</v>
       </c>
       <c r="H41" s="2" t="s">
-        <v>366</v>
+        <v>374</v>
       </c>
     </row>
     <row r="42" ht="14.25" customHeight="1">
       <c r="A42" s="2" t="s">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>367</v>
+        <v>375</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>368</v>
+        <v>376</v>
       </c>
       <c r="D42" s="2">
-        <v>0.0</v>
+        <v>5.0</v>
       </c>
       <c r="E42" s="2">
-        <v>0.0</v>
+        <v>5.0</v>
       </c>
       <c r="F42" s="2">
         <v>1.0</v>
       </c>
       <c r="G42" s="2">
-        <v>10.0</v>
+        <v>50.0</v>
       </c>
       <c r="H42" s="2" t="s">
-        <v>369</v>
+        <v>377</v>
       </c>
     </row>
     <row r="43" ht="14.25" customHeight="1">
       <c r="A43" s="2" t="s">
-        <v>228</v>
+        <v>234</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>370</v>
+        <v>378</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>371</v>
+        <v>379</v>
       </c>
       <c r="D43" s="2">
         <v>0.0</v>
@@ -11599,21 +11878,21 @@
         <v>1.0</v>
       </c>
       <c r="G43" s="2">
-        <v>20.0</v>
+        <v>10.0</v>
       </c>
       <c r="H43" s="2" t="s">
-        <v>372</v>
+        <v>380</v>
       </c>
     </row>
     <row r="44" ht="14.25" customHeight="1">
       <c r="A44" s="2" t="s">
-        <v>228</v>
+        <v>234</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>373</v>
+        <v>381</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>374</v>
+        <v>382</v>
       </c>
       <c r="D44" s="2">
         <v>0.0</v>
@@ -11625,21 +11904,21 @@
         <v>1.0</v>
       </c>
       <c r="G44" s="2">
-        <v>30.0</v>
+        <v>20.0</v>
       </c>
       <c r="H44" s="2" t="s">
-        <v>375</v>
+        <v>383</v>
       </c>
     </row>
     <row r="45" ht="14.25" customHeight="1">
       <c r="A45" s="2" t="s">
-        <v>228</v>
+        <v>234</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>376</v>
+        <v>384</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>377</v>
+        <v>385</v>
       </c>
       <c r="D45" s="2">
         <v>0.0</v>
@@ -11651,21 +11930,21 @@
         <v>1.0</v>
       </c>
       <c r="G45" s="2">
-        <v>40.0</v>
+        <v>30.0</v>
       </c>
       <c r="H45" s="2" t="s">
-        <v>378</v>
+        <v>386</v>
       </c>
     </row>
     <row r="46" ht="14.25" customHeight="1">
       <c r="A46" s="2" t="s">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>379</v>
+        <v>387</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>380</v>
+        <v>388</v>
       </c>
       <c r="D46" s="2">
         <v>0.0</v>
@@ -11677,21 +11956,21 @@
         <v>1.0</v>
       </c>
       <c r="G46" s="2">
-        <v>10.0</v>
+        <v>40.0</v>
       </c>
       <c r="H46" s="2" t="s">
-        <v>381</v>
+        <v>389</v>
       </c>
     </row>
     <row r="47" ht="14.25" customHeight="1">
       <c r="A47" s="2" t="s">
-        <v>230</v>
+        <v>236</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>382</v>
+        <v>390</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>383</v>
+        <v>391</v>
       </c>
       <c r="D47" s="2">
         <v>0.0</v>
@@ -11703,21 +11982,21 @@
         <v>1.0</v>
       </c>
       <c r="G47" s="2">
-        <v>20.0</v>
+        <v>10.0</v>
       </c>
       <c r="H47" s="2" t="s">
-        <v>384</v>
+        <v>392</v>
       </c>
     </row>
     <row r="48" ht="14.25" customHeight="1">
       <c r="A48" s="2" t="s">
-        <v>230</v>
+        <v>236</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>385</v>
+        <v>393</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>386</v>
+        <v>394</v>
       </c>
       <c r="D48" s="2">
         <v>0.0</v>
@@ -11729,21 +12008,21 @@
         <v>1.0</v>
       </c>
       <c r="G48" s="2">
-        <v>30.0</v>
+        <v>20.0</v>
       </c>
       <c r="H48" s="2" t="s">
-        <v>387</v>
+        <v>395</v>
       </c>
     </row>
     <row r="49" ht="14.25" customHeight="1">
       <c r="A49" s="2" t="s">
-        <v>230</v>
+        <v>236</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>388</v>
+        <v>396</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>389</v>
+        <v>397</v>
       </c>
       <c r="D49" s="2">
         <v>0.0</v>
@@ -11755,21 +12034,21 @@
         <v>1.0</v>
       </c>
       <c r="G49" s="2">
-        <v>40.0</v>
+        <v>30.0</v>
       </c>
       <c r="H49" s="2" t="s">
-        <v>390</v>
+        <v>398</v>
       </c>
     </row>
     <row r="50" ht="14.25" customHeight="1">
       <c r="A50" s="2" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>391</v>
+        <v>399</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>392</v>
+        <v>400</v>
       </c>
       <c r="D50" s="2">
         <v>0.0</v>
@@ -11781,21 +12060,21 @@
         <v>1.0</v>
       </c>
       <c r="G50" s="2">
-        <v>10.0</v>
+        <v>40.0</v>
       </c>
       <c r="H50" s="2" t="s">
-        <v>393</v>
+        <v>401</v>
       </c>
     </row>
     <row r="51" ht="14.25" customHeight="1">
       <c r="A51" s="2" t="s">
-        <v>232</v>
+        <v>238</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>394</v>
+        <v>402</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>395</v>
+        <v>403</v>
       </c>
       <c r="D51" s="2">
         <v>0.0</v>
@@ -11807,21 +12086,21 @@
         <v>1.0</v>
       </c>
       <c r="G51" s="2">
-        <v>20.0</v>
+        <v>10.0</v>
       </c>
       <c r="H51" s="2" t="s">
-        <v>396</v>
+        <v>404</v>
       </c>
     </row>
     <row r="52" ht="14.25" customHeight="1">
       <c r="A52" s="2" t="s">
-        <v>232</v>
+        <v>238</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>397</v>
+        <v>405</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>398</v>
+        <v>406</v>
       </c>
       <c r="D52" s="2">
         <v>0.0</v>
@@ -11833,21 +12112,21 @@
         <v>1.0</v>
       </c>
       <c r="G52" s="2">
-        <v>10.0</v>
+        <v>20.0</v>
       </c>
       <c r="H52" s="2" t="s">
-        <v>399</v>
+        <v>407</v>
       </c>
     </row>
     <row r="53" ht="14.25" customHeight="1">
       <c r="A53" s="2" t="s">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>400</v>
+        <v>408</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>401</v>
+        <v>409</v>
       </c>
       <c r="D53" s="2">
         <v>0.0</v>
@@ -11859,21 +12138,21 @@
         <v>1.0</v>
       </c>
       <c r="G53" s="2">
-        <v>20.0</v>
+        <v>10.0</v>
       </c>
       <c r="H53" s="2" t="s">
-        <v>402</v>
+        <v>410</v>
       </c>
     </row>
     <row r="54" ht="14.25" customHeight="1">
       <c r="A54" s="2" t="s">
-        <v>234</v>
+        <v>240</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>403</v>
+        <v>411</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>404</v>
+        <v>412</v>
       </c>
       <c r="D54" s="2">
         <v>0.0</v>
@@ -11885,21 +12164,21 @@
         <v>1.0</v>
       </c>
       <c r="G54" s="2">
-        <v>30.0</v>
+        <v>20.0</v>
       </c>
       <c r="H54" s="2" t="s">
-        <v>405</v>
+        <v>413</v>
       </c>
     </row>
     <row r="55" ht="14.25" customHeight="1">
       <c r="A55" s="2" t="s">
-        <v>234</v>
+        <v>240</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>406</v>
+        <v>414</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>407</v>
+        <v>415</v>
       </c>
       <c r="D55" s="2">
         <v>0.0</v>
@@ -11911,21 +12190,21 @@
         <v>1.0</v>
       </c>
       <c r="G55" s="2">
-        <v>40.0</v>
+        <v>30.0</v>
       </c>
       <c r="H55" s="2" t="s">
-        <v>408</v>
+        <v>416</v>
       </c>
     </row>
     <row r="56" ht="14.25" customHeight="1">
       <c r="A56" s="2" t="s">
-        <v>234</v>
+        <v>240</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>409</v>
+        <v>417</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>410</v>
+        <v>418</v>
       </c>
       <c r="D56" s="2">
         <v>0.0</v>
@@ -11937,21 +12216,21 @@
         <v>1.0</v>
       </c>
       <c r="G56" s="2">
-        <v>50.0</v>
+        <v>40.0</v>
       </c>
       <c r="H56" s="2" t="s">
-        <v>411</v>
+        <v>419</v>
       </c>
     </row>
     <row r="57" ht="14.25" customHeight="1">
       <c r="A57" s="2" t="s">
-        <v>234</v>
+        <v>240</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>412</v>
+        <v>420</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>413</v>
+        <v>421</v>
       </c>
       <c r="D57" s="2">
         <v>0.0</v>
@@ -11963,21 +12242,21 @@
         <v>1.0</v>
       </c>
       <c r="G57" s="2">
-        <v>60.0</v>
+        <v>50.0</v>
       </c>
       <c r="H57" s="2" t="s">
-        <v>414</v>
+        <v>422</v>
       </c>
     </row>
     <row r="58" ht="14.25" customHeight="1">
       <c r="A58" s="2" t="s">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>415</v>
+        <v>423</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>416</v>
+        <v>424</v>
       </c>
       <c r="D58" s="2">
         <v>0.0</v>
@@ -11989,21 +12268,21 @@
         <v>1.0</v>
       </c>
       <c r="G58" s="2">
-        <v>10.0</v>
+        <v>60.0</v>
       </c>
       <c r="H58" s="2" t="s">
-        <v>417</v>
+        <v>425</v>
       </c>
     </row>
     <row r="59" ht="14.25" customHeight="1">
       <c r="A59" s="2" t="s">
-        <v>236</v>
-      </c>
-      <c r="B59" s="2" t="s">
-        <v>418</v>
-      </c>
-      <c r="C59" s="2" t="s">
-        <v>419</v>
+        <v>240</v>
+      </c>
+      <c r="B59" s="4" t="s">
+        <v>426</v>
+      </c>
+      <c r="C59" s="4" t="s">
+        <v>427</v>
       </c>
       <c r="D59" s="2">
         <v>0.0</v>
@@ -12014,22 +12293,22 @@
       <c r="F59" s="2">
         <v>1.0</v>
       </c>
-      <c r="G59" s="2">
-        <v>20.0</v>
-      </c>
-      <c r="H59" s="2" t="s">
-        <v>420</v>
+      <c r="G59" s="4">
+        <v>70.0</v>
+      </c>
+      <c r="H59" s="4" t="s">
+        <v>428</v>
       </c>
     </row>
     <row r="60" ht="14.25" customHeight="1">
       <c r="A60" s="2" t="s">
-        <v>238</v>
+        <v>242</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>421</v>
+        <v>429</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>422</v>
+        <v>430</v>
       </c>
       <c r="D60" s="2">
         <v>0.0</v>
@@ -12044,18 +12323,18 @@
         <v>10.0</v>
       </c>
       <c r="H60" s="2" t="s">
-        <v>422</v>
+        <v>431</v>
       </c>
     </row>
     <row r="61" ht="14.25" customHeight="1">
       <c r="A61" s="2" t="s">
-        <v>238</v>
+        <v>242</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>423</v>
+        <v>432</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>424</v>
+        <v>433</v>
       </c>
       <c r="D61" s="2">
         <v>0.0</v>
@@ -12070,18 +12349,18 @@
         <v>20.0</v>
       </c>
       <c r="H61" s="2" t="s">
-        <v>424</v>
+        <v>434</v>
       </c>
     </row>
     <row r="62" ht="14.25" customHeight="1">
       <c r="A62" s="2" t="s">
-        <v>238</v>
+        <v>244</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>425</v>
+        <v>435</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>426</v>
+        <v>436</v>
       </c>
       <c r="D62" s="2">
         <v>0.0</v>
@@ -12093,21 +12372,21 @@
         <v>1.0</v>
       </c>
       <c r="G62" s="2">
-        <v>30.0</v>
+        <v>10.0</v>
       </c>
       <c r="H62" s="2" t="s">
-        <v>426</v>
+        <v>436</v>
       </c>
     </row>
     <row r="63" ht="14.25" customHeight="1">
       <c r="A63" s="2" t="s">
-        <v>238</v>
+        <v>244</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>427</v>
+        <v>437</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>428</v>
+        <v>438</v>
       </c>
       <c r="D63" s="2">
         <v>0.0</v>
@@ -12119,21 +12398,21 @@
         <v>1.0</v>
       </c>
       <c r="G63" s="2">
-        <v>40.0</v>
+        <v>20.0</v>
       </c>
       <c r="H63" s="2" t="s">
-        <v>428</v>
+        <v>438</v>
       </c>
     </row>
     <row r="64" ht="14.25" customHeight="1">
       <c r="A64" s="2" t="s">
-        <v>238</v>
+        <v>244</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>429</v>
+        <v>439</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>430</v>
+        <v>440</v>
       </c>
       <c r="D64" s="2">
         <v>0.0</v>
@@ -12145,21 +12424,21 @@
         <v>1.0</v>
       </c>
       <c r="G64" s="2">
-        <v>50.0</v>
+        <v>30.0</v>
       </c>
       <c r="H64" s="2" t="s">
-        <v>430</v>
+        <v>440</v>
       </c>
     </row>
     <row r="65" ht="14.25" customHeight="1">
       <c r="A65" s="2" t="s">
-        <v>238</v>
+        <v>244</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>431</v>
+        <v>441</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>432</v>
+        <v>442</v>
       </c>
       <c r="D65" s="2">
         <v>0.0</v>
@@ -12171,21 +12450,21 @@
         <v>1.0</v>
       </c>
       <c r="G65" s="2">
-        <v>60.0</v>
+        <v>40.0</v>
       </c>
       <c r="H65" s="2" t="s">
-        <v>432</v>
+        <v>442</v>
       </c>
     </row>
     <row r="66" ht="14.25" customHeight="1">
       <c r="A66" s="2" t="s">
-        <v>238</v>
+        <v>244</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>433</v>
+        <v>443</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>434</v>
+        <v>444</v>
       </c>
       <c r="D66" s="2">
         <v>0.0</v>
@@ -12197,21 +12476,21 @@
         <v>1.0</v>
       </c>
       <c r="G66" s="2">
-        <v>70.0</v>
+        <v>50.0</v>
       </c>
       <c r="H66" s="2" t="s">
-        <v>434</v>
+        <v>444</v>
       </c>
     </row>
     <row r="67" ht="14.25" customHeight="1">
       <c r="A67" s="2" t="s">
-        <v>238</v>
+        <v>244</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>435</v>
+        <v>445</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>436</v>
+        <v>446</v>
       </c>
       <c r="D67" s="2">
         <v>0.0</v>
@@ -12223,21 +12502,21 @@
         <v>1.0</v>
       </c>
       <c r="G67" s="2">
-        <v>80.0</v>
+        <v>60.0</v>
       </c>
       <c r="H67" s="2" t="s">
-        <v>436</v>
+        <v>446</v>
       </c>
     </row>
     <row r="68" ht="14.25" customHeight="1">
       <c r="A68" s="2" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>437</v>
+        <v>447</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>438</v>
+        <v>448</v>
       </c>
       <c r="D68" s="2">
         <v>0.0</v>
@@ -12249,21 +12528,21 @@
         <v>1.0</v>
       </c>
       <c r="G68" s="2">
-        <v>10.0</v>
+        <v>70.0</v>
       </c>
       <c r="H68" s="2" t="s">
-        <v>438</v>
+        <v>448</v>
       </c>
     </row>
     <row r="69" ht="14.25" customHeight="1">
       <c r="A69" s="2" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>439</v>
+        <v>449</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>440</v>
+        <v>450</v>
       </c>
       <c r="D69" s="2">
         <v>0.0</v>
@@ -12275,21 +12554,21 @@
         <v>1.0</v>
       </c>
       <c r="G69" s="2">
-        <v>20.0</v>
+        <v>80.0</v>
       </c>
       <c r="H69" s="2" t="s">
-        <v>440</v>
+        <v>450</v>
       </c>
     </row>
     <row r="70" ht="14.25" customHeight="1">
       <c r="A70" s="2" t="s">
-        <v>240</v>
+        <v>246</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>441</v>
+        <v>451</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>442</v>
+        <v>452</v>
       </c>
       <c r="D70" s="2">
         <v>0.0</v>
@@ -12301,21 +12580,21 @@
         <v>1.0</v>
       </c>
       <c r="G70" s="2">
-        <v>30.0</v>
+        <v>10.0</v>
       </c>
       <c r="H70" s="2" t="s">
-        <v>442</v>
+        <v>452</v>
       </c>
     </row>
     <row r="71" ht="14.25" customHeight="1">
       <c r="A71" s="2" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>242</v>
+        <v>453</v>
       </c>
       <c r="C71" s="2" t="s">
-        <v>243</v>
+        <v>454</v>
       </c>
       <c r="D71" s="2">
         <v>0.0</v>
@@ -12327,255 +12606,255 @@
         <v>1.0</v>
       </c>
       <c r="G71" s="2">
-        <v>10.0</v>
+        <v>20.0</v>
       </c>
       <c r="H71" s="2" t="s">
-        <v>243</v>
+        <v>454</v>
       </c>
     </row>
     <row r="72" ht="14.25" customHeight="1">
       <c r="A72" s="2" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>80</v>
+        <v>455</v>
       </c>
       <c r="C72" s="2" t="s">
-        <v>443</v>
+        <v>456</v>
       </c>
       <c r="D72" s="2">
-        <v>35.0</v>
+        <v>0.0</v>
       </c>
       <c r="E72" s="2">
-        <v>16.0</v>
+        <v>0.0</v>
       </c>
       <c r="F72" s="2">
         <v>1.0</v>
       </c>
       <c r="G72" s="2">
-        <v>10.0</v>
+        <v>30.0</v>
       </c>
       <c r="H72" s="2" t="s">
-        <v>444</v>
+        <v>456</v>
       </c>
     </row>
     <row r="73" ht="14.25" customHeight="1">
       <c r="A73" s="2" t="s">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>189</v>
+        <v>248</v>
       </c>
       <c r="C73" s="2" t="s">
-        <v>445</v>
+        <v>249</v>
       </c>
       <c r="D73" s="2">
-        <v>35.0</v>
+        <v>0.0</v>
       </c>
       <c r="E73" s="2">
-        <v>17.0</v>
+        <v>0.0</v>
       </c>
       <c r="F73" s="2">
         <v>1.0</v>
       </c>
       <c r="G73" s="2">
-        <v>20.0</v>
+        <v>10.0</v>
       </c>
       <c r="H73" s="2" t="s">
-        <v>446</v>
+        <v>249</v>
       </c>
     </row>
     <row r="74" ht="14.25" customHeight="1">
       <c r="A74" s="2" t="s">
-        <v>244</v>
+        <v>250</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>185</v>
+        <v>80</v>
       </c>
       <c r="C74" s="2" t="s">
-        <v>447</v>
+        <v>457</v>
       </c>
       <c r="D74" s="2">
         <v>35.0</v>
       </c>
       <c r="E74" s="2">
-        <v>18.0</v>
+        <v>16.0</v>
       </c>
       <c r="F74" s="2">
         <v>1.0</v>
       </c>
       <c r="G74" s="2">
-        <v>30.0</v>
+        <v>10.0</v>
       </c>
       <c r="H74" s="2" t="s">
-        <v>448</v>
+        <v>458</v>
       </c>
     </row>
     <row r="75" ht="14.25" customHeight="1">
       <c r="A75" s="2" t="s">
-        <v>244</v>
+        <v>250</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="C75" s="2" t="s">
-        <v>449</v>
+        <v>459</v>
       </c>
       <c r="D75" s="2">
         <v>35.0</v>
       </c>
       <c r="E75" s="2">
-        <v>18.0</v>
+        <v>17.0</v>
       </c>
       <c r="F75" s="2">
         <v>1.0</v>
       </c>
       <c r="G75" s="2">
-        <v>40.0</v>
+        <v>20.0</v>
       </c>
       <c r="H75" s="2" t="s">
-        <v>450</v>
+        <v>460</v>
       </c>
     </row>
     <row r="76" ht="14.25" customHeight="1">
       <c r="A76" s="2" t="s">
-        <v>244</v>
+        <v>250</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="C76" s="2" t="s">
-        <v>451</v>
+        <v>461</v>
       </c>
       <c r="D76" s="2">
         <v>35.0</v>
       </c>
       <c r="E76" s="2">
-        <v>14.0</v>
+        <v>18.0</v>
       </c>
       <c r="F76" s="2">
         <v>1.0</v>
       </c>
       <c r="G76" s="2">
-        <v>50.0</v>
+        <v>30.0</v>
       </c>
       <c r="H76" s="2" t="s">
-        <v>452</v>
+        <v>462</v>
       </c>
     </row>
     <row r="77" ht="14.25" customHeight="1">
       <c r="A77" s="2" t="s">
-        <v>244</v>
+        <v>250</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>187</v>
+        <v>198</v>
       </c>
       <c r="C77" s="2" t="s">
-        <v>453</v>
+        <v>463</v>
       </c>
       <c r="D77" s="2">
-        <v>55.0</v>
+        <v>35.0</v>
       </c>
       <c r="E77" s="2">
-        <v>27.0</v>
+        <v>18.0</v>
       </c>
       <c r="F77" s="2">
         <v>1.0</v>
       </c>
       <c r="G77" s="2">
-        <v>60.0</v>
+        <v>40.0</v>
       </c>
       <c r="H77" s="2" t="s">
-        <v>454</v>
+        <v>464</v>
       </c>
     </row>
     <row r="78" ht="14.25" customHeight="1">
       <c r="A78" s="2" t="s">
-        <v>244</v>
+        <v>250</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>455</v>
+        <v>200</v>
       </c>
       <c r="C78" s="2" t="s">
-        <v>456</v>
+        <v>465</v>
       </c>
       <c r="D78" s="2">
-        <v>40.0</v>
+        <v>35.0</v>
       </c>
       <c r="E78" s="2">
-        <v>18.0</v>
+        <v>14.0</v>
       </c>
       <c r="F78" s="2">
         <v>1.0</v>
       </c>
       <c r="G78" s="2">
-        <v>70.0</v>
+        <v>50.0</v>
       </c>
       <c r="H78" s="2" t="s">
-        <v>457</v>
+        <v>466</v>
       </c>
     </row>
     <row r="79" ht="14.25" customHeight="1">
       <c r="A79" s="2" t="s">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>458</v>
+        <v>193</v>
       </c>
       <c r="C79" s="2" t="s">
-        <v>459</v>
+        <v>467</v>
       </c>
       <c r="D79" s="2">
-        <v>0.0</v>
+        <v>55.0</v>
       </c>
       <c r="E79" s="2">
-        <v>0.0</v>
+        <v>27.0</v>
       </c>
       <c r="F79" s="2">
         <v>1.0</v>
       </c>
       <c r="G79" s="2">
-        <v>10.0</v>
+        <v>60.0</v>
       </c>
       <c r="H79" s="2" t="s">
-        <v>460</v>
+        <v>468</v>
       </c>
     </row>
     <row r="80" ht="14.25" customHeight="1">
       <c r="A80" s="2" t="s">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>461</v>
+        <v>469</v>
       </c>
       <c r="C80" s="2" t="s">
-        <v>462</v>
+        <v>470</v>
       </c>
       <c r="D80" s="2">
-        <v>5.0</v>
+        <v>40.0</v>
       </c>
       <c r="E80" s="2">
-        <v>5.0</v>
+        <v>18.0</v>
       </c>
       <c r="F80" s="2">
         <v>1.0</v>
       </c>
       <c r="G80" s="2">
-        <v>20.0</v>
+        <v>70.0</v>
       </c>
       <c r="H80" s="2" t="s">
-        <v>463</v>
+        <v>471</v>
       </c>
     </row>
     <row r="81" ht="14.25" customHeight="1">
       <c r="A81" s="2" t="s">
-        <v>248</v>
+        <v>252</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>464</v>
+        <v>472</v>
       </c>
       <c r="C81" s="2" t="s">
-        <v>465</v>
+        <v>473</v>
       </c>
       <c r="D81" s="2">
         <v>0.0</v>
@@ -12590,24 +12869,24 @@
         <v>10.0</v>
       </c>
       <c r="H81" s="2" t="s">
-        <v>465</v>
+        <v>474</v>
       </c>
     </row>
     <row r="82" ht="14.25" customHeight="1">
       <c r="A82" s="2" t="s">
-        <v>248</v>
+        <v>252</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>466</v>
+        <v>475</v>
       </c>
       <c r="C82" s="2" t="s">
-        <v>467</v>
+        <v>476</v>
       </c>
       <c r="D82" s="2">
-        <v>0.0</v>
+        <v>5.0</v>
       </c>
       <c r="E82" s="2">
-        <v>0.0</v>
+        <v>5.0</v>
       </c>
       <c r="F82" s="2">
         <v>1.0</v>
@@ -12616,18 +12895,18 @@
         <v>20.0</v>
       </c>
       <c r="H82" s="2" t="s">
-        <v>467</v>
+        <v>477</v>
       </c>
     </row>
     <row r="83" ht="14.25" customHeight="1">
       <c r="A83" s="2" t="s">
-        <v>248</v>
+        <v>254</v>
       </c>
       <c r="B83" s="2" t="s">
-        <v>468</v>
+        <v>478</v>
       </c>
       <c r="C83" s="2" t="s">
-        <v>469</v>
+        <v>479</v>
       </c>
       <c r="D83" s="2">
         <v>0.0</v>
@@ -12639,73 +12918,73 @@
         <v>1.0</v>
       </c>
       <c r="G83" s="2">
-        <v>30.0</v>
+        <v>10.0</v>
       </c>
       <c r="H83" s="2" t="s">
-        <v>469</v>
+        <v>479</v>
       </c>
     </row>
     <row r="84" ht="14.25" customHeight="1">
       <c r="A84" s="2" t="s">
-        <v>248</v>
-      </c>
-      <c r="B84" s="4" t="s">
-        <v>470</v>
-      </c>
-      <c r="C84" s="4" t="s">
-        <v>471</v>
-      </c>
-      <c r="D84" s="4">
-        <v>0.0</v>
-      </c>
-      <c r="E84" s="4">
-        <v>0.0</v>
-      </c>
-      <c r="F84" s="4">
-        <v>1.0</v>
-      </c>
-      <c r="G84" s="4">
-        <v>40.0</v>
-      </c>
-      <c r="H84" s="4" t="s">
-        <v>471</v>
+        <v>254</v>
+      </c>
+      <c r="B84" s="2" t="s">
+        <v>480</v>
+      </c>
+      <c r="C84" s="2" t="s">
+        <v>481</v>
+      </c>
+      <c r="D84" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="E84" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="F84" s="2">
+        <v>1.0</v>
+      </c>
+      <c r="G84" s="2">
+        <v>20.0</v>
+      </c>
+      <c r="H84" s="2" t="s">
+        <v>481</v>
       </c>
     </row>
     <row r="85" ht="14.25" customHeight="1">
       <c r="A85" s="2" t="s">
-        <v>250</v>
+        <v>254</v>
       </c>
       <c r="B85" s="2" t="s">
-        <v>472</v>
+        <v>482</v>
       </c>
       <c r="C85" s="2" t="s">
-        <v>473</v>
+        <v>483</v>
       </c>
       <c r="D85" s="2">
-        <v>7.0</v>
+        <v>0.0</v>
       </c>
       <c r="E85" s="2">
-        <v>7.0</v>
+        <v>0.0</v>
       </c>
       <c r="F85" s="2">
         <v>1.0</v>
       </c>
       <c r="G85" s="2">
-        <v>10.0</v>
+        <v>30.0</v>
       </c>
       <c r="H85" s="2" t="s">
-        <v>473</v>
+        <v>483</v>
       </c>
     </row>
     <row r="86" ht="14.25" customHeight="1">
       <c r="A86" s="2" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="B86" s="2" t="s">
-        <v>252</v>
+        <v>484</v>
       </c>
       <c r="C86" s="2" t="s">
-        <v>253</v>
+        <v>485</v>
       </c>
       <c r="D86" s="2">
         <v>0.0</v>
@@ -12717,47 +12996,47 @@
         <v>1.0</v>
       </c>
       <c r="G86" s="2">
-        <v>10.0</v>
+        <v>40.0</v>
       </c>
       <c r="H86" s="2" t="s">
-        <v>253</v>
+        <v>485</v>
       </c>
     </row>
     <row r="87" ht="14.25" customHeight="1">
       <c r="A87" s="2" t="s">
-        <v>218</v>
+        <v>256</v>
       </c>
       <c r="B87" s="2" t="s">
-        <v>474</v>
+        <v>486</v>
       </c>
       <c r="C87" s="2" t="s">
-        <v>475</v>
+        <v>487</v>
       </c>
       <c r="D87" s="2">
-        <v>0.0</v>
+        <v>7.0</v>
       </c>
       <c r="E87" s="2">
-        <v>0.0</v>
+        <v>7.0</v>
       </c>
       <c r="F87" s="2">
         <v>1.0</v>
       </c>
       <c r="G87" s="2">
-        <v>60.0</v>
+        <v>10.0</v>
       </c>
       <c r="H87" s="2" t="s">
-        <v>476</v>
+        <v>487</v>
       </c>
     </row>
     <row r="88" ht="14.25" customHeight="1">
-      <c r="A88" s="3" t="s">
-        <v>254</v>
-      </c>
-      <c r="B88" s="3" t="s">
-        <v>477</v>
-      </c>
-      <c r="C88" s="3" t="s">
-        <v>478</v>
+      <c r="A88" s="2" t="s">
+        <v>258</v>
+      </c>
+      <c r="B88" s="2" t="s">
+        <v>258</v>
+      </c>
+      <c r="C88" s="2" t="s">
+        <v>259</v>
       </c>
       <c r="D88" s="2">
         <v>0.0</v>
@@ -12771,19 +13050,19 @@
       <c r="G88" s="2">
         <v>10.0</v>
       </c>
-      <c r="H88" s="3" t="s">
-        <v>479</v>
+      <c r="H88" s="2" t="s">
+        <v>259</v>
       </c>
     </row>
     <row r="89" ht="14.25" customHeight="1">
-      <c r="A89" s="3" t="s">
-        <v>254</v>
-      </c>
-      <c r="B89" s="3" t="s">
-        <v>480</v>
-      </c>
-      <c r="C89" s="3" t="s">
-        <v>481</v>
+      <c r="A89" s="2" t="s">
+        <v>224</v>
+      </c>
+      <c r="B89" s="2" t="s">
+        <v>488</v>
+      </c>
+      <c r="C89" s="2" t="s">
+        <v>489</v>
       </c>
       <c r="D89" s="2">
         <v>0.0</v>
@@ -12795,21 +13074,21 @@
         <v>1.0</v>
       </c>
       <c r="G89" s="2">
-        <v>20.0</v>
-      </c>
-      <c r="H89" s="3" t="s">
-        <v>482</v>
+        <v>60.0</v>
+      </c>
+      <c r="H89" s="2" t="s">
+        <v>490</v>
       </c>
     </row>
     <row r="90" ht="14.25" customHeight="1">
       <c r="A90" s="3" t="s">
-        <v>254</v>
+        <v>260</v>
       </c>
       <c r="B90" s="3" t="s">
-        <v>483</v>
+        <v>491</v>
       </c>
       <c r="C90" s="3" t="s">
-        <v>484</v>
+        <v>492</v>
       </c>
       <c r="D90" s="2">
         <v>0.0</v>
@@ -12821,21 +13100,21 @@
         <v>1.0</v>
       </c>
       <c r="G90" s="2">
-        <v>30.0</v>
+        <v>10.0</v>
       </c>
       <c r="H90" s="3" t="s">
-        <v>485</v>
+        <v>493</v>
       </c>
     </row>
     <row r="91" ht="14.25" customHeight="1">
       <c r="A91" s="3" t="s">
-        <v>254</v>
+        <v>260</v>
       </c>
       <c r="B91" s="3" t="s">
-        <v>486</v>
+        <v>494</v>
       </c>
       <c r="C91" s="3" t="s">
-        <v>487</v>
+        <v>495</v>
       </c>
       <c r="D91" s="2">
         <v>0.0</v>
@@ -12847,70 +13126,220 @@
         <v>1.0</v>
       </c>
       <c r="G91" s="2">
+        <v>20.0</v>
+      </c>
+      <c r="H91" s="3" t="s">
+        <v>496</v>
+      </c>
+    </row>
+    <row r="92" ht="14.25" customHeight="1">
+      <c r="A92" s="3" t="s">
+        <v>260</v>
+      </c>
+      <c r="B92" s="3" t="s">
+        <v>497</v>
+      </c>
+      <c r="C92" s="3" t="s">
+        <v>498</v>
+      </c>
+      <c r="D92" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="E92" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="F92" s="2">
+        <v>1.0</v>
+      </c>
+      <c r="G92" s="2">
+        <v>30.0</v>
+      </c>
+      <c r="H92" s="3" t="s">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="93" ht="14.25" customHeight="1">
+      <c r="A93" s="3" t="s">
+        <v>260</v>
+      </c>
+      <c r="B93" s="3" t="s">
+        <v>500</v>
+      </c>
+      <c r="C93" s="3" t="s">
+        <v>501</v>
+      </c>
+      <c r="D93" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="E93" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="F93" s="2">
+        <v>1.0</v>
+      </c>
+      <c r="G93" s="2">
         <v>40.0</v>
       </c>
-      <c r="H91" s="3" t="s">
-        <v>488</v>
-      </c>
-    </row>
-    <row r="92" ht="14.25" customHeight="1">
-      <c r="A92" s="2" t="s">
-        <v>256</v>
-      </c>
-      <c r="B92" s="2" t="s">
-        <v>489</v>
-      </c>
-      <c r="C92" s="2" t="s">
-        <v>490</v>
-      </c>
-      <c r="D92" s="2">
-        <v>0.0</v>
-      </c>
-      <c r="E92" s="2">
-        <v>0.0</v>
-      </c>
-      <c r="F92" s="2">
-        <v>1.0</v>
-      </c>
-      <c r="G92" s="2">
+      <c r="H93" s="3" t="s">
+        <v>502</v>
+      </c>
+    </row>
+    <row r="94" ht="14.25" customHeight="1">
+      <c r="A94" s="2" t="s">
+        <v>262</v>
+      </c>
+      <c r="B94" s="2" t="s">
+        <v>503</v>
+      </c>
+      <c r="C94" s="2" t="s">
+        <v>504</v>
+      </c>
+      <c r="D94" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="E94" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="F94" s="2">
+        <v>1.0</v>
+      </c>
+      <c r="G94" s="2">
         <v>10.0</v>
       </c>
-      <c r="H92" s="2" t="s">
-        <v>491</v>
-      </c>
-    </row>
-    <row r="93" ht="14.25" customHeight="1">
-      <c r="A93" s="2" t="s">
-        <v>256</v>
-      </c>
-      <c r="B93" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="C93" s="2" t="s">
-        <v>492</v>
-      </c>
-      <c r="D93" s="2">
-        <v>0.0</v>
-      </c>
-      <c r="E93" s="2">
-        <v>0.0</v>
-      </c>
-      <c r="F93" s="2">
-        <v>1.0</v>
-      </c>
-      <c r="G93" s="2">
+      <c r="H94" s="2" t="s">
+        <v>505</v>
+      </c>
+    </row>
+    <row r="95" ht="14.25" customHeight="1">
+      <c r="A95" s="2" t="s">
+        <v>262</v>
+      </c>
+      <c r="B95" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="C95" s="2" t="s">
+        <v>506</v>
+      </c>
+      <c r="D95" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="E95" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="F95" s="2">
+        <v>1.0</v>
+      </c>
+      <c r="G95" s="2">
         <v>20.0</v>
       </c>
-      <c r="H93" s="2" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="94" ht="14.25" customHeight="1"/>
-    <row r="95" ht="14.25" customHeight="1"/>
-    <row r="96" ht="14.25" customHeight="1"/>
-    <row r="97" ht="14.25" customHeight="1"/>
-    <row r="98" ht="14.25" customHeight="1"/>
-    <row r="99" ht="14.25" customHeight="1"/>
+      <c r="H95" s="2" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="96" ht="14.25" customHeight="1">
+      <c r="A96" s="5" t="s">
+        <v>264</v>
+      </c>
+      <c r="B96" s="5" t="s">
+        <v>507</v>
+      </c>
+      <c r="C96" s="5" t="s">
+        <v>508</v>
+      </c>
+      <c r="D96" s="5">
+        <v>0.0</v>
+      </c>
+      <c r="E96" s="5">
+        <v>0.0</v>
+      </c>
+      <c r="F96" s="5">
+        <v>1.0</v>
+      </c>
+      <c r="G96" s="5">
+        <v>10.0</v>
+      </c>
+      <c r="H96" s="5" t="s">
+        <v>509</v>
+      </c>
+    </row>
+    <row r="97" ht="14.25" customHeight="1">
+      <c r="A97" s="5" t="s">
+        <v>264</v>
+      </c>
+      <c r="B97" s="5" t="s">
+        <v>510</v>
+      </c>
+      <c r="C97" s="5" t="s">
+        <v>511</v>
+      </c>
+      <c r="D97" s="5">
+        <v>0.0</v>
+      </c>
+      <c r="E97" s="5">
+        <v>0.0</v>
+      </c>
+      <c r="F97" s="5">
+        <v>1.0</v>
+      </c>
+      <c r="G97" s="5">
+        <v>20.0</v>
+      </c>
+      <c r="H97" s="5" t="s">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="98" ht="14.25" customHeight="1">
+      <c r="A98" s="5" t="s">
+        <v>264</v>
+      </c>
+      <c r="B98" s="5" t="s">
+        <v>513</v>
+      </c>
+      <c r="C98" s="5" t="s">
+        <v>514</v>
+      </c>
+      <c r="D98" s="5">
+        <v>0.0</v>
+      </c>
+      <c r="E98" s="5">
+        <v>0.0</v>
+      </c>
+      <c r="F98" s="5">
+        <v>1.0</v>
+      </c>
+      <c r="G98" s="5">
+        <v>30.0</v>
+      </c>
+      <c r="H98" s="5" t="s">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="99" ht="14.25" customHeight="1">
+      <c r="A99" s="5" t="s">
+        <v>264</v>
+      </c>
+      <c r="B99" s="5" t="s">
+        <v>516</v>
+      </c>
+      <c r="C99" s="5" t="s">
+        <v>517</v>
+      </c>
+      <c r="D99" s="5">
+        <v>0.0</v>
+      </c>
+      <c r="E99" s="5">
+        <v>0.0</v>
+      </c>
+      <c r="F99" s="5">
+        <v>1.0</v>
+      </c>
+      <c r="G99" s="5">
+        <v>40.0</v>
+      </c>
+      <c r="H99" s="5" t="s">
+        <v>518</v>
+      </c>
+    </row>
     <row r="100" ht="14.25" customHeight="1"/>
     <row r="101" ht="14.25" customHeight="1"/>
     <row r="102" ht="14.25" customHeight="1"/>
@@ -13105,8 +13534,8 @@
     <row r="291" ht="14.25" customHeight="1"/>
     <row r="292" ht="14.25" customHeight="1"/>
     <row r="293" ht="14.25" customHeight="1"/>
-    <row r="294" ht="15.75" customHeight="1"/>
-    <row r="295" ht="15.75" customHeight="1"/>
+    <row r="294" ht="14.25" customHeight="1"/>
+    <row r="295" ht="14.25" customHeight="1"/>
     <row r="296" ht="15.75" customHeight="1"/>
     <row r="297" ht="15.75" customHeight="1"/>
     <row r="298" ht="15.75" customHeight="1"/>
@@ -13813,6 +14242,7 @@
     <row r="999" ht="15.75" customHeight="1"/>
     <row r="1000" ht="15.75" customHeight="1"/>
     <row r="1001" ht="15.75" customHeight="1"/>
+    <row r="1002" ht="15.75" customHeight="1"/>
   </sheetData>
   <autoFilter ref="$A$1:$H$1"/>
   <printOptions/>
@@ -13840,22 +14270,22 @@
   <sheetData>
     <row r="1" ht="14.25" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>493</v>
+        <v>519</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>258</v>
+        <v>266</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>199</v>
+        <v>205</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>201</v>
+        <v>207</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>200</v>
+        <v>206</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>3</v>
@@ -13866,7 +14296,7 @@
         <v>38</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>218</v>
+        <v>224</v>
       </c>
       <c r="C2" s="2">
         <v>1.0</v>
@@ -13875,7 +14305,7 @@
         <v>0.0</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>208</v>
+        <v>214</v>
       </c>
       <c r="F2" s="2">
         <v>5.0</v>
@@ -13889,7 +14319,7 @@
         <v>42</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>205</v>
+        <v>211</v>
       </c>
       <c r="C3" s="2">
         <v>1.0</v>
@@ -13898,7 +14328,7 @@
         <v>0.0</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>208</v>
+        <v>214</v>
       </c>
       <c r="F3" s="2">
         <v>5.0</v>
@@ -13912,7 +14342,7 @@
         <v>44</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>220</v>
+        <v>226</v>
       </c>
       <c r="C4" s="2">
         <v>1.0</v>
@@ -13921,7 +14351,7 @@
         <v>0.0</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>208</v>
+        <v>214</v>
       </c>
       <c r="F4" s="2">
         <v>5.0</v>
@@ -13935,7 +14365,7 @@
         <v>46</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>209</v>
+        <v>215</v>
       </c>
       <c r="C5" s="2">
         <v>0.0</v>
@@ -13944,7 +14374,7 @@
         <v>1.0</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>208</v>
+        <v>214</v>
       </c>
       <c r="F5" s="2">
         <v>5.0</v>
@@ -13958,7 +14388,7 @@
         <v>48</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>222</v>
+        <v>228</v>
       </c>
       <c r="C6" s="2">
         <v>1.0</v>
@@ -13967,7 +14397,7 @@
         <v>0.0</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>208</v>
+        <v>214</v>
       </c>
       <c r="F6" s="2">
         <v>5.0</v>
@@ -13981,7 +14411,7 @@
         <v>32</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>205</v>
+        <v>211</v>
       </c>
       <c r="C7" s="2">
         <v>1.0</v>
@@ -13990,7 +14420,7 @@
         <v>0.0</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>208</v>
+        <v>214</v>
       </c>
       <c r="F7" s="2">
         <v>5.0</v>
@@ -14004,7 +14434,7 @@
         <v>32</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>216</v>
+        <v>222</v>
       </c>
       <c r="C8" s="2">
         <v>0.0</v>
@@ -14013,7 +14443,7 @@
         <v>1.0</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>208</v>
+        <v>214</v>
       </c>
       <c r="F8" s="2">
         <v>10.0</v>
@@ -14027,7 +14457,7 @@
         <v>34</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>205</v>
+        <v>211</v>
       </c>
       <c r="C9" s="2">
         <v>1.0</v>
@@ -14036,7 +14466,7 @@
         <v>0.0</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>208</v>
+        <v>214</v>
       </c>
       <c r="F9" s="2">
         <v>5.0</v>
@@ -14050,7 +14480,7 @@
         <v>34</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>216</v>
+        <v>222</v>
       </c>
       <c r="C10" s="2">
         <v>0.0</v>
@@ -14059,7 +14489,7 @@
         <v>1.0</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>208</v>
+        <v>214</v>
       </c>
       <c r="F10" s="2">
         <v>10.0</v>
@@ -14073,7 +14503,7 @@
         <v>58</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>205</v>
+        <v>211</v>
       </c>
       <c r="C11" s="2">
         <v>1.0</v>
@@ -14082,7 +14512,7 @@
         <v>0.0</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>208</v>
+        <v>214</v>
       </c>
       <c r="F11" s="2">
         <v>5.0</v>
@@ -14096,16 +14526,16 @@
         <v>102</v>
       </c>
       <c r="B12" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="C12" s="2">
+        <v>1.0</v>
+      </c>
+      <c r="D12" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="E12" s="2" t="s">
         <v>214</v>
-      </c>
-      <c r="C12" s="2">
-        <v>1.0</v>
-      </c>
-      <c r="D12" s="2">
-        <v>0.0</v>
-      </c>
-      <c r="E12" s="2" t="s">
-        <v>208</v>
       </c>
       <c r="F12" s="2">
         <v>5.0</v>
@@ -14119,7 +14549,7 @@
         <v>104</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>212</v>
+        <v>218</v>
       </c>
       <c r="C13" s="2">
         <v>1.0</v>
@@ -14128,7 +14558,7 @@
         <v>0.0</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>208</v>
+        <v>214</v>
       </c>
       <c r="F13" s="2">
         <v>5.0</v>
@@ -14142,7 +14572,7 @@
         <v>36</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>224</v>
+        <v>230</v>
       </c>
       <c r="C14" s="2">
         <v>1.0</v>
@@ -14151,7 +14581,7 @@
         <v>0.0</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>208</v>
+        <v>214</v>
       </c>
       <c r="F14" s="2">
         <v>5.0</v>
@@ -14165,7 +14595,7 @@
         <v>36</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>226</v>
+        <v>232</v>
       </c>
       <c r="C15" s="2">
         <v>1.0</v>
@@ -14174,7 +14604,7 @@
         <v>0.0</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>208</v>
+        <v>214</v>
       </c>
       <c r="F15" s="2">
         <v>10.0</v>
@@ -14185,10 +14615,10 @@
     </row>
     <row r="16" ht="14.25" customHeight="1">
       <c r="A16" s="2" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>224</v>
+        <v>230</v>
       </c>
       <c r="C16" s="2">
         <v>1.0</v>
@@ -14197,7 +14627,7 @@
         <v>0.0</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>208</v>
+        <v>214</v>
       </c>
       <c r="F16" s="2">
         <v>5.0</v>
@@ -14208,10 +14638,10 @@
     </row>
     <row r="17" ht="14.25" customHeight="1">
       <c r="A17" s="2" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>228</v>
+        <v>234</v>
       </c>
       <c r="C17" s="2">
         <v>1.0</v>
@@ -14220,7 +14650,7 @@
         <v>0.0</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>208</v>
+        <v>214</v>
       </c>
       <c r="F17" s="2">
         <v>5.0</v>
@@ -14231,10 +14661,10 @@
     </row>
     <row r="18" ht="14.25" customHeight="1">
       <c r="A18" s="2" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>230</v>
+        <v>236</v>
       </c>
       <c r="C18" s="2">
         <v>1.0</v>
@@ -14243,7 +14673,7 @@
         <v>0.0</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>208</v>
+        <v>214</v>
       </c>
       <c r="F18" s="2">
         <v>5.0</v>
@@ -14254,10 +14684,10 @@
     </row>
     <row r="19" ht="14.25" customHeight="1">
       <c r="A19" s="2" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>224</v>
+        <v>230</v>
       </c>
       <c r="C19" s="2">
         <v>1.0</v>
@@ -14266,7 +14696,7 @@
         <v>0.0</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>208</v>
+        <v>214</v>
       </c>
       <c r="F19" s="2">
         <v>5.0</v>
@@ -14277,10 +14707,10 @@
     </row>
     <row r="20" ht="14.25" customHeight="1">
       <c r="A20" s="2" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>232</v>
+        <v>238</v>
       </c>
       <c r="C20" s="2">
         <v>1.0</v>
@@ -14289,7 +14719,7 @@
         <v>0.0</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>208</v>
+        <v>214</v>
       </c>
       <c r="F20" s="2">
         <v>10.0</v>
@@ -14300,10 +14730,10 @@
     </row>
     <row r="21" ht="14.25" customHeight="1">
       <c r="A21" s="2" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>224</v>
+        <v>230</v>
       </c>
       <c r="C21" s="2">
         <v>1.0</v>
@@ -14312,7 +14742,7 @@
         <v>0.0</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>208</v>
+        <v>214</v>
       </c>
       <c r="F21" s="2">
         <v>5.0</v>
@@ -14323,10 +14753,10 @@
     </row>
     <row r="22" ht="14.25" customHeight="1">
       <c r="A22" s="2" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>234</v>
+        <v>240</v>
       </c>
       <c r="C22" s="2">
         <v>1.0</v>
@@ -14335,7 +14765,7 @@
         <v>0.0</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>208</v>
+        <v>214</v>
       </c>
       <c r="F22" s="2">
         <v>10.0</v>
@@ -14346,10 +14776,10 @@
     </row>
     <row r="23" ht="14.25" customHeight="1">
       <c r="A23" s="2" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>236</v>
+        <v>242</v>
       </c>
       <c r="C23" s="2">
         <v>1.0</v>
@@ -14358,7 +14788,7 @@
         <v>0.0</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>208</v>
+        <v>214</v>
       </c>
       <c r="F23" s="2">
         <v>5.0</v>
@@ -14369,10 +14799,10 @@
     </row>
     <row r="24" ht="14.25" customHeight="1">
       <c r="A24" s="2" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>238</v>
+        <v>244</v>
       </c>
       <c r="C24" s="2">
         <v>1.0</v>
@@ -14381,7 +14811,7 @@
         <v>0.0</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>208</v>
+        <v>214</v>
       </c>
       <c r="F24" s="2">
         <v>5.0</v>
@@ -14392,10 +14822,10 @@
     </row>
     <row r="25" ht="14.25" customHeight="1">
       <c r="A25" s="2" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>244</v>
+        <v>250</v>
       </c>
       <c r="C25" s="2">
         <v>1.0</v>
@@ -14404,7 +14834,7 @@
         <v>0.0</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>208</v>
+        <v>214</v>
       </c>
       <c r="F25" s="2">
         <v>5.0</v>
@@ -14415,10 +14845,10 @@
     </row>
     <row r="26" ht="14.25" customHeight="1">
       <c r="A26" s="2" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>246</v>
+        <v>252</v>
       </c>
       <c r="C26" s="2">
         <v>1.0</v>
@@ -14427,7 +14857,7 @@
         <v>0.0</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>208</v>
+        <v>214</v>
       </c>
       <c r="F26" s="2">
         <v>10.0</v>
@@ -14438,10 +14868,10 @@
     </row>
     <row r="27" ht="14.25" customHeight="1">
       <c r="A27" s="2" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>248</v>
+        <v>254</v>
       </c>
       <c r="C27" s="2">
         <v>1.0</v>
@@ -14450,7 +14880,7 @@
         <v>0.0</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>208</v>
+        <v>214</v>
       </c>
       <c r="F27" s="2">
         <v>15.0</v>
@@ -14461,10 +14891,10 @@
     </row>
     <row r="28" ht="14.25" customHeight="1">
       <c r="A28" s="2" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>250</v>
+        <v>256</v>
       </c>
       <c r="C28" s="2">
         <v>0.0</v>
@@ -14473,7 +14903,7 @@
         <v>0.0</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>208</v>
+        <v>214</v>
       </c>
       <c r="F28" s="2">
         <v>20.0</v>
@@ -14484,10 +14914,10 @@
     </row>
     <row r="29" ht="14.25" customHeight="1">
       <c r="A29" s="2" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>252</v>
+        <v>258</v>
       </c>
       <c r="C29" s="2">
         <v>0.0</v>
@@ -14496,7 +14926,7 @@
         <v>0.0</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>208</v>
+        <v>214</v>
       </c>
       <c r="F29" s="2">
         <v>5.0</v>
@@ -14510,7 +14940,7 @@
         <v>70</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>254</v>
+        <v>260</v>
       </c>
       <c r="C30" s="2">
         <v>1.0</v>
@@ -14519,7 +14949,7 @@
         <v>0.0</v>
       </c>
       <c r="E30" s="3" t="s">
-        <v>208</v>
+        <v>214</v>
       </c>
       <c r="F30" s="2">
         <v>5.0</v>
@@ -14533,7 +14963,7 @@
         <v>72</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>254</v>
+        <v>260</v>
       </c>
       <c r="C31" s="2">
         <v>1.0</v>
@@ -14542,7 +14972,7 @@
         <v>0.0</v>
       </c>
       <c r="E31" s="3" t="s">
-        <v>208</v>
+        <v>214</v>
       </c>
       <c r="F31" s="2">
         <v>10.0</v>
@@ -14556,7 +14986,7 @@
         <v>74</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>254</v>
+        <v>260</v>
       </c>
       <c r="C32" s="2">
         <v>1.0</v>
@@ -14565,7 +14995,7 @@
         <v>0.0</v>
       </c>
       <c r="E32" s="3" t="s">
-        <v>208</v>
+        <v>214</v>
       </c>
       <c r="F32" s="2">
         <v>15.0</v>
@@ -14579,7 +15009,7 @@
         <v>76</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>254</v>
+        <v>260</v>
       </c>
       <c r="C33" s="2">
         <v>1.0</v>
@@ -14588,7 +15018,7 @@
         <v>0.0</v>
       </c>
       <c r="E33" s="3" t="s">
-        <v>208</v>
+        <v>214</v>
       </c>
       <c r="F33" s="2">
         <v>20.0</v>
@@ -14602,7 +15032,7 @@
         <v>78</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>254</v>
+        <v>260</v>
       </c>
       <c r="C34" s="2">
         <v>1.0</v>
@@ -14611,7 +15041,7 @@
         <v>0.0</v>
       </c>
       <c r="E34" s="3" t="s">
-        <v>208</v>
+        <v>214</v>
       </c>
       <c r="F34" s="2">
         <v>25.0</v>
@@ -14625,7 +15055,7 @@
         <v>80</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>254</v>
+        <v>260</v>
       </c>
       <c r="C35" s="2">
         <v>1.0</v>
@@ -14634,7 +15064,7 @@
         <v>0.0</v>
       </c>
       <c r="E35" s="3" t="s">
-        <v>208</v>
+        <v>214</v>
       </c>
       <c r="F35" s="2">
         <v>30.0</v>
@@ -14643,8 +15073,52 @@
         <v>1.0</v>
       </c>
     </row>
-    <row r="36" ht="14.25" customHeight="1"/>
-    <row r="37" ht="14.25" customHeight="1"/>
+    <row r="36" ht="14.25" customHeight="1">
+      <c r="A36" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="B36" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="C36" s="2">
+        <v>1.0</v>
+      </c>
+      <c r="D36" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="E36" s="2" t="s">
+        <v>214</v>
+      </c>
+      <c r="F36" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="G36" s="2">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="37" ht="14.25" customHeight="1">
+      <c r="A37" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="B37" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="C37" s="2">
+        <v>1.0</v>
+      </c>
+      <c r="D37" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="E37" s="2" t="s">
+        <v>214</v>
+      </c>
+      <c r="F37" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="G37" s="2">
+        <v>1.0</v>
+      </c>
+    </row>
     <row r="38" ht="14.25" customHeight="1"/>
     <row r="39" ht="14.25" customHeight="1"/>
     <row r="40" ht="14.25" customHeight="1"/>
@@ -14653,52 +15127,8 @@
     <row r="43" ht="14.25" customHeight="1"/>
     <row r="44" ht="14.25" customHeight="1"/>
     <row r="45" ht="14.25" customHeight="1"/>
-    <row r="46" ht="14.25" customHeight="1">
-      <c r="A46" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="B46" s="2" t="s">
-        <v>205</v>
-      </c>
-      <c r="C46" s="2">
-        <v>1.0</v>
-      </c>
-      <c r="D46" s="2">
-        <v>0.0</v>
-      </c>
-      <c r="E46" s="2" t="s">
-        <v>208</v>
-      </c>
-      <c r="F46" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="G46" s="2">
-        <v>1.0</v>
-      </c>
-    </row>
-    <row r="47" ht="14.25" customHeight="1">
-      <c r="A47" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="B47" s="2" t="s">
-        <v>205</v>
-      </c>
-      <c r="C47" s="2">
-        <v>1.0</v>
-      </c>
-      <c r="D47" s="2">
-        <v>0.0</v>
-      </c>
-      <c r="E47" s="2" t="s">
-        <v>208</v>
-      </c>
-      <c r="F47" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="G47" s="2">
-        <v>1.0</v>
-      </c>
-    </row>
+    <row r="46" ht="14.25" customHeight="1"/>
+    <row r="47" ht="14.25" customHeight="1"/>
     <row r="48" ht="14.25" customHeight="1"/>
     <row r="49" ht="14.25" customHeight="1"/>
     <row r="50" ht="14.25" customHeight="1"/>
@@ -15679,19 +16109,19 @@
   <sheetData>
     <row r="1" ht="14.25" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>493</v>
+        <v>519</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>494</v>
+        <v>520</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>495</v>
+        <v>521</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>496</v>
+        <v>522</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>497</v>
+        <v>523</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>4</v>
@@ -15705,13 +16135,13 @@
         <v>32</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>208</v>
+        <v>214</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>7</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>498</v>
+        <v>524</v>
       </c>
       <c r="E2" s="2">
         <v>1.0</v>
@@ -15728,13 +16158,13 @@
         <v>34</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>208</v>
+        <v>214</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>7</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>499</v>
+        <v>525</v>
       </c>
       <c r="E3" s="2">
         <v>1.0</v>
@@ -15751,13 +16181,13 @@
         <v>36</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>500</v>
+        <v>526</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>10</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>501</v>
+        <v>527</v>
       </c>
       <c r="E4" s="2">
         <v>1.0</v>
@@ -15774,13 +16204,13 @@
         <v>38</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>208</v>
+        <v>214</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>7</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>502</v>
+        <v>528</v>
       </c>
       <c r="E5" s="2">
         <v>1.0</v>
@@ -15797,13 +16227,13 @@
         <v>40</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>208</v>
+        <v>214</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>7</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>503</v>
+        <v>529</v>
       </c>
       <c r="E6" s="2">
         <v>1.0</v>
@@ -15820,13 +16250,13 @@
         <v>42</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>208</v>
+        <v>214</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>7</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>504</v>
+        <v>530</v>
       </c>
       <c r="E7" s="2">
         <v>1.0</v>
@@ -15843,13 +16273,13 @@
         <v>44</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>208</v>
+        <v>214</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>7</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>505</v>
+        <v>531</v>
       </c>
       <c r="E8" s="2">
         <v>1.0</v>
@@ -15866,13 +16296,13 @@
         <v>46</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>208</v>
+        <v>214</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>7</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>506</v>
+        <v>532</v>
       </c>
       <c r="E9" s="2">
         <v>1.0</v>
@@ -15889,13 +16319,13 @@
         <v>48</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>208</v>
+        <v>214</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>7</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>507</v>
+        <v>533</v>
       </c>
       <c r="E10" s="2">
         <v>1.0</v>
@@ -15912,13 +16342,13 @@
         <v>50</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>208</v>
+        <v>214</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>7</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>508</v>
+        <v>534</v>
       </c>
       <c r="E11" s="2">
         <v>1.0</v>
@@ -15935,13 +16365,13 @@
         <v>52</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>208</v>
+        <v>214</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>509</v>
+        <v>535</v>
       </c>
       <c r="E12" s="2">
         <v>1.0</v>
@@ -15958,13 +16388,13 @@
         <v>54</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>208</v>
+        <v>214</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>7</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>510</v>
+        <v>536</v>
       </c>
       <c r="E13" s="2">
         <v>1.0</v>
@@ -15981,13 +16411,13 @@
         <v>56</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>208</v>
+        <v>214</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>7</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>511</v>
+        <v>537</v>
       </c>
       <c r="E14" s="2">
         <v>1.0</v>
@@ -16004,13 +16434,13 @@
         <v>58</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>208</v>
+        <v>214</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>7</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>512</v>
+        <v>538</v>
       </c>
       <c r="E15" s="2">
         <v>1.0</v>
@@ -16027,13 +16457,13 @@
         <v>60</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>208</v>
+        <v>214</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>7</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>513</v>
+        <v>539</v>
       </c>
       <c r="E16" s="2">
         <v>1.0</v>
@@ -16050,13 +16480,13 @@
         <v>62</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>208</v>
+        <v>214</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>7</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>514</v>
+        <v>540</v>
       </c>
       <c r="E17" s="2">
         <v>1.0</v>
@@ -16073,13 +16503,13 @@
         <v>64</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>208</v>
+        <v>214</v>
       </c>
       <c r="C18" s="2" t="s">
         <v>7</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>515</v>
+        <v>541</v>
       </c>
       <c r="E18" s="2">
         <v>1.0</v>
@@ -16096,13 +16526,13 @@
         <v>66</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>208</v>
+        <v>214</v>
       </c>
       <c r="C19" s="2" t="s">
         <v>7</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>516</v>
+        <v>542</v>
       </c>
       <c r="E19" s="2">
         <v>1.0</v>
@@ -16119,13 +16549,13 @@
         <v>68</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>208</v>
+        <v>214</v>
       </c>
       <c r="C20" s="2" t="s">
         <v>7</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>517</v>
+        <v>543</v>
       </c>
       <c r="E20" s="2">
         <v>1.0</v>
@@ -16142,13 +16572,13 @@
         <v>70</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>208</v>
+        <v>214</v>
       </c>
       <c r="C21" s="2" t="s">
         <v>7</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>518</v>
+        <v>544</v>
       </c>
       <c r="E21" s="2">
         <v>1.0</v>
@@ -16165,13 +16595,13 @@
         <v>72</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>208</v>
+        <v>214</v>
       </c>
       <c r="C22" s="2" t="s">
         <v>7</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>519</v>
+        <v>545</v>
       </c>
       <c r="E22" s="2">
         <v>1.0</v>
@@ -16188,13 +16618,13 @@
         <v>74</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>208</v>
+        <v>214</v>
       </c>
       <c r="C23" s="2" t="s">
         <v>7</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>520</v>
+        <v>546</v>
       </c>
       <c r="E23" s="2">
         <v>1.0</v>
@@ -16211,13 +16641,13 @@
         <v>76</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>208</v>
+        <v>214</v>
       </c>
       <c r="C24" s="2" t="s">
         <v>7</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>521</v>
+        <v>547</v>
       </c>
       <c r="E24" s="2">
         <v>1.0</v>
@@ -16234,13 +16664,13 @@
         <v>78</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>208</v>
+        <v>214</v>
       </c>
       <c r="C25" s="2" t="s">
         <v>7</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>522</v>
+        <v>548</v>
       </c>
       <c r="E25" s="2">
         <v>1.0</v>
@@ -16257,13 +16687,13 @@
         <v>80</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>208</v>
+        <v>214</v>
       </c>
       <c r="C26" s="2" t="s">
         <v>7</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>523</v>
+        <v>549</v>
       </c>
       <c r="E26" s="2">
         <v>1.0</v>
@@ -16280,13 +16710,13 @@
         <v>82</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>524</v>
+        <v>550</v>
       </c>
       <c r="C27" s="2" t="s">
         <v>7</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>525</v>
+        <v>551</v>
       </c>
       <c r="E27" s="2">
         <v>1.0</v>
@@ -16303,13 +16733,13 @@
         <v>84</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>500</v>
+        <v>526</v>
       </c>
       <c r="C28" s="2" t="s">
         <v>7</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>526</v>
+        <v>552</v>
       </c>
       <c r="E28" s="2">
         <v>1.0</v>
@@ -16326,13 +16756,13 @@
         <v>86</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>500</v>
+        <v>526</v>
       </c>
       <c r="C29" s="2" t="s">
         <v>7</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>527</v>
+        <v>553</v>
       </c>
       <c r="E29" s="2">
         <v>1.0</v>
@@ -16349,13 +16779,13 @@
         <v>88</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>500</v>
+        <v>526</v>
       </c>
       <c r="C30" s="2" t="s">
         <v>7</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>528</v>
+        <v>554</v>
       </c>
       <c r="E30" s="2">
         <v>1.0</v>
@@ -16372,13 +16802,13 @@
         <v>90</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>208</v>
+        <v>214</v>
       </c>
       <c r="C31" s="2" t="s">
         <v>7</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>529</v>
+        <v>555</v>
       </c>
       <c r="E31" s="2">
         <v>1.0</v>
@@ -16395,13 +16825,13 @@
         <v>92</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>208</v>
+        <v>214</v>
       </c>
       <c r="C32" s="2" t="s">
         <v>7</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>530</v>
+        <v>556</v>
       </c>
       <c r="E32" s="2">
         <v>1.0</v>
@@ -16418,13 +16848,13 @@
         <v>94</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>208</v>
+        <v>214</v>
       </c>
       <c r="C33" s="2" t="s">
         <v>7</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>531</v>
+        <v>557</v>
       </c>
       <c r="E33" s="2">
         <v>1.0</v>
@@ -16441,13 +16871,13 @@
         <v>96</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>208</v>
+        <v>214</v>
       </c>
       <c r="C34" s="2" t="s">
         <v>7</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>532</v>
+        <v>558</v>
       </c>
       <c r="E34" s="2">
         <v>1.0</v>
@@ -16464,13 +16894,13 @@
         <v>98</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>208</v>
+        <v>214</v>
       </c>
       <c r="C35" s="2" t="s">
         <v>7</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>533</v>
+        <v>559</v>
       </c>
       <c r="E35" s="2">
         <v>1.0</v>
@@ -16487,13 +16917,13 @@
         <v>100</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>500</v>
+        <v>526</v>
       </c>
       <c r="C36" s="2" t="s">
         <v>7</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>534</v>
+        <v>560</v>
       </c>
       <c r="E36" s="2">
         <v>1.0</v>
@@ -16510,13 +16940,13 @@
         <v>102</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>500</v>
+        <v>526</v>
       </c>
       <c r="C37" s="2" t="s">
         <v>7</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>535</v>
+        <v>561</v>
       </c>
       <c r="E37" s="2">
         <v>1.0</v>
@@ -16533,13 +16963,13 @@
         <v>104</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>500</v>
+        <v>526</v>
       </c>
       <c r="C38" s="2" t="s">
         <v>7</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>536</v>
+        <v>562</v>
       </c>
       <c r="E38" s="2">
         <v>1.0</v>
@@ -16552,25 +16982,25 @@
       </c>
     </row>
     <row r="39" ht="14.25" customHeight="1">
-      <c r="A39" s="2" t="s">
+      <c r="A39" s="4" t="s">
         <v>106</v>
       </c>
-      <c r="B39" s="2" t="s">
-        <v>500</v>
-      </c>
-      <c r="C39" s="2" t="s">
+      <c r="B39" s="4" t="s">
+        <v>526</v>
+      </c>
+      <c r="C39" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="D39" s="2" t="s">
-        <v>537</v>
-      </c>
-      <c r="E39" s="2">
-        <v>1.0</v>
-      </c>
-      <c r="F39" s="2">
+      <c r="D39" s="4" t="s">
+        <v>563</v>
+      </c>
+      <c r="E39" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="F39" s="4">
         <v>380.0</v>
       </c>
-      <c r="G39" s="2">
+      <c r="G39" s="4">
         <v>1.0</v>
       </c>
     </row>
@@ -16579,13 +17009,13 @@
         <v>108</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>500</v>
+        <v>526</v>
       </c>
       <c r="C40" s="2" t="s">
         <v>10</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>538</v>
+        <v>564</v>
       </c>
       <c r="E40" s="2">
         <v>1.0</v>
@@ -16602,13 +17032,13 @@
         <v>110</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>500</v>
+        <v>526</v>
       </c>
       <c r="C41" s="2" t="s">
         <v>10</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>539</v>
+        <v>565</v>
       </c>
       <c r="E41" s="2">
         <v>1.0</v>
@@ -16625,18 +17055,18 @@
         <v>112</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>500</v>
+        <v>526</v>
       </c>
       <c r="C42" s="2" t="s">
         <v>10</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>540</v>
+        <v>566</v>
       </c>
       <c r="E42" s="2">
         <v>1.0</v>
       </c>
-      <c r="F42" s="2">
+      <c r="F42" s="4">
         <v>410.0</v>
       </c>
       <c r="G42" s="2">
@@ -16648,13 +17078,13 @@
         <v>114</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>500</v>
+        <v>526</v>
       </c>
       <c r="C43" s="2" t="s">
         <v>10</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>541</v>
+        <v>567</v>
       </c>
       <c r="E43" s="2">
         <v>1.0</v>
@@ -16671,13 +17101,13 @@
         <v>116</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>500</v>
+        <v>526</v>
       </c>
       <c r="C44" s="2" t="s">
         <v>10</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>542</v>
+        <v>568</v>
       </c>
       <c r="E44" s="2">
         <v>1.0</v>
@@ -16694,18 +17124,18 @@
         <v>118</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>500</v>
+        <v>526</v>
       </c>
       <c r="C45" s="2" t="s">
         <v>10</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>543</v>
+        <v>569</v>
       </c>
       <c r="E45" s="2">
         <v>1.0</v>
       </c>
-      <c r="F45" s="2">
+      <c r="F45" s="4">
         <v>440.0</v>
       </c>
       <c r="G45" s="2">
@@ -16717,13 +17147,13 @@
         <v>120</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>500</v>
+        <v>526</v>
       </c>
       <c r="C46" s="2" t="s">
         <v>10</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>544</v>
+        <v>570</v>
       </c>
       <c r="E46" s="2">
         <v>1.0</v>
@@ -16740,13 +17170,13 @@
         <v>122</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>500</v>
+        <v>526</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>545</v>
+        <v>571</v>
       </c>
       <c r="E47" s="2">
         <v>1.0</v>
@@ -16763,18 +17193,18 @@
         <v>124</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>500</v>
+        <v>526</v>
       </c>
       <c r="C48" s="2" t="s">
         <v>7</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>546</v>
+        <v>572</v>
       </c>
       <c r="E48" s="2">
         <v>1.0</v>
       </c>
-      <c r="F48" s="2">
+      <c r="F48" s="4">
         <v>470.0</v>
       </c>
       <c r="G48" s="2">
@@ -16786,13 +17216,13 @@
         <v>126</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>500</v>
+        <v>526</v>
       </c>
       <c r="C49" s="2" t="s">
         <v>7</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>547</v>
+        <v>573</v>
       </c>
       <c r="E49" s="2">
         <v>1.0</v>
@@ -16809,13 +17239,13 @@
         <v>128</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>500</v>
+        <v>526</v>
       </c>
       <c r="C50" s="2" t="s">
         <v>7</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>548</v>
+        <v>574</v>
       </c>
       <c r="E50" s="2">
         <v>1.0</v>
@@ -16832,18 +17262,18 @@
         <v>130</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>500</v>
+        <v>526</v>
       </c>
       <c r="C51" s="2" t="s">
         <v>7</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>549</v>
+        <v>575</v>
       </c>
       <c r="E51" s="2">
         <v>1.0</v>
       </c>
-      <c r="F51" s="2">
+      <c r="F51" s="4">
         <v>500.0</v>
       </c>
       <c r="G51" s="2">
@@ -16855,13 +17285,13 @@
         <v>132</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>500</v>
+        <v>526</v>
       </c>
       <c r="C52" s="2" t="s">
         <v>7</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>550</v>
+        <v>576</v>
       </c>
       <c r="E52" s="2">
         <v>1.0</v>
@@ -16873,9 +17303,75 @@
         <v>1.0</v>
       </c>
     </row>
-    <row r="53" ht="14.25" customHeight="1"/>
-    <row r="54" ht="14.25" customHeight="1"/>
-    <row r="55" ht="14.25" customHeight="1"/>
+    <row r="53" ht="14.25" customHeight="1">
+      <c r="A53" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="B53" s="2" t="s">
+        <v>526</v>
+      </c>
+      <c r="C53" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D53" s="2" t="s">
+        <v>577</v>
+      </c>
+      <c r="E53" s="2">
+        <v>1.0</v>
+      </c>
+      <c r="F53" s="2">
+        <v>520.0</v>
+      </c>
+      <c r="G53" s="2">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="54" ht="14.25" customHeight="1">
+      <c r="A54" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="B54" s="5" t="s">
+        <v>526</v>
+      </c>
+      <c r="C54" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D54" s="5" t="s">
+        <v>578</v>
+      </c>
+      <c r="E54" s="5">
+        <v>1.0</v>
+      </c>
+      <c r="F54" s="4">
+        <v>530.0</v>
+      </c>
+      <c r="G54" s="5">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="55" ht="14.25" customHeight="1">
+      <c r="A55" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="B55" s="5" t="s">
+        <v>526</v>
+      </c>
+      <c r="C55" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D55" s="5" t="s">
+        <v>579</v>
+      </c>
+      <c r="E55" s="5">
+        <v>1.0</v>
+      </c>
+      <c r="F55" s="2">
+        <v>540.0</v>
+      </c>
+      <c r="G55" s="5">
+        <v>1.0</v>
+      </c>
+    </row>
     <row r="56" ht="14.25" customHeight="1"/>
     <row r="57" ht="14.25" customHeight="1"/>
     <row r="58" ht="14.25" customHeight="1"/>
@@ -17073,7 +17569,7 @@
     <row r="250" ht="14.25" customHeight="1"/>
     <row r="251" ht="14.25" customHeight="1"/>
     <row r="252" ht="14.25" customHeight="1"/>
-    <row r="253" ht="15.75" customHeight="1"/>
+    <row r="253" ht="14.25" customHeight="1"/>
     <row r="254" ht="15.75" customHeight="1"/>
     <row r="255" ht="15.75" customHeight="1"/>
     <row r="256" ht="15.75" customHeight="1"/>
@@ -17821,6 +18317,7 @@
     <row r="998" ht="15.75" customHeight="1"/>
     <row r="999" ht="15.75" customHeight="1"/>
     <row r="1000" ht="15.75" customHeight="1"/>
+    <row r="1001" ht="15.75" customHeight="1"/>
   </sheetData>
   <autoFilter ref="$A$1:$G$1"/>
   <printOptions/>
@@ -17856,7 +18353,7 @@
         <v>1</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>551</v>
+        <v>580</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>3</v>
@@ -17867,13 +18364,13 @@
     </row>
     <row r="2" ht="14.25" customHeight="1">
       <c r="A2" s="2" t="s">
-        <v>552</v>
+        <v>581</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>553</v>
+        <v>582</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>554</v>
+        <v>583</v>
       </c>
       <c r="E2" s="2">
         <v>1.0</v>
@@ -17884,13 +18381,13 @@
     </row>
     <row r="3" ht="14.25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>555</v>
+        <v>584</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>553</v>
+        <v>582</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>556</v>
+        <v>585</v>
       </c>
       <c r="E3" s="2">
         <v>1.0</v>
@@ -18918,924 +19415,924 @@
   </cols>
   <sheetData>
     <row r="1" ht="15.75" customHeight="1">
-      <c r="A1" s="5" t="s">
-        <v>557</v>
-      </c>
-      <c r="B1" s="5" t="s">
-        <v>558</v>
+      <c r="A1" s="6" t="s">
+        <v>586</v>
+      </c>
+      <c r="B1" s="6" t="s">
+        <v>587</v>
       </c>
     </row>
     <row r="2" ht="15.75" customHeight="1">
-      <c r="A2" s="6" t="s">
-        <v>559</v>
-      </c>
-      <c r="B2" s="6" t="s">
-        <v>560</v>
+      <c r="A2" s="7" t="s">
+        <v>588</v>
+      </c>
+      <c r="B2" s="7" t="s">
+        <v>589</v>
       </c>
     </row>
     <row r="3" ht="15.75" customHeight="1">
-      <c r="A3" s="6" t="s">
-        <v>561</v>
-      </c>
-      <c r="B3" s="6" t="s">
-        <v>562</v>
+      <c r="A3" s="7" t="s">
+        <v>590</v>
+      </c>
+      <c r="B3" s="7" t="s">
+        <v>591</v>
       </c>
     </row>
     <row r="4" ht="15.75" customHeight="1">
-      <c r="A4" s="6" t="s">
-        <v>563</v>
-      </c>
-      <c r="B4" s="6" t="s">
-        <v>564</v>
+      <c r="A4" s="7" t="s">
+        <v>592</v>
+      </c>
+      <c r="B4" s="7" t="s">
+        <v>593</v>
       </c>
     </row>
     <row r="5" ht="15.75" customHeight="1">
-      <c r="A5" s="6" t="s">
-        <v>565</v>
-      </c>
-      <c r="B5" s="6" t="s">
-        <v>566</v>
+      <c r="A5" s="7" t="s">
+        <v>594</v>
+      </c>
+      <c r="B5" s="7" t="s">
+        <v>595</v>
       </c>
     </row>
     <row r="6" ht="15.75" customHeight="1">
-      <c r="A6" s="6" t="s">
-        <v>206</v>
-      </c>
-      <c r="B6" s="6" t="s">
-        <v>567</v>
+      <c r="A6" s="7" t="s">
+        <v>212</v>
+      </c>
+      <c r="B6" s="7" t="s">
+        <v>596</v>
       </c>
     </row>
     <row r="7" ht="15.75" customHeight="1">
-      <c r="A7" s="6" t="s">
+      <c r="A7" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="B7" s="6" t="s">
-        <v>568</v>
+      <c r="B7" s="7" t="s">
+        <v>597</v>
       </c>
     </row>
     <row r="8" ht="15.75" customHeight="1">
-      <c r="A8" s="6" t="s">
-        <v>569</v>
-      </c>
-      <c r="B8" s="6" t="s">
-        <v>570</v>
+      <c r="A8" s="7" t="s">
+        <v>598</v>
+      </c>
+      <c r="B8" s="7" t="s">
+        <v>599</v>
       </c>
     </row>
     <row r="9" ht="15.75" customHeight="1">
-      <c r="A9" s="6" t="s">
-        <v>571</v>
-      </c>
-      <c r="B9" s="6" t="s">
-        <v>572</v>
+      <c r="A9" s="7" t="s">
+        <v>600</v>
+      </c>
+      <c r="B9" s="7" t="s">
+        <v>601</v>
       </c>
     </row>
     <row r="10" ht="15.75" customHeight="1">
-      <c r="A10" s="6" t="s">
-        <v>573</v>
-      </c>
-      <c r="B10" s="6" t="s">
-        <v>574</v>
+      <c r="A10" s="7" t="s">
+        <v>602</v>
+      </c>
+      <c r="B10" s="7" t="s">
+        <v>603</v>
       </c>
     </row>
     <row r="11" ht="14.25" customHeight="1">
-      <c r="A11" s="6"/>
-      <c r="B11" s="6"/>
+      <c r="A11" s="7"/>
+      <c r="B11" s="7"/>
     </row>
     <row r="12" ht="14.25" customHeight="1">
-      <c r="A12" s="6"/>
-      <c r="B12" s="6"/>
+      <c r="A12" s="7"/>
+      <c r="B12" s="7"/>
     </row>
     <row r="13" ht="14.25" customHeight="1">
-      <c r="A13" s="6"/>
-      <c r="B13" s="6"/>
+      <c r="A13" s="7"/>
+      <c r="B13" s="7"/>
     </row>
     <row r="14" ht="14.25" customHeight="1">
-      <c r="A14" s="6"/>
-      <c r="B14" s="6"/>
+      <c r="A14" s="7"/>
+      <c r="B14" s="7"/>
     </row>
     <row r="15" ht="14.25" customHeight="1">
-      <c r="A15" s="6"/>
-      <c r="B15" s="6"/>
+      <c r="A15" s="7"/>
+      <c r="B15" s="7"/>
     </row>
     <row r="16" ht="14.25" customHeight="1">
-      <c r="A16" s="6"/>
-      <c r="B16" s="6"/>
+      <c r="A16" s="7"/>
+      <c r="B16" s="7"/>
     </row>
     <row r="17" ht="14.25" customHeight="1">
-      <c r="A17" s="6"/>
-      <c r="B17" s="6"/>
+      <c r="A17" s="7"/>
+      <c r="B17" s="7"/>
     </row>
     <row r="18" ht="14.25" customHeight="1">
-      <c r="A18" s="6"/>
-      <c r="B18" s="6"/>
+      <c r="A18" s="7"/>
+      <c r="B18" s="7"/>
     </row>
     <row r="19" ht="14.25" customHeight="1">
-      <c r="A19" s="6"/>
-      <c r="B19" s="6"/>
+      <c r="A19" s="7"/>
+      <c r="B19" s="7"/>
     </row>
     <row r="20" ht="14.25" customHeight="1">
-      <c r="A20" s="6"/>
-      <c r="B20" s="6"/>
+      <c r="A20" s="7"/>
+      <c r="B20" s="7"/>
     </row>
     <row r="21" ht="14.25" customHeight="1">
-      <c r="A21" s="6"/>
-      <c r="B21" s="6"/>
+      <c r="A21" s="7"/>
+      <c r="B21" s="7"/>
     </row>
     <row r="22" ht="14.25" customHeight="1">
-      <c r="A22" s="6"/>
-      <c r="B22" s="6"/>
+      <c r="A22" s="7"/>
+      <c r="B22" s="7"/>
     </row>
     <row r="23" ht="14.25" customHeight="1">
-      <c r="A23" s="6"/>
-      <c r="B23" s="6"/>
+      <c r="A23" s="7"/>
+      <c r="B23" s="7"/>
     </row>
     <row r="24" ht="14.25" customHeight="1">
-      <c r="A24" s="6"/>
-      <c r="B24" s="6"/>
+      <c r="A24" s="7"/>
+      <c r="B24" s="7"/>
     </row>
     <row r="25" ht="14.25" customHeight="1">
-      <c r="A25" s="6"/>
-      <c r="B25" s="6"/>
+      <c r="A25" s="7"/>
+      <c r="B25" s="7"/>
     </row>
     <row r="26" ht="14.25" customHeight="1">
-      <c r="A26" s="6"/>
-      <c r="B26" s="6"/>
+      <c r="A26" s="7"/>
+      <c r="B26" s="7"/>
     </row>
     <row r="27" ht="14.25" customHeight="1">
-      <c r="A27" s="6"/>
-      <c r="B27" s="6"/>
+      <c r="A27" s="7"/>
+      <c r="B27" s="7"/>
     </row>
     <row r="28" ht="14.25" customHeight="1">
-      <c r="A28" s="6"/>
-      <c r="B28" s="6"/>
+      <c r="A28" s="7"/>
+      <c r="B28" s="7"/>
     </row>
     <row r="29" ht="14.25" customHeight="1">
-      <c r="A29" s="6"/>
-      <c r="B29" s="6"/>
+      <c r="A29" s="7"/>
+      <c r="B29" s="7"/>
     </row>
     <row r="30" ht="14.25" customHeight="1">
-      <c r="A30" s="6"/>
-      <c r="B30" s="6"/>
+      <c r="A30" s="7"/>
+      <c r="B30" s="7"/>
     </row>
     <row r="31" ht="14.25" customHeight="1">
-      <c r="A31" s="6"/>
-      <c r="B31" s="6"/>
+      <c r="A31" s="7"/>
+      <c r="B31" s="7"/>
     </row>
     <row r="32" ht="14.25" customHeight="1">
-      <c r="A32" s="6"/>
-      <c r="B32" s="6"/>
+      <c r="A32" s="7"/>
+      <c r="B32" s="7"/>
     </row>
     <row r="33" ht="14.25" customHeight="1">
-      <c r="A33" s="6"/>
-      <c r="B33" s="6"/>
+      <c r="A33" s="7"/>
+      <c r="B33" s="7"/>
     </row>
     <row r="34" ht="14.25" customHeight="1">
-      <c r="A34" s="6"/>
-      <c r="B34" s="6"/>
+      <c r="A34" s="7"/>
+      <c r="B34" s="7"/>
     </row>
     <row r="35" ht="14.25" customHeight="1">
-      <c r="A35" s="6"/>
-      <c r="B35" s="6"/>
+      <c r="A35" s="7"/>
+      <c r="B35" s="7"/>
     </row>
     <row r="36" ht="14.25" customHeight="1">
-      <c r="A36" s="6"/>
-      <c r="B36" s="6"/>
+      <c r="A36" s="7"/>
+      <c r="B36" s="7"/>
     </row>
     <row r="37" ht="14.25" customHeight="1">
-      <c r="A37" s="6"/>
-      <c r="B37" s="6"/>
+      <c r="A37" s="7"/>
+      <c r="B37" s="7"/>
     </row>
     <row r="38" ht="14.25" customHeight="1">
-      <c r="A38" s="6"/>
-      <c r="B38" s="6"/>
+      <c r="A38" s="7"/>
+      <c r="B38" s="7"/>
     </row>
     <row r="39" ht="14.25" customHeight="1">
-      <c r="A39" s="6"/>
-      <c r="B39" s="6"/>
+      <c r="A39" s="7"/>
+      <c r="B39" s="7"/>
     </row>
     <row r="40" ht="14.25" customHeight="1">
-      <c r="A40" s="6"/>
-      <c r="B40" s="6"/>
+      <c r="A40" s="7"/>
+      <c r="B40" s="7"/>
     </row>
     <row r="41" ht="14.25" customHeight="1">
-      <c r="A41" s="6"/>
-      <c r="B41" s="6"/>
+      <c r="A41" s="7"/>
+      <c r="B41" s="7"/>
     </row>
     <row r="42" ht="14.25" customHeight="1">
-      <c r="A42" s="6"/>
-      <c r="B42" s="6"/>
+      <c r="A42" s="7"/>
+      <c r="B42" s="7"/>
     </row>
     <row r="43" ht="14.25" customHeight="1">
-      <c r="A43" s="6"/>
-      <c r="B43" s="6"/>
+      <c r="A43" s="7"/>
+      <c r="B43" s="7"/>
     </row>
     <row r="44" ht="14.25" customHeight="1">
-      <c r="A44" s="6"/>
-      <c r="B44" s="6"/>
+      <c r="A44" s="7"/>
+      <c r="B44" s="7"/>
     </row>
     <row r="45" ht="14.25" customHeight="1">
-      <c r="A45" s="6"/>
-      <c r="B45" s="6"/>
+      <c r="A45" s="7"/>
+      <c r="B45" s="7"/>
     </row>
     <row r="46" ht="14.25" customHeight="1">
-      <c r="A46" s="6"/>
-      <c r="B46" s="6"/>
+      <c r="A46" s="7"/>
+      <c r="B46" s="7"/>
     </row>
     <row r="47" ht="14.25" customHeight="1">
-      <c r="A47" s="6"/>
-      <c r="B47" s="6"/>
+      <c r="A47" s="7"/>
+      <c r="B47" s="7"/>
     </row>
     <row r="48" ht="14.25" customHeight="1">
-      <c r="A48" s="6"/>
-      <c r="B48" s="6"/>
+      <c r="A48" s="7"/>
+      <c r="B48" s="7"/>
     </row>
     <row r="49" ht="14.25" customHeight="1">
-      <c r="A49" s="6"/>
-      <c r="B49" s="6"/>
+      <c r="A49" s="7"/>
+      <c r="B49" s="7"/>
     </row>
     <row r="50" ht="14.25" customHeight="1">
-      <c r="A50" s="6"/>
-      <c r="B50" s="6"/>
+      <c r="A50" s="7"/>
+      <c r="B50" s="7"/>
     </row>
     <row r="51" ht="14.25" customHeight="1">
-      <c r="A51" s="6"/>
-      <c r="B51" s="6"/>
+      <c r="A51" s="7"/>
+      <c r="B51" s="7"/>
     </row>
     <row r="52" ht="14.25" customHeight="1">
-      <c r="A52" s="6"/>
-      <c r="B52" s="6"/>
+      <c r="A52" s="7"/>
+      <c r="B52" s="7"/>
     </row>
     <row r="53" ht="14.25" customHeight="1">
-      <c r="A53" s="6"/>
-      <c r="B53" s="6"/>
+      <c r="A53" s="7"/>
+      <c r="B53" s="7"/>
     </row>
     <row r="54" ht="14.25" customHeight="1">
-      <c r="A54" s="6"/>
-      <c r="B54" s="6"/>
+      <c r="A54" s="7"/>
+      <c r="B54" s="7"/>
     </row>
     <row r="55" ht="14.25" customHeight="1">
-      <c r="A55" s="6"/>
-      <c r="B55" s="6"/>
+      <c r="A55" s="7"/>
+      <c r="B55" s="7"/>
     </row>
     <row r="56" ht="14.25" customHeight="1">
-      <c r="A56" s="6"/>
-      <c r="B56" s="6"/>
+      <c r="A56" s="7"/>
+      <c r="B56" s="7"/>
     </row>
     <row r="57" ht="14.25" customHeight="1">
-      <c r="A57" s="6"/>
-      <c r="B57" s="6"/>
+      <c r="A57" s="7"/>
+      <c r="B57" s="7"/>
     </row>
     <row r="58" ht="14.25" customHeight="1">
-      <c r="A58" s="6"/>
-      <c r="B58" s="6"/>
+      <c r="A58" s="7"/>
+      <c r="B58" s="7"/>
     </row>
     <row r="59" ht="14.25" customHeight="1">
-      <c r="A59" s="6"/>
-      <c r="B59" s="6"/>
+      <c r="A59" s="7"/>
+      <c r="B59" s="7"/>
     </row>
     <row r="60" ht="14.25" customHeight="1">
-      <c r="A60" s="6"/>
-      <c r="B60" s="6"/>
+      <c r="A60" s="7"/>
+      <c r="B60" s="7"/>
     </row>
     <row r="61" ht="14.25" customHeight="1">
-      <c r="A61" s="6"/>
-      <c r="B61" s="6"/>
+      <c r="A61" s="7"/>
+      <c r="B61" s="7"/>
     </row>
     <row r="62" ht="14.25" customHeight="1">
-      <c r="A62" s="6"/>
-      <c r="B62" s="6"/>
+      <c r="A62" s="7"/>
+      <c r="B62" s="7"/>
     </row>
     <row r="63" ht="14.25" customHeight="1">
-      <c r="A63" s="6"/>
-      <c r="B63" s="6"/>
+      <c r="A63" s="7"/>
+      <c r="B63" s="7"/>
     </row>
     <row r="64" ht="14.25" customHeight="1">
-      <c r="A64" s="6"/>
-      <c r="B64" s="6"/>
+      <c r="A64" s="7"/>
+      <c r="B64" s="7"/>
     </row>
     <row r="65" ht="14.25" customHeight="1">
-      <c r="A65" s="6"/>
-      <c r="B65" s="6"/>
+      <c r="A65" s="7"/>
+      <c r="B65" s="7"/>
     </row>
     <row r="66" ht="14.25" customHeight="1">
-      <c r="A66" s="6"/>
-      <c r="B66" s="6"/>
+      <c r="A66" s="7"/>
+      <c r="B66" s="7"/>
     </row>
     <row r="67" ht="14.25" customHeight="1">
-      <c r="A67" s="6"/>
-      <c r="B67" s="6"/>
+      <c r="A67" s="7"/>
+      <c r="B67" s="7"/>
     </row>
     <row r="68" ht="14.25" customHeight="1">
-      <c r="A68" s="6"/>
-      <c r="B68" s="6"/>
+      <c r="A68" s="7"/>
+      <c r="B68" s="7"/>
     </row>
     <row r="69" ht="14.25" customHeight="1">
-      <c r="A69" s="6"/>
-      <c r="B69" s="6"/>
+      <c r="A69" s="7"/>
+      <c r="B69" s="7"/>
     </row>
     <row r="70" ht="14.25" customHeight="1">
-      <c r="A70" s="6"/>
-      <c r="B70" s="6"/>
+      <c r="A70" s="7"/>
+      <c r="B70" s="7"/>
     </row>
     <row r="71" ht="14.25" customHeight="1">
-      <c r="A71" s="6"/>
-      <c r="B71" s="6"/>
+      <c r="A71" s="7"/>
+      <c r="B71" s="7"/>
     </row>
     <row r="72" ht="14.25" customHeight="1">
-      <c r="A72" s="6"/>
-      <c r="B72" s="6"/>
+      <c r="A72" s="7"/>
+      <c r="B72" s="7"/>
     </row>
     <row r="73" ht="14.25" customHeight="1">
-      <c r="A73" s="6"/>
-      <c r="B73" s="6"/>
+      <c r="A73" s="7"/>
+      <c r="B73" s="7"/>
     </row>
     <row r="74" ht="14.25" customHeight="1">
-      <c r="A74" s="6"/>
-      <c r="B74" s="6"/>
+      <c r="A74" s="7"/>
+      <c r="B74" s="7"/>
     </row>
     <row r="75" ht="14.25" customHeight="1">
-      <c r="A75" s="6"/>
-      <c r="B75" s="6"/>
+      <c r="A75" s="7"/>
+      <c r="B75" s="7"/>
     </row>
     <row r="76" ht="14.25" customHeight="1">
-      <c r="A76" s="6"/>
-      <c r="B76" s="6"/>
+      <c r="A76" s="7"/>
+      <c r="B76" s="7"/>
     </row>
     <row r="77" ht="14.25" customHeight="1">
-      <c r="A77" s="6"/>
-      <c r="B77" s="6"/>
+      <c r="A77" s="7"/>
+      <c r="B77" s="7"/>
     </row>
     <row r="78" ht="14.25" customHeight="1">
-      <c r="A78" s="6"/>
-      <c r="B78" s="6"/>
+      <c r="A78" s="7"/>
+      <c r="B78" s="7"/>
     </row>
     <row r="79" ht="14.25" customHeight="1">
-      <c r="A79" s="6"/>
-      <c r="B79" s="6"/>
+      <c r="A79" s="7"/>
+      <c r="B79" s="7"/>
     </row>
     <row r="80" ht="14.25" customHeight="1">
-      <c r="A80" s="6"/>
-      <c r="B80" s="6"/>
+      <c r="A80" s="7"/>
+      <c r="B80" s="7"/>
     </row>
     <row r="81" ht="14.25" customHeight="1">
-      <c r="A81" s="6"/>
-      <c r="B81" s="6"/>
+      <c r="A81" s="7"/>
+      <c r="B81" s="7"/>
     </row>
     <row r="82" ht="14.25" customHeight="1">
-      <c r="A82" s="6"/>
-      <c r="B82" s="6"/>
+      <c r="A82" s="7"/>
+      <c r="B82" s="7"/>
     </row>
     <row r="83" ht="14.25" customHeight="1">
-      <c r="A83" s="6"/>
-      <c r="B83" s="6"/>
+      <c r="A83" s="7"/>
+      <c r="B83" s="7"/>
     </row>
     <row r="84" ht="14.25" customHeight="1">
-      <c r="A84" s="6"/>
-      <c r="B84" s="6"/>
+      <c r="A84" s="7"/>
+      <c r="B84" s="7"/>
     </row>
     <row r="85" ht="14.25" customHeight="1">
-      <c r="A85" s="6"/>
-      <c r="B85" s="6"/>
+      <c r="A85" s="7"/>
+      <c r="B85" s="7"/>
     </row>
     <row r="86" ht="14.25" customHeight="1">
-      <c r="A86" s="6"/>
-      <c r="B86" s="6"/>
+      <c r="A86" s="7"/>
+      <c r="B86" s="7"/>
     </row>
     <row r="87" ht="14.25" customHeight="1">
-      <c r="A87" s="6"/>
-      <c r="B87" s="6"/>
+      <c r="A87" s="7"/>
+      <c r="B87" s="7"/>
     </row>
     <row r="88" ht="14.25" customHeight="1">
-      <c r="A88" s="6"/>
-      <c r="B88" s="6"/>
+      <c r="A88" s="7"/>
+      <c r="B88" s="7"/>
     </row>
     <row r="89" ht="14.25" customHeight="1">
-      <c r="A89" s="6"/>
-      <c r="B89" s="6"/>
+      <c r="A89" s="7"/>
+      <c r="B89" s="7"/>
     </row>
     <row r="90" ht="14.25" customHeight="1">
-      <c r="A90" s="6"/>
-      <c r="B90" s="6"/>
+      <c r="A90" s="7"/>
+      <c r="B90" s="7"/>
     </row>
     <row r="91" ht="14.25" customHeight="1">
-      <c r="A91" s="6"/>
-      <c r="B91" s="6"/>
+      <c r="A91" s="7"/>
+      <c r="B91" s="7"/>
     </row>
     <row r="92" ht="14.25" customHeight="1">
-      <c r="A92" s="6"/>
-      <c r="B92" s="6"/>
+      <c r="A92" s="7"/>
+      <c r="B92" s="7"/>
     </row>
     <row r="93" ht="14.25" customHeight="1">
-      <c r="A93" s="6"/>
-      <c r="B93" s="6"/>
+      <c r="A93" s="7"/>
+      <c r="B93" s="7"/>
     </row>
     <row r="94" ht="14.25" customHeight="1">
-      <c r="A94" s="6"/>
-      <c r="B94" s="6"/>
+      <c r="A94" s="7"/>
+      <c r="B94" s="7"/>
     </row>
     <row r="95" ht="14.25" customHeight="1">
-      <c r="A95" s="6"/>
-      <c r="B95" s="6"/>
+      <c r="A95" s="7"/>
+      <c r="B95" s="7"/>
     </row>
     <row r="96" ht="14.25" customHeight="1">
-      <c r="A96" s="6"/>
-      <c r="B96" s="6"/>
+      <c r="A96" s="7"/>
+      <c r="B96" s="7"/>
     </row>
     <row r="97" ht="14.25" customHeight="1">
-      <c r="A97" s="6"/>
-      <c r="B97" s="6"/>
+      <c r="A97" s="7"/>
+      <c r="B97" s="7"/>
     </row>
     <row r="98" ht="14.25" customHeight="1">
-      <c r="A98" s="6"/>
-      <c r="B98" s="6"/>
+      <c r="A98" s="7"/>
+      <c r="B98" s="7"/>
     </row>
     <row r="99" ht="14.25" customHeight="1">
-      <c r="A99" s="6"/>
-      <c r="B99" s="6"/>
+      <c r="A99" s="7"/>
+      <c r="B99" s="7"/>
     </row>
     <row r="100" ht="14.25" customHeight="1">
-      <c r="A100" s="6"/>
-      <c r="B100" s="6"/>
+      <c r="A100" s="7"/>
+      <c r="B100" s="7"/>
     </row>
     <row r="101" ht="14.25" customHeight="1">
-      <c r="A101" s="6"/>
-      <c r="B101" s="6"/>
+      <c r="A101" s="7"/>
+      <c r="B101" s="7"/>
     </row>
     <row r="102" ht="14.25" customHeight="1">
-      <c r="A102" s="6"/>
-      <c r="B102" s="6"/>
+      <c r="A102" s="7"/>
+      <c r="B102" s="7"/>
     </row>
     <row r="103" ht="14.25" customHeight="1">
-      <c r="A103" s="6"/>
-      <c r="B103" s="6"/>
+      <c r="A103" s="7"/>
+      <c r="B103" s="7"/>
     </row>
     <row r="104" ht="14.25" customHeight="1">
-      <c r="A104" s="6"/>
-      <c r="B104" s="6"/>
+      <c r="A104" s="7"/>
+      <c r="B104" s="7"/>
     </row>
     <row r="105" ht="14.25" customHeight="1">
-      <c r="A105" s="6"/>
-      <c r="B105" s="6"/>
+      <c r="A105" s="7"/>
+      <c r="B105" s="7"/>
     </row>
     <row r="106" ht="14.25" customHeight="1">
-      <c r="A106" s="6"/>
-      <c r="B106" s="6"/>
+      <c r="A106" s="7"/>
+      <c r="B106" s="7"/>
     </row>
     <row r="107" ht="14.25" customHeight="1">
-      <c r="A107" s="6"/>
-      <c r="B107" s="6"/>
+      <c r="A107" s="7"/>
+      <c r="B107" s="7"/>
     </row>
     <row r="108" ht="14.25" customHeight="1">
-      <c r="A108" s="6"/>
-      <c r="B108" s="6"/>
+      <c r="A108" s="7"/>
+      <c r="B108" s="7"/>
     </row>
     <row r="109" ht="14.25" customHeight="1">
-      <c r="A109" s="6"/>
-      <c r="B109" s="6"/>
+      <c r="A109" s="7"/>
+      <c r="B109" s="7"/>
     </row>
     <row r="110" ht="14.25" customHeight="1">
-      <c r="A110" s="6"/>
-      <c r="B110" s="6"/>
+      <c r="A110" s="7"/>
+      <c r="B110" s="7"/>
     </row>
     <row r="111" ht="14.25" customHeight="1">
-      <c r="A111" s="6"/>
-      <c r="B111" s="6"/>
+      <c r="A111" s="7"/>
+      <c r="B111" s="7"/>
     </row>
     <row r="112" ht="14.25" customHeight="1">
-      <c r="A112" s="6"/>
-      <c r="B112" s="6"/>
+      <c r="A112" s="7"/>
+      <c r="B112" s="7"/>
     </row>
     <row r="113" ht="14.25" customHeight="1">
-      <c r="A113" s="6"/>
-      <c r="B113" s="6"/>
+      <c r="A113" s="7"/>
+      <c r="B113" s="7"/>
     </row>
     <row r="114" ht="14.25" customHeight="1">
-      <c r="A114" s="6"/>
-      <c r="B114" s="6"/>
+      <c r="A114" s="7"/>
+      <c r="B114" s="7"/>
     </row>
     <row r="115" ht="14.25" customHeight="1">
-      <c r="A115" s="6"/>
-      <c r="B115" s="6"/>
+      <c r="A115" s="7"/>
+      <c r="B115" s="7"/>
     </row>
     <row r="116" ht="14.25" customHeight="1">
-      <c r="A116" s="6"/>
-      <c r="B116" s="6"/>
+      <c r="A116" s="7"/>
+      <c r="B116" s="7"/>
     </row>
     <row r="117" ht="14.25" customHeight="1">
-      <c r="A117" s="6"/>
-      <c r="B117" s="6"/>
+      <c r="A117" s="7"/>
+      <c r="B117" s="7"/>
     </row>
     <row r="118" ht="14.25" customHeight="1">
-      <c r="A118" s="6"/>
-      <c r="B118" s="6"/>
+      <c r="A118" s="7"/>
+      <c r="B118" s="7"/>
     </row>
     <row r="119" ht="14.25" customHeight="1">
-      <c r="A119" s="6"/>
-      <c r="B119" s="6"/>
+      <c r="A119" s="7"/>
+      <c r="B119" s="7"/>
     </row>
     <row r="120" ht="14.25" customHeight="1">
-      <c r="A120" s="6"/>
-      <c r="B120" s="6"/>
+      <c r="A120" s="7"/>
+      <c r="B120" s="7"/>
     </row>
     <row r="121" ht="14.25" customHeight="1">
-      <c r="A121" s="6"/>
-      <c r="B121" s="6"/>
+      <c r="A121" s="7"/>
+      <c r="B121" s="7"/>
     </row>
     <row r="122" ht="14.25" customHeight="1">
-      <c r="A122" s="6"/>
-      <c r="B122" s="6"/>
+      <c r="A122" s="7"/>
+      <c r="B122" s="7"/>
     </row>
     <row r="123" ht="14.25" customHeight="1">
-      <c r="A123" s="6"/>
-      <c r="B123" s="6"/>
+      <c r="A123" s="7"/>
+      <c r="B123" s="7"/>
     </row>
     <row r="124" ht="14.25" customHeight="1">
-      <c r="A124" s="6"/>
-      <c r="B124" s="6"/>
+      <c r="A124" s="7"/>
+      <c r="B124" s="7"/>
     </row>
     <row r="125" ht="14.25" customHeight="1">
-      <c r="A125" s="6"/>
-      <c r="B125" s="6"/>
+      <c r="A125" s="7"/>
+      <c r="B125" s="7"/>
     </row>
     <row r="126" ht="14.25" customHeight="1">
-      <c r="A126" s="6"/>
-      <c r="B126" s="6"/>
+      <c r="A126" s="7"/>
+      <c r="B126" s="7"/>
     </row>
     <row r="127" ht="14.25" customHeight="1">
-      <c r="A127" s="6"/>
-      <c r="B127" s="6"/>
+      <c r="A127" s="7"/>
+      <c r="B127" s="7"/>
     </row>
     <row r="128" ht="14.25" customHeight="1">
-      <c r="A128" s="6"/>
-      <c r="B128" s="6"/>
+      <c r="A128" s="7"/>
+      <c r="B128" s="7"/>
     </row>
     <row r="129" ht="14.25" customHeight="1">
-      <c r="A129" s="6"/>
-      <c r="B129" s="6"/>
+      <c r="A129" s="7"/>
+      <c r="B129" s="7"/>
     </row>
     <row r="130" ht="14.25" customHeight="1">
-      <c r="A130" s="6"/>
-      <c r="B130" s="6"/>
+      <c r="A130" s="7"/>
+      <c r="B130" s="7"/>
     </row>
     <row r="131" ht="14.25" customHeight="1">
-      <c r="A131" s="6"/>
-      <c r="B131" s="6"/>
+      <c r="A131" s="7"/>
+      <c r="B131" s="7"/>
     </row>
     <row r="132" ht="14.25" customHeight="1">
-      <c r="A132" s="6"/>
-      <c r="B132" s="6"/>
+      <c r="A132" s="7"/>
+      <c r="B132" s="7"/>
     </row>
     <row r="133" ht="14.25" customHeight="1">
-      <c r="A133" s="6"/>
-      <c r="B133" s="6"/>
+      <c r="A133" s="7"/>
+      <c r="B133" s="7"/>
     </row>
     <row r="134" ht="14.25" customHeight="1">
-      <c r="A134" s="6"/>
-      <c r="B134" s="6"/>
+      <c r="A134" s="7"/>
+      <c r="B134" s="7"/>
     </row>
     <row r="135" ht="14.25" customHeight="1">
-      <c r="A135" s="6"/>
-      <c r="B135" s="6"/>
+      <c r="A135" s="7"/>
+      <c r="B135" s="7"/>
     </row>
     <row r="136" ht="14.25" customHeight="1">
-      <c r="A136" s="6"/>
-      <c r="B136" s="6"/>
+      <c r="A136" s="7"/>
+      <c r="B136" s="7"/>
     </row>
     <row r="137" ht="14.25" customHeight="1">
-      <c r="A137" s="6"/>
-      <c r="B137" s="6"/>
+      <c r="A137" s="7"/>
+      <c r="B137" s="7"/>
     </row>
     <row r="138" ht="14.25" customHeight="1">
-      <c r="A138" s="6"/>
-      <c r="B138" s="6"/>
+      <c r="A138" s="7"/>
+      <c r="B138" s="7"/>
     </row>
     <row r="139" ht="14.25" customHeight="1">
-      <c r="A139" s="6"/>
-      <c r="B139" s="6"/>
+      <c r="A139" s="7"/>
+      <c r="B139" s="7"/>
     </row>
     <row r="140" ht="14.25" customHeight="1">
-      <c r="A140" s="6"/>
-      <c r="B140" s="6"/>
+      <c r="A140" s="7"/>
+      <c r="B140" s="7"/>
     </row>
     <row r="141" ht="14.25" customHeight="1">
-      <c r="A141" s="6"/>
-      <c r="B141" s="6"/>
+      <c r="A141" s="7"/>
+      <c r="B141" s="7"/>
     </row>
     <row r="142" ht="14.25" customHeight="1">
-      <c r="A142" s="6"/>
-      <c r="B142" s="6"/>
+      <c r="A142" s="7"/>
+      <c r="B142" s="7"/>
     </row>
     <row r="143" ht="14.25" customHeight="1">
-      <c r="A143" s="6"/>
-      <c r="B143" s="6"/>
+      <c r="A143" s="7"/>
+      <c r="B143" s="7"/>
     </row>
     <row r="144" ht="14.25" customHeight="1">
-      <c r="A144" s="6"/>
-      <c r="B144" s="6"/>
+      <c r="A144" s="7"/>
+      <c r="B144" s="7"/>
     </row>
     <row r="145" ht="14.25" customHeight="1">
-      <c r="A145" s="6"/>
-      <c r="B145" s="6"/>
+      <c r="A145" s="7"/>
+      <c r="B145" s="7"/>
     </row>
     <row r="146" ht="14.25" customHeight="1">
-      <c r="A146" s="6"/>
-      <c r="B146" s="6"/>
+      <c r="A146" s="7"/>
+      <c r="B146" s="7"/>
     </row>
     <row r="147" ht="14.25" customHeight="1">
-      <c r="A147" s="6"/>
-      <c r="B147" s="6"/>
+      <c r="A147" s="7"/>
+      <c r="B147" s="7"/>
     </row>
     <row r="148" ht="14.25" customHeight="1">
-      <c r="A148" s="6"/>
-      <c r="B148" s="6"/>
+      <c r="A148" s="7"/>
+      <c r="B148" s="7"/>
     </row>
     <row r="149" ht="14.25" customHeight="1">
-      <c r="A149" s="6"/>
-      <c r="B149" s="6"/>
+      <c r="A149" s="7"/>
+      <c r="B149" s="7"/>
     </row>
     <row r="150" ht="14.25" customHeight="1">
-      <c r="A150" s="6"/>
-      <c r="B150" s="6"/>
+      <c r="A150" s="7"/>
+      <c r="B150" s="7"/>
     </row>
     <row r="151" ht="14.25" customHeight="1">
-      <c r="A151" s="6"/>
-      <c r="B151" s="6"/>
+      <c r="A151" s="7"/>
+      <c r="B151" s="7"/>
     </row>
     <row r="152" ht="14.25" customHeight="1">
-      <c r="A152" s="6"/>
-      <c r="B152" s="6"/>
+      <c r="A152" s="7"/>
+      <c r="B152" s="7"/>
     </row>
     <row r="153" ht="14.25" customHeight="1">
-      <c r="A153" s="6"/>
-      <c r="B153" s="6"/>
+      <c r="A153" s="7"/>
+      <c r="B153" s="7"/>
     </row>
     <row r="154" ht="14.25" customHeight="1">
-      <c r="A154" s="6"/>
-      <c r="B154" s="6"/>
+      <c r="A154" s="7"/>
+      <c r="B154" s="7"/>
     </row>
     <row r="155" ht="14.25" customHeight="1">
-      <c r="A155" s="6"/>
-      <c r="B155" s="6"/>
+      <c r="A155" s="7"/>
+      <c r="B155" s="7"/>
     </row>
     <row r="156" ht="14.25" customHeight="1">
-      <c r="A156" s="6"/>
-      <c r="B156" s="6"/>
+      <c r="A156" s="7"/>
+      <c r="B156" s="7"/>
     </row>
     <row r="157" ht="14.25" customHeight="1">
-      <c r="A157" s="6"/>
-      <c r="B157" s="6"/>
+      <c r="A157" s="7"/>
+      <c r="B157" s="7"/>
     </row>
     <row r="158" ht="14.25" customHeight="1">
-      <c r="A158" s="6"/>
-      <c r="B158" s="6"/>
+      <c r="A158" s="7"/>
+      <c r="B158" s="7"/>
     </row>
     <row r="159" ht="14.25" customHeight="1">
-      <c r="A159" s="6"/>
-      <c r="B159" s="6"/>
+      <c r="A159" s="7"/>
+      <c r="B159" s="7"/>
     </row>
     <row r="160" ht="14.25" customHeight="1">
-      <c r="A160" s="6"/>
-      <c r="B160" s="6"/>
+      <c r="A160" s="7"/>
+      <c r="B160" s="7"/>
     </row>
     <row r="161" ht="14.25" customHeight="1">
-      <c r="A161" s="6"/>
-      <c r="B161" s="6"/>
+      <c r="A161" s="7"/>
+      <c r="B161" s="7"/>
     </row>
     <row r="162" ht="14.25" customHeight="1">
-      <c r="A162" s="6"/>
-      <c r="B162" s="6"/>
+      <c r="A162" s="7"/>
+      <c r="B162" s="7"/>
     </row>
     <row r="163" ht="14.25" customHeight="1">
-      <c r="A163" s="6"/>
-      <c r="B163" s="6"/>
+      <c r="A163" s="7"/>
+      <c r="B163" s="7"/>
     </row>
     <row r="164" ht="14.25" customHeight="1">
-      <c r="A164" s="6"/>
-      <c r="B164" s="6"/>
+      <c r="A164" s="7"/>
+      <c r="B164" s="7"/>
     </row>
     <row r="165" ht="14.25" customHeight="1">
-      <c r="A165" s="6"/>
-      <c r="B165" s="6"/>
+      <c r="A165" s="7"/>
+      <c r="B165" s="7"/>
     </row>
     <row r="166" ht="14.25" customHeight="1">
-      <c r="A166" s="6"/>
-      <c r="B166" s="6"/>
+      <c r="A166" s="7"/>
+      <c r="B166" s="7"/>
     </row>
     <row r="167" ht="14.25" customHeight="1">
-      <c r="A167" s="6"/>
-      <c r="B167" s="6"/>
+      <c r="A167" s="7"/>
+      <c r="B167" s="7"/>
     </row>
     <row r="168" ht="14.25" customHeight="1">
-      <c r="A168" s="6"/>
-      <c r="B168" s="6"/>
+      <c r="A168" s="7"/>
+      <c r="B168" s="7"/>
     </row>
     <row r="169" ht="14.25" customHeight="1">
-      <c r="A169" s="6"/>
-      <c r="B169" s="6"/>
+      <c r="A169" s="7"/>
+      <c r="B169" s="7"/>
     </row>
     <row r="170" ht="14.25" customHeight="1">
-      <c r="A170" s="6"/>
-      <c r="B170" s="6"/>
+      <c r="A170" s="7"/>
+      <c r="B170" s="7"/>
     </row>
     <row r="171" ht="14.25" customHeight="1">
-      <c r="A171" s="6"/>
-      <c r="B171" s="6"/>
+      <c r="A171" s="7"/>
+      <c r="B171" s="7"/>
     </row>
     <row r="172" ht="14.25" customHeight="1">
-      <c r="A172" s="6"/>
-      <c r="B172" s="6"/>
+      <c r="A172" s="7"/>
+      <c r="B172" s="7"/>
     </row>
     <row r="173" ht="14.25" customHeight="1">
-      <c r="A173" s="6"/>
-      <c r="B173" s="6"/>
+      <c r="A173" s="7"/>
+      <c r="B173" s="7"/>
     </row>
     <row r="174" ht="14.25" customHeight="1">
-      <c r="A174" s="6"/>
-      <c r="B174" s="6"/>
+      <c r="A174" s="7"/>
+      <c r="B174" s="7"/>
     </row>
     <row r="175" ht="14.25" customHeight="1">
-      <c r="A175" s="6"/>
-      <c r="B175" s="6"/>
+      <c r="A175" s="7"/>
+      <c r="B175" s="7"/>
     </row>
     <row r="176" ht="14.25" customHeight="1">
-      <c r="A176" s="6"/>
-      <c r="B176" s="6"/>
+      <c r="A176" s="7"/>
+      <c r="B176" s="7"/>
     </row>
     <row r="177" ht="14.25" customHeight="1">
-      <c r="A177" s="6"/>
-      <c r="B177" s="6"/>
+      <c r="A177" s="7"/>
+      <c r="B177" s="7"/>
     </row>
     <row r="178" ht="14.25" customHeight="1">
-      <c r="A178" s="6"/>
-      <c r="B178" s="6"/>
+      <c r="A178" s="7"/>
+      <c r="B178" s="7"/>
     </row>
     <row r="179" ht="14.25" customHeight="1">
-      <c r="A179" s="6"/>
-      <c r="B179" s="6"/>
+      <c r="A179" s="7"/>
+      <c r="B179" s="7"/>
     </row>
     <row r="180" ht="14.25" customHeight="1">
-      <c r="A180" s="6"/>
-      <c r="B180" s="6"/>
+      <c r="A180" s="7"/>
+      <c r="B180" s="7"/>
     </row>
     <row r="181" ht="14.25" customHeight="1">
-      <c r="A181" s="6"/>
-      <c r="B181" s="6"/>
+      <c r="A181" s="7"/>
+      <c r="B181" s="7"/>
     </row>
     <row r="182" ht="14.25" customHeight="1">
-      <c r="A182" s="6"/>
-      <c r="B182" s="6"/>
+      <c r="A182" s="7"/>
+      <c r="B182" s="7"/>
     </row>
     <row r="183" ht="14.25" customHeight="1">
-      <c r="A183" s="6"/>
-      <c r="B183" s="6"/>
+      <c r="A183" s="7"/>
+      <c r="B183" s="7"/>
     </row>
     <row r="184" ht="14.25" customHeight="1">
-      <c r="A184" s="6"/>
-      <c r="B184" s="6"/>
+      <c r="A184" s="7"/>
+      <c r="B184" s="7"/>
     </row>
     <row r="185" ht="14.25" customHeight="1">
-      <c r="A185" s="6"/>
-      <c r="B185" s="6"/>
+      <c r="A185" s="7"/>
+      <c r="B185" s="7"/>
     </row>
     <row r="186" ht="14.25" customHeight="1">
-      <c r="A186" s="6"/>
-      <c r="B186" s="6"/>
+      <c r="A186" s="7"/>
+      <c r="B186" s="7"/>
     </row>
     <row r="187" ht="14.25" customHeight="1">
-      <c r="A187" s="6"/>
-      <c r="B187" s="6"/>
+      <c r="A187" s="7"/>
+      <c r="B187" s="7"/>
     </row>
     <row r="188" ht="14.25" customHeight="1">
-      <c r="A188" s="6"/>
-      <c r="B188" s="6"/>
+      <c r="A188" s="7"/>
+      <c r="B188" s="7"/>
     </row>
     <row r="189" ht="14.25" customHeight="1">
-      <c r="A189" s="6"/>
-      <c r="B189" s="6"/>
+      <c r="A189" s="7"/>
+      <c r="B189" s="7"/>
     </row>
     <row r="190" ht="14.25" customHeight="1">
-      <c r="A190" s="6"/>
-      <c r="B190" s="6"/>
+      <c r="A190" s="7"/>
+      <c r="B190" s="7"/>
     </row>
     <row r="191" ht="14.25" customHeight="1">
-      <c r="A191" s="6"/>
-      <c r="B191" s="6"/>
+      <c r="A191" s="7"/>
+      <c r="B191" s="7"/>
     </row>
     <row r="192" ht="14.25" customHeight="1">
-      <c r="A192" s="6"/>
-      <c r="B192" s="6"/>
+      <c r="A192" s="7"/>
+      <c r="B192" s="7"/>
     </row>
     <row r="193" ht="14.25" customHeight="1">
-      <c r="A193" s="6"/>
-      <c r="B193" s="6"/>
+      <c r="A193" s="7"/>
+      <c r="B193" s="7"/>
     </row>
     <row r="194" ht="14.25" customHeight="1">
-      <c r="A194" s="6"/>
-      <c r="B194" s="6"/>
+      <c r="A194" s="7"/>
+      <c r="B194" s="7"/>
     </row>
     <row r="195" ht="14.25" customHeight="1">
-      <c r="A195" s="6"/>
-      <c r="B195" s="6"/>
+      <c r="A195" s="7"/>
+      <c r="B195" s="7"/>
     </row>
     <row r="196" ht="14.25" customHeight="1">
-      <c r="A196" s="6"/>
-      <c r="B196" s="6"/>
+      <c r="A196" s="7"/>
+      <c r="B196" s="7"/>
     </row>
     <row r="197" ht="14.25" customHeight="1">
-      <c r="A197" s="6"/>
-      <c r="B197" s="6"/>
+      <c r="A197" s="7"/>
+      <c r="B197" s="7"/>
     </row>
     <row r="198" ht="14.25" customHeight="1">
-      <c r="A198" s="6"/>
-      <c r="B198" s="6"/>
+      <c r="A198" s="7"/>
+      <c r="B198" s="7"/>
     </row>
     <row r="199" ht="14.25" customHeight="1">
-      <c r="A199" s="6"/>
-      <c r="B199" s="6"/>
+      <c r="A199" s="7"/>
+      <c r="B199" s="7"/>
     </row>
     <row r="200" ht="14.25" customHeight="1">
-      <c r="A200" s="6"/>
-      <c r="B200" s="6"/>
+      <c r="A200" s="7"/>
+      <c r="B200" s="7"/>
     </row>
     <row r="201" ht="14.25" customHeight="1">
-      <c r="A201" s="6"/>
-      <c r="B201" s="6"/>
+      <c r="A201" s="7"/>
+      <c r="B201" s="7"/>
     </row>
     <row r="202" ht="14.25" customHeight="1">
-      <c r="A202" s="6"/>
-      <c r="B202" s="6"/>
+      <c r="A202" s="7"/>
+      <c r="B202" s="7"/>
     </row>
     <row r="203" ht="14.25" customHeight="1">
-      <c r="A203" s="6"/>
-      <c r="B203" s="6"/>
+      <c r="A203" s="7"/>
+      <c r="B203" s="7"/>
     </row>
     <row r="204" ht="14.25" customHeight="1">
-      <c r="A204" s="6"/>
-      <c r="B204" s="6"/>
+      <c r="A204" s="7"/>
+      <c r="B204" s="7"/>
     </row>
     <row r="205" ht="14.25" customHeight="1">
-      <c r="A205" s="6"/>
-      <c r="B205" s="6"/>
+      <c r="A205" s="7"/>
+      <c r="B205" s="7"/>
     </row>
     <row r="206" ht="14.25" customHeight="1">
-      <c r="A206" s="6"/>
-      <c r="B206" s="6"/>
+      <c r="A206" s="7"/>
+      <c r="B206" s="7"/>
     </row>
     <row r="207" ht="14.25" customHeight="1">
-      <c r="A207" s="6"/>
-      <c r="B207" s="6"/>
+      <c r="A207" s="7"/>
+      <c r="B207" s="7"/>
     </row>
     <row r="208" ht="14.25" customHeight="1">
-      <c r="A208" s="6"/>
-      <c r="B208" s="6"/>
+      <c r="A208" s="7"/>
+      <c r="B208" s="7"/>
     </row>
     <row r="209" ht="14.25" customHeight="1">
-      <c r="A209" s="6"/>
-      <c r="B209" s="6"/>
+      <c r="A209" s="7"/>
+      <c r="B209" s="7"/>
     </row>
     <row r="210" ht="14.25" customHeight="1">
-      <c r="A210" s="6"/>
-      <c r="B210" s="6"/>
+      <c r="A210" s="7"/>
+      <c r="B210" s="7"/>
     </row>
     <row r="211" ht="14.25" customHeight="1">
-      <c r="A211" s="6"/>
-      <c r="B211" s="6"/>
+      <c r="A211" s="7"/>
+      <c r="B211" s="7"/>
     </row>
     <row r="212" ht="14.25" customHeight="1">
-      <c r="A212" s="6"/>
-      <c r="B212" s="6"/>
+      <c r="A212" s="7"/>
+      <c r="B212" s="7"/>
     </row>
     <row r="213" ht="14.25" customHeight="1">
-      <c r="A213" s="6"/>
-      <c r="B213" s="6"/>
+      <c r="A213" s="7"/>
+      <c r="B213" s="7"/>
     </row>
     <row r="214" ht="14.25" customHeight="1">
-      <c r="A214" s="6"/>
-      <c r="B214" s="6"/>
+      <c r="A214" s="7"/>
+      <c r="B214" s="7"/>
     </row>
     <row r="215" ht="14.25" customHeight="1">
-      <c r="A215" s="6"/>
-      <c r="B215" s="6"/>
+      <c r="A215" s="7"/>
+      <c r="B215" s="7"/>
     </row>
     <row r="216" ht="14.25" customHeight="1">
-      <c r="A216" s="6"/>
-      <c r="B216" s="6"/>
+      <c r="A216" s="7"/>
+      <c r="B216" s="7"/>
     </row>
     <row r="217" ht="14.25" customHeight="1">
-      <c r="A217" s="6"/>
-      <c r="B217" s="6"/>
+      <c r="A217" s="7"/>
+      <c r="B217" s="7"/>
     </row>
     <row r="218" ht="14.25" customHeight="1">
-      <c r="A218" s="6"/>
-      <c r="B218" s="6"/>
+      <c r="A218" s="7"/>
+      <c r="B218" s="7"/>
     </row>
     <row r="219" ht="14.25" customHeight="1">
-      <c r="A219" s="6"/>
-      <c r="B219" s="6"/>
+      <c r="A219" s="7"/>
+      <c r="B219" s="7"/>
     </row>
     <row r="220" ht="14.25" customHeight="1">
-      <c r="A220" s="6"/>
-      <c r="B220" s="6"/>
+      <c r="A220" s="7"/>
+      <c r="B220" s="7"/>
     </row>
     <row r="221" ht="15.75" customHeight="1"/>
     <row r="222" ht="15.75" customHeight="1"/>

--- a/database/catalogos/catalogo_maestro.xlsx
+++ b/database/catalogos/catalogo_maestro.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1193" uniqueCount="604">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1205" uniqueCount="609">
   <si>
     <t>slug</t>
   </si>
@@ -439,16 +439,10 @@
     <t>Desechable grande</t>
   </si>
   <si>
-    <t>pozole_chico</t>
-  </si>
-  <si>
-    <t>Pozole chico</t>
-  </si>
-  <si>
-    <t>pozole_grande</t>
-  </si>
-  <si>
-    <t>Pozole grande</t>
+    <t>pozole</t>
+  </si>
+  <si>
+    <t>Pozole</t>
   </si>
   <si>
     <t>otro</t>
@@ -823,6 +817,12 @@
     <t>Bebida del paquete</t>
   </si>
   <si>
+    <t>tamano_pozole</t>
+  </si>
+  <si>
+    <t>Tamano Pozole</t>
+  </si>
+  <si>
     <t>proteina_pozole</t>
   </si>
   <si>
@@ -1552,6 +1552,24 @@
     <t>Bebida del paquete: Te</t>
   </si>
   <si>
+    <t>tamano_pozole_chico</t>
+  </si>
+  <si>
+    <t>Tamano Pozole: Chico</t>
+  </si>
+  <si>
+    <t>Pozole Grande</t>
+  </si>
+  <si>
+    <t>tamano_pozole_grande</t>
+  </si>
+  <si>
+    <t>Tamano Pozole: Grande</t>
+  </si>
+  <si>
+    <t>Pozole Chico</t>
+  </si>
+  <si>
     <t>proteina_pozole_sin_proteina</t>
   </si>
   <si>
@@ -1765,10 +1783,7 @@
     <t>DESECHABLE GRANDE</t>
   </si>
   <si>
-    <t>POZOLE CHICO</t>
-  </si>
-  <si>
-    <t>POZOLE GRANDE</t>
+    <t>POZOLE</t>
   </si>
   <si>
     <t>fecha</t>
@@ -5944,7 +5959,7 @@
       <c r="G53" s="2">
         <v>1.0</v>
       </c>
-      <c r="H53" s="2">
+      <c r="H53" s="4">
         <v>0.0</v>
       </c>
       <c r="I53" s="2">
@@ -5983,10 +5998,10 @@
         <v>13</v>
       </c>
       <c r="D54" s="4">
-        <v>55.0</v>
+        <v>0.0</v>
       </c>
       <c r="E54" s="4">
-        <v>20.0</v>
+        <v>0.0</v>
       </c>
       <c r="F54" s="2">
         <v>1.0</v>
@@ -5994,8 +6009,8 @@
       <c r="G54" s="2">
         <v>1.0</v>
       </c>
-      <c r="H54" s="2">
-        <v>0.0</v>
+      <c r="H54" s="4">
+        <v>1.0</v>
       </c>
       <c r="I54" s="2">
         <v>0.0</v>
@@ -6018,25 +6033,25 @@
       <c r="O54" s="2">
         <v>0.0</v>
       </c>
-      <c r="P54" s="4">
+      <c r="P54" s="2">
         <v>530.0</v>
       </c>
     </row>
     <row r="55" ht="14.25" customHeight="1">
-      <c r="A55" s="4" t="s">
+      <c r="A55" s="2" t="s">
         <v>138</v>
       </c>
-      <c r="B55" s="4" t="s">
+      <c r="B55" s="2" t="s">
         <v>139</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="D55" s="4">
-        <v>95.0</v>
-      </c>
-      <c r="E55" s="4">
-        <v>28.0</v>
+        <v>5</v>
+      </c>
+      <c r="D55" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="E55" s="2">
+        <v>0.0</v>
       </c>
       <c r="F55" s="2">
         <v>1.0</v>
@@ -6060,10 +6075,10 @@
         <v>0.0</v>
       </c>
       <c r="M55" s="2">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="N55" s="2">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="O55" s="2">
         <v>0.0</v>
@@ -6072,56 +6087,7 @@
         <v>540.0</v>
       </c>
     </row>
-    <row r="56" ht="14.25" customHeight="1">
-      <c r="A56" s="2" t="s">
-        <v>140</v>
-      </c>
-      <c r="B56" s="2" t="s">
-        <v>141</v>
-      </c>
-      <c r="C56" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="D56" s="2">
-        <v>0.0</v>
-      </c>
-      <c r="E56" s="2">
-        <v>0.0</v>
-      </c>
-      <c r="F56" s="2">
-        <v>1.0</v>
-      </c>
-      <c r="G56" s="2">
-        <v>1.0</v>
-      </c>
-      <c r="H56" s="2">
-        <v>0.0</v>
-      </c>
-      <c r="I56" s="2">
-        <v>0.0</v>
-      </c>
-      <c r="J56" s="2">
-        <v>0.0</v>
-      </c>
-      <c r="K56" s="2">
-        <v>0.0</v>
-      </c>
-      <c r="L56" s="2">
-        <v>0.0</v>
-      </c>
-      <c r="M56" s="2">
-        <v>0.0</v>
-      </c>
-      <c r="N56" s="2">
-        <v>0.0</v>
-      </c>
-      <c r="O56" s="2">
-        <v>0.0</v>
-      </c>
-      <c r="P56" s="2">
-        <v>550.0</v>
-      </c>
-    </row>
+    <row r="56" ht="14.25" customHeight="1"/>
     <row r="57" ht="14.25" customHeight="1"/>
     <row r="58" ht="14.25" customHeight="1"/>
     <row r="59" ht="14.25" customHeight="1"/>
@@ -6321,7 +6287,7 @@
     <row r="253" ht="14.25" customHeight="1"/>
     <row r="254" ht="14.25" customHeight="1"/>
     <row r="255" ht="14.25" customHeight="1"/>
-    <row r="256" ht="14.25" customHeight="1"/>
+    <row r="256" ht="15.75" customHeight="1"/>
     <row r="257" ht="15.75" customHeight="1"/>
     <row r="258" ht="15.75" customHeight="1"/>
     <row r="259" ht="15.75" customHeight="1"/>
@@ -7068,7 +7034,6 @@
     <row r="1000" ht="15.75" customHeight="1"/>
     <row r="1001" ht="15.75" customHeight="1"/>
     <row r="1002" ht="15.75" customHeight="1"/>
-    <row r="1003" ht="15.75" customHeight="1"/>
   </sheetData>
   <autoFilter ref="$A$1:$P$1"/>
   <printOptions/>
@@ -7105,7 +7070,7 @@
         <v>3</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>4</v>
@@ -7113,10 +7078,10 @@
     </row>
     <row r="2" ht="14.25" customHeight="1">
       <c r="A2" s="2" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="C2" s="2">
         <v>10.0</v>
@@ -7133,10 +7098,10 @@
     </row>
     <row r="3" ht="14.25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="C3" s="2">
         <v>10.0</v>
@@ -7153,10 +7118,10 @@
     </row>
     <row r="4" ht="14.25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="C4" s="2">
         <v>10.0</v>
@@ -7173,10 +7138,10 @@
     </row>
     <row r="5" ht="14.25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="C5" s="2">
         <v>10.0</v>
@@ -7193,10 +7158,10 @@
     </row>
     <row r="6" ht="14.25" customHeight="1">
       <c r="A6" s="2" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="C6" s="2">
         <v>10.0</v>
@@ -7213,10 +7178,10 @@
     </row>
     <row r="7" ht="14.25" customHeight="1">
       <c r="A7" s="2" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="C7" s="2">
         <v>10.0</v>
@@ -7233,10 +7198,10 @@
     </row>
     <row r="8" ht="14.25" customHeight="1">
       <c r="A8" s="2" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="C8" s="2">
         <v>15.0</v>
@@ -7253,10 +7218,10 @@
     </row>
     <row r="9" ht="14.25" customHeight="1">
       <c r="A9" s="2" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="C9" s="2">
         <v>10.0</v>
@@ -7273,10 +7238,10 @@
     </row>
     <row r="10" ht="14.25" customHeight="1">
       <c r="A10" s="2" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="C10" s="2">
         <v>10.0</v>
@@ -7293,10 +7258,10 @@
     </row>
     <row r="11" ht="14.25" customHeight="1">
       <c r="A11" s="2" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="C11" s="2">
         <v>5.0</v>
@@ -7313,10 +7278,10 @@
     </row>
     <row r="12" ht="14.25" customHeight="1">
       <c r="A12" s="2" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="C12" s="2">
         <v>5.0</v>
@@ -7333,10 +7298,10 @@
     </row>
     <row r="13" ht="14.25" customHeight="1">
       <c r="A13" s="2" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="C13" s="2">
         <v>5.0</v>
@@ -7353,10 +7318,10 @@
     </row>
     <row r="14" ht="14.25" customHeight="1">
       <c r="A14" s="2" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="C14" s="2">
         <v>5.0</v>
@@ -7373,10 +7338,10 @@
     </row>
     <row r="15" ht="14.25" customHeight="1">
       <c r="A15" s="2" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="C15" s="2">
         <v>5.0</v>
@@ -7393,10 +7358,10 @@
     </row>
     <row r="16" ht="14.25" customHeight="1">
       <c r="A16" s="2" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="C16" s="2">
         <v>10.0</v>
@@ -7413,10 +7378,10 @@
     </row>
     <row r="17" ht="14.25" customHeight="1">
       <c r="A17" s="2" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="C17" s="2">
         <v>10.0</v>
@@ -7433,10 +7398,10 @@
     </row>
     <row r="18" ht="14.25" customHeight="1">
       <c r="A18" s="2" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="C18" s="2">
         <v>10.0</v>
@@ -7453,10 +7418,10 @@
     </row>
     <row r="19" ht="14.25" customHeight="1">
       <c r="A19" s="2" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="C19" s="2">
         <v>10.0</v>
@@ -7573,10 +7538,10 @@
     </row>
     <row r="25" ht="14.25" customHeight="1">
       <c r="A25" s="2" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="C25" s="2">
         <v>10.0</v>
@@ -7593,10 +7558,10 @@
     </row>
     <row r="26" ht="14.25" customHeight="1">
       <c r="A26" s="2" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="C26" s="2">
         <v>15.0</v>
@@ -7613,10 +7578,10 @@
     </row>
     <row r="27" ht="14.25" customHeight="1">
       <c r="A27" s="2" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="C27" s="2">
         <v>10.0</v>
@@ -7633,10 +7598,10 @@
     </row>
     <row r="28" ht="14.25" customHeight="1">
       <c r="A28" s="2" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="C28" s="2">
         <v>10.0</v>
@@ -7653,10 +7618,10 @@
     </row>
     <row r="29" ht="14.25" customHeight="1">
       <c r="A29" s="2" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="C29" s="2">
         <v>5.0</v>
@@ -7673,10 +7638,10 @@
     </row>
     <row r="30" ht="14.25" customHeight="1">
       <c r="A30" s="2" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="C30" s="2">
         <v>5.0</v>
@@ -7693,10 +7658,10 @@
     </row>
     <row r="31" ht="14.25" customHeight="1">
       <c r="A31" s="2" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="C31" s="2">
         <v>35.0</v>
@@ -7713,10 +7678,10 @@
     </row>
     <row r="32" ht="14.25" customHeight="1">
       <c r="A32" s="2" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="C32" s="2">
         <v>25.0</v>
@@ -7733,10 +7698,10 @@
     </row>
     <row r="33" ht="14.25" customHeight="1">
       <c r="A33" s="2" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="C33" s="2">
         <v>15.0</v>
@@ -7756,7 +7721,7 @@
         <v>80</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="C34" s="2">
         <v>40.0</v>
@@ -7773,10 +7738,10 @@
     </row>
     <row r="35" ht="14.25" customHeight="1">
       <c r="A35" s="2" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="C35" s="2">
         <v>35.0</v>
@@ -7793,10 +7758,10 @@
     </row>
     <row r="36" ht="14.25" customHeight="1">
       <c r="A36" s="2" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="C36" s="2">
         <v>15.0</v>
@@ -7813,10 +7778,10 @@
     </row>
     <row r="37" ht="14.25" customHeight="1">
       <c r="A37" s="2" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="C37" s="2">
         <v>7.0</v>
@@ -8833,39 +8798,39 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>3</v>
       </c>
       <c r="G1" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="I1" s="1" t="s">
         <v>206</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>207</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>208</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>209</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>210</v>
       </c>
     </row>
     <row r="2" ht="14.25" customHeight="1">
       <c r="A2" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>210</v>
+      </c>
+      <c r="C2" s="2" t="s">
         <v>211</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>212</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>213</v>
       </c>
       <c r="D2" s="2">
         <v>1.0</v>
@@ -8880,7 +8845,7 @@
         <v>5.0</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="I2" s="2" t="s">
         <v>7</v>
@@ -8894,13 +8859,13 @@
     </row>
     <row r="3" ht="14.25" customHeight="1">
       <c r="A3" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>214</v>
+      </c>
+      <c r="C3" s="2" t="s">
         <v>215</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>216</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>217</v>
       </c>
       <c r="D3" s="2">
         <v>0.0</v>
@@ -8915,7 +8880,7 @@
         <v>15.0</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="I3" s="2" t="s">
         <v>7</v>
@@ -8929,13 +8894,13 @@
     </row>
     <row r="4" ht="14.25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="D4" s="2">
         <v>1.0</v>
@@ -8950,7 +8915,7 @@
         <v>20.0</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="I4" s="2" t="s">
         <v>7</v>
@@ -8964,13 +8929,13 @@
     </row>
     <row r="5" ht="14.25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="D5" s="2">
         <v>1.0</v>
@@ -8985,7 +8950,7 @@
         <v>25.0</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="I5" s="2" t="s">
         <v>7</v>
@@ -8999,13 +8964,13 @@
     </row>
     <row r="6" ht="14.25" customHeight="1">
       <c r="A6" s="2" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="D6" s="2">
         <v>0.0</v>
@@ -9020,7 +8985,7 @@
         <v>30.0</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="I6" s="2" t="s">
         <v>7</v>
@@ -9034,13 +8999,13 @@
     </row>
     <row r="7" ht="14.25" customHeight="1">
       <c r="A7" s="2" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="D7" s="2">
         <v>1.0</v>
@@ -9055,7 +9020,7 @@
         <v>35.0</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="I7" s="2" t="s">
         <v>7</v>
@@ -9069,13 +9034,13 @@
     </row>
     <row r="8" ht="14.25" customHeight="1">
       <c r="A8" s="2" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="D8" s="2">
         <v>1.0</v>
@@ -9090,7 +9055,7 @@
         <v>45.0</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="I8" s="2" t="s">
         <v>7</v>
@@ -9104,13 +9069,13 @@
     </row>
     <row r="9" ht="14.25" customHeight="1">
       <c r="A9" s="2" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="D9" s="2">
         <v>1.0</v>
@@ -9125,7 +9090,7 @@
         <v>50.0</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="I9" s="2" t="s">
         <v>7</v>
@@ -9139,13 +9104,13 @@
     </row>
     <row r="10" ht="14.25" customHeight="1">
       <c r="A10" s="2" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="D10" s="2">
         <v>1.0</v>
@@ -9160,7 +9125,7 @@
         <v>55.0</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="I10" s="2" t="s">
         <v>10</v>
@@ -9174,13 +9139,13 @@
     </row>
     <row r="11" ht="14.25" customHeight="1">
       <c r="A11" s="2" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="D11" s="2">
         <v>1.0</v>
@@ -9195,7 +9160,7 @@
         <v>60.0</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="I11" s="2" t="s">
         <v>10</v>
@@ -9209,13 +9174,13 @@
     </row>
     <row r="12" ht="14.25" customHeight="1">
       <c r="A12" s="2" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="D12" s="2">
         <v>1.0</v>
@@ -9230,7 +9195,7 @@
         <v>65.0</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="I12" s="2" t="s">
         <v>10</v>
@@ -9244,13 +9209,13 @@
     </row>
     <row r="13" ht="14.25" customHeight="1">
       <c r="A13" s="2" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="D13" s="2">
         <v>1.0</v>
@@ -9265,7 +9230,7 @@
         <v>70.0</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="I13" s="2" t="s">
         <v>10</v>
@@ -9279,13 +9244,13 @@
     </row>
     <row r="14" ht="14.25" customHeight="1">
       <c r="A14" s="2" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="D14" s="2">
         <v>1.0</v>
@@ -9300,7 +9265,7 @@
         <v>80.0</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="I14" s="2" t="s">
         <v>10</v>
@@ -9314,13 +9279,13 @@
     </row>
     <row r="15" ht="14.25" customHeight="1">
       <c r="A15" s="2" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="D15" s="2">
         <v>1.0</v>
@@ -9335,7 +9300,7 @@
         <v>90.0</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="I15" s="2" t="s">
         <v>10</v>
@@ -9349,13 +9314,13 @@
     </row>
     <row r="16" ht="14.25" customHeight="1">
       <c r="A16" s="2" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="D16" s="2">
         <v>1.0</v>
@@ -9370,7 +9335,7 @@
         <v>100.0</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="I16" s="2" t="s">
         <v>10</v>
@@ -9384,13 +9349,13 @@
     </row>
     <row r="17" ht="14.25" customHeight="1">
       <c r="A17" s="2" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="D17" s="2">
         <v>1.0</v>
@@ -9405,7 +9370,7 @@
         <v>110.0</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="I17" s="2" t="s">
         <v>10</v>
@@ -9419,13 +9384,13 @@
     </row>
     <row r="18" ht="14.25" customHeight="1">
       <c r="A18" s="2" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="D18" s="2">
         <v>0.0</v>
@@ -9440,7 +9405,7 @@
         <v>120.0</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="I18" s="2" t="s">
         <v>10</v>
@@ -9454,13 +9419,13 @@
     </row>
     <row r="19" ht="14.25" customHeight="1">
       <c r="A19" s="2" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="D19" s="2">
         <v>0.0</v>
@@ -9475,7 +9440,7 @@
         <v>130.0</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="I19" s="2" t="s">
         <v>10</v>
@@ -9489,13 +9454,13 @@
     </row>
     <row r="20" ht="14.25" customHeight="1">
       <c r="A20" s="2" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="D20" s="2">
         <v>1.0</v>
@@ -9510,7 +9475,7 @@
         <v>140.0</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="I20" s="2" t="s">
         <v>7</v>
@@ -9524,13 +9489,13 @@
     </row>
     <row r="21" ht="14.25" customHeight="1">
       <c r="A21" s="2" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="D21" s="2">
         <v>1.0</v>
@@ -9545,7 +9510,7 @@
         <v>150.0</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="I21" s="2" t="s">
         <v>7</v>
@@ -9559,13 +9524,13 @@
     </row>
     <row r="22" ht="14.25" customHeight="1">
       <c r="A22" s="2" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="D22" s="2">
         <v>1.0</v>
@@ -9580,7 +9545,7 @@
         <v>160.0</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="I22" s="2" t="s">
         <v>7</v>
@@ -9594,13 +9559,13 @@
     </row>
     <row r="23" ht="14.25" customHeight="1">
       <c r="A23" s="2" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="D23" s="2">
         <v>0.0</v>
@@ -9615,7 +9580,7 @@
         <v>170.0</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="I23" s="2" t="s">
         <v>7</v>
@@ -9629,13 +9594,13 @@
     </row>
     <row r="24" ht="14.25" customHeight="1">
       <c r="A24" s="2" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="D24" s="2">
         <v>0.0</v>
@@ -9650,7 +9615,7 @@
         <v>180.0</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="I24" s="2" t="s">
         <v>7</v>
@@ -9664,13 +9629,13 @@
     </row>
     <row r="25" ht="14.25" customHeight="1">
       <c r="A25" s="3" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="D25" s="2">
         <v>1.0</v>
@@ -9685,7 +9650,7 @@
         <v>190.0</v>
       </c>
       <c r="H25" s="3" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="I25" s="2" t="s">
         <v>7</v>
@@ -9699,13 +9664,13 @@
     </row>
     <row r="26" ht="14.25" customHeight="1">
       <c r="A26" s="2" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="D26" s="2">
         <v>0.0</v>
@@ -9720,7 +9685,7 @@
         <v>62.0</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="I26" s="2" t="s">
         <v>10</v>
@@ -9734,13 +9699,13 @@
     </row>
     <row r="27" ht="14.25" customHeight="1">
       <c r="A27" s="5" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="D27" s="5">
         <v>1.0</v>
@@ -9755,7 +9720,7 @@
         <v>200.0</v>
       </c>
       <c r="H27" s="5" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="I27" s="5" t="s">
         <v>7</v>
@@ -9767,7 +9732,41 @@
         <v>0.0</v>
       </c>
     </row>
-    <row r="28" ht="14.25" customHeight="1"/>
+    <row r="28" ht="14.25" customHeight="1">
+      <c r="A28" s="5" t="s">
+        <v>264</v>
+      </c>
+      <c r="B28" s="5" t="s">
+        <v>265</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="D28" s="5">
+        <v>1.0</v>
+      </c>
+      <c r="E28" s="5">
+        <v>0.0</v>
+      </c>
+      <c r="F28" s="5">
+        <v>1.0</v>
+      </c>
+      <c r="G28" s="5">
+        <v>210.0</v>
+      </c>
+      <c r="H28" s="5" t="s">
+        <v>212</v>
+      </c>
+      <c r="I28" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="J28" s="5">
+        <v>0.0</v>
+      </c>
+      <c r="K28" s="5">
+        <v>0.0</v>
+      </c>
+    </row>
     <row r="29" ht="14.25" customHeight="1"/>
     <row r="30" ht="14.25" customHeight="1"/>
     <row r="31" ht="14.25" customHeight="1"/>
@@ -9966,7 +9965,7 @@
     <row r="224" ht="14.25" customHeight="1"/>
     <row r="225" ht="14.25" customHeight="1"/>
     <row r="226" ht="14.25" customHeight="1"/>
-    <row r="227" ht="15.75" customHeight="1"/>
+    <row r="227" ht="14.25" customHeight="1"/>
     <row r="228" ht="15.75" customHeight="1"/>
     <row r="229" ht="15.75" customHeight="1"/>
     <row r="230" ht="15.75" customHeight="1"/>
@@ -10740,6 +10739,7 @@
     <row r="998" ht="15.75" customHeight="1"/>
     <row r="999" ht="15.75" customHeight="1"/>
     <row r="1000" ht="15.75" customHeight="1"/>
+    <row r="1001" ht="15.75" customHeight="1"/>
   </sheetData>
   <autoFilter ref="$A$1:$K$1"/>
   <printOptions/>
@@ -10794,7 +10794,7 @@
     </row>
     <row r="2" ht="14.25" customHeight="1">
       <c r="A2" s="2" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>268</v>
@@ -10820,7 +10820,7 @@
     </row>
     <row r="3" ht="14.25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>271</v>
@@ -10846,7 +10846,7 @@
     </row>
     <row r="4" ht="14.25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>274</v>
@@ -10872,7 +10872,7 @@
     </row>
     <row r="5" ht="14.25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>277</v>
@@ -10898,7 +10898,7 @@
     </row>
     <row r="6" ht="14.25" customHeight="1">
       <c r="A6" s="2" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>280</v>
@@ -10924,10 +10924,10 @@
     </row>
     <row r="7" ht="14.25" customHeight="1">
       <c r="A7" s="2" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>283</v>
@@ -10945,15 +10945,15 @@
         <v>10.0</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
     </row>
     <row r="8" ht="14.25" customHeight="1">
       <c r="A8" s="2" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>284</v>
@@ -10976,10 +10976,10 @@
     </row>
     <row r="9" ht="14.25" customHeight="1">
       <c r="A9" s="2" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>286</v>
@@ -10997,12 +10997,12 @@
         <v>30.0</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
     </row>
     <row r="10" ht="14.25" customHeight="1">
       <c r="A10" s="2" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>287</v>
@@ -11028,10 +11028,10 @@
     </row>
     <row r="11" ht="14.25" customHeight="1">
       <c r="A11" s="2" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>290</v>
@@ -11049,12 +11049,12 @@
         <v>50.0</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
     </row>
     <row r="12" ht="14.25" customHeight="1">
       <c r="A12" s="2" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>291</v>
@@ -11080,7 +11080,7 @@
     </row>
     <row r="13" ht="14.25" customHeight="1">
       <c r="A13" s="2" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>294</v>
@@ -11106,7 +11106,7 @@
     </row>
     <row r="14" ht="14.25" customHeight="1">
       <c r="A14" s="2" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>297</v>
@@ -11132,7 +11132,7 @@
     </row>
     <row r="15" ht="14.25" customHeight="1">
       <c r="A15" s="2" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="B15" s="4" t="s">
         <v>300</v>
@@ -11158,7 +11158,7 @@
     </row>
     <row r="16" ht="14.25" customHeight="1">
       <c r="A16" s="2" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>303</v>
@@ -11184,7 +11184,7 @@
     </row>
     <row r="17" ht="14.25" customHeight="1">
       <c r="A17" s="2" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>306</v>
@@ -11210,10 +11210,10 @@
     </row>
     <row r="18" ht="14.25" customHeight="1">
       <c r="A18" s="2" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="C18" s="2" t="s">
         <v>309</v>
@@ -11231,12 +11231,12 @@
         <v>10.0</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
     </row>
     <row r="19" ht="14.25" customHeight="1">
       <c r="A19" s="2" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>310</v>
@@ -11262,7 +11262,7 @@
     </row>
     <row r="20" ht="14.25" customHeight="1">
       <c r="A20" s="2" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>70</v>
@@ -11288,7 +11288,7 @@
     </row>
     <row r="21" ht="14.25" customHeight="1">
       <c r="A21" s="2" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>72</v>
@@ -11314,7 +11314,7 @@
     </row>
     <row r="22" ht="14.25" customHeight="1">
       <c r="A22" s="2" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>74</v>
@@ -11340,7 +11340,7 @@
     </row>
     <row r="23" ht="14.25" customHeight="1">
       <c r="A23" s="2" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="B23" s="2" t="s">
         <v>76</v>
@@ -11366,7 +11366,7 @@
     </row>
     <row r="24" ht="14.25" customHeight="1">
       <c r="A24" s="2" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>321</v>
@@ -11392,7 +11392,7 @@
     </row>
     <row r="25" ht="14.25" customHeight="1">
       <c r="A25" s="2" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="B25" s="2" t="s">
         <v>324</v>
@@ -11418,7 +11418,7 @@
     </row>
     <row r="26" ht="14.25" customHeight="1">
       <c r="A26" s="2" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="B26" s="2" t="s">
         <v>327</v>
@@ -11444,7 +11444,7 @@
     </row>
     <row r="27" ht="14.25" customHeight="1">
       <c r="A27" s="2" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="B27" s="2" t="s">
         <v>330</v>
@@ -11470,7 +11470,7 @@
     </row>
     <row r="28" ht="14.25" customHeight="1">
       <c r="A28" s="2" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="B28" s="2" t="s">
         <v>333</v>
@@ -11496,7 +11496,7 @@
     </row>
     <row r="29" ht="14.25" customHeight="1">
       <c r="A29" s="2" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="B29" s="2" t="s">
         <v>336</v>
@@ -11522,7 +11522,7 @@
     </row>
     <row r="30" ht="14.25" customHeight="1">
       <c r="A30" s="2" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="B30" s="2" t="s">
         <v>339</v>
@@ -11548,7 +11548,7 @@
     </row>
     <row r="31" ht="14.25" customHeight="1">
       <c r="A31" s="2" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="B31" s="2" t="s">
         <v>342</v>
@@ -11574,7 +11574,7 @@
     </row>
     <row r="32" ht="14.25" customHeight="1">
       <c r="A32" s="2" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="B32" s="2" t="s">
         <v>345</v>
@@ -11600,7 +11600,7 @@
     </row>
     <row r="33" ht="14.25" customHeight="1">
       <c r="A33" s="2" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="B33" s="2" t="s">
         <v>348</v>
@@ -11626,7 +11626,7 @@
     </row>
     <row r="34" ht="14.25" customHeight="1">
       <c r="A34" s="2" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="B34" s="2" t="s">
         <v>351</v>
@@ -11652,7 +11652,7 @@
     </row>
     <row r="35" ht="14.25" customHeight="1">
       <c r="A35" s="2" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="B35" s="2" t="s">
         <v>354</v>
@@ -11678,7 +11678,7 @@
     </row>
     <row r="36" ht="14.25" customHeight="1">
       <c r="A36" s="2" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="B36" s="2" t="s">
         <v>357</v>
@@ -11704,7 +11704,7 @@
     </row>
     <row r="37" ht="14.25" customHeight="1">
       <c r="A37" s="2" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="B37" s="2" t="s">
         <v>360</v>
@@ -11730,7 +11730,7 @@
     </row>
     <row r="38" ht="14.25" customHeight="1">
       <c r="A38" s="2" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="B38" s="2" t="s">
         <v>363</v>
@@ -11756,7 +11756,7 @@
     </row>
     <row r="39" ht="14.25" customHeight="1">
       <c r="A39" s="2" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="B39" s="2" t="s">
         <v>366</v>
@@ -11782,7 +11782,7 @@
     </row>
     <row r="40" ht="14.25" customHeight="1">
       <c r="A40" s="2" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="B40" s="2" t="s">
         <v>369</v>
@@ -11808,7 +11808,7 @@
     </row>
     <row r="41" ht="14.25" customHeight="1">
       <c r="A41" s="2" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="B41" s="2" t="s">
         <v>372</v>
@@ -11834,7 +11834,7 @@
     </row>
     <row r="42" ht="14.25" customHeight="1">
       <c r="A42" s="2" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="B42" s="2" t="s">
         <v>375</v>
@@ -11860,7 +11860,7 @@
     </row>
     <row r="43" ht="14.25" customHeight="1">
       <c r="A43" s="2" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="B43" s="2" t="s">
         <v>378</v>
@@ -11886,7 +11886,7 @@
     </row>
     <row r="44" ht="14.25" customHeight="1">
       <c r="A44" s="2" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="B44" s="2" t="s">
         <v>381</v>
@@ -11912,7 +11912,7 @@
     </row>
     <row r="45" ht="14.25" customHeight="1">
       <c r="A45" s="2" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="B45" s="2" t="s">
         <v>384</v>
@@ -11938,7 +11938,7 @@
     </row>
     <row r="46" ht="14.25" customHeight="1">
       <c r="A46" s="2" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="B46" s="2" t="s">
         <v>387</v>
@@ -11964,7 +11964,7 @@
     </row>
     <row r="47" ht="14.25" customHeight="1">
       <c r="A47" s="2" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="B47" s="2" t="s">
         <v>390</v>
@@ -11990,7 +11990,7 @@
     </row>
     <row r="48" ht="14.25" customHeight="1">
       <c r="A48" s="2" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="B48" s="2" t="s">
         <v>393</v>
@@ -12016,7 +12016,7 @@
     </row>
     <row r="49" ht="14.25" customHeight="1">
       <c r="A49" s="2" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="B49" s="2" t="s">
         <v>396</v>
@@ -12042,7 +12042,7 @@
     </row>
     <row r="50" ht="14.25" customHeight="1">
       <c r="A50" s="2" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="B50" s="2" t="s">
         <v>399</v>
@@ -12068,7 +12068,7 @@
     </row>
     <row r="51" ht="14.25" customHeight="1">
       <c r="A51" s="2" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="B51" s="2" t="s">
         <v>402</v>
@@ -12094,7 +12094,7 @@
     </row>
     <row r="52" ht="14.25" customHeight="1">
       <c r="A52" s="2" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="B52" s="2" t="s">
         <v>405</v>
@@ -12120,7 +12120,7 @@
     </row>
     <row r="53" ht="14.25" customHeight="1">
       <c r="A53" s="2" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="B53" s="2" t="s">
         <v>408</v>
@@ -12146,7 +12146,7 @@
     </row>
     <row r="54" ht="14.25" customHeight="1">
       <c r="A54" s="2" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="B54" s="2" t="s">
         <v>411</v>
@@ -12172,7 +12172,7 @@
     </row>
     <row r="55" ht="14.25" customHeight="1">
       <c r="A55" s="2" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="B55" s="2" t="s">
         <v>414</v>
@@ -12198,7 +12198,7 @@
     </row>
     <row r="56" ht="14.25" customHeight="1">
       <c r="A56" s="2" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="B56" s="2" t="s">
         <v>417</v>
@@ -12224,7 +12224,7 @@
     </row>
     <row r="57" ht="14.25" customHeight="1">
       <c r="A57" s="2" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="B57" s="2" t="s">
         <v>420</v>
@@ -12250,7 +12250,7 @@
     </row>
     <row r="58" ht="14.25" customHeight="1">
       <c r="A58" s="2" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="B58" s="2" t="s">
         <v>423</v>
@@ -12276,7 +12276,7 @@
     </row>
     <row r="59" ht="14.25" customHeight="1">
       <c r="A59" s="2" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="B59" s="4" t="s">
         <v>426</v>
@@ -12302,7 +12302,7 @@
     </row>
     <row r="60" ht="14.25" customHeight="1">
       <c r="A60" s="2" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="B60" s="2" t="s">
         <v>429</v>
@@ -12328,7 +12328,7 @@
     </row>
     <row r="61" ht="14.25" customHeight="1">
       <c r="A61" s="2" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="B61" s="2" t="s">
         <v>432</v>
@@ -12354,7 +12354,7 @@
     </row>
     <row r="62" ht="14.25" customHeight="1">
       <c r="A62" s="2" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="B62" s="2" t="s">
         <v>435</v>
@@ -12380,7 +12380,7 @@
     </row>
     <row r="63" ht="14.25" customHeight="1">
       <c r="A63" s="2" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="B63" s="2" t="s">
         <v>437</v>
@@ -12406,7 +12406,7 @@
     </row>
     <row r="64" ht="14.25" customHeight="1">
       <c r="A64" s="2" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="B64" s="2" t="s">
         <v>439</v>
@@ -12432,7 +12432,7 @@
     </row>
     <row r="65" ht="14.25" customHeight="1">
       <c r="A65" s="2" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="B65" s="2" t="s">
         <v>441</v>
@@ -12458,7 +12458,7 @@
     </row>
     <row r="66" ht="14.25" customHeight="1">
       <c r="A66" s="2" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="B66" s="2" t="s">
         <v>443</v>
@@ -12484,7 +12484,7 @@
     </row>
     <row r="67" ht="14.25" customHeight="1">
       <c r="A67" s="2" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="B67" s="2" t="s">
         <v>445</v>
@@ -12510,7 +12510,7 @@
     </row>
     <row r="68" ht="14.25" customHeight="1">
       <c r="A68" s="2" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="B68" s="2" t="s">
         <v>447</v>
@@ -12536,7 +12536,7 @@
     </row>
     <row r="69" ht="14.25" customHeight="1">
       <c r="A69" s="2" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="B69" s="2" t="s">
         <v>449</v>
@@ -12562,7 +12562,7 @@
     </row>
     <row r="70" ht="14.25" customHeight="1">
       <c r="A70" s="2" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="B70" s="2" t="s">
         <v>451</v>
@@ -12588,7 +12588,7 @@
     </row>
     <row r="71" ht="14.25" customHeight="1">
       <c r="A71" s="2" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="B71" s="2" t="s">
         <v>453</v>
@@ -12614,7 +12614,7 @@
     </row>
     <row r="72" ht="14.25" customHeight="1">
       <c r="A72" s="2" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="B72" s="2" t="s">
         <v>455</v>
@@ -12640,13 +12640,13 @@
     </row>
     <row r="73" ht="14.25" customHeight="1">
       <c r="A73" s="2" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="C73" s="2" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="D73" s="2">
         <v>0.0</v>
@@ -12661,12 +12661,12 @@
         <v>10.0</v>
       </c>
       <c r="H73" s="2" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
     </row>
     <row r="74" ht="14.25" customHeight="1">
       <c r="A74" s="2" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="B74" s="2" t="s">
         <v>80</v>
@@ -12692,10 +12692,10 @@
     </row>
     <row r="75" ht="14.25" customHeight="1">
       <c r="A75" s="2" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="C75" s="2" t="s">
         <v>459</v>
@@ -12718,10 +12718,10 @@
     </row>
     <row r="76" ht="14.25" customHeight="1">
       <c r="A76" s="2" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="C76" s="2" t="s">
         <v>461</v>
@@ -12744,10 +12744,10 @@
     </row>
     <row r="77" ht="14.25" customHeight="1">
       <c r="A77" s="2" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="C77" s="2" t="s">
         <v>463</v>
@@ -12770,10 +12770,10 @@
     </row>
     <row r="78" ht="14.25" customHeight="1">
       <c r="A78" s="2" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="C78" s="2" t="s">
         <v>465</v>
@@ -12796,10 +12796,10 @@
     </row>
     <row r="79" ht="14.25" customHeight="1">
       <c r="A79" s="2" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="C79" s="2" t="s">
         <v>467</v>
@@ -12822,7 +12822,7 @@
     </row>
     <row r="80" ht="14.25" customHeight="1">
       <c r="A80" s="2" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="B80" s="2" t="s">
         <v>469</v>
@@ -12848,7 +12848,7 @@
     </row>
     <row r="81" ht="14.25" customHeight="1">
       <c r="A81" s="2" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="B81" s="2" t="s">
         <v>472</v>
@@ -12874,7 +12874,7 @@
     </row>
     <row r="82" ht="14.25" customHeight="1">
       <c r="A82" s="2" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="B82" s="2" t="s">
         <v>475</v>
@@ -12900,7 +12900,7 @@
     </row>
     <row r="83" ht="14.25" customHeight="1">
       <c r="A83" s="2" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="B83" s="2" t="s">
         <v>478</v>
@@ -12926,7 +12926,7 @@
     </row>
     <row r="84" ht="14.25" customHeight="1">
       <c r="A84" s="2" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="B84" s="2" t="s">
         <v>480</v>
@@ -12952,7 +12952,7 @@
     </row>
     <row r="85" ht="14.25" customHeight="1">
       <c r="A85" s="2" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="B85" s="2" t="s">
         <v>482</v>
@@ -12978,7 +12978,7 @@
     </row>
     <row r="86" ht="14.25" customHeight="1">
       <c r="A86" s="2" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="B86" s="2" t="s">
         <v>484</v>
@@ -13004,7 +13004,7 @@
     </row>
     <row r="87" ht="14.25" customHeight="1">
       <c r="A87" s="2" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="B87" s="2" t="s">
         <v>486</v>
@@ -13030,13 +13030,13 @@
     </row>
     <row r="88" ht="14.25" customHeight="1">
       <c r="A88" s="2" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="B88" s="2" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C88" s="2" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="D88" s="2">
         <v>0.0</v>
@@ -13051,12 +13051,12 @@
         <v>10.0</v>
       </c>
       <c r="H88" s="2" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
     </row>
     <row r="89" ht="14.25" customHeight="1">
       <c r="A89" s="2" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="B89" s="2" t="s">
         <v>488</v>
@@ -13082,7 +13082,7 @@
     </row>
     <row r="90" ht="14.25" customHeight="1">
       <c r="A90" s="3" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="B90" s="3" t="s">
         <v>491</v>
@@ -13108,7 +13108,7 @@
     </row>
     <row r="91" ht="14.25" customHeight="1">
       <c r="A91" s="3" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="B91" s="3" t="s">
         <v>494</v>
@@ -13134,7 +13134,7 @@
     </row>
     <row r="92" ht="14.25" customHeight="1">
       <c r="A92" s="3" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="B92" s="3" t="s">
         <v>497</v>
@@ -13160,7 +13160,7 @@
     </row>
     <row r="93" ht="14.25" customHeight="1">
       <c r="A93" s="3" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="B93" s="3" t="s">
         <v>500</v>
@@ -13186,7 +13186,7 @@
     </row>
     <row r="94" ht="14.25" customHeight="1">
       <c r="A94" s="2" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="B94" s="2" t="s">
         <v>503</v>
@@ -13212,7 +13212,7 @@
     </row>
     <row r="95" ht="14.25" customHeight="1">
       <c r="A95" s="2" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="B95" s="2" t="s">
         <v>110</v>
@@ -13238,7 +13238,7 @@
     </row>
     <row r="96" ht="14.25" customHeight="1">
       <c r="A96" s="5" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="B96" s="5" t="s">
         <v>507</v>
@@ -13247,10 +13247,10 @@
         <v>508</v>
       </c>
       <c r="D96" s="5">
-        <v>0.0</v>
+        <v>55.0</v>
       </c>
       <c r="E96" s="5">
-        <v>0.0</v>
+        <v>20.0</v>
       </c>
       <c r="F96" s="5">
         <v>1.0</v>
@@ -13264,7 +13264,7 @@
     </row>
     <row r="97" ht="14.25" customHeight="1">
       <c r="A97" s="5" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="B97" s="5" t="s">
         <v>510</v>
@@ -13273,10 +13273,10 @@
         <v>511</v>
       </c>
       <c r="D97" s="5">
-        <v>0.0</v>
+        <v>95.0</v>
       </c>
       <c r="E97" s="5">
-        <v>0.0</v>
+        <v>28.0</v>
       </c>
       <c r="F97" s="5">
         <v>1.0</v>
@@ -13308,7 +13308,7 @@
         <v>1.0</v>
       </c>
       <c r="G98" s="5">
-        <v>30.0</v>
+        <v>10.0</v>
       </c>
       <c r="H98" s="5" t="s">
         <v>515</v>
@@ -13334,14 +13334,64 @@
         <v>1.0</v>
       </c>
       <c r="G99" s="5">
-        <v>40.0</v>
+        <v>20.0</v>
       </c>
       <c r="H99" s="5" t="s">
         <v>518</v>
       </c>
     </row>
-    <row r="100" ht="14.25" customHeight="1"/>
-    <row r="101" ht="14.25" customHeight="1"/>
+    <row r="100" ht="14.25" customHeight="1">
+      <c r="A100" s="5" t="s">
+        <v>264</v>
+      </c>
+      <c r="B100" s="5" t="s">
+        <v>519</v>
+      </c>
+      <c r="C100" s="5" t="s">
+        <v>520</v>
+      </c>
+      <c r="D100" s="5">
+        <v>0.0</v>
+      </c>
+      <c r="E100" s="5">
+        <v>0.0</v>
+      </c>
+      <c r="F100" s="5">
+        <v>1.0</v>
+      </c>
+      <c r="G100" s="5">
+        <v>30.0</v>
+      </c>
+      <c r="H100" s="5" t="s">
+        <v>521</v>
+      </c>
+    </row>
+    <row r="101" ht="14.25" customHeight="1">
+      <c r="A101" s="5" t="s">
+        <v>264</v>
+      </c>
+      <c r="B101" s="5" t="s">
+        <v>522</v>
+      </c>
+      <c r="C101" s="5" t="s">
+        <v>523</v>
+      </c>
+      <c r="D101" s="5">
+        <v>0.0</v>
+      </c>
+      <c r="E101" s="5">
+        <v>0.0</v>
+      </c>
+      <c r="F101" s="5">
+        <v>1.0</v>
+      </c>
+      <c r="G101" s="5">
+        <v>40.0</v>
+      </c>
+      <c r="H101" s="5" t="s">
+        <v>524</v>
+      </c>
+    </row>
     <row r="102" ht="14.25" customHeight="1"/>
     <row r="103" ht="14.25" customHeight="1"/>
     <row r="104" ht="14.25" customHeight="1"/>
@@ -13536,8 +13586,8 @@
     <row r="293" ht="14.25" customHeight="1"/>
     <row r="294" ht="14.25" customHeight="1"/>
     <row r="295" ht="14.25" customHeight="1"/>
-    <row r="296" ht="15.75" customHeight="1"/>
-    <row r="297" ht="15.75" customHeight="1"/>
+    <row r="296" ht="14.25" customHeight="1"/>
+    <row r="297" ht="14.25" customHeight="1"/>
     <row r="298" ht="15.75" customHeight="1"/>
     <row r="299" ht="15.75" customHeight="1"/>
     <row r="300" ht="15.75" customHeight="1"/>
@@ -14243,6 +14293,8 @@
     <row r="1000" ht="15.75" customHeight="1"/>
     <row r="1001" ht="15.75" customHeight="1"/>
     <row r="1002" ht="15.75" customHeight="1"/>
+    <row r="1003" ht="15.75" customHeight="1"/>
+    <row r="1004" ht="15.75" customHeight="1"/>
   </sheetData>
   <autoFilter ref="$A$1:$H$1"/>
   <printOptions/>
@@ -14270,22 +14322,22 @@
   <sheetData>
     <row r="1" ht="14.25" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>519</v>
+        <v>525</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>266</v>
       </c>
       <c r="C1" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>204</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>205</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>207</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>206</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>3</v>
@@ -14296,7 +14348,7 @@
         <v>38</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="C2" s="2">
         <v>1.0</v>
@@ -14305,7 +14357,7 @@
         <v>0.0</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="F2" s="2">
         <v>5.0</v>
@@ -14319,7 +14371,7 @@
         <v>42</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="C3" s="2">
         <v>1.0</v>
@@ -14328,7 +14380,7 @@
         <v>0.0</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="F3" s="2">
         <v>5.0</v>
@@ -14342,7 +14394,7 @@
         <v>44</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="C4" s="2">
         <v>1.0</v>
@@ -14351,7 +14403,7 @@
         <v>0.0</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="F4" s="2">
         <v>5.0</v>
@@ -14365,7 +14417,7 @@
         <v>46</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="C5" s="2">
         <v>0.0</v>
@@ -14374,7 +14426,7 @@
         <v>1.0</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="F5" s="2">
         <v>5.0</v>
@@ -14388,7 +14440,7 @@
         <v>48</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="C6" s="2">
         <v>1.0</v>
@@ -14397,7 +14449,7 @@
         <v>0.0</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="F6" s="2">
         <v>5.0</v>
@@ -14411,7 +14463,7 @@
         <v>32</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="C7" s="2">
         <v>1.0</v>
@@ -14420,7 +14472,7 @@
         <v>0.0</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="F7" s="2">
         <v>5.0</v>
@@ -14434,7 +14486,7 @@
         <v>32</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="C8" s="2">
         <v>0.0</v>
@@ -14443,7 +14495,7 @@
         <v>1.0</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="F8" s="2">
         <v>10.0</v>
@@ -14457,7 +14509,7 @@
         <v>34</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="C9" s="2">
         <v>1.0</v>
@@ -14466,7 +14518,7 @@
         <v>0.0</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="F9" s="2">
         <v>5.0</v>
@@ -14480,7 +14532,7 @@
         <v>34</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="C10" s="2">
         <v>0.0</v>
@@ -14489,7 +14541,7 @@
         <v>1.0</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="F10" s="2">
         <v>10.0</v>
@@ -14503,7 +14555,7 @@
         <v>58</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="C11" s="2">
         <v>1.0</v>
@@ -14512,7 +14564,7 @@
         <v>0.0</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="F11" s="2">
         <v>5.0</v>
@@ -14526,7 +14578,7 @@
         <v>102</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="C12" s="2">
         <v>1.0</v>
@@ -14535,7 +14587,7 @@
         <v>0.0</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="F12" s="2">
         <v>5.0</v>
@@ -14549,7 +14601,7 @@
         <v>104</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="C13" s="2">
         <v>1.0</v>
@@ -14558,7 +14610,7 @@
         <v>0.0</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="F13" s="2">
         <v>5.0</v>
@@ -14572,7 +14624,7 @@
         <v>36</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="C14" s="2">
         <v>1.0</v>
@@ -14581,7 +14633,7 @@
         <v>0.0</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="F14" s="2">
         <v>5.0</v>
@@ -14595,7 +14647,7 @@
         <v>36</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="C15" s="2">
         <v>1.0</v>
@@ -14604,7 +14656,7 @@
         <v>0.0</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="F15" s="2">
         <v>10.0</v>
@@ -14618,7 +14670,7 @@
         <v>112</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="C16" s="2">
         <v>1.0</v>
@@ -14627,7 +14679,7 @@
         <v>0.0</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="F16" s="2">
         <v>5.0</v>
@@ -14641,7 +14693,7 @@
         <v>110</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="C17" s="2">
         <v>1.0</v>
@@ -14650,7 +14702,7 @@
         <v>0.0</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="F17" s="2">
         <v>5.0</v>
@@ -14664,7 +14716,7 @@
         <v>114</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="C18" s="2">
         <v>1.0</v>
@@ -14673,7 +14725,7 @@
         <v>0.0</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="F18" s="2">
         <v>5.0</v>
@@ -14687,7 +14739,7 @@
         <v>116</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="C19" s="2">
         <v>1.0</v>
@@ -14696,7 +14748,7 @@
         <v>0.0</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="F19" s="2">
         <v>5.0</v>
@@ -14710,7 +14762,7 @@
         <v>116</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="C20" s="2">
         <v>1.0</v>
@@ -14719,7 +14771,7 @@
         <v>0.0</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="F20" s="2">
         <v>10.0</v>
@@ -14733,7 +14785,7 @@
         <v>118</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="C21" s="2">
         <v>1.0</v>
@@ -14742,7 +14794,7 @@
         <v>0.0</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="F21" s="2">
         <v>5.0</v>
@@ -14756,7 +14808,7 @@
         <v>118</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="C22" s="2">
         <v>1.0</v>
@@ -14765,7 +14817,7 @@
         <v>0.0</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="F22" s="2">
         <v>10.0</v>
@@ -14779,7 +14831,7 @@
         <v>120</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="C23" s="2">
         <v>1.0</v>
@@ -14788,7 +14840,7 @@
         <v>0.0</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="F23" s="2">
         <v>5.0</v>
@@ -14802,7 +14854,7 @@
         <v>122</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="C24" s="2">
         <v>1.0</v>
@@ -14811,7 +14863,7 @@
         <v>0.0</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="F24" s="2">
         <v>5.0</v>
@@ -14825,7 +14877,7 @@
         <v>124</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="C25" s="2">
         <v>1.0</v>
@@ -14834,7 +14886,7 @@
         <v>0.0</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="F25" s="2">
         <v>5.0</v>
@@ -14848,7 +14900,7 @@
         <v>124</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="C26" s="2">
         <v>1.0</v>
@@ -14857,7 +14909,7 @@
         <v>0.0</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="F26" s="2">
         <v>10.0</v>
@@ -14871,7 +14923,7 @@
         <v>124</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="C27" s="2">
         <v>1.0</v>
@@ -14880,7 +14932,7 @@
         <v>0.0</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="F27" s="2">
         <v>15.0</v>
@@ -14894,7 +14946,7 @@
         <v>124</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="C28" s="2">
         <v>0.0</v>
@@ -14903,7 +14955,7 @@
         <v>0.0</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="F28" s="2">
         <v>20.0</v>
@@ -14917,7 +14969,7 @@
         <v>126</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C29" s="2">
         <v>0.0</v>
@@ -14926,7 +14978,7 @@
         <v>0.0</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="F29" s="2">
         <v>5.0</v>
@@ -14940,7 +14992,7 @@
         <v>70</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="C30" s="2">
         <v>1.0</v>
@@ -14949,7 +15001,7 @@
         <v>0.0</v>
       </c>
       <c r="E30" s="3" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="F30" s="2">
         <v>5.0</v>
@@ -14963,7 +15015,7 @@
         <v>72</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="C31" s="2">
         <v>1.0</v>
@@ -14972,7 +15024,7 @@
         <v>0.0</v>
       </c>
       <c r="E31" s="3" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="F31" s="2">
         <v>10.0</v>
@@ -14986,7 +15038,7 @@
         <v>74</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="C32" s="2">
         <v>1.0</v>
@@ -14995,7 +15047,7 @@
         <v>0.0</v>
       </c>
       <c r="E32" s="3" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="F32" s="2">
         <v>15.0</v>
@@ -15009,7 +15061,7 @@
         <v>76</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="C33" s="2">
         <v>1.0</v>
@@ -15018,7 +15070,7 @@
         <v>0.0</v>
       </c>
       <c r="E33" s="3" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="F33" s="2">
         <v>20.0</v>
@@ -15032,7 +15084,7 @@
         <v>78</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="C34" s="2">
         <v>1.0</v>
@@ -15041,7 +15093,7 @@
         <v>0.0</v>
       </c>
       <c r="E34" s="3" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="F34" s="2">
         <v>25.0</v>
@@ -15055,7 +15107,7 @@
         <v>80</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="C35" s="2">
         <v>1.0</v>
@@ -15064,7 +15116,7 @@
         <v>0.0</v>
       </c>
       <c r="E35" s="3" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="F35" s="2">
         <v>30.0</v>
@@ -15078,7 +15130,7 @@
         <v>40</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="C36" s="2">
         <v>1.0</v>
@@ -15087,7 +15139,7 @@
         <v>0.0</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="F36" s="2">
         <v>5.0</v>
@@ -15101,7 +15153,7 @@
         <v>60</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="C37" s="2">
         <v>1.0</v>
@@ -15110,7 +15162,7 @@
         <v>0.0</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="F37" s="2">
         <v>5.0</v>
@@ -15119,8 +15171,52 @@
         <v>1.0</v>
       </c>
     </row>
-    <row r="38" ht="14.25" customHeight="1"/>
-    <row r="39" ht="14.25" customHeight="1"/>
+    <row r="38" ht="14.25" customHeight="1">
+      <c r="A38" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="B38" s="5" t="s">
+        <v>262</v>
+      </c>
+      <c r="C38" s="5">
+        <v>1.0</v>
+      </c>
+      <c r="D38" s="5">
+        <v>0.0</v>
+      </c>
+      <c r="E38" s="2" t="s">
+        <v>212</v>
+      </c>
+      <c r="F38" s="5">
+        <v>5.0</v>
+      </c>
+      <c r="G38" s="5">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="39" ht="14.25" customHeight="1">
+      <c r="A39" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="B39" s="5" t="s">
+        <v>264</v>
+      </c>
+      <c r="C39" s="5">
+        <v>1.0</v>
+      </c>
+      <c r="D39" s="5">
+        <v>0.0</v>
+      </c>
+      <c r="E39" s="2" t="s">
+        <v>212</v>
+      </c>
+      <c r="F39" s="5">
+        <v>10.0</v>
+      </c>
+      <c r="G39" s="5">
+        <v>1.0</v>
+      </c>
+    </row>
     <row r="40" ht="14.25" customHeight="1"/>
     <row r="41" ht="14.25" customHeight="1"/>
     <row r="42" ht="14.25" customHeight="1"/>
@@ -16109,19 +16205,19 @@
   <sheetData>
     <row r="1" ht="14.25" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>519</v>
+        <v>525</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>520</v>
+        <v>526</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>521</v>
+        <v>527</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>522</v>
+        <v>528</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>523</v>
+        <v>529</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>4</v>
@@ -16135,13 +16231,13 @@
         <v>32</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>7</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>524</v>
+        <v>530</v>
       </c>
       <c r="E2" s="2">
         <v>1.0</v>
@@ -16158,13 +16254,13 @@
         <v>34</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>7</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>525</v>
+        <v>531</v>
       </c>
       <c r="E3" s="2">
         <v>1.0</v>
@@ -16181,13 +16277,13 @@
         <v>36</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>526</v>
+        <v>532</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>10</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>527</v>
+        <v>533</v>
       </c>
       <c r="E4" s="2">
         <v>1.0</v>
@@ -16204,13 +16300,13 @@
         <v>38</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>7</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>528</v>
+        <v>534</v>
       </c>
       <c r="E5" s="2">
         <v>1.0</v>
@@ -16227,13 +16323,13 @@
         <v>40</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>7</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>529</v>
+        <v>535</v>
       </c>
       <c r="E6" s="2">
         <v>1.0</v>
@@ -16250,13 +16346,13 @@
         <v>42</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>7</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>530</v>
+        <v>536</v>
       </c>
       <c r="E7" s="2">
         <v>1.0</v>
@@ -16273,13 +16369,13 @@
         <v>44</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>7</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>531</v>
+        <v>537</v>
       </c>
       <c r="E8" s="2">
         <v>1.0</v>
@@ -16296,13 +16392,13 @@
         <v>46</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>7</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>532</v>
+        <v>538</v>
       </c>
       <c r="E9" s="2">
         <v>1.0</v>
@@ -16319,13 +16415,13 @@
         <v>48</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>7</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>533</v>
+        <v>539</v>
       </c>
       <c r="E10" s="2">
         <v>1.0</v>
@@ -16342,13 +16438,13 @@
         <v>50</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>7</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>534</v>
+        <v>540</v>
       </c>
       <c r="E11" s="2">
         <v>1.0</v>
@@ -16365,13 +16461,13 @@
         <v>52</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>535</v>
+        <v>541</v>
       </c>
       <c r="E12" s="2">
         <v>1.0</v>
@@ -16388,13 +16484,13 @@
         <v>54</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>7</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>536</v>
+        <v>542</v>
       </c>
       <c r="E13" s="2">
         <v>1.0</v>
@@ -16411,13 +16507,13 @@
         <v>56</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>7</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>537</v>
+        <v>543</v>
       </c>
       <c r="E14" s="2">
         <v>1.0</v>
@@ -16434,13 +16530,13 @@
         <v>58</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>7</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>538</v>
+        <v>544</v>
       </c>
       <c r="E15" s="2">
         <v>1.0</v>
@@ -16457,13 +16553,13 @@
         <v>60</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>7</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>539</v>
+        <v>545</v>
       </c>
       <c r="E16" s="2">
         <v>1.0</v>
@@ -16480,13 +16576,13 @@
         <v>62</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>7</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>540</v>
+        <v>546</v>
       </c>
       <c r="E17" s="2">
         <v>1.0</v>
@@ -16503,13 +16599,13 @@
         <v>64</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="C18" s="2" t="s">
         <v>7</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>541</v>
+        <v>547</v>
       </c>
       <c r="E18" s="2">
         <v>1.0</v>
@@ -16526,13 +16622,13 @@
         <v>66</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="C19" s="2" t="s">
         <v>7</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>542</v>
+        <v>548</v>
       </c>
       <c r="E19" s="2">
         <v>1.0</v>
@@ -16549,13 +16645,13 @@
         <v>68</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="C20" s="2" t="s">
         <v>7</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>543</v>
+        <v>549</v>
       </c>
       <c r="E20" s="2">
         <v>1.0</v>
@@ -16572,13 +16668,13 @@
         <v>70</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="C21" s="2" t="s">
         <v>7</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>544</v>
+        <v>550</v>
       </c>
       <c r="E21" s="2">
         <v>1.0</v>
@@ -16595,13 +16691,13 @@
         <v>72</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="C22" s="2" t="s">
         <v>7</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>545</v>
+        <v>551</v>
       </c>
       <c r="E22" s="2">
         <v>1.0</v>
@@ -16618,13 +16714,13 @@
         <v>74</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="C23" s="2" t="s">
         <v>7</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>546</v>
+        <v>552</v>
       </c>
       <c r="E23" s="2">
         <v>1.0</v>
@@ -16641,13 +16737,13 @@
         <v>76</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="C24" s="2" t="s">
         <v>7</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>547</v>
+        <v>553</v>
       </c>
       <c r="E24" s="2">
         <v>1.0</v>
@@ -16664,13 +16760,13 @@
         <v>78</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="C25" s="2" t="s">
         <v>7</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>548</v>
+        <v>554</v>
       </c>
       <c r="E25" s="2">
         <v>1.0</v>
@@ -16687,13 +16783,13 @@
         <v>80</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="C26" s="2" t="s">
         <v>7</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>549</v>
+        <v>555</v>
       </c>
       <c r="E26" s="2">
         <v>1.0</v>
@@ -16710,13 +16806,13 @@
         <v>82</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>550</v>
+        <v>556</v>
       </c>
       <c r="C27" s="2" t="s">
         <v>7</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>551</v>
+        <v>557</v>
       </c>
       <c r="E27" s="2">
         <v>1.0</v>
@@ -16733,13 +16829,13 @@
         <v>84</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>526</v>
+        <v>532</v>
       </c>
       <c r="C28" s="2" t="s">
         <v>7</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>552</v>
+        <v>558</v>
       </c>
       <c r="E28" s="2">
         <v>1.0</v>
@@ -16756,13 +16852,13 @@
         <v>86</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>526</v>
+        <v>532</v>
       </c>
       <c r="C29" s="2" t="s">
         <v>7</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>553</v>
+        <v>559</v>
       </c>
       <c r="E29" s="2">
         <v>1.0</v>
@@ -16779,13 +16875,13 @@
         <v>88</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>526</v>
+        <v>532</v>
       </c>
       <c r="C30" s="2" t="s">
         <v>7</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>554</v>
+        <v>560</v>
       </c>
       <c r="E30" s="2">
         <v>1.0</v>
@@ -16802,13 +16898,13 @@
         <v>90</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="C31" s="2" t="s">
         <v>7</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>555</v>
+        <v>561</v>
       </c>
       <c r="E31" s="2">
         <v>1.0</v>
@@ -16825,13 +16921,13 @@
         <v>92</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="C32" s="2" t="s">
         <v>7</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>556</v>
+        <v>562</v>
       </c>
       <c r="E32" s="2">
         <v>1.0</v>
@@ -16848,13 +16944,13 @@
         <v>94</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="C33" s="2" t="s">
         <v>7</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>557</v>
+        <v>563</v>
       </c>
       <c r="E33" s="2">
         <v>1.0</v>
@@ -16871,13 +16967,13 @@
         <v>96</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="C34" s="2" t="s">
         <v>7</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>558</v>
+        <v>564</v>
       </c>
       <c r="E34" s="2">
         <v>1.0</v>
@@ -16894,13 +16990,13 @@
         <v>98</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="C35" s="2" t="s">
         <v>7</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>559</v>
+        <v>565</v>
       </c>
       <c r="E35" s="2">
         <v>1.0</v>
@@ -16917,13 +17013,13 @@
         <v>100</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>526</v>
+        <v>532</v>
       </c>
       <c r="C36" s="2" t="s">
         <v>7</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>560</v>
+        <v>566</v>
       </c>
       <c r="E36" s="2">
         <v>1.0</v>
@@ -16940,13 +17036,13 @@
         <v>102</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>526</v>
+        <v>532</v>
       </c>
       <c r="C37" s="2" t="s">
         <v>7</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>561</v>
+        <v>567</v>
       </c>
       <c r="E37" s="2">
         <v>1.0</v>
@@ -16963,13 +17059,13 @@
         <v>104</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>526</v>
+        <v>532</v>
       </c>
       <c r="C38" s="2" t="s">
         <v>7</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>562</v>
+        <v>568</v>
       </c>
       <c r="E38" s="2">
         <v>1.0</v>
@@ -16986,13 +17082,13 @@
         <v>106</v>
       </c>
       <c r="B39" s="4" t="s">
-        <v>526</v>
+        <v>532</v>
       </c>
       <c r="C39" s="4" t="s">
         <v>10</v>
       </c>
       <c r="D39" s="4" t="s">
-        <v>563</v>
+        <v>569</v>
       </c>
       <c r="E39" s="4">
         <v>1.0</v>
@@ -17009,13 +17105,13 @@
         <v>108</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>526</v>
+        <v>532</v>
       </c>
       <c r="C40" s="2" t="s">
         <v>10</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>564</v>
+        <v>570</v>
       </c>
       <c r="E40" s="2">
         <v>1.0</v>
@@ -17032,13 +17128,13 @@
         <v>110</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>526</v>
+        <v>532</v>
       </c>
       <c r="C41" s="2" t="s">
         <v>10</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>565</v>
+        <v>571</v>
       </c>
       <c r="E41" s="2">
         <v>1.0</v>
@@ -17055,13 +17151,13 @@
         <v>112</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>526</v>
+        <v>532</v>
       </c>
       <c r="C42" s="2" t="s">
         <v>10</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>566</v>
+        <v>572</v>
       </c>
       <c r="E42" s="2">
         <v>1.0</v>
@@ -17078,13 +17174,13 @@
         <v>114</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>526</v>
+        <v>532</v>
       </c>
       <c r="C43" s="2" t="s">
         <v>10</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>567</v>
+        <v>573</v>
       </c>
       <c r="E43" s="2">
         <v>1.0</v>
@@ -17101,13 +17197,13 @@
         <v>116</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>526</v>
+        <v>532</v>
       </c>
       <c r="C44" s="2" t="s">
         <v>10</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>568</v>
+        <v>574</v>
       </c>
       <c r="E44" s="2">
         <v>1.0</v>
@@ -17124,13 +17220,13 @@
         <v>118</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>526</v>
+        <v>532</v>
       </c>
       <c r="C45" s="2" t="s">
         <v>10</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>569</v>
+        <v>575</v>
       </c>
       <c r="E45" s="2">
         <v>1.0</v>
@@ -17147,13 +17243,13 @@
         <v>120</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>526</v>
+        <v>532</v>
       </c>
       <c r="C46" s="2" t="s">
         <v>10</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>570</v>
+        <v>576</v>
       </c>
       <c r="E46" s="2">
         <v>1.0</v>
@@ -17170,13 +17266,13 @@
         <v>122</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>526</v>
+        <v>532</v>
       </c>
       <c r="C47" s="2" t="s">
         <v>10</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>571</v>
+        <v>577</v>
       </c>
       <c r="E47" s="2">
         <v>1.0</v>
@@ -17193,13 +17289,13 @@
         <v>124</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>526</v>
+        <v>532</v>
       </c>
       <c r="C48" s="2" t="s">
         <v>7</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>572</v>
+        <v>578</v>
       </c>
       <c r="E48" s="2">
         <v>1.0</v>
@@ -17216,13 +17312,13 @@
         <v>126</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>526</v>
+        <v>532</v>
       </c>
       <c r="C49" s="2" t="s">
         <v>7</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>573</v>
+        <v>579</v>
       </c>
       <c r="E49" s="2">
         <v>1.0</v>
@@ -17239,13 +17335,13 @@
         <v>128</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>526</v>
+        <v>532</v>
       </c>
       <c r="C50" s="2" t="s">
         <v>7</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>574</v>
+        <v>580</v>
       </c>
       <c r="E50" s="2">
         <v>1.0</v>
@@ -17262,13 +17358,13 @@
         <v>130</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>526</v>
+        <v>532</v>
       </c>
       <c r="C51" s="2" t="s">
         <v>7</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>575</v>
+        <v>581</v>
       </c>
       <c r="E51" s="2">
         <v>1.0</v>
@@ -17285,13 +17381,13 @@
         <v>132</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>526</v>
+        <v>532</v>
       </c>
       <c r="C52" s="2" t="s">
         <v>7</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>576</v>
+        <v>582</v>
       </c>
       <c r="E52" s="2">
         <v>1.0</v>
@@ -17308,13 +17404,13 @@
         <v>134</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>526</v>
+        <v>532</v>
       </c>
       <c r="C53" s="2" t="s">
         <v>7</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>577</v>
+        <v>583</v>
       </c>
       <c r="E53" s="2">
         <v>1.0</v>
@@ -17331,13 +17427,13 @@
         <v>136</v>
       </c>
       <c r="B54" s="5" t="s">
-        <v>526</v>
+        <v>532</v>
       </c>
       <c r="C54" s="2" t="s">
         <v>7</v>
       </c>
       <c r="D54" s="5" t="s">
-        <v>578</v>
+        <v>584</v>
       </c>
       <c r="E54" s="5">
         <v>1.0</v>
@@ -17349,29 +17445,7 @@
         <v>1.0</v>
       </c>
     </row>
-    <row r="55" ht="14.25" customHeight="1">
-      <c r="A55" s="4" t="s">
-        <v>138</v>
-      </c>
-      <c r="B55" s="5" t="s">
-        <v>526</v>
-      </c>
-      <c r="C55" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D55" s="5" t="s">
-        <v>579</v>
-      </c>
-      <c r="E55" s="5">
-        <v>1.0</v>
-      </c>
-      <c r="F55" s="2">
-        <v>540.0</v>
-      </c>
-      <c r="G55" s="5">
-        <v>1.0</v>
-      </c>
-    </row>
+    <row r="55" ht="14.25" customHeight="1"/>
     <row r="56" ht="14.25" customHeight="1"/>
     <row r="57" ht="14.25" customHeight="1"/>
     <row r="58" ht="14.25" customHeight="1"/>
@@ -17569,7 +17643,7 @@
     <row r="250" ht="14.25" customHeight="1"/>
     <row r="251" ht="14.25" customHeight="1"/>
     <row r="252" ht="14.25" customHeight="1"/>
-    <row r="253" ht="14.25" customHeight="1"/>
+    <row r="253" ht="15.75" customHeight="1"/>
     <row r="254" ht="15.75" customHeight="1"/>
     <row r="255" ht="15.75" customHeight="1"/>
     <row r="256" ht="15.75" customHeight="1"/>
@@ -18317,7 +18391,6 @@
     <row r="998" ht="15.75" customHeight="1"/>
     <row r="999" ht="15.75" customHeight="1"/>
     <row r="1000" ht="15.75" customHeight="1"/>
-    <row r="1001" ht="15.75" customHeight="1"/>
   </sheetData>
   <autoFilter ref="$A$1:$G$1"/>
   <printOptions/>
@@ -18353,7 +18426,7 @@
         <v>1</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>580</v>
+        <v>585</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>3</v>
@@ -18364,13 +18437,13 @@
     </row>
     <row r="2" ht="14.25" customHeight="1">
       <c r="A2" s="2" t="s">
-        <v>581</v>
+        <v>586</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>582</v>
+        <v>587</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>583</v>
+        <v>588</v>
       </c>
       <c r="E2" s="2">
         <v>1.0</v>
@@ -18381,13 +18454,13 @@
     </row>
     <row r="3" ht="14.25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>584</v>
+        <v>589</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>582</v>
+        <v>587</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>585</v>
+        <v>590</v>
       </c>
       <c r="E3" s="2">
         <v>1.0</v>
@@ -19416,50 +19489,50 @@
   <sheetData>
     <row r="1" ht="15.75" customHeight="1">
       <c r="A1" s="6" t="s">
-        <v>586</v>
+        <v>591</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>587</v>
+        <v>592</v>
       </c>
     </row>
     <row r="2" ht="15.75" customHeight="1">
       <c r="A2" s="7" t="s">
-        <v>588</v>
+        <v>593</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>589</v>
+        <v>594</v>
       </c>
     </row>
     <row r="3" ht="15.75" customHeight="1">
       <c r="A3" s="7" t="s">
-        <v>590</v>
+        <v>595</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>591</v>
+        <v>596</v>
       </c>
     </row>
     <row r="4" ht="15.75" customHeight="1">
       <c r="A4" s="7" t="s">
-        <v>592</v>
+        <v>597</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>593</v>
+        <v>598</v>
       </c>
     </row>
     <row r="5" ht="15.75" customHeight="1">
       <c r="A5" s="7" t="s">
-        <v>594</v>
+        <v>599</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>595</v>
+        <v>600</v>
       </c>
     </row>
     <row r="6" ht="15.75" customHeight="1">
       <c r="A6" s="7" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>596</v>
+        <v>601</v>
       </c>
     </row>
     <row r="7" ht="15.75" customHeight="1">
@@ -19467,31 +19540,31 @@
         <v>37</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>597</v>
+        <v>602</v>
       </c>
     </row>
     <row r="8" ht="15.75" customHeight="1">
       <c r="A8" s="7" t="s">
-        <v>598</v>
+        <v>603</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>599</v>
+        <v>604</v>
       </c>
     </row>
     <row r="9" ht="15.75" customHeight="1">
       <c r="A9" s="7" t="s">
-        <v>600</v>
+        <v>605</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>601</v>
+        <v>606</v>
       </c>
     </row>
     <row r="10" ht="15.75" customHeight="1">
       <c r="A10" s="7" t="s">
-        <v>602</v>
+        <v>607</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>603</v>
+        <v>608</v>
       </c>
     </row>
     <row r="11" ht="14.25" customHeight="1">

--- a/database/catalogos/catalogo_maestro.xlsx
+++ b/database/catalogos/catalogo_maestro.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1205" uniqueCount="609">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1242" uniqueCount="627">
   <si>
     <t>slug</t>
   </si>
@@ -445,6 +445,12 @@
     <t>Pozole</t>
   </si>
   <si>
+    <t>tiramisu</t>
+  </si>
+  <si>
+    <t>Tiramisu</t>
+  </si>
+  <si>
     <t>otro</t>
   </si>
   <si>
@@ -610,6 +616,12 @@
     <t>Chorizo argentino</t>
   </si>
   <si>
+    <t>bistec</t>
+  </si>
+  <si>
+    <t>Bistec</t>
+  </si>
+  <si>
     <t>chistorra</t>
   </si>
   <si>
@@ -988,6 +1000,9 @@
     <t>Bistec Asado</t>
   </si>
   <si>
+    <t>Proteina: Costilla</t>
+  </si>
+  <si>
     <t>Proteina: Bistec Empanizado</t>
   </si>
   <si>
@@ -1384,6 +1399,36 @@
     <t>Agua Mineral</t>
   </si>
   <si>
+    <t>jarrito_piña</t>
+  </si>
+  <si>
+    <t>Jarrito Piña</t>
+  </si>
+  <si>
+    <t>jarrito_limon</t>
+  </si>
+  <si>
+    <t>Jarrito Limon</t>
+  </si>
+  <si>
+    <t>jarrito_tamarindo</t>
+  </si>
+  <si>
+    <t>Jarrito Tamarindo</t>
+  </si>
+  <si>
+    <t>jarrito_uva</t>
+  </si>
+  <si>
+    <t>Jarrito Uva</t>
+  </si>
+  <si>
+    <t>jarrito_tutti_frutti</t>
+  </si>
+  <si>
+    <t>Jarrito Tutti Frutti</t>
+  </si>
+  <si>
     <t>papaya</t>
   </si>
   <si>
@@ -1426,6 +1471,12 @@
     <t>Taco Suadero</t>
   </si>
   <si>
+    <t>Proteina Taco: Bistec</t>
+  </si>
+  <si>
+    <t>Taco Bistec</t>
+  </si>
+  <si>
     <t>Proteina Taco: Longaniza</t>
   </si>
   <si>
@@ -1781,6 +1832,9 @@
   </si>
   <si>
     <t>DESECHABLE GRANDE</t>
+  </si>
+  <si>
+    <t>TIRAMISU</t>
   </si>
   <si>
     <t>POZOLE</t>
@@ -1862,7 +1916,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="5">
+  <fonts count="4">
     <font>
       <sz val="11.0"/>
       <color rgb="FF000000"/>
@@ -1883,11 +1937,6 @@
       <sz val="11.0"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
-    </font>
-    <font>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="3">
@@ -1916,7 +1965,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="7">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -1924,9 +1973,6 @@
     <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyFont="1"/>
     <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyFont="1"/>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
     <xf borderId="1" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
@@ -5238,52 +5284,52 @@
       </c>
     </row>
     <row r="39" ht="14.25" customHeight="1">
-      <c r="A39" s="4" t="s">
+      <c r="A39" s="2" t="s">
         <v>106</v>
       </c>
-      <c r="B39" s="4" t="s">
+      <c r="B39" s="2" t="s">
         <v>107</v>
       </c>
       <c r="C39" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="D39" s="4">
+      <c r="D39" s="2">
         <v>40.0</v>
       </c>
-      <c r="E39" s="4">
+      <c r="E39" s="2">
         <v>15.0</v>
       </c>
-      <c r="F39" s="4">
-        <v>1.0</v>
-      </c>
-      <c r="G39" s="4">
-        <v>1.0</v>
-      </c>
-      <c r="H39" s="4">
-        <v>0.0</v>
-      </c>
-      <c r="I39" s="4">
-        <v>0.0</v>
-      </c>
-      <c r="J39" s="4">
-        <v>0.0</v>
-      </c>
-      <c r="K39" s="4">
-        <v>0.0</v>
-      </c>
-      <c r="L39" s="4">
-        <v>0.0</v>
-      </c>
-      <c r="M39" s="4">
-        <v>1.0</v>
-      </c>
-      <c r="N39" s="4">
-        <v>1.0</v>
-      </c>
-      <c r="O39" s="4">
-        <v>0.0</v>
-      </c>
-      <c r="P39" s="4">
+      <c r="F39" s="2">
+        <v>1.0</v>
+      </c>
+      <c r="G39" s="2">
+        <v>1.0</v>
+      </c>
+      <c r="H39" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="I39" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="J39" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="K39" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="L39" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="M39" s="2">
+        <v>1.0</v>
+      </c>
+      <c r="N39" s="2">
+        <v>1.0</v>
+      </c>
+      <c r="O39" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="P39" s="2">
         <v>380.0</v>
       </c>
     </row>
@@ -5433,7 +5479,7 @@
       <c r="O42" s="2">
         <v>0.0</v>
       </c>
-      <c r="P42" s="4">
+      <c r="P42" s="2">
         <v>410.0</v>
       </c>
     </row>
@@ -5583,7 +5629,7 @@
       <c r="O45" s="2">
         <v>0.0</v>
       </c>
-      <c r="P45" s="4">
+      <c r="P45" s="2">
         <v>440.0</v>
       </c>
     </row>
@@ -5647,7 +5693,7 @@
       <c r="C47" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="D47" s="2">
+      <c r="D47" s="4">
         <v>30.0</v>
       </c>
       <c r="E47" s="4">
@@ -5733,7 +5779,7 @@
       <c r="O48" s="2">
         <v>0.0</v>
       </c>
-      <c r="P48" s="4">
+      <c r="P48" s="2">
         <v>470.0</v>
       </c>
     </row>
@@ -5883,7 +5929,7 @@
       <c r="O51" s="2">
         <v>0.0</v>
       </c>
-      <c r="P51" s="4">
+      <c r="P51" s="2">
         <v>500.0</v>
       </c>
     </row>
@@ -5959,7 +6005,7 @@
       <c r="G53" s="2">
         <v>1.0</v>
       </c>
-      <c r="H53" s="4">
+      <c r="H53" s="2">
         <v>0.0</v>
       </c>
       <c r="I53" s="2">
@@ -5988,19 +6034,19 @@
       </c>
     </row>
     <row r="54" ht="14.25" customHeight="1">
-      <c r="A54" s="4" t="s">
+      <c r="A54" s="2" t="s">
         <v>136</v>
       </c>
-      <c r="B54" s="4" t="s">
+      <c r="B54" s="2" t="s">
         <v>137</v>
       </c>
       <c r="C54" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="D54" s="4">
-        <v>0.0</v>
-      </c>
-      <c r="E54" s="4">
+      <c r="D54" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="E54" s="2">
         <v>0.0</v>
       </c>
       <c r="F54" s="2">
@@ -6009,14 +6055,14 @@
       <c r="G54" s="2">
         <v>1.0</v>
       </c>
-      <c r="H54" s="4">
+      <c r="H54" s="2">
         <v>1.0</v>
       </c>
       <c r="I54" s="2">
         <v>0.0</v>
       </c>
-      <c r="J54" s="2">
-        <v>0.0</v>
+      <c r="J54" s="4">
+        <v>30.0</v>
       </c>
       <c r="K54" s="2">
         <v>0.0</v>
@@ -6038,56 +6084,105 @@
       </c>
     </row>
     <row r="55" ht="14.25" customHeight="1">
-      <c r="A55" s="2" t="s">
+      <c r="A55" s="4" t="s">
         <v>138</v>
       </c>
-      <c r="B55" s="2" t="s">
+      <c r="B55" s="4" t="s">
         <v>139</v>
       </c>
       <c r="C55" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D55" s="4">
+        <v>65.0</v>
+      </c>
+      <c r="E55" s="4">
+        <v>30.0</v>
+      </c>
+      <c r="F55" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="G55" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="H55" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="I55" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="J55" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="K55" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="L55" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="M55" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="N55" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="O55" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="P55" s="4">
+        <v>540.0</v>
+      </c>
+    </row>
+    <row r="56" ht="14.25" customHeight="1">
+      <c r="A56" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="B56" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="C56" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="D55" s="2">
-        <v>0.0</v>
-      </c>
-      <c r="E55" s="2">
-        <v>0.0</v>
-      </c>
-      <c r="F55" s="2">
-        <v>1.0</v>
-      </c>
-      <c r="G55" s="2">
-        <v>1.0</v>
-      </c>
-      <c r="H55" s="2">
-        <v>0.0</v>
-      </c>
-      <c r="I55" s="2">
-        <v>0.0</v>
-      </c>
-      <c r="J55" s="2">
-        <v>0.0</v>
-      </c>
-      <c r="K55" s="2">
-        <v>0.0</v>
-      </c>
-      <c r="L55" s="2">
-        <v>0.0</v>
-      </c>
-      <c r="M55" s="2">
-        <v>0.0</v>
-      </c>
-      <c r="N55" s="2">
-        <v>0.0</v>
-      </c>
-      <c r="O55" s="2">
-        <v>0.0</v>
-      </c>
-      <c r="P55" s="2">
-        <v>540.0</v>
-      </c>
-    </row>
-    <row r="56" ht="14.25" customHeight="1"/>
+      <c r="D56" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="E56" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="F56" s="2">
+        <v>1.0</v>
+      </c>
+      <c r="G56" s="2">
+        <v>1.0</v>
+      </c>
+      <c r="H56" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="I56" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="J56" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="K56" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="L56" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="M56" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="N56" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="O56" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="P56" s="4">
+        <v>550.0</v>
+      </c>
+    </row>
     <row r="57" ht="14.25" customHeight="1"/>
     <row r="58" ht="14.25" customHeight="1"/>
     <row r="59" ht="14.25" customHeight="1"/>
@@ -6287,7 +6382,7 @@
     <row r="253" ht="14.25" customHeight="1"/>
     <row r="254" ht="14.25" customHeight="1"/>
     <row r="255" ht="14.25" customHeight="1"/>
-    <row r="256" ht="15.75" customHeight="1"/>
+    <row r="256" ht="14.25" customHeight="1"/>
     <row r="257" ht="15.75" customHeight="1"/>
     <row r="258" ht="15.75" customHeight="1"/>
     <row r="259" ht="15.75" customHeight="1"/>
@@ -7033,7 +7128,6 @@
     <row r="999" ht="15.75" customHeight="1"/>
     <row r="1000" ht="15.75" customHeight="1"/>
     <row r="1001" ht="15.75" customHeight="1"/>
-    <row r="1002" ht="15.75" customHeight="1"/>
   </sheetData>
   <autoFilter ref="$A$1:$P$1"/>
   <printOptions/>
@@ -7070,7 +7164,7 @@
         <v>3</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>4</v>
@@ -7078,10 +7172,10 @@
     </row>
     <row r="2" ht="14.25" customHeight="1">
       <c r="A2" s="2" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="C2" s="2">
         <v>10.0</v>
@@ -7098,10 +7192,10 @@
     </row>
     <row r="3" ht="14.25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="C3" s="2">
         <v>10.0</v>
@@ -7118,10 +7212,10 @@
     </row>
     <row r="4" ht="14.25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="C4" s="2">
         <v>10.0</v>
@@ -7138,10 +7232,10 @@
     </row>
     <row r="5" ht="14.25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="C5" s="2">
         <v>10.0</v>
@@ -7158,10 +7252,10 @@
     </row>
     <row r="6" ht="14.25" customHeight="1">
       <c r="A6" s="2" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="C6" s="2">
         <v>10.0</v>
@@ -7178,10 +7272,10 @@
     </row>
     <row r="7" ht="14.25" customHeight="1">
       <c r="A7" s="2" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="C7" s="2">
         <v>10.0</v>
@@ -7198,10 +7292,10 @@
     </row>
     <row r="8" ht="14.25" customHeight="1">
       <c r="A8" s="2" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="C8" s="2">
         <v>15.0</v>
@@ -7218,10 +7312,10 @@
     </row>
     <row r="9" ht="14.25" customHeight="1">
       <c r="A9" s="2" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="C9" s="2">
         <v>10.0</v>
@@ -7238,10 +7332,10 @@
     </row>
     <row r="10" ht="14.25" customHeight="1">
       <c r="A10" s="2" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="C10" s="2">
         <v>10.0</v>
@@ -7258,10 +7352,10 @@
     </row>
     <row r="11" ht="14.25" customHeight="1">
       <c r="A11" s="2" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="C11" s="2">
         <v>5.0</v>
@@ -7278,10 +7372,10 @@
     </row>
     <row r="12" ht="14.25" customHeight="1">
       <c r="A12" s="2" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="C12" s="2">
         <v>5.0</v>
@@ -7298,10 +7392,10 @@
     </row>
     <row r="13" ht="14.25" customHeight="1">
       <c r="A13" s="2" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="C13" s="2">
         <v>5.0</v>
@@ -7318,10 +7412,10 @@
     </row>
     <row r="14" ht="14.25" customHeight="1">
       <c r="A14" s="2" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="C14" s="2">
         <v>5.0</v>
@@ -7338,10 +7432,10 @@
     </row>
     <row r="15" ht="14.25" customHeight="1">
       <c r="A15" s="2" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="C15" s="2">
         <v>5.0</v>
@@ -7358,10 +7452,10 @@
     </row>
     <row r="16" ht="14.25" customHeight="1">
       <c r="A16" s="2" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="C16" s="2">
         <v>10.0</v>
@@ -7378,10 +7472,10 @@
     </row>
     <row r="17" ht="14.25" customHeight="1">
       <c r="A17" s="2" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="C17" s="2">
         <v>10.0</v>
@@ -7398,10 +7492,10 @@
     </row>
     <row r="18" ht="14.25" customHeight="1">
       <c r="A18" s="2" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="C18" s="2">
         <v>10.0</v>
@@ -7418,10 +7512,10 @@
     </row>
     <row r="19" ht="14.25" customHeight="1">
       <c r="A19" s="2" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="C19" s="2">
         <v>10.0</v>
@@ -7538,10 +7632,10 @@
     </row>
     <row r="25" ht="14.25" customHeight="1">
       <c r="A25" s="2" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="C25" s="2">
         <v>10.0</v>
@@ -7558,10 +7652,10 @@
     </row>
     <row r="26" ht="14.25" customHeight="1">
       <c r="A26" s="2" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="C26" s="2">
         <v>15.0</v>
@@ -7578,10 +7672,10 @@
     </row>
     <row r="27" ht="14.25" customHeight="1">
       <c r="A27" s="2" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="C27" s="2">
         <v>10.0</v>
@@ -7598,10 +7692,10 @@
     </row>
     <row r="28" ht="14.25" customHeight="1">
       <c r="A28" s="2" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="C28" s="2">
         <v>10.0</v>
@@ -7618,10 +7712,10 @@
     </row>
     <row r="29" ht="14.25" customHeight="1">
       <c r="A29" s="2" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="C29" s="2">
         <v>5.0</v>
@@ -7638,10 +7732,10 @@
     </row>
     <row r="30" ht="14.25" customHeight="1">
       <c r="A30" s="2" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="C30" s="2">
         <v>5.0</v>
@@ -7658,10 +7752,10 @@
     </row>
     <row r="31" ht="14.25" customHeight="1">
       <c r="A31" s="2" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="C31" s="2">
         <v>35.0</v>
@@ -7678,10 +7772,10 @@
     </row>
     <row r="32" ht="14.25" customHeight="1">
       <c r="A32" s="2" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="C32" s="2">
         <v>25.0</v>
@@ -7697,34 +7791,34 @@
       </c>
     </row>
     <row r="33" ht="14.25" customHeight="1">
-      <c r="A33" s="2" t="s">
-        <v>193</v>
-      </c>
-      <c r="B33" s="2" t="s">
-        <v>194</v>
-      </c>
-      <c r="C33" s="2">
-        <v>15.0</v>
-      </c>
-      <c r="D33" s="2">
-        <v>1.0</v>
-      </c>
-      <c r="E33" s="2">
-        <v>1.0</v>
-      </c>
-      <c r="F33" s="2">
+      <c r="A33" s="4" t="s">
+        <v>195</v>
+      </c>
+      <c r="B33" s="4" t="s">
+        <v>196</v>
+      </c>
+      <c r="C33" s="4">
+        <v>35.0</v>
+      </c>
+      <c r="D33" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="E33" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="F33" s="4">
         <v>320.0</v>
       </c>
     </row>
     <row r="34" ht="14.25" customHeight="1">
       <c r="A34" s="2" t="s">
-        <v>80</v>
+        <v>197</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="C34" s="2">
-        <v>40.0</v>
+        <v>15.0</v>
       </c>
       <c r="D34" s="2">
         <v>1.0</v>
@@ -7738,13 +7832,13 @@
     </row>
     <row r="35" ht="14.25" customHeight="1">
       <c r="A35" s="2" t="s">
-        <v>196</v>
+        <v>80</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="C35" s="2">
-        <v>35.0</v>
+        <v>40.0</v>
       </c>
       <c r="D35" s="2">
         <v>1.0</v>
@@ -7758,13 +7852,13 @@
     </row>
     <row r="36" ht="14.25" customHeight="1">
       <c r="A36" s="2" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="C36" s="2">
-        <v>15.0</v>
+        <v>35.0</v>
       </c>
       <c r="D36" s="2">
         <v>1.0</v>
@@ -7772,19 +7866,19 @@
       <c r="E36" s="2">
         <v>1.0</v>
       </c>
-      <c r="F36" s="2">
+      <c r="F36" s="4">
         <v>350.0</v>
       </c>
     </row>
     <row r="37" ht="14.25" customHeight="1">
       <c r="A37" s="2" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="C37" s="2">
-        <v>7.0</v>
+        <v>15.0</v>
       </c>
       <c r="D37" s="2">
         <v>1.0</v>
@@ -7796,7 +7890,26 @@
         <v>360.0</v>
       </c>
     </row>
-    <row r="38" ht="14.25" customHeight="1"/>
+    <row r="38" ht="14.25" customHeight="1">
+      <c r="A38" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="B38" s="2" t="s">
+        <v>205</v>
+      </c>
+      <c r="C38" s="2">
+        <v>7.0</v>
+      </c>
+      <c r="D38" s="2">
+        <v>1.0</v>
+      </c>
+      <c r="E38" s="2">
+        <v>1.0</v>
+      </c>
+      <c r="F38" s="2">
+        <v>370.0</v>
+      </c>
+    </row>
     <row r="39" ht="14.25" customHeight="1"/>
     <row r="40" ht="14.25" customHeight="1"/>
     <row r="41" ht="14.25" customHeight="1"/>
@@ -7996,7 +8109,7 @@
     <row r="235" ht="14.25" customHeight="1"/>
     <row r="236" ht="14.25" customHeight="1"/>
     <row r="237" ht="14.25" customHeight="1"/>
-    <row r="238" ht="15.75" customHeight="1"/>
+    <row r="238" ht="14.25" customHeight="1"/>
     <row r="239" ht="15.75" customHeight="1"/>
     <row r="240" ht="15.75" customHeight="1"/>
     <row r="241" ht="15.75" customHeight="1"/>
@@ -8759,6 +8872,7 @@
     <row r="998" ht="15.75" customHeight="1"/>
     <row r="999" ht="15.75" customHeight="1"/>
     <row r="1000" ht="15.75" customHeight="1"/>
+    <row r="1001" ht="15.75" customHeight="1"/>
   </sheetData>
   <autoFilter ref="$A$1:$F$1"/>
   <printOptions/>
@@ -8798,39 +8912,39 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>3</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>206</v>
+        <v>210</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>208</v>
+        <v>212</v>
       </c>
     </row>
     <row r="2" ht="14.25" customHeight="1">
       <c r="A2" s="2" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="D2" s="2">
         <v>1.0</v>
@@ -8845,7 +8959,7 @@
         <v>5.0</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="I2" s="2" t="s">
         <v>7</v>
@@ -8859,13 +8973,13 @@
     </row>
     <row r="3" ht="14.25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="D3" s="2">
         <v>0.0</v>
@@ -8880,7 +8994,7 @@
         <v>15.0</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="I3" s="2" t="s">
         <v>7</v>
@@ -8894,13 +9008,13 @@
     </row>
     <row r="4" ht="14.25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="D4" s="2">
         <v>1.0</v>
@@ -8915,7 +9029,7 @@
         <v>20.0</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="I4" s="2" t="s">
         <v>7</v>
@@ -8929,13 +9043,13 @@
     </row>
     <row r="5" ht="14.25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="D5" s="2">
         <v>1.0</v>
@@ -8950,7 +9064,7 @@
         <v>25.0</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="I5" s="2" t="s">
         <v>7</v>
@@ -8964,13 +9078,13 @@
     </row>
     <row r="6" ht="14.25" customHeight="1">
       <c r="A6" s="2" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="D6" s="2">
         <v>0.0</v>
@@ -8985,7 +9099,7 @@
         <v>30.0</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="I6" s="2" t="s">
         <v>7</v>
@@ -8999,13 +9113,13 @@
     </row>
     <row r="7" ht="14.25" customHeight="1">
       <c r="A7" s="2" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="D7" s="2">
         <v>1.0</v>
@@ -9020,7 +9134,7 @@
         <v>35.0</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="I7" s="2" t="s">
         <v>7</v>
@@ -9034,13 +9148,13 @@
     </row>
     <row r="8" ht="14.25" customHeight="1">
       <c r="A8" s="2" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="D8" s="2">
         <v>1.0</v>
@@ -9055,7 +9169,7 @@
         <v>45.0</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="I8" s="2" t="s">
         <v>7</v>
@@ -9069,13 +9183,13 @@
     </row>
     <row r="9" ht="14.25" customHeight="1">
       <c r="A9" s="2" t="s">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="D9" s="2">
         <v>1.0</v>
@@ -9090,7 +9204,7 @@
         <v>50.0</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="I9" s="2" t="s">
         <v>7</v>
@@ -9104,13 +9218,13 @@
     </row>
     <row r="10" ht="14.25" customHeight="1">
       <c r="A10" s="2" t="s">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="D10" s="2">
         <v>1.0</v>
@@ -9125,7 +9239,7 @@
         <v>55.0</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="I10" s="2" t="s">
         <v>10</v>
@@ -9139,13 +9253,13 @@
     </row>
     <row r="11" ht="14.25" customHeight="1">
       <c r="A11" s="2" t="s">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>231</v>
+        <v>235</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="D11" s="2">
         <v>1.0</v>
@@ -9160,7 +9274,7 @@
         <v>60.0</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="I11" s="2" t="s">
         <v>10</v>
@@ -9174,13 +9288,13 @@
     </row>
     <row r="12" ht="14.25" customHeight="1">
       <c r="A12" s="2" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="D12" s="2">
         <v>1.0</v>
@@ -9195,7 +9309,7 @@
         <v>65.0</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="I12" s="2" t="s">
         <v>10</v>
@@ -9209,13 +9323,13 @@
     </row>
     <row r="13" ht="14.25" customHeight="1">
       <c r="A13" s="2" t="s">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="D13" s="2">
         <v>1.0</v>
@@ -9230,7 +9344,7 @@
         <v>70.0</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="I13" s="2" t="s">
         <v>10</v>
@@ -9244,13 +9358,13 @@
     </row>
     <row r="14" ht="14.25" customHeight="1">
       <c r="A14" s="2" t="s">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="D14" s="2">
         <v>1.0</v>
@@ -9265,7 +9379,7 @@
         <v>80.0</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="I14" s="2" t="s">
         <v>10</v>
@@ -9279,13 +9393,13 @@
     </row>
     <row r="15" ht="14.25" customHeight="1">
       <c r="A15" s="2" t="s">
-        <v>238</v>
+        <v>242</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="D15" s="2">
         <v>1.0</v>
@@ -9300,7 +9414,7 @@
         <v>90.0</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="I15" s="2" t="s">
         <v>10</v>
@@ -9314,13 +9428,13 @@
     </row>
     <row r="16" ht="14.25" customHeight="1">
       <c r="A16" s="2" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="D16" s="2">
         <v>1.0</v>
@@ -9335,7 +9449,7 @@
         <v>100.0</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="I16" s="2" t="s">
         <v>10</v>
@@ -9349,13 +9463,13 @@
     </row>
     <row r="17" ht="14.25" customHeight="1">
       <c r="A17" s="2" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="D17" s="2">
         <v>1.0</v>
@@ -9370,7 +9484,7 @@
         <v>110.0</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="I17" s="2" t="s">
         <v>10</v>
@@ -9384,13 +9498,13 @@
     </row>
     <row r="18" ht="14.25" customHeight="1">
       <c r="A18" s="2" t="s">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="D18" s="2">
         <v>0.0</v>
@@ -9405,7 +9519,7 @@
         <v>120.0</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="I18" s="2" t="s">
         <v>10</v>
@@ -9419,13 +9533,13 @@
     </row>
     <row r="19" ht="14.25" customHeight="1">
       <c r="A19" s="2" t="s">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="D19" s="2">
         <v>0.0</v>
@@ -9440,7 +9554,7 @@
         <v>130.0</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="I19" s="2" t="s">
         <v>10</v>
@@ -9454,13 +9568,13 @@
     </row>
     <row r="20" ht="14.25" customHeight="1">
       <c r="A20" s="2" t="s">
-        <v>248</v>
+        <v>252</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>249</v>
+        <v>253</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="D20" s="2">
         <v>1.0</v>
@@ -9475,7 +9589,7 @@
         <v>140.0</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="I20" s="2" t="s">
         <v>7</v>
@@ -9489,13 +9603,13 @@
     </row>
     <row r="21" ht="14.25" customHeight="1">
       <c r="A21" s="2" t="s">
-        <v>250</v>
+        <v>254</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="D21" s="2">
         <v>1.0</v>
@@ -9510,7 +9624,7 @@
         <v>150.0</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="I21" s="2" t="s">
         <v>7</v>
@@ -9524,13 +9638,13 @@
     </row>
     <row r="22" ht="14.25" customHeight="1">
       <c r="A22" s="2" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="D22" s="2">
         <v>1.0</v>
@@ -9545,7 +9659,7 @@
         <v>160.0</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="I22" s="2" t="s">
         <v>7</v>
@@ -9559,13 +9673,13 @@
     </row>
     <row r="23" ht="14.25" customHeight="1">
       <c r="A23" s="2" t="s">
-        <v>254</v>
+        <v>258</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>255</v>
+        <v>259</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="D23" s="2">
         <v>0.0</v>
@@ -9580,7 +9694,7 @@
         <v>170.0</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="I23" s="2" t="s">
         <v>7</v>
@@ -9594,13 +9708,13 @@
     </row>
     <row r="24" ht="14.25" customHeight="1">
       <c r="A24" s="2" t="s">
-        <v>256</v>
+        <v>260</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="D24" s="2">
         <v>0.0</v>
@@ -9615,7 +9729,7 @@
         <v>180.0</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="I24" s="2" t="s">
         <v>7</v>
@@ -9629,13 +9743,13 @@
     </row>
     <row r="25" ht="14.25" customHeight="1">
       <c r="A25" s="3" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="D25" s="2">
         <v>1.0</v>
@@ -9650,7 +9764,7 @@
         <v>190.0</v>
       </c>
       <c r="H25" s="3" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="I25" s="2" t="s">
         <v>7</v>
@@ -9664,13 +9778,13 @@
     </row>
     <row r="26" ht="14.25" customHeight="1">
       <c r="A26" s="2" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="D26" s="2">
         <v>0.0</v>
@@ -9685,7 +9799,7 @@
         <v>62.0</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="I26" s="2" t="s">
         <v>10</v>
@@ -9698,72 +9812,72 @@
       </c>
     </row>
     <row r="27" ht="14.25" customHeight="1">
-      <c r="A27" s="5" t="s">
-        <v>262</v>
-      </c>
-      <c r="B27" s="5" t="s">
-        <v>263</v>
+      <c r="A27" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>267</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>211</v>
-      </c>
-      <c r="D27" s="5">
-        <v>1.0</v>
-      </c>
-      <c r="E27" s="5">
-        <v>0.0</v>
-      </c>
-      <c r="F27" s="5">
-        <v>1.0</v>
-      </c>
-      <c r="G27" s="5">
+        <v>215</v>
+      </c>
+      <c r="D27" s="2">
+        <v>1.0</v>
+      </c>
+      <c r="E27" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="F27" s="2">
+        <v>1.0</v>
+      </c>
+      <c r="G27" s="2">
         <v>200.0</v>
       </c>
-      <c r="H27" s="5" t="s">
-        <v>212</v>
-      </c>
-      <c r="I27" s="5" t="s">
+      <c r="H27" s="2" t="s">
+        <v>216</v>
+      </c>
+      <c r="I27" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="J27" s="5">
-        <v>0.0</v>
-      </c>
-      <c r="K27" s="5">
+      <c r="J27" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="K27" s="2">
         <v>0.0</v>
       </c>
     </row>
     <row r="28" ht="14.25" customHeight="1">
-      <c r="A28" s="5" t="s">
-        <v>264</v>
-      </c>
-      <c r="B28" s="5" t="s">
-        <v>265</v>
+      <c r="A28" s="2" t="s">
+        <v>268</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>269</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>211</v>
-      </c>
-      <c r="D28" s="5">
-        <v>1.0</v>
-      </c>
-      <c r="E28" s="5">
-        <v>0.0</v>
-      </c>
-      <c r="F28" s="5">
-        <v>1.0</v>
-      </c>
-      <c r="G28" s="5">
+        <v>215</v>
+      </c>
+      <c r="D28" s="2">
+        <v>1.0</v>
+      </c>
+      <c r="E28" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="F28" s="2">
+        <v>1.0</v>
+      </c>
+      <c r="G28" s="2">
         <v>210.0</v>
       </c>
-      <c r="H28" s="5" t="s">
-        <v>212</v>
-      </c>
-      <c r="I28" s="5" t="s">
+      <c r="H28" s="2" t="s">
+        <v>216</v>
+      </c>
+      <c r="I28" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="J28" s="5">
-        <v>0.0</v>
-      </c>
-      <c r="K28" s="5">
+      <c r="J28" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="K28" s="2">
         <v>0.0</v>
       </c>
     </row>
@@ -10739,7 +10853,6 @@
     <row r="998" ht="15.75" customHeight="1"/>
     <row r="999" ht="15.75" customHeight="1"/>
     <row r="1000" ht="15.75" customHeight="1"/>
-    <row r="1001" ht="15.75" customHeight="1"/>
   </sheetData>
   <autoFilter ref="$A$1:$K$1"/>
   <printOptions/>
@@ -10768,7 +10881,7 @@
   <sheetData>
     <row r="1" ht="14.25" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>0</v>
@@ -10789,18 +10902,18 @@
         <v>4</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
     </row>
     <row r="2" ht="14.25" customHeight="1">
       <c r="A2" s="2" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c r="D2" s="2">
         <v>0.0</v>
@@ -10815,18 +10928,18 @@
         <v>10.0</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
     </row>
     <row r="3" ht="14.25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="D3" s="2">
         <v>0.0</v>
@@ -10841,18 +10954,18 @@
         <v>20.0</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>273</v>
+        <v>277</v>
       </c>
     </row>
     <row r="4" ht="14.25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>275</v>
+        <v>279</v>
       </c>
       <c r="D4" s="2">
         <v>0.0</v>
@@ -10867,18 +10980,18 @@
         <v>30.0</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>276</v>
+        <v>280</v>
       </c>
     </row>
     <row r="5" ht="14.25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>277</v>
+        <v>281</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>278</v>
+        <v>282</v>
       </c>
       <c r="D5" s="2">
         <v>0.0</v>
@@ -10893,18 +11006,18 @@
         <v>10.0</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>279</v>
+        <v>283</v>
       </c>
     </row>
     <row r="6" ht="14.25" customHeight="1">
       <c r="A6" s="2" t="s">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>280</v>
+        <v>284</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>281</v>
+        <v>285</v>
       </c>
       <c r="D6" s="2">
         <v>0.0</v>
@@ -10919,18 +11032,18 @@
         <v>20.0</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>282</v>
+        <v>286</v>
       </c>
     </row>
     <row r="7" ht="14.25" customHeight="1">
       <c r="A7" s="2" t="s">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>283</v>
+        <v>287</v>
       </c>
       <c r="D7" s="2">
         <v>0.0</v>
@@ -10945,18 +11058,18 @@
         <v>10.0</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
     </row>
     <row r="8" ht="14.25" customHeight="1">
       <c r="A8" s="2" t="s">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>284</v>
+        <v>288</v>
       </c>
       <c r="D8" s="2">
         <v>0.0</v>
@@ -10971,18 +11084,18 @@
         <v>20.0</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>285</v>
+        <v>289</v>
       </c>
     </row>
     <row r="9" ht="14.25" customHeight="1">
       <c r="A9" s="2" t="s">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>286</v>
+        <v>290</v>
       </c>
       <c r="D9" s="2">
         <v>0.0</v>
@@ -10997,18 +11110,18 @@
         <v>30.0</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
     </row>
     <row r="10" ht="14.25" customHeight="1">
       <c r="A10" s="2" t="s">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>287</v>
+        <v>291</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="D10" s="2">
         <v>0.0</v>
@@ -11023,18 +11136,18 @@
         <v>40.0</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>289</v>
+        <v>293</v>
       </c>
     </row>
     <row r="11" ht="14.25" customHeight="1">
       <c r="A11" s="2" t="s">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="D11" s="2">
         <v>0.0</v>
@@ -11049,18 +11162,18 @@
         <v>50.0</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
     </row>
     <row r="12" ht="14.25" customHeight="1">
       <c r="A12" s="2" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>291</v>
+        <v>295</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>292</v>
+        <v>296</v>
       </c>
       <c r="D12" s="2">
         <v>0.0</v>
@@ -11075,18 +11188,18 @@
         <v>10.0</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>293</v>
+        <v>297</v>
       </c>
     </row>
     <row r="13" ht="14.25" customHeight="1">
       <c r="A13" s="2" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>294</v>
+        <v>298</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>295</v>
+        <v>299</v>
       </c>
       <c r="D13" s="2">
         <v>0.0</v>
@@ -11101,18 +11214,18 @@
         <v>20.0</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>296</v>
+        <v>300</v>
       </c>
     </row>
     <row r="14" ht="14.25" customHeight="1">
       <c r="A14" s="2" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>297</v>
+        <v>301</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>298</v>
+        <v>302</v>
       </c>
       <c r="D14" s="2">
         <v>0.0</v>
@@ -11120,25 +11233,25 @@
       <c r="E14" s="2">
         <v>0.0</v>
       </c>
-      <c r="F14" s="4">
+      <c r="F14" s="2">
         <v>1.0</v>
       </c>
       <c r="G14" s="2">
         <v>30.0</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>299</v>
+        <v>303</v>
       </c>
     </row>
     <row r="15" ht="14.25" customHeight="1">
       <c r="A15" s="2" t="s">
-        <v>216</v>
-      </c>
-      <c r="B15" s="4" t="s">
-        <v>300</v>
-      </c>
-      <c r="C15" s="4" t="s">
-        <v>301</v>
+        <v>220</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>304</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>305</v>
       </c>
       <c r="D15" s="2">
         <v>0.0</v>
@@ -11146,25 +11259,25 @@
       <c r="E15" s="2">
         <v>0.0</v>
       </c>
-      <c r="F15" s="4">
-        <v>1.0</v>
-      </c>
-      <c r="G15" s="4">
+      <c r="F15" s="2">
+        <v>1.0</v>
+      </c>
+      <c r="G15" s="2">
         <v>40.0</v>
       </c>
-      <c r="H15" s="4" t="s">
-        <v>302</v>
+      <c r="H15" s="2" t="s">
+        <v>306</v>
       </c>
     </row>
     <row r="16" ht="14.25" customHeight="1">
       <c r="A16" s="2" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>303</v>
+        <v>307</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>304</v>
+        <v>308</v>
       </c>
       <c r="D16" s="2">
         <v>0.0</v>
@@ -11179,18 +11292,18 @@
         <v>10.0</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>305</v>
+        <v>309</v>
       </c>
     </row>
     <row r="17" ht="14.25" customHeight="1">
       <c r="A17" s="2" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>306</v>
+        <v>310</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="D17" s="2">
         <v>0.0</v>
@@ -11205,18 +11318,18 @@
         <v>20.0</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>308</v>
+        <v>312</v>
       </c>
     </row>
     <row r="18" ht="14.25" customHeight="1">
       <c r="A18" s="2" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>309</v>
+        <v>313</v>
       </c>
       <c r="D18" s="2">
         <v>10.0</v>
@@ -11231,18 +11344,18 @@
         <v>10.0</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
     </row>
     <row r="19" ht="14.25" customHeight="1">
       <c r="A19" s="2" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>310</v>
+        <v>314</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>311</v>
+        <v>315</v>
       </c>
       <c r="D19" s="2">
         <v>10.0</v>
@@ -11257,18 +11370,18 @@
         <v>20.0</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>312</v>
+        <v>316</v>
       </c>
     </row>
     <row r="20" ht="14.25" customHeight="1">
       <c r="A20" s="2" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>70</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>313</v>
+        <v>317</v>
       </c>
       <c r="D20" s="2">
         <v>25.0</v>
@@ -11283,18 +11396,18 @@
         <v>30.0</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>314</v>
+        <v>318</v>
       </c>
     </row>
     <row r="21" ht="14.25" customHeight="1">
       <c r="A21" s="2" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>72</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>315</v>
+        <v>319</v>
       </c>
       <c r="D21" s="2">
         <v>30.0</v>
@@ -11309,18 +11422,18 @@
         <v>40.0</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>316</v>
+        <v>320</v>
       </c>
     </row>
     <row r="22" ht="14.25" customHeight="1">
       <c r="A22" s="2" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>74</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>317</v>
+        <v>321</v>
       </c>
       <c r="D22" s="2">
         <v>30.0</v>
@@ -11335,70 +11448,70 @@
         <v>50.0</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>318</v>
+        <v>322</v>
       </c>
     </row>
     <row r="23" ht="14.25" customHeight="1">
       <c r="A23" s="2" t="s">
-        <v>220</v>
-      </c>
-      <c r="B23" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="C23" s="2" t="s">
-        <v>319</v>
+        <v>224</v>
+      </c>
+      <c r="B23" s="4" t="s">
+        <v>191</v>
+      </c>
+      <c r="C23" s="4" t="s">
+        <v>323</v>
       </c>
       <c r="D23" s="2">
-        <v>35.0</v>
+        <v>30.0</v>
       </c>
       <c r="E23" s="2">
-        <v>25.0</v>
+        <v>20.0</v>
       </c>
       <c r="F23" s="2">
         <v>1.0</v>
       </c>
-      <c r="G23" s="2">
+      <c r="G23" s="4">
         <v>60.0</v>
       </c>
-      <c r="H23" s="2" t="s">
-        <v>320</v>
+      <c r="H23" s="4" t="s">
+        <v>192</v>
       </c>
     </row>
     <row r="24" ht="14.25" customHeight="1">
       <c r="A24" s="2" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>321</v>
+        <v>76</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="D24" s="2">
-        <v>0.0</v>
+        <v>35.0</v>
       </c>
       <c r="E24" s="2">
-        <v>0.0</v>
+        <v>25.0</v>
       </c>
       <c r="F24" s="2">
         <v>1.0</v>
       </c>
-      <c r="G24" s="2">
-        <v>10.0</v>
+      <c r="G24" s="4">
+        <v>70.0</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
     </row>
     <row r="25" ht="14.25" customHeight="1">
       <c r="A25" s="2" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="D25" s="2">
         <v>0.0</v>
@@ -11410,21 +11523,21 @@
         <v>1.0</v>
       </c>
       <c r="G25" s="2">
-        <v>20.0</v>
+        <v>10.0</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
     </row>
     <row r="26" ht="14.25" customHeight="1">
       <c r="A26" s="2" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="D26" s="2">
         <v>0.0</v>
@@ -11436,21 +11549,21 @@
         <v>1.0</v>
       </c>
       <c r="G26" s="2">
-        <v>30.0</v>
+        <v>20.0</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
     </row>
     <row r="27" ht="14.25" customHeight="1">
       <c r="A27" s="2" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="D27" s="2">
         <v>0.0</v>
@@ -11462,21 +11575,21 @@
         <v>1.0</v>
       </c>
       <c r="G27" s="2">
-        <v>40.0</v>
+        <v>30.0</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
     </row>
     <row r="28" ht="14.25" customHeight="1">
       <c r="A28" s="2" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="D28" s="2">
         <v>0.0</v>
@@ -11488,21 +11601,21 @@
         <v>1.0</v>
       </c>
       <c r="G28" s="2">
-        <v>50.0</v>
+        <v>40.0</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
     </row>
     <row r="29" ht="14.25" customHeight="1">
       <c r="A29" s="2" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="D29" s="2">
         <v>0.0</v>
@@ -11514,21 +11627,21 @@
         <v>1.0</v>
       </c>
       <c r="G29" s="2">
-        <v>10.0</v>
+        <v>50.0</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
     </row>
     <row r="30" ht="14.25" customHeight="1">
       <c r="A30" s="2" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="D30" s="2">
         <v>0.0</v>
@@ -11540,21 +11653,21 @@
         <v>1.0</v>
       </c>
       <c r="G30" s="2">
-        <v>20.0</v>
+        <v>10.0</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
     </row>
     <row r="31" ht="14.25" customHeight="1">
       <c r="A31" s="2" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="D31" s="2">
         <v>0.0</v>
@@ -11566,21 +11679,21 @@
         <v>1.0</v>
       </c>
       <c r="G31" s="2">
-        <v>30.0</v>
+        <v>20.0</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
     </row>
     <row r="32" ht="14.25" customHeight="1">
       <c r="A32" s="2" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="D32" s="2">
         <v>0.0</v>
@@ -11592,21 +11705,21 @@
         <v>1.0</v>
       </c>
       <c r="G32" s="2">
-        <v>40.0</v>
+        <v>30.0</v>
       </c>
       <c r="H32" s="2" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
     </row>
     <row r="33" ht="14.25" customHeight="1">
       <c r="A33" s="2" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="D33" s="2">
         <v>0.0</v>
@@ -11618,21 +11731,21 @@
         <v>1.0</v>
       </c>
       <c r="G33" s="2">
-        <v>50.0</v>
+        <v>40.0</v>
       </c>
       <c r="H33" s="2" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
     </row>
     <row r="34" ht="14.25" customHeight="1">
       <c r="A34" s="2" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="D34" s="2">
         <v>0.0</v>
@@ -11644,73 +11757,73 @@
         <v>1.0</v>
       </c>
       <c r="G34" s="2">
-        <v>10.0</v>
+        <v>50.0</v>
       </c>
       <c r="H34" s="2" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
     </row>
     <row r="35" ht="14.25" customHeight="1">
       <c r="A35" s="2" t="s">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="D35" s="2">
-        <v>5.0</v>
+        <v>0.0</v>
       </c>
       <c r="E35" s="2">
-        <v>5.0</v>
+        <v>0.0</v>
       </c>
       <c r="F35" s="2">
         <v>1.0</v>
       </c>
       <c r="G35" s="2">
-        <v>20.0</v>
+        <v>10.0</v>
       </c>
       <c r="H35" s="2" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
     </row>
     <row r="36" ht="14.25" customHeight="1">
       <c r="A36" s="2" t="s">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="D36" s="2">
-        <v>10.0</v>
+        <v>5.0</v>
       </c>
       <c r="E36" s="2">
-        <v>10.0</v>
+        <v>5.0</v>
       </c>
       <c r="F36" s="2">
         <v>1.0</v>
       </c>
       <c r="G36" s="2">
-        <v>30.0</v>
+        <v>20.0</v>
       </c>
       <c r="H36" s="2" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
     </row>
     <row r="37" ht="14.25" customHeight="1">
       <c r="A37" s="2" t="s">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="D37" s="2">
         <v>10.0</v>
@@ -11722,10 +11835,10 @@
         <v>1.0</v>
       </c>
       <c r="G37" s="2">
-        <v>40.0</v>
+        <v>30.0</v>
       </c>
       <c r="H37" s="2" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
     </row>
     <row r="38" ht="14.25" customHeight="1">
@@ -11733,62 +11846,62 @@
         <v>230</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="D38" s="2">
-        <v>0.0</v>
+        <v>10.0</v>
       </c>
       <c r="E38" s="2">
-        <v>0.0</v>
+        <v>10.0</v>
       </c>
       <c r="F38" s="2">
         <v>1.0</v>
       </c>
       <c r="G38" s="2">
-        <v>10.0</v>
+        <v>40.0</v>
       </c>
       <c r="H38" s="2" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
     </row>
     <row r="39" ht="14.25" customHeight="1">
       <c r="A39" s="2" t="s">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="D39" s="2">
-        <v>5.0</v>
+        <v>0.0</v>
       </c>
       <c r="E39" s="2">
-        <v>5.0</v>
+        <v>0.0</v>
       </c>
       <c r="F39" s="2">
         <v>1.0</v>
       </c>
       <c r="G39" s="2">
-        <v>20.0</v>
+        <v>10.0</v>
       </c>
       <c r="H39" s="2" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
     </row>
     <row r="40" ht="14.25" customHeight="1">
       <c r="A40" s="2" t="s">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="D40" s="2">
         <v>5.0</v>
@@ -11800,21 +11913,21 @@
         <v>1.0</v>
       </c>
       <c r="G40" s="2">
-        <v>30.0</v>
+        <v>20.0</v>
       </c>
       <c r="H40" s="2" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
     </row>
     <row r="41" ht="14.25" customHeight="1">
       <c r="A41" s="2" t="s">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="D41" s="2">
         <v>5.0</v>
@@ -11826,21 +11939,21 @@
         <v>1.0</v>
       </c>
       <c r="G41" s="2">
-        <v>40.0</v>
+        <v>30.0</v>
       </c>
       <c r="H41" s="2" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
     </row>
     <row r="42" ht="14.25" customHeight="1">
       <c r="A42" s="2" t="s">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="D42" s="2">
         <v>5.0</v>
@@ -11852,47 +11965,47 @@
         <v>1.0</v>
       </c>
       <c r="G42" s="2">
-        <v>50.0</v>
+        <v>40.0</v>
       </c>
       <c r="H42" s="2" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
     </row>
     <row r="43" ht="14.25" customHeight="1">
       <c r="A43" s="2" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="D43" s="2">
-        <v>0.0</v>
+        <v>5.0</v>
       </c>
       <c r="E43" s="2">
-        <v>0.0</v>
+        <v>5.0</v>
       </c>
       <c r="F43" s="2">
         <v>1.0</v>
       </c>
       <c r="G43" s="2">
-        <v>10.0</v>
+        <v>50.0</v>
       </c>
       <c r="H43" s="2" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
     </row>
     <row r="44" ht="14.25" customHeight="1">
       <c r="A44" s="2" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="D44" s="2">
         <v>0.0</v>
@@ -11904,21 +12017,21 @@
         <v>1.0</v>
       </c>
       <c r="G44" s="2">
-        <v>20.0</v>
+        <v>10.0</v>
       </c>
       <c r="H44" s="2" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
     </row>
     <row r="45" ht="14.25" customHeight="1">
       <c r="A45" s="2" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="D45" s="2">
         <v>0.0</v>
@@ -11930,21 +12043,21 @@
         <v>1.0</v>
       </c>
       <c r="G45" s="2">
-        <v>30.0</v>
+        <v>20.0</v>
       </c>
       <c r="H45" s="2" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
     </row>
     <row r="46" ht="14.25" customHeight="1">
       <c r="A46" s="2" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="D46" s="2">
         <v>0.0</v>
@@ -11956,21 +12069,21 @@
         <v>1.0</v>
       </c>
       <c r="G46" s="2">
-        <v>40.0</v>
+        <v>30.0</v>
       </c>
       <c r="H46" s="2" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
     </row>
     <row r="47" ht="14.25" customHeight="1">
       <c r="A47" s="2" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="D47" s="2">
         <v>0.0</v>
@@ -11982,21 +12095,21 @@
         <v>1.0</v>
       </c>
       <c r="G47" s="2">
-        <v>10.0</v>
+        <v>40.0</v>
       </c>
       <c r="H47" s="2" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
     </row>
     <row r="48" ht="14.25" customHeight="1">
       <c r="A48" s="2" t="s">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="D48" s="2">
         <v>0.0</v>
@@ -12008,21 +12121,21 @@
         <v>1.0</v>
       </c>
       <c r="G48" s="2">
-        <v>20.0</v>
+        <v>10.0</v>
       </c>
       <c r="H48" s="2" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
     </row>
     <row r="49" ht="14.25" customHeight="1">
       <c r="A49" s="2" t="s">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="D49" s="2">
         <v>0.0</v>
@@ -12034,21 +12147,21 @@
         <v>1.0</v>
       </c>
       <c r="G49" s="2">
-        <v>30.0</v>
+        <v>20.0</v>
       </c>
       <c r="H49" s="2" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
     </row>
     <row r="50" ht="14.25" customHeight="1">
       <c r="A50" s="2" t="s">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="D50" s="2">
         <v>0.0</v>
@@ -12060,21 +12173,21 @@
         <v>1.0</v>
       </c>
       <c r="G50" s="2">
-        <v>40.0</v>
+        <v>30.0</v>
       </c>
       <c r="H50" s="2" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
     </row>
     <row r="51" ht="14.25" customHeight="1">
       <c r="A51" s="2" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="D51" s="2">
         <v>0.0</v>
@@ -12086,21 +12199,21 @@
         <v>1.0</v>
       </c>
       <c r="G51" s="2">
-        <v>10.0</v>
+        <v>40.0</v>
       </c>
       <c r="H51" s="2" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
     </row>
     <row r="52" ht="14.25" customHeight="1">
       <c r="A52" s="2" t="s">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="D52" s="2">
         <v>0.0</v>
@@ -12112,21 +12225,21 @@
         <v>1.0</v>
       </c>
       <c r="G52" s="2">
-        <v>20.0</v>
+        <v>10.0</v>
       </c>
       <c r="H52" s="2" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
     </row>
     <row r="53" ht="14.25" customHeight="1">
       <c r="A53" s="2" t="s">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="D53" s="2">
         <v>0.0</v>
@@ -12138,21 +12251,21 @@
         <v>1.0</v>
       </c>
       <c r="G53" s="2">
-        <v>10.0</v>
+        <v>20.0</v>
       </c>
       <c r="H53" s="2" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
     </row>
     <row r="54" ht="14.25" customHeight="1">
       <c r="A54" s="2" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="D54" s="2">
         <v>0.0</v>
@@ -12164,21 +12277,21 @@
         <v>1.0</v>
       </c>
       <c r="G54" s="2">
-        <v>20.0</v>
+        <v>10.0</v>
       </c>
       <c r="H54" s="2" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
     </row>
     <row r="55" ht="14.25" customHeight="1">
       <c r="A55" s="2" t="s">
-        <v>238</v>
+        <v>242</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="D55" s="2">
         <v>0.0</v>
@@ -12190,21 +12303,21 @@
         <v>1.0</v>
       </c>
       <c r="G55" s="2">
-        <v>30.0</v>
+        <v>20.0</v>
       </c>
       <c r="H55" s="2" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
     </row>
     <row r="56" ht="14.25" customHeight="1">
       <c r="A56" s="2" t="s">
-        <v>238</v>
+        <v>242</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="D56" s="2">
         <v>0.0</v>
@@ -12216,21 +12329,21 @@
         <v>1.0</v>
       </c>
       <c r="G56" s="2">
-        <v>40.0</v>
+        <v>30.0</v>
       </c>
       <c r="H56" s="2" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
     </row>
     <row r="57" ht="14.25" customHeight="1">
       <c r="A57" s="2" t="s">
-        <v>238</v>
+        <v>242</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="D57" s="2">
         <v>0.0</v>
@@ -12242,21 +12355,21 @@
         <v>1.0</v>
       </c>
       <c r="G57" s="2">
-        <v>50.0</v>
+        <v>40.0</v>
       </c>
       <c r="H57" s="2" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
     </row>
     <row r="58" ht="14.25" customHeight="1">
       <c r="A58" s="2" t="s">
-        <v>238</v>
+        <v>242</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="D58" s="2">
         <v>0.0</v>
@@ -12268,21 +12381,21 @@
         <v>1.0</v>
       </c>
       <c r="G58" s="2">
-        <v>60.0</v>
+        <v>50.0</v>
       </c>
       <c r="H58" s="2" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
     </row>
     <row r="59" ht="14.25" customHeight="1">
       <c r="A59" s="2" t="s">
-        <v>238</v>
-      </c>
-      <c r="B59" s="4" t="s">
-        <v>426</v>
-      </c>
-      <c r="C59" s="4" t="s">
-        <v>427</v>
+        <v>242</v>
+      </c>
+      <c r="B59" s="2" t="s">
+        <v>428</v>
+      </c>
+      <c r="C59" s="2" t="s">
+        <v>429</v>
       </c>
       <c r="D59" s="2">
         <v>0.0</v>
@@ -12293,22 +12406,22 @@
       <c r="F59" s="2">
         <v>1.0</v>
       </c>
-      <c r="G59" s="4">
-        <v>70.0</v>
-      </c>
-      <c r="H59" s="4" t="s">
-        <v>428</v>
+      <c r="G59" s="2">
+        <v>60.0</v>
+      </c>
+      <c r="H59" s="2" t="s">
+        <v>430</v>
       </c>
     </row>
     <row r="60" ht="14.25" customHeight="1">
       <c r="A60" s="2" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="D60" s="2">
         <v>0.0</v>
@@ -12320,21 +12433,21 @@
         <v>1.0</v>
       </c>
       <c r="G60" s="2">
-        <v>10.0</v>
+        <v>70.0</v>
       </c>
       <c r="H60" s="2" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
     </row>
     <row r="61" ht="14.25" customHeight="1">
       <c r="A61" s="2" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="D61" s="2">
         <v>0.0</v>
@@ -12346,21 +12459,21 @@
         <v>1.0</v>
       </c>
       <c r="G61" s="2">
-        <v>20.0</v>
+        <v>10.0</v>
       </c>
       <c r="H61" s="2" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
     </row>
     <row r="62" ht="14.25" customHeight="1">
       <c r="A62" s="2" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="D62" s="2">
         <v>0.0</v>
@@ -12372,348 +12485,348 @@
         <v>1.0</v>
       </c>
       <c r="G62" s="2">
-        <v>10.0</v>
+        <v>20.0</v>
       </c>
       <c r="H62" s="2" t="s">
-        <v>436</v>
+        <v>439</v>
       </c>
     </row>
     <row r="63" ht="14.25" customHeight="1">
       <c r="A63" s="2" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>437</v>
+        <v>440</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>438</v>
-      </c>
-      <c r="D63" s="2">
-        <v>0.0</v>
-      </c>
-      <c r="E63" s="2">
+        <v>441</v>
+      </c>
+      <c r="D63" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="E63" s="4">
         <v>0.0</v>
       </c>
       <c r="F63" s="2">
         <v>1.0</v>
       </c>
       <c r="G63" s="2">
-        <v>20.0</v>
+        <v>10.0</v>
       </c>
       <c r="H63" s="2" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
     </row>
     <row r="64" ht="14.25" customHeight="1">
       <c r="A64" s="2" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>439</v>
+        <v>442</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>440</v>
-      </c>
-      <c r="D64" s="2">
-        <v>0.0</v>
-      </c>
-      <c r="E64" s="2">
+        <v>443</v>
+      </c>
+      <c r="D64" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="E64" s="4">
         <v>0.0</v>
       </c>
       <c r="F64" s="2">
         <v>1.0</v>
       </c>
       <c r="G64" s="2">
-        <v>30.0</v>
+        <v>20.0</v>
       </c>
       <c r="H64" s="2" t="s">
-        <v>440</v>
+        <v>443</v>
       </c>
     </row>
     <row r="65" ht="14.25" customHeight="1">
       <c r="A65" s="2" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>441</v>
+        <v>444</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>442</v>
-      </c>
-      <c r="D65" s="2">
-        <v>0.0</v>
-      </c>
-      <c r="E65" s="2">
+        <v>445</v>
+      </c>
+      <c r="D65" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="E65" s="4">
         <v>0.0</v>
       </c>
       <c r="F65" s="2">
         <v>1.0</v>
       </c>
       <c r="G65" s="2">
-        <v>40.0</v>
+        <v>30.0</v>
       </c>
       <c r="H65" s="2" t="s">
-        <v>442</v>
+        <v>445</v>
       </c>
     </row>
     <row r="66" ht="14.25" customHeight="1">
       <c r="A66" s="2" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>443</v>
+        <v>446</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>444</v>
-      </c>
-      <c r="D66" s="2">
-        <v>0.0</v>
-      </c>
-      <c r="E66" s="2">
+        <v>447</v>
+      </c>
+      <c r="D66" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="E66" s="4">
         <v>0.0</v>
       </c>
       <c r="F66" s="2">
         <v>1.0</v>
       </c>
       <c r="G66" s="2">
-        <v>50.0</v>
+        <v>40.0</v>
       </c>
       <c r="H66" s="2" t="s">
-        <v>444</v>
+        <v>447</v>
       </c>
     </row>
     <row r="67" ht="14.25" customHeight="1">
       <c r="A67" s="2" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>445</v>
+        <v>448</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>446</v>
-      </c>
-      <c r="D67" s="2">
-        <v>0.0</v>
-      </c>
-      <c r="E67" s="2">
+        <v>449</v>
+      </c>
+      <c r="D67" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="E67" s="4">
         <v>0.0</v>
       </c>
       <c r="F67" s="2">
         <v>1.0</v>
       </c>
       <c r="G67" s="2">
-        <v>60.0</v>
+        <v>50.0</v>
       </c>
       <c r="H67" s="2" t="s">
-        <v>446</v>
+        <v>449</v>
       </c>
     </row>
     <row r="68" ht="14.25" customHeight="1">
       <c r="A68" s="2" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>447</v>
+        <v>450</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>448</v>
-      </c>
-      <c r="D68" s="2">
-        <v>0.0</v>
-      </c>
-      <c r="E68" s="2">
+        <v>451</v>
+      </c>
+      <c r="D68" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="E68" s="4">
         <v>0.0</v>
       </c>
       <c r="F68" s="2">
         <v>1.0</v>
       </c>
       <c r="G68" s="2">
-        <v>70.0</v>
+        <v>60.0</v>
       </c>
       <c r="H68" s="2" t="s">
-        <v>448</v>
+        <v>451</v>
       </c>
     </row>
     <row r="69" ht="14.25" customHeight="1">
       <c r="A69" s="2" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>449</v>
+        <v>452</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>450</v>
-      </c>
-      <c r="D69" s="2">
-        <v>0.0</v>
-      </c>
-      <c r="E69" s="2">
+        <v>453</v>
+      </c>
+      <c r="D69" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="E69" s="4">
         <v>0.0</v>
       </c>
       <c r="F69" s="2">
         <v>1.0</v>
       </c>
       <c r="G69" s="2">
-        <v>80.0</v>
+        <v>70.0</v>
       </c>
       <c r="H69" s="2" t="s">
-        <v>450</v>
+        <v>453</v>
       </c>
     </row>
     <row r="70" ht="14.25" customHeight="1">
       <c r="A70" s="2" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>451</v>
+        <v>454</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>452</v>
-      </c>
-      <c r="D70" s="2">
-        <v>0.0</v>
-      </c>
-      <c r="E70" s="2">
+        <v>455</v>
+      </c>
+      <c r="D70" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="E70" s="4">
         <v>0.0</v>
       </c>
       <c r="F70" s="2">
         <v>1.0</v>
       </c>
       <c r="G70" s="2">
-        <v>10.0</v>
+        <v>80.0</v>
       </c>
       <c r="H70" s="2" t="s">
-        <v>452</v>
+        <v>455</v>
       </c>
     </row>
     <row r="71" ht="14.25" customHeight="1">
       <c r="A71" s="2" t="s">
-        <v>244</v>
-      </c>
-      <c r="B71" s="2" t="s">
-        <v>453</v>
-      </c>
-      <c r="C71" s="2" t="s">
-        <v>454</v>
-      </c>
-      <c r="D71" s="2">
-        <v>0.0</v>
-      </c>
-      <c r="E71" s="2">
+        <v>246</v>
+      </c>
+      <c r="B71" s="4" t="s">
+        <v>456</v>
+      </c>
+      <c r="C71" s="4" t="s">
+        <v>457</v>
+      </c>
+      <c r="D71" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="E71" s="4">
         <v>0.0</v>
       </c>
       <c r="F71" s="2">
         <v>1.0</v>
       </c>
-      <c r="G71" s="2">
-        <v>20.0</v>
-      </c>
-      <c r="H71" s="2" t="s">
-        <v>454</v>
+      <c r="G71" s="4">
+        <v>90.0</v>
+      </c>
+      <c r="H71" s="4" t="s">
+        <v>457</v>
       </c>
     </row>
     <row r="72" ht="14.25" customHeight="1">
       <c r="A72" s="2" t="s">
-        <v>244</v>
-      </c>
-      <c r="B72" s="2" t="s">
-        <v>455</v>
-      </c>
-      <c r="C72" s="2" t="s">
-        <v>456</v>
-      </c>
-      <c r="D72" s="2">
-        <v>0.0</v>
-      </c>
-      <c r="E72" s="2">
+        <v>246</v>
+      </c>
+      <c r="B72" s="4" t="s">
+        <v>458</v>
+      </c>
+      <c r="C72" s="4" t="s">
+        <v>459</v>
+      </c>
+      <c r="D72" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="E72" s="4">
         <v>0.0</v>
       </c>
       <c r="F72" s="2">
         <v>1.0</v>
       </c>
       <c r="G72" s="2">
-        <v>30.0</v>
-      </c>
-      <c r="H72" s="2" t="s">
-        <v>456</v>
+        <v>100.0</v>
+      </c>
+      <c r="H72" s="4" t="s">
+        <v>459</v>
       </c>
     </row>
     <row r="73" ht="14.25" customHeight="1">
       <c r="A73" s="2" t="s">
         <v>246</v>
       </c>
-      <c r="B73" s="2" t="s">
-        <v>246</v>
-      </c>
-      <c r="C73" s="2" t="s">
-        <v>247</v>
-      </c>
-      <c r="D73" s="2">
-        <v>0.0</v>
-      </c>
-      <c r="E73" s="2">
+      <c r="B73" s="4" t="s">
+        <v>460</v>
+      </c>
+      <c r="C73" s="4" t="s">
+        <v>461</v>
+      </c>
+      <c r="D73" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="E73" s="4">
         <v>0.0</v>
       </c>
       <c r="F73" s="2">
         <v>1.0</v>
       </c>
       <c r="G73" s="2">
-        <v>10.0</v>
-      </c>
-      <c r="H73" s="2" t="s">
-        <v>247</v>
+        <v>110.0</v>
+      </c>
+      <c r="H73" s="4" t="s">
+        <v>461</v>
       </c>
     </row>
     <row r="74" ht="14.25" customHeight="1">
       <c r="A74" s="2" t="s">
-        <v>248</v>
-      </c>
-      <c r="B74" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="C74" s="2" t="s">
-        <v>457</v>
-      </c>
-      <c r="D74" s="2">
-        <v>35.0</v>
-      </c>
-      <c r="E74" s="2">
-        <v>16.0</v>
+        <v>246</v>
+      </c>
+      <c r="B74" s="4" t="s">
+        <v>462</v>
+      </c>
+      <c r="C74" s="4" t="s">
+        <v>463</v>
+      </c>
+      <c r="D74" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="E74" s="4">
+        <v>0.0</v>
       </c>
       <c r="F74" s="2">
         <v>1.0</v>
       </c>
-      <c r="G74" s="2">
-        <v>10.0</v>
-      </c>
-      <c r="H74" s="2" t="s">
-        <v>458</v>
+      <c r="G74" s="4">
+        <v>120.0</v>
+      </c>
+      <c r="H74" s="4" t="s">
+        <v>463</v>
       </c>
     </row>
     <row r="75" ht="14.25" customHeight="1">
       <c r="A75" s="2" t="s">
-        <v>248</v>
-      </c>
-      <c r="B75" s="2" t="s">
-        <v>193</v>
-      </c>
-      <c r="C75" s="2" t="s">
-        <v>459</v>
-      </c>
-      <c r="D75" s="2">
-        <v>35.0</v>
-      </c>
-      <c r="E75" s="2">
-        <v>17.0</v>
+        <v>246</v>
+      </c>
+      <c r="B75" s="4" t="s">
+        <v>464</v>
+      </c>
+      <c r="C75" s="4" t="s">
+        <v>465</v>
+      </c>
+      <c r="D75" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="E75" s="4">
+        <v>0.0</v>
       </c>
       <c r="F75" s="2">
         <v>1.0</v>
       </c>
       <c r="G75" s="2">
-        <v>20.0</v>
-      </c>
-      <c r="H75" s="2" t="s">
-        <v>460</v>
+        <v>130.0</v>
+      </c>
+      <c r="H75" s="4" t="s">
+        <v>465</v>
       </c>
     </row>
     <row r="76" ht="14.25" customHeight="1">
@@ -12721,25 +12834,25 @@
         <v>248</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>189</v>
+        <v>466</v>
       </c>
       <c r="C76" s="2" t="s">
-        <v>461</v>
+        <v>467</v>
       </c>
       <c r="D76" s="2">
-        <v>35.0</v>
+        <v>0.0</v>
       </c>
       <c r="E76" s="2">
-        <v>18.0</v>
+        <v>0.0</v>
       </c>
       <c r="F76" s="2">
         <v>1.0</v>
       </c>
       <c r="G76" s="2">
-        <v>30.0</v>
+        <v>10.0</v>
       </c>
       <c r="H76" s="2" t="s">
-        <v>462</v>
+        <v>467</v>
       </c>
     </row>
     <row r="77" ht="14.25" customHeight="1">
@@ -12747,25 +12860,25 @@
         <v>248</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>196</v>
+        <v>468</v>
       </c>
       <c r="C77" s="2" t="s">
-        <v>463</v>
+        <v>469</v>
       </c>
       <c r="D77" s="2">
-        <v>35.0</v>
+        <v>0.0</v>
       </c>
       <c r="E77" s="2">
-        <v>18.0</v>
+        <v>0.0</v>
       </c>
       <c r="F77" s="2">
         <v>1.0</v>
       </c>
       <c r="G77" s="2">
-        <v>40.0</v>
+        <v>20.0</v>
       </c>
       <c r="H77" s="2" t="s">
-        <v>464</v>
+        <v>469</v>
       </c>
     </row>
     <row r="78" ht="14.25" customHeight="1">
@@ -12773,126 +12886,126 @@
         <v>248</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>198</v>
+        <v>470</v>
       </c>
       <c r="C78" s="2" t="s">
-        <v>465</v>
+        <v>471</v>
       </c>
       <c r="D78" s="2">
-        <v>35.0</v>
+        <v>0.0</v>
       </c>
       <c r="E78" s="2">
-        <v>14.0</v>
+        <v>0.0</v>
       </c>
       <c r="F78" s="2">
         <v>1.0</v>
       </c>
       <c r="G78" s="2">
-        <v>50.0</v>
+        <v>30.0</v>
       </c>
       <c r="H78" s="2" t="s">
-        <v>466</v>
+        <v>471</v>
       </c>
     </row>
     <row r="79" ht="14.25" customHeight="1">
       <c r="A79" s="2" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>191</v>
+        <v>250</v>
       </c>
       <c r="C79" s="2" t="s">
-        <v>467</v>
+        <v>251</v>
       </c>
       <c r="D79" s="2">
-        <v>55.0</v>
+        <v>0.0</v>
       </c>
       <c r="E79" s="2">
-        <v>27.0</v>
+        <v>0.0</v>
       </c>
       <c r="F79" s="2">
         <v>1.0</v>
       </c>
       <c r="G79" s="2">
-        <v>60.0</v>
+        <v>10.0</v>
       </c>
       <c r="H79" s="2" t="s">
-        <v>468</v>
+        <v>251</v>
       </c>
     </row>
     <row r="80" ht="14.25" customHeight="1">
       <c r="A80" s="2" t="s">
-        <v>248</v>
+        <v>252</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>469</v>
+        <v>80</v>
       </c>
       <c r="C80" s="2" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="D80" s="2">
-        <v>40.0</v>
+        <v>35.0</v>
       </c>
       <c r="E80" s="2">
-        <v>18.0</v>
+        <v>16.0</v>
       </c>
       <c r="F80" s="2">
         <v>1.0</v>
       </c>
       <c r="G80" s="2">
-        <v>70.0</v>
+        <v>10.0</v>
       </c>
       <c r="H80" s="2" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
     </row>
     <row r="81" ht="14.25" customHeight="1">
       <c r="A81" s="2" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>472</v>
+        <v>197</v>
       </c>
       <c r="C81" s="2" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="D81" s="2">
-        <v>0.0</v>
+        <v>35.0</v>
       </c>
       <c r="E81" s="2">
-        <v>0.0</v>
+        <v>17.0</v>
       </c>
       <c r="F81" s="2">
         <v>1.0</v>
       </c>
       <c r="G81" s="2">
-        <v>10.0</v>
+        <v>20.0</v>
       </c>
       <c r="H81" s="2" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
     </row>
     <row r="82" ht="14.25" customHeight="1">
       <c r="A82" s="2" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>475</v>
+        <v>191</v>
       </c>
       <c r="C82" s="2" t="s">
         <v>476</v>
       </c>
       <c r="D82" s="2">
-        <v>5.0</v>
+        <v>35.0</v>
       </c>
       <c r="E82" s="2">
-        <v>5.0</v>
+        <v>18.0</v>
       </c>
       <c r="F82" s="2">
         <v>1.0</v>
       </c>
       <c r="G82" s="2">
-        <v>20.0</v>
+        <v>30.0</v>
       </c>
       <c r="H82" s="2" t="s">
         <v>477</v>
@@ -12903,22 +13016,22 @@
         <v>252</v>
       </c>
       <c r="B83" s="2" t="s">
+        <v>200</v>
+      </c>
+      <c r="C83" s="2" t="s">
         <v>478</v>
       </c>
-      <c r="C83" s="2" t="s">
-        <v>479</v>
-      </c>
       <c r="D83" s="2">
-        <v>0.0</v>
+        <v>35.0</v>
       </c>
       <c r="E83" s="2">
-        <v>0.0</v>
+        <v>18.0</v>
       </c>
       <c r="F83" s="2">
         <v>1.0</v>
       </c>
       <c r="G83" s="2">
-        <v>10.0</v>
+        <v>40.0</v>
       </c>
       <c r="H83" s="2" t="s">
         <v>479</v>
@@ -12928,25 +13041,25 @@
       <c r="A84" s="2" t="s">
         <v>252</v>
       </c>
-      <c r="B84" s="2" t="s">
+      <c r="B84" s="4" t="s">
+        <v>195</v>
+      </c>
+      <c r="C84" s="4" t="s">
         <v>480</v>
       </c>
-      <c r="C84" s="2" t="s">
-        <v>481</v>
-      </c>
       <c r="D84" s="2">
-        <v>0.0</v>
+        <v>35.0</v>
       </c>
       <c r="E84" s="2">
-        <v>0.0</v>
+        <v>18.0</v>
       </c>
       <c r="F84" s="2">
         <v>1.0</v>
       </c>
-      <c r="G84" s="2">
-        <v>20.0</v>
-      </c>
-      <c r="H84" s="2" t="s">
+      <c r="G84" s="4">
+        <v>50.0</v>
+      </c>
+      <c r="H84" s="4" t="s">
         <v>481</v>
       </c>
     </row>
@@ -12955,22 +13068,22 @@
         <v>252</v>
       </c>
       <c r="B85" s="2" t="s">
+        <v>202</v>
+      </c>
+      <c r="C85" s="2" t="s">
         <v>482</v>
       </c>
-      <c r="C85" s="2" t="s">
-        <v>483</v>
-      </c>
       <c r="D85" s="2">
-        <v>0.0</v>
+        <v>35.0</v>
       </c>
       <c r="E85" s="2">
-        <v>0.0</v>
+        <v>14.0</v>
       </c>
       <c r="F85" s="2">
         <v>1.0</v>
       </c>
       <c r="G85" s="2">
-        <v>30.0</v>
+        <v>60.0</v>
       </c>
       <c r="H85" s="2" t="s">
         <v>483</v>
@@ -12981,22 +13094,22 @@
         <v>252</v>
       </c>
       <c r="B86" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="C86" s="2" t="s">
         <v>484</v>
       </c>
-      <c r="C86" s="2" t="s">
-        <v>485</v>
-      </c>
       <c r="D86" s="2">
-        <v>0.0</v>
+        <v>55.0</v>
       </c>
       <c r="E86" s="2">
-        <v>0.0</v>
+        <v>27.0</v>
       </c>
       <c r="F86" s="2">
         <v>1.0</v>
       </c>
       <c r="G86" s="2">
-        <v>40.0</v>
+        <v>70.0</v>
       </c>
       <c r="H86" s="2" t="s">
         <v>485</v>
@@ -13004,7 +13117,7 @@
     </row>
     <row r="87" ht="14.25" customHeight="1">
       <c r="A87" s="2" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="B87" s="2" t="s">
         <v>486</v>
@@ -13013,30 +13126,30 @@
         <v>487</v>
       </c>
       <c r="D87" s="2">
-        <v>7.0</v>
+        <v>40.0</v>
       </c>
       <c r="E87" s="2">
-        <v>7.0</v>
+        <v>18.0</v>
       </c>
       <c r="F87" s="2">
         <v>1.0</v>
       </c>
-      <c r="G87" s="2">
-        <v>10.0</v>
+      <c r="G87" s="4">
+        <v>80.0</v>
       </c>
       <c r="H87" s="2" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
     </row>
     <row r="88" ht="14.25" customHeight="1">
       <c r="A88" s="2" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="B88" s="2" t="s">
-        <v>256</v>
+        <v>489</v>
       </c>
       <c r="C88" s="2" t="s">
-        <v>257</v>
+        <v>490</v>
       </c>
       <c r="D88" s="2">
         <v>0.0</v>
@@ -13051,44 +13164,44 @@
         <v>10.0</v>
       </c>
       <c r="H88" s="2" t="s">
-        <v>257</v>
+        <v>491</v>
       </c>
     </row>
     <row r="89" ht="14.25" customHeight="1">
       <c r="A89" s="2" t="s">
-        <v>222</v>
+        <v>254</v>
       </c>
       <c r="B89" s="2" t="s">
-        <v>488</v>
+        <v>492</v>
       </c>
       <c r="C89" s="2" t="s">
-        <v>489</v>
+        <v>493</v>
       </c>
       <c r="D89" s="2">
-        <v>0.0</v>
+        <v>5.0</v>
       </c>
       <c r="E89" s="2">
-        <v>0.0</v>
+        <v>5.0</v>
       </c>
       <c r="F89" s="2">
         <v>1.0</v>
       </c>
       <c r="G89" s="2">
-        <v>60.0</v>
+        <v>20.0</v>
       </c>
       <c r="H89" s="2" t="s">
-        <v>490</v>
+        <v>494</v>
       </c>
     </row>
     <row r="90" ht="14.25" customHeight="1">
-      <c r="A90" s="3" t="s">
-        <v>258</v>
-      </c>
-      <c r="B90" s="3" t="s">
-        <v>491</v>
-      </c>
-      <c r="C90" s="3" t="s">
-        <v>492</v>
+      <c r="A90" s="2" t="s">
+        <v>256</v>
+      </c>
+      <c r="B90" s="2" t="s">
+        <v>495</v>
+      </c>
+      <c r="C90" s="2" t="s">
+        <v>496</v>
       </c>
       <c r="D90" s="2">
         <v>0.0</v>
@@ -13102,19 +13215,19 @@
       <c r="G90" s="2">
         <v>10.0</v>
       </c>
-      <c r="H90" s="3" t="s">
-        <v>493</v>
+      <c r="H90" s="2" t="s">
+        <v>496</v>
       </c>
     </row>
     <row r="91" ht="14.25" customHeight="1">
-      <c r="A91" s="3" t="s">
-        <v>258</v>
-      </c>
-      <c r="B91" s="3" t="s">
-        <v>494</v>
-      </c>
-      <c r="C91" s="3" t="s">
-        <v>495</v>
+      <c r="A91" s="2" t="s">
+        <v>256</v>
+      </c>
+      <c r="B91" s="2" t="s">
+        <v>497</v>
+      </c>
+      <c r="C91" s="2" t="s">
+        <v>498</v>
       </c>
       <c r="D91" s="2">
         <v>0.0</v>
@@ -13128,19 +13241,19 @@
       <c r="G91" s="2">
         <v>20.0</v>
       </c>
-      <c r="H91" s="3" t="s">
-        <v>496</v>
+      <c r="H91" s="2" t="s">
+        <v>498</v>
       </c>
     </row>
     <row r="92" ht="14.25" customHeight="1">
-      <c r="A92" s="3" t="s">
-        <v>258</v>
-      </c>
-      <c r="B92" s="3" t="s">
-        <v>497</v>
-      </c>
-      <c r="C92" s="3" t="s">
-        <v>498</v>
+      <c r="A92" s="2" t="s">
+        <v>256</v>
+      </c>
+      <c r="B92" s="2" t="s">
+        <v>499</v>
+      </c>
+      <c r="C92" s="2" t="s">
+        <v>500</v>
       </c>
       <c r="D92" s="2">
         <v>0.0</v>
@@ -13154,19 +13267,19 @@
       <c r="G92" s="2">
         <v>30.0</v>
       </c>
-      <c r="H92" s="3" t="s">
-        <v>499</v>
+      <c r="H92" s="2" t="s">
+        <v>500</v>
       </c>
     </row>
     <row r="93" ht="14.25" customHeight="1">
-      <c r="A93" s="3" t="s">
-        <v>258</v>
-      </c>
-      <c r="B93" s="3" t="s">
-        <v>500</v>
-      </c>
-      <c r="C93" s="3" t="s">
+      <c r="A93" s="2" t="s">
+        <v>256</v>
+      </c>
+      <c r="B93" s="2" t="s">
         <v>501</v>
+      </c>
+      <c r="C93" s="2" t="s">
+        <v>502</v>
       </c>
       <c r="D93" s="2">
         <v>0.0</v>
@@ -13180,13 +13293,13 @@
       <c r="G93" s="2">
         <v>40.0</v>
       </c>
-      <c r="H93" s="3" t="s">
+      <c r="H93" s="2" t="s">
         <v>502</v>
       </c>
     </row>
     <row r="94" ht="14.25" customHeight="1">
       <c r="A94" s="2" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="B94" s="2" t="s">
         <v>503</v>
@@ -13195,10 +13308,10 @@
         <v>504</v>
       </c>
       <c r="D94" s="2">
-        <v>0.0</v>
+        <v>7.0</v>
       </c>
       <c r="E94" s="2">
-        <v>0.0</v>
+        <v>7.0</v>
       </c>
       <c r="F94" s="2">
         <v>1.0</v>
@@ -13207,7 +13320,7 @@
         <v>10.0</v>
       </c>
       <c r="H94" s="2" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
     </row>
     <row r="95" ht="14.25" customHeight="1">
@@ -13215,190 +13328,365 @@
         <v>260</v>
       </c>
       <c r="B95" s="2" t="s">
+        <v>260</v>
+      </c>
+      <c r="C95" s="2" t="s">
+        <v>261</v>
+      </c>
+      <c r="D95" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="E95" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="F95" s="2">
+        <v>1.0</v>
+      </c>
+      <c r="G95" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="H95" s="2" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="96" ht="14.25" customHeight="1">
+      <c r="A96" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="B96" s="2" t="s">
+        <v>505</v>
+      </c>
+      <c r="C96" s="2" t="s">
+        <v>506</v>
+      </c>
+      <c r="D96" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="E96" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="F96" s="2">
+        <v>1.0</v>
+      </c>
+      <c r="G96" s="2">
+        <v>60.0</v>
+      </c>
+      <c r="H96" s="2" t="s">
+        <v>507</v>
+      </c>
+    </row>
+    <row r="97" ht="14.25" customHeight="1">
+      <c r="A97" s="3" t="s">
+        <v>262</v>
+      </c>
+      <c r="B97" s="3" t="s">
+        <v>508</v>
+      </c>
+      <c r="C97" s="3" t="s">
+        <v>509</v>
+      </c>
+      <c r="D97" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="E97" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="F97" s="2">
+        <v>1.0</v>
+      </c>
+      <c r="G97" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="H97" s="3" t="s">
+        <v>510</v>
+      </c>
+    </row>
+    <row r="98" ht="14.25" customHeight="1">
+      <c r="A98" s="3" t="s">
+        <v>262</v>
+      </c>
+      <c r="B98" s="3" t="s">
+        <v>511</v>
+      </c>
+      <c r="C98" s="3" t="s">
+        <v>512</v>
+      </c>
+      <c r="D98" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="E98" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="F98" s="2">
+        <v>1.0</v>
+      </c>
+      <c r="G98" s="2">
+        <v>20.0</v>
+      </c>
+      <c r="H98" s="3" t="s">
+        <v>513</v>
+      </c>
+    </row>
+    <row r="99" ht="14.25" customHeight="1">
+      <c r="A99" s="3" t="s">
+        <v>262</v>
+      </c>
+      <c r="B99" s="3" t="s">
+        <v>514</v>
+      </c>
+      <c r="C99" s="3" t="s">
+        <v>515</v>
+      </c>
+      <c r="D99" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="E99" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="F99" s="2">
+        <v>1.0</v>
+      </c>
+      <c r="G99" s="2">
+        <v>30.0</v>
+      </c>
+      <c r="H99" s="3" t="s">
+        <v>516</v>
+      </c>
+    </row>
+    <row r="100" ht="14.25" customHeight="1">
+      <c r="A100" s="3" t="s">
+        <v>262</v>
+      </c>
+      <c r="B100" s="3" t="s">
+        <v>517</v>
+      </c>
+      <c r="C100" s="3" t="s">
+        <v>518</v>
+      </c>
+      <c r="D100" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="E100" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="F100" s="2">
+        <v>1.0</v>
+      </c>
+      <c r="G100" s="2">
+        <v>40.0</v>
+      </c>
+      <c r="H100" s="3" t="s">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="101" ht="14.25" customHeight="1">
+      <c r="A101" s="2" t="s">
+        <v>264</v>
+      </c>
+      <c r="B101" s="2" t="s">
+        <v>520</v>
+      </c>
+      <c r="C101" s="2" t="s">
+        <v>521</v>
+      </c>
+      <c r="D101" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="E101" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="F101" s="2">
+        <v>1.0</v>
+      </c>
+      <c r="G101" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="H101" s="2" t="s">
+        <v>522</v>
+      </c>
+    </row>
+    <row r="102" ht="14.25" customHeight="1">
+      <c r="A102" s="2" t="s">
+        <v>264</v>
+      </c>
+      <c r="B102" s="2" t="s">
         <v>110</v>
       </c>
-      <c r="C95" s="2" t="s">
-        <v>506</v>
-      </c>
-      <c r="D95" s="2">
-        <v>0.0</v>
-      </c>
-      <c r="E95" s="2">
-        <v>0.0</v>
-      </c>
-      <c r="F95" s="2">
-        <v>1.0</v>
-      </c>
-      <c r="G95" s="2">
+      <c r="C102" s="2" t="s">
+        <v>523</v>
+      </c>
+      <c r="D102" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="E102" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="F102" s="2">
+        <v>1.0</v>
+      </c>
+      <c r="G102" s="2">
         <v>20.0</v>
       </c>
-      <c r="H95" s="2" t="s">
+      <c r="H102" s="2" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="96" ht="14.25" customHeight="1">
-      <c r="A96" s="5" t="s">
-        <v>262</v>
-      </c>
-      <c r="B96" s="5" t="s">
-        <v>507</v>
-      </c>
-      <c r="C96" s="5" t="s">
-        <v>508</v>
-      </c>
-      <c r="D96" s="5">
+    <row r="103" ht="14.25" customHeight="1">
+      <c r="A103" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="B103" s="2" t="s">
+        <v>524</v>
+      </c>
+      <c r="C103" s="2" t="s">
+        <v>525</v>
+      </c>
+      <c r="D103" s="2">
         <v>55.0</v>
       </c>
-      <c r="E96" s="5">
+      <c r="E103" s="2">
         <v>20.0</v>
       </c>
-      <c r="F96" s="5">
-        <v>1.0</v>
-      </c>
-      <c r="G96" s="5">
+      <c r="F103" s="2">
+        <v>1.0</v>
+      </c>
+      <c r="G103" s="2">
         <v>10.0</v>
       </c>
-      <c r="H96" s="5" t="s">
-        <v>509</v>
-      </c>
-    </row>
-    <row r="97" ht="14.25" customHeight="1">
-      <c r="A97" s="5" t="s">
-        <v>262</v>
-      </c>
-      <c r="B97" s="5" t="s">
-        <v>510</v>
-      </c>
-      <c r="C97" s="5" t="s">
-        <v>511</v>
-      </c>
-      <c r="D97" s="5">
+      <c r="H103" s="2" t="s">
+        <v>526</v>
+      </c>
+    </row>
+    <row r="104" ht="14.25" customHeight="1">
+      <c r="A104" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="B104" s="2" t="s">
+        <v>527</v>
+      </c>
+      <c r="C104" s="2" t="s">
+        <v>528</v>
+      </c>
+      <c r="D104" s="2">
         <v>95.0</v>
       </c>
-      <c r="E97" s="5">
+      <c r="E104" s="2">
         <v>28.0</v>
       </c>
-      <c r="F97" s="5">
-        <v>1.0</v>
-      </c>
-      <c r="G97" s="5">
+      <c r="F104" s="2">
+        <v>1.0</v>
+      </c>
+      <c r="G104" s="2">
         <v>20.0</v>
       </c>
-      <c r="H97" s="5" t="s">
-        <v>512</v>
-      </c>
-    </row>
-    <row r="98" ht="14.25" customHeight="1">
-      <c r="A98" s="5" t="s">
-        <v>264</v>
-      </c>
-      <c r="B98" s="5" t="s">
-        <v>513</v>
-      </c>
-      <c r="C98" s="5" t="s">
-        <v>514</v>
-      </c>
-      <c r="D98" s="5">
-        <v>0.0</v>
-      </c>
-      <c r="E98" s="5">
-        <v>0.0</v>
-      </c>
-      <c r="F98" s="5">
-        <v>1.0</v>
-      </c>
-      <c r="G98" s="5">
+      <c r="H104" s="2" t="s">
+        <v>529</v>
+      </c>
+    </row>
+    <row r="105" ht="14.25" customHeight="1">
+      <c r="A105" s="2" t="s">
+        <v>268</v>
+      </c>
+      <c r="B105" s="2" t="s">
+        <v>530</v>
+      </c>
+      <c r="C105" s="2" t="s">
+        <v>531</v>
+      </c>
+      <c r="D105" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="E105" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="F105" s="2">
+        <v>1.0</v>
+      </c>
+      <c r="G105" s="2">
         <v>10.0</v>
       </c>
-      <c r="H98" s="5" t="s">
-        <v>515</v>
-      </c>
-    </row>
-    <row r="99" ht="14.25" customHeight="1">
-      <c r="A99" s="5" t="s">
-        <v>264</v>
-      </c>
-      <c r="B99" s="5" t="s">
-        <v>516</v>
-      </c>
-      <c r="C99" s="5" t="s">
-        <v>517</v>
-      </c>
-      <c r="D99" s="5">
-        <v>0.0</v>
-      </c>
-      <c r="E99" s="5">
-        <v>0.0</v>
-      </c>
-      <c r="F99" s="5">
-        <v>1.0</v>
-      </c>
-      <c r="G99" s="5">
+      <c r="H105" s="2" t="s">
+        <v>532</v>
+      </c>
+    </row>
+    <row r="106" ht="14.25" customHeight="1">
+      <c r="A106" s="2" t="s">
+        <v>268</v>
+      </c>
+      <c r="B106" s="2" t="s">
+        <v>533</v>
+      </c>
+      <c r="C106" s="2" t="s">
+        <v>534</v>
+      </c>
+      <c r="D106" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="E106" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="F106" s="2">
+        <v>1.0</v>
+      </c>
+      <c r="G106" s="2">
         <v>20.0</v>
       </c>
-      <c r="H99" s="5" t="s">
-        <v>518</v>
-      </c>
-    </row>
-    <row r="100" ht="14.25" customHeight="1">
-      <c r="A100" s="5" t="s">
-        <v>264</v>
-      </c>
-      <c r="B100" s="5" t="s">
-        <v>519</v>
-      </c>
-      <c r="C100" s="5" t="s">
-        <v>520</v>
-      </c>
-      <c r="D100" s="5">
-        <v>0.0</v>
-      </c>
-      <c r="E100" s="5">
-        <v>0.0</v>
-      </c>
-      <c r="F100" s="5">
-        <v>1.0</v>
-      </c>
-      <c r="G100" s="5">
+      <c r="H106" s="2" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="107" ht="14.25" customHeight="1">
+      <c r="A107" s="2" t="s">
+        <v>268</v>
+      </c>
+      <c r="B107" s="2" t="s">
+        <v>536</v>
+      </c>
+      <c r="C107" s="2" t="s">
+        <v>537</v>
+      </c>
+      <c r="D107" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="E107" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="F107" s="2">
+        <v>1.0</v>
+      </c>
+      <c r="G107" s="2">
         <v>30.0</v>
       </c>
-      <c r="H100" s="5" t="s">
-        <v>521</v>
-      </c>
-    </row>
-    <row r="101" ht="14.25" customHeight="1">
-      <c r="A101" s="5" t="s">
-        <v>264</v>
-      </c>
-      <c r="B101" s="5" t="s">
-        <v>522</v>
-      </c>
-      <c r="C101" s="5" t="s">
-        <v>523</v>
-      </c>
-      <c r="D101" s="5">
-        <v>0.0</v>
-      </c>
-      <c r="E101" s="5">
-        <v>0.0</v>
-      </c>
-      <c r="F101" s="5">
-        <v>1.0</v>
-      </c>
-      <c r="G101" s="5">
+      <c r="H107" s="2" t="s">
+        <v>538</v>
+      </c>
+    </row>
+    <row r="108" ht="14.25" customHeight="1">
+      <c r="A108" s="2" t="s">
+        <v>268</v>
+      </c>
+      <c r="B108" s="2" t="s">
+        <v>539</v>
+      </c>
+      <c r="C108" s="2" t="s">
+        <v>540</v>
+      </c>
+      <c r="D108" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="E108" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="F108" s="2">
+        <v>1.0</v>
+      </c>
+      <c r="G108" s="2">
         <v>40.0</v>
       </c>
-      <c r="H101" s="5" t="s">
-        <v>524</v>
-      </c>
-    </row>
-    <row r="102" ht="14.25" customHeight="1"/>
-    <row r="103" ht="14.25" customHeight="1"/>
-    <row r="104" ht="14.25" customHeight="1"/>
-    <row r="105" ht="14.25" customHeight="1"/>
-    <row r="106" ht="14.25" customHeight="1"/>
-    <row r="107" ht="14.25" customHeight="1"/>
-    <row r="108" ht="14.25" customHeight="1"/>
+      <c r="H108" s="2" t="s">
+        <v>541</v>
+      </c>
+    </row>
     <row r="109" ht="14.25" customHeight="1"/>
     <row r="110" ht="14.25" customHeight="1"/>
     <row r="111" ht="14.25" customHeight="1"/>
@@ -13588,13 +13876,13 @@
     <row r="295" ht="14.25" customHeight="1"/>
     <row r="296" ht="14.25" customHeight="1"/>
     <row r="297" ht="14.25" customHeight="1"/>
-    <row r="298" ht="15.75" customHeight="1"/>
-    <row r="299" ht="15.75" customHeight="1"/>
-    <row r="300" ht="15.75" customHeight="1"/>
-    <row r="301" ht="15.75" customHeight="1"/>
-    <row r="302" ht="15.75" customHeight="1"/>
-    <row r="303" ht="15.75" customHeight="1"/>
-    <row r="304" ht="15.75" customHeight="1"/>
+    <row r="298" ht="14.25" customHeight="1"/>
+    <row r="299" ht="14.25" customHeight="1"/>
+    <row r="300" ht="14.25" customHeight="1"/>
+    <row r="301" ht="14.25" customHeight="1"/>
+    <row r="302" ht="14.25" customHeight="1"/>
+    <row r="303" ht="14.25" customHeight="1"/>
+    <row r="304" ht="14.25" customHeight="1"/>
     <row r="305" ht="15.75" customHeight="1"/>
     <row r="306" ht="15.75" customHeight="1"/>
     <row r="307" ht="15.75" customHeight="1"/>
@@ -14295,6 +14583,9 @@
     <row r="1002" ht="15.75" customHeight="1"/>
     <row r="1003" ht="15.75" customHeight="1"/>
     <row r="1004" ht="15.75" customHeight="1"/>
+    <row r="1005" ht="15.75" customHeight="1"/>
+    <row r="1006" ht="15.75" customHeight="1"/>
+    <row r="1007" ht="15.75" customHeight="1"/>
   </sheetData>
   <autoFilter ref="$A$1:$H$1"/>
   <printOptions/>
@@ -14322,22 +14613,22 @@
   <sheetData>
     <row r="1" ht="14.25" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>525</v>
+        <v>542</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>3</v>
@@ -14348,7 +14639,7 @@
         <v>38</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="C2" s="2">
         <v>1.0</v>
@@ -14357,7 +14648,7 @@
         <v>0.0</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="F2" s="2">
         <v>5.0</v>
@@ -14371,7 +14662,7 @@
         <v>42</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="C3" s="2">
         <v>1.0</v>
@@ -14380,7 +14671,7 @@
         <v>0.0</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="F3" s="2">
         <v>5.0</v>
@@ -14394,7 +14685,7 @@
         <v>44</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="C4" s="2">
         <v>1.0</v>
@@ -14403,7 +14694,7 @@
         <v>0.0</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="F4" s="2">
         <v>5.0</v>
@@ -14417,7 +14708,7 @@
         <v>46</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="C5" s="2">
         <v>0.0</v>
@@ -14426,7 +14717,7 @@
         <v>1.0</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="F5" s="2">
         <v>5.0</v>
@@ -14440,7 +14731,7 @@
         <v>48</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="C6" s="2">
         <v>1.0</v>
@@ -14449,7 +14740,7 @@
         <v>0.0</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="F6" s="2">
         <v>5.0</v>
@@ -14463,7 +14754,7 @@
         <v>32</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="C7" s="2">
         <v>1.0</v>
@@ -14472,7 +14763,7 @@
         <v>0.0</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="F7" s="2">
         <v>5.0</v>
@@ -14486,7 +14777,7 @@
         <v>32</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="C8" s="2">
         <v>0.0</v>
@@ -14495,7 +14786,7 @@
         <v>1.0</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="F8" s="2">
         <v>10.0</v>
@@ -14509,7 +14800,7 @@
         <v>34</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="C9" s="2">
         <v>1.0</v>
@@ -14518,7 +14809,7 @@
         <v>0.0</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="F9" s="2">
         <v>5.0</v>
@@ -14532,7 +14823,7 @@
         <v>34</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="C10" s="2">
         <v>0.0</v>
@@ -14541,7 +14832,7 @@
         <v>1.0</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="F10" s="2">
         <v>10.0</v>
@@ -14555,7 +14846,7 @@
         <v>58</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="C11" s="2">
         <v>1.0</v>
@@ -14564,7 +14855,7 @@
         <v>0.0</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="F11" s="2">
         <v>5.0</v>
@@ -14578,7 +14869,7 @@
         <v>102</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="C12" s="2">
         <v>1.0</v>
@@ -14587,7 +14878,7 @@
         <v>0.0</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="F12" s="2">
         <v>5.0</v>
@@ -14601,16 +14892,16 @@
         <v>104</v>
       </c>
       <c r="B13" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="C13" s="2">
+        <v>1.0</v>
+      </c>
+      <c r="D13" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="E13" s="2" t="s">
         <v>216</v>
-      </c>
-      <c r="C13" s="2">
-        <v>1.0</v>
-      </c>
-      <c r="D13" s="2">
-        <v>0.0</v>
-      </c>
-      <c r="E13" s="2" t="s">
-        <v>212</v>
       </c>
       <c r="F13" s="2">
         <v>5.0</v>
@@ -14624,7 +14915,7 @@
         <v>36</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="C14" s="2">
         <v>1.0</v>
@@ -14633,7 +14924,7 @@
         <v>0.0</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="F14" s="2">
         <v>5.0</v>
@@ -14647,7 +14938,7 @@
         <v>36</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="C15" s="2">
         <v>1.0</v>
@@ -14656,7 +14947,7 @@
         <v>0.0</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="F15" s="2">
         <v>10.0</v>
@@ -14670,7 +14961,7 @@
         <v>112</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="C16" s="2">
         <v>1.0</v>
@@ -14679,7 +14970,7 @@
         <v>0.0</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="F16" s="2">
         <v>5.0</v>
@@ -14693,7 +14984,7 @@
         <v>110</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="C17" s="2">
         <v>1.0</v>
@@ -14702,7 +14993,7 @@
         <v>0.0</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="F17" s="2">
         <v>5.0</v>
@@ -14716,7 +15007,7 @@
         <v>114</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="C18" s="2">
         <v>1.0</v>
@@ -14725,7 +15016,7 @@
         <v>0.0</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="F18" s="2">
         <v>5.0</v>
@@ -14739,7 +15030,7 @@
         <v>116</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="C19" s="2">
         <v>1.0</v>
@@ -14748,7 +15039,7 @@
         <v>0.0</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="F19" s="2">
         <v>5.0</v>
@@ -14762,7 +15053,7 @@
         <v>116</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="C20" s="2">
         <v>1.0</v>
@@ -14771,7 +15062,7 @@
         <v>0.0</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="F20" s="2">
         <v>10.0</v>
@@ -14785,7 +15076,7 @@
         <v>118</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="C21" s="2">
         <v>1.0</v>
@@ -14794,7 +15085,7 @@
         <v>0.0</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="F21" s="2">
         <v>5.0</v>
@@ -14808,7 +15099,7 @@
         <v>118</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>238</v>
+        <v>242</v>
       </c>
       <c r="C22" s="2">
         <v>1.0</v>
@@ -14817,7 +15108,7 @@
         <v>0.0</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="F22" s="2">
         <v>10.0</v>
@@ -14831,7 +15122,7 @@
         <v>120</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="C23" s="2">
         <v>1.0</v>
@@ -14840,7 +15131,7 @@
         <v>0.0</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="F23" s="2">
         <v>5.0</v>
@@ -14854,7 +15145,7 @@
         <v>122</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="C24" s="2">
         <v>1.0</v>
@@ -14863,7 +15154,7 @@
         <v>0.0</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="F24" s="2">
         <v>5.0</v>
@@ -14877,7 +15168,7 @@
         <v>124</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>248</v>
+        <v>252</v>
       </c>
       <c r="C25" s="2">
         <v>1.0</v>
@@ -14886,7 +15177,7 @@
         <v>0.0</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="F25" s="2">
         <v>5.0</v>
@@ -14900,7 +15191,7 @@
         <v>124</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>250</v>
+        <v>254</v>
       </c>
       <c r="C26" s="2">
         <v>1.0</v>
@@ -14909,7 +15200,7 @@
         <v>0.0</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="F26" s="2">
         <v>10.0</v>
@@ -14923,7 +15214,7 @@
         <v>124</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="C27" s="2">
         <v>1.0</v>
@@ -14932,7 +15223,7 @@
         <v>0.0</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="F27" s="2">
         <v>15.0</v>
@@ -14946,7 +15237,7 @@
         <v>124</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>254</v>
+        <v>258</v>
       </c>
       <c r="C28" s="2">
         <v>0.0</v>
@@ -14955,7 +15246,7 @@
         <v>0.0</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="F28" s="2">
         <v>20.0</v>
@@ -14969,7 +15260,7 @@
         <v>126</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>256</v>
+        <v>260</v>
       </c>
       <c r="C29" s="2">
         <v>0.0</v>
@@ -14978,7 +15269,7 @@
         <v>0.0</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="F29" s="2">
         <v>5.0</v>
@@ -14992,7 +15283,7 @@
         <v>70</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="C30" s="2">
         <v>1.0</v>
@@ -15001,7 +15292,7 @@
         <v>0.0</v>
       </c>
       <c r="E30" s="3" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="F30" s="2">
         <v>5.0</v>
@@ -15015,7 +15306,7 @@
         <v>72</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="C31" s="2">
         <v>1.0</v>
@@ -15024,7 +15315,7 @@
         <v>0.0</v>
       </c>
       <c r="E31" s="3" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="F31" s="2">
         <v>10.0</v>
@@ -15038,7 +15329,7 @@
         <v>74</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="C32" s="2">
         <v>1.0</v>
@@ -15047,7 +15338,7 @@
         <v>0.0</v>
       </c>
       <c r="E32" s="3" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="F32" s="2">
         <v>15.0</v>
@@ -15061,7 +15352,7 @@
         <v>76</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="C33" s="2">
         <v>1.0</v>
@@ -15070,7 +15361,7 @@
         <v>0.0</v>
       </c>
       <c r="E33" s="3" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="F33" s="2">
         <v>20.0</v>
@@ -15084,7 +15375,7 @@
         <v>78</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="C34" s="2">
         <v>1.0</v>
@@ -15093,7 +15384,7 @@
         <v>0.0</v>
       </c>
       <c r="E34" s="3" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="F34" s="2">
         <v>25.0</v>
@@ -15107,7 +15398,7 @@
         <v>80</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="C35" s="2">
         <v>1.0</v>
@@ -15116,7 +15407,7 @@
         <v>0.0</v>
       </c>
       <c r="E35" s="3" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="F35" s="2">
         <v>30.0</v>
@@ -15130,7 +15421,7 @@
         <v>40</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="C36" s="2">
         <v>1.0</v>
@@ -15139,7 +15430,7 @@
         <v>0.0</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="F36" s="2">
         <v>5.0</v>
@@ -15153,7 +15444,7 @@
         <v>60</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="C37" s="2">
         <v>1.0</v>
@@ -15162,7 +15453,7 @@
         <v>0.0</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="F37" s="2">
         <v>5.0</v>
@@ -15172,48 +15463,48 @@
       </c>
     </row>
     <row r="38" ht="14.25" customHeight="1">
-      <c r="A38" s="4" t="s">
+      <c r="A38" s="2" t="s">
         <v>136</v>
       </c>
-      <c r="B38" s="5" t="s">
-        <v>262</v>
-      </c>
-      <c r="C38" s="5">
-        <v>1.0</v>
-      </c>
-      <c r="D38" s="5">
+      <c r="B38" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="C38" s="2">
+        <v>1.0</v>
+      </c>
+      <c r="D38" s="2">
         <v>0.0</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>212</v>
-      </c>
-      <c r="F38" s="5">
+        <v>216</v>
+      </c>
+      <c r="F38" s="2">
         <v>5.0</v>
       </c>
-      <c r="G38" s="5">
+      <c r="G38" s="2">
         <v>1.0</v>
       </c>
     </row>
     <row r="39" ht="14.25" customHeight="1">
-      <c r="A39" s="4" t="s">
+      <c r="A39" s="2" t="s">
         <v>136</v>
       </c>
-      <c r="B39" s="5" t="s">
-        <v>264</v>
-      </c>
-      <c r="C39" s="5">
-        <v>1.0</v>
-      </c>
-      <c r="D39" s="5">
+      <c r="B39" s="2" t="s">
+        <v>268</v>
+      </c>
+      <c r="C39" s="2">
+        <v>1.0</v>
+      </c>
+      <c r="D39" s="2">
         <v>0.0</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>212</v>
-      </c>
-      <c r="F39" s="5">
+        <v>216</v>
+      </c>
+      <c r="F39" s="2">
         <v>10.0</v>
       </c>
-      <c r="G39" s="5">
+      <c r="G39" s="2">
         <v>1.0</v>
       </c>
     </row>
@@ -15417,14 +15708,14 @@
     <row r="237" ht="14.25" customHeight="1"/>
     <row r="238" ht="14.25" customHeight="1"/>
     <row r="239" ht="14.25" customHeight="1"/>
-    <row r="240" ht="14.25" customHeight="1"/>
-    <row r="241" ht="14.25" customHeight="1"/>
-    <row r="242" ht="14.25" customHeight="1"/>
-    <row r="243" ht="14.25" customHeight="1"/>
-    <row r="244" ht="14.25" customHeight="1"/>
-    <row r="245" ht="14.25" customHeight="1"/>
-    <row r="246" ht="14.25" customHeight="1"/>
-    <row r="247" ht="14.25" customHeight="1"/>
+    <row r="240" ht="15.75" customHeight="1"/>
+    <row r="241" ht="15.75" customHeight="1"/>
+    <row r="242" ht="15.75" customHeight="1"/>
+    <row r="243" ht="15.75" customHeight="1"/>
+    <row r="244" ht="15.75" customHeight="1"/>
+    <row r="245" ht="15.75" customHeight="1"/>
+    <row r="246" ht="15.75" customHeight="1"/>
+    <row r="247" ht="15.75" customHeight="1"/>
     <row r="248" ht="15.75" customHeight="1"/>
     <row r="249" ht="15.75" customHeight="1"/>
     <row r="250" ht="15.75" customHeight="1"/>
@@ -16205,19 +16496,19 @@
   <sheetData>
     <row r="1" ht="14.25" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>525</v>
+        <v>542</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>526</v>
+        <v>543</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>527</v>
+        <v>544</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>528</v>
+        <v>545</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>529</v>
+        <v>546</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>4</v>
@@ -16231,13 +16522,13 @@
         <v>32</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>7</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>530</v>
+        <v>547</v>
       </c>
       <c r="E2" s="2">
         <v>1.0</v>
@@ -16254,13 +16545,13 @@
         <v>34</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>7</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>531</v>
+        <v>548</v>
       </c>
       <c r="E3" s="2">
         <v>1.0</v>
@@ -16277,13 +16568,13 @@
         <v>36</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>532</v>
+        <v>549</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>10</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>533</v>
+        <v>550</v>
       </c>
       <c r="E4" s="2">
         <v>1.0</v>
@@ -16300,13 +16591,13 @@
         <v>38</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>7</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>534</v>
+        <v>551</v>
       </c>
       <c r="E5" s="2">
         <v>1.0</v>
@@ -16323,13 +16614,13 @@
         <v>40</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>7</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>535</v>
+        <v>552</v>
       </c>
       <c r="E6" s="2">
         <v>1.0</v>
@@ -16346,13 +16637,13 @@
         <v>42</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>7</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>536</v>
+        <v>553</v>
       </c>
       <c r="E7" s="2">
         <v>1.0</v>
@@ -16369,13 +16660,13 @@
         <v>44</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>7</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>537</v>
+        <v>554</v>
       </c>
       <c r="E8" s="2">
         <v>1.0</v>
@@ -16392,13 +16683,13 @@
         <v>46</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>7</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>538</v>
+        <v>555</v>
       </c>
       <c r="E9" s="2">
         <v>1.0</v>
@@ -16415,13 +16706,13 @@
         <v>48</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>7</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>539</v>
+        <v>556</v>
       </c>
       <c r="E10" s="2">
         <v>1.0</v>
@@ -16438,13 +16729,13 @@
         <v>50</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>7</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>540</v>
+        <v>557</v>
       </c>
       <c r="E11" s="2">
         <v>1.0</v>
@@ -16461,13 +16752,13 @@
         <v>52</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>541</v>
+        <v>558</v>
       </c>
       <c r="E12" s="2">
         <v>1.0</v>
@@ -16484,13 +16775,13 @@
         <v>54</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>7</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>542</v>
+        <v>559</v>
       </c>
       <c r="E13" s="2">
         <v>1.0</v>
@@ -16507,13 +16798,13 @@
         <v>56</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>7</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>543</v>
+        <v>560</v>
       </c>
       <c r="E14" s="2">
         <v>1.0</v>
@@ -16530,13 +16821,13 @@
         <v>58</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>7</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>544</v>
+        <v>561</v>
       </c>
       <c r="E15" s="2">
         <v>1.0</v>
@@ -16553,13 +16844,13 @@
         <v>60</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>7</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>545</v>
+        <v>562</v>
       </c>
       <c r="E16" s="2">
         <v>1.0</v>
@@ -16576,13 +16867,13 @@
         <v>62</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>7</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>546</v>
+        <v>563</v>
       </c>
       <c r="E17" s="2">
         <v>1.0</v>
@@ -16599,13 +16890,13 @@
         <v>64</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="C18" s="2" t="s">
         <v>7</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>547</v>
+        <v>564</v>
       </c>
       <c r="E18" s="2">
         <v>1.0</v>
@@ -16622,13 +16913,13 @@
         <v>66</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="C19" s="2" t="s">
         <v>7</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>548</v>
+        <v>565</v>
       </c>
       <c r="E19" s="2">
         <v>1.0</v>
@@ -16645,13 +16936,13 @@
         <v>68</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="C20" s="2" t="s">
         <v>7</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>549</v>
+        <v>566</v>
       </c>
       <c r="E20" s="2">
         <v>1.0</v>
@@ -16668,13 +16959,13 @@
         <v>70</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="C21" s="2" t="s">
         <v>7</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>550</v>
+        <v>567</v>
       </c>
       <c r="E21" s="2">
         <v>1.0</v>
@@ -16691,13 +16982,13 @@
         <v>72</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="C22" s="2" t="s">
         <v>7</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>551</v>
+        <v>568</v>
       </c>
       <c r="E22" s="2">
         <v>1.0</v>
@@ -16714,13 +17005,13 @@
         <v>74</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="C23" s="2" t="s">
         <v>7</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>552</v>
+        <v>569</v>
       </c>
       <c r="E23" s="2">
         <v>1.0</v>
@@ -16737,13 +17028,13 @@
         <v>76</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="C24" s="2" t="s">
         <v>7</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>553</v>
+        <v>570</v>
       </c>
       <c r="E24" s="2">
         <v>1.0</v>
@@ -16760,13 +17051,13 @@
         <v>78</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="C25" s="2" t="s">
         <v>7</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>554</v>
+        <v>571</v>
       </c>
       <c r="E25" s="2">
         <v>1.0</v>
@@ -16783,13 +17074,13 @@
         <v>80</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="C26" s="2" t="s">
         <v>7</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>555</v>
+        <v>572</v>
       </c>
       <c r="E26" s="2">
         <v>1.0</v>
@@ -16806,13 +17097,13 @@
         <v>82</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>556</v>
+        <v>573</v>
       </c>
       <c r="C27" s="2" t="s">
         <v>7</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>557</v>
+        <v>574</v>
       </c>
       <c r="E27" s="2">
         <v>1.0</v>
@@ -16829,13 +17120,13 @@
         <v>84</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>532</v>
+        <v>549</v>
       </c>
       <c r="C28" s="2" t="s">
         <v>7</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>558</v>
+        <v>575</v>
       </c>
       <c r="E28" s="2">
         <v>1.0</v>
@@ -16852,13 +17143,13 @@
         <v>86</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>532</v>
+        <v>549</v>
       </c>
       <c r="C29" s="2" t="s">
         <v>7</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>559</v>
+        <v>576</v>
       </c>
       <c r="E29" s="2">
         <v>1.0</v>
@@ -16875,13 +17166,13 @@
         <v>88</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>532</v>
+        <v>549</v>
       </c>
       <c r="C30" s="2" t="s">
         <v>7</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>560</v>
+        <v>577</v>
       </c>
       <c r="E30" s="2">
         <v>1.0</v>
@@ -16898,13 +17189,13 @@
         <v>90</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="C31" s="2" t="s">
         <v>7</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>561</v>
+        <v>578</v>
       </c>
       <c r="E31" s="2">
         <v>1.0</v>
@@ -16921,13 +17212,13 @@
         <v>92</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="C32" s="2" t="s">
         <v>7</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>562</v>
+        <v>579</v>
       </c>
       <c r="E32" s="2">
         <v>1.0</v>
@@ -16944,13 +17235,13 @@
         <v>94</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="C33" s="2" t="s">
         <v>7</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>563</v>
+        <v>580</v>
       </c>
       <c r="E33" s="2">
         <v>1.0</v>
@@ -16967,13 +17258,13 @@
         <v>96</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="C34" s="2" t="s">
         <v>7</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>564</v>
+        <v>581</v>
       </c>
       <c r="E34" s="2">
         <v>1.0</v>
@@ -16990,13 +17281,13 @@
         <v>98</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="C35" s="2" t="s">
         <v>7</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>565</v>
+        <v>582</v>
       </c>
       <c r="E35" s="2">
         <v>1.0</v>
@@ -17013,13 +17304,13 @@
         <v>100</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>532</v>
+        <v>549</v>
       </c>
       <c r="C36" s="2" t="s">
         <v>7</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>566</v>
+        <v>583</v>
       </c>
       <c r="E36" s="2">
         <v>1.0</v>
@@ -17036,13 +17327,13 @@
         <v>102</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>532</v>
+        <v>549</v>
       </c>
       <c r="C37" s="2" t="s">
         <v>7</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>567</v>
+        <v>584</v>
       </c>
       <c r="E37" s="2">
         <v>1.0</v>
@@ -17059,13 +17350,13 @@
         <v>104</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>532</v>
+        <v>549</v>
       </c>
       <c r="C38" s="2" t="s">
         <v>7</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>568</v>
+        <v>585</v>
       </c>
       <c r="E38" s="2">
         <v>1.0</v>
@@ -17078,25 +17369,25 @@
       </c>
     </row>
     <row r="39" ht="14.25" customHeight="1">
-      <c r="A39" s="4" t="s">
+      <c r="A39" s="2" t="s">
         <v>106</v>
       </c>
-      <c r="B39" s="4" t="s">
-        <v>532</v>
-      </c>
-      <c r="C39" s="4" t="s">
+      <c r="B39" s="2" t="s">
+        <v>549</v>
+      </c>
+      <c r="C39" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="D39" s="4" t="s">
-        <v>569</v>
-      </c>
-      <c r="E39" s="4">
-        <v>1.0</v>
-      </c>
-      <c r="F39" s="4">
+      <c r="D39" s="2" t="s">
+        <v>586</v>
+      </c>
+      <c r="E39" s="2">
+        <v>1.0</v>
+      </c>
+      <c r="F39" s="2">
         <v>380.0</v>
       </c>
-      <c r="G39" s="4">
+      <c r="G39" s="2">
         <v>1.0</v>
       </c>
     </row>
@@ -17105,13 +17396,13 @@
         <v>108</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>532</v>
+        <v>549</v>
       </c>
       <c r="C40" s="2" t="s">
         <v>10</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>570</v>
+        <v>587</v>
       </c>
       <c r="E40" s="2">
         <v>1.0</v>
@@ -17128,13 +17419,13 @@
         <v>110</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>532</v>
+        <v>549</v>
       </c>
       <c r="C41" s="2" t="s">
         <v>10</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>571</v>
+        <v>588</v>
       </c>
       <c r="E41" s="2">
         <v>1.0</v>
@@ -17151,18 +17442,18 @@
         <v>112</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>532</v>
+        <v>549</v>
       </c>
       <c r="C42" s="2" t="s">
         <v>10</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>572</v>
+        <v>589</v>
       </c>
       <c r="E42" s="2">
         <v>1.0</v>
       </c>
-      <c r="F42" s="4">
+      <c r="F42" s="2">
         <v>410.0</v>
       </c>
       <c r="G42" s="2">
@@ -17174,13 +17465,13 @@
         <v>114</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>532</v>
+        <v>549</v>
       </c>
       <c r="C43" s="2" t="s">
         <v>10</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>573</v>
+        <v>590</v>
       </c>
       <c r="E43" s="2">
         <v>1.0</v>
@@ -17197,13 +17488,13 @@
         <v>116</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>532</v>
+        <v>549</v>
       </c>
       <c r="C44" s="2" t="s">
         <v>10</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>574</v>
+        <v>591</v>
       </c>
       <c r="E44" s="2">
         <v>1.0</v>
@@ -17220,18 +17511,18 @@
         <v>118</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>532</v>
+        <v>549</v>
       </c>
       <c r="C45" s="2" t="s">
         <v>10</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>575</v>
+        <v>592</v>
       </c>
       <c r="E45" s="2">
         <v>1.0</v>
       </c>
-      <c r="F45" s="4">
+      <c r="F45" s="2">
         <v>440.0</v>
       </c>
       <c r="G45" s="2">
@@ -17243,13 +17534,13 @@
         <v>120</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>532</v>
+        <v>549</v>
       </c>
       <c r="C46" s="2" t="s">
         <v>10</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>576</v>
+        <v>593</v>
       </c>
       <c r="E46" s="2">
         <v>1.0</v>
@@ -17266,13 +17557,13 @@
         <v>122</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>532</v>
+        <v>549</v>
       </c>
       <c r="C47" s="2" t="s">
         <v>10</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>577</v>
+        <v>594</v>
       </c>
       <c r="E47" s="2">
         <v>1.0</v>
@@ -17289,18 +17580,18 @@
         <v>124</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>532</v>
+        <v>549</v>
       </c>
       <c r="C48" s="2" t="s">
         <v>7</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>578</v>
+        <v>595</v>
       </c>
       <c r="E48" s="2">
         <v>1.0</v>
       </c>
-      <c r="F48" s="4">
+      <c r="F48" s="2">
         <v>470.0</v>
       </c>
       <c r="G48" s="2">
@@ -17312,13 +17603,13 @@
         <v>126</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>532</v>
+        <v>549</v>
       </c>
       <c r="C49" s="2" t="s">
         <v>7</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>579</v>
+        <v>596</v>
       </c>
       <c r="E49" s="2">
         <v>1.0</v>
@@ -17335,13 +17626,13 @@
         <v>128</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>532</v>
+        <v>549</v>
       </c>
       <c r="C50" s="2" t="s">
         <v>7</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>580</v>
+        <v>597</v>
       </c>
       <c r="E50" s="2">
         <v>1.0</v>
@@ -17358,18 +17649,18 @@
         <v>130</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>532</v>
+        <v>549</v>
       </c>
       <c r="C51" s="2" t="s">
         <v>7</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>581</v>
+        <v>598</v>
       </c>
       <c r="E51" s="2">
         <v>1.0</v>
       </c>
-      <c r="F51" s="4">
+      <c r="F51" s="2">
         <v>500.0</v>
       </c>
       <c r="G51" s="2">
@@ -17381,13 +17672,13 @@
         <v>132</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>532</v>
+        <v>549</v>
       </c>
       <c r="C52" s="2" t="s">
         <v>7</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>582</v>
+        <v>599</v>
       </c>
       <c r="E52" s="2">
         <v>1.0</v>
@@ -17404,13 +17695,13 @@
         <v>134</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>532</v>
+        <v>549</v>
       </c>
       <c r="C53" s="2" t="s">
         <v>7</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>583</v>
+        <v>600</v>
       </c>
       <c r="E53" s="2">
         <v>1.0</v>
@@ -17424,28 +17715,50 @@
     </row>
     <row r="54" ht="14.25" customHeight="1">
       <c r="A54" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="B54" s="4" t="s">
+        <v>549</v>
+      </c>
+      <c r="C54" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D54" s="4" t="s">
+        <v>601</v>
+      </c>
+      <c r="E54" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="F54" s="4">
+        <v>540.0</v>
+      </c>
+      <c r="G54" s="4">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="55" ht="14.25" customHeight="1">
+      <c r="A55" s="2" t="s">
         <v>136</v>
       </c>
-      <c r="B54" s="5" t="s">
-        <v>532</v>
-      </c>
-      <c r="C54" s="2" t="s">
+      <c r="B55" s="2" t="s">
+        <v>549</v>
+      </c>
+      <c r="C55" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="D54" s="5" t="s">
-        <v>584</v>
-      </c>
-      <c r="E54" s="5">
-        <v>1.0</v>
-      </c>
-      <c r="F54" s="4">
-        <v>530.0</v>
-      </c>
-      <c r="G54" s="5">
-        <v>1.0</v>
-      </c>
-    </row>
-    <row r="55" ht="14.25" customHeight="1"/>
+      <c r="D55" s="2" t="s">
+        <v>602</v>
+      </c>
+      <c r="E55" s="2">
+        <v>1.0</v>
+      </c>
+      <c r="F55" s="4">
+        <v>550.0</v>
+      </c>
+      <c r="G55" s="2">
+        <v>1.0</v>
+      </c>
+    </row>
     <row r="56" ht="14.25" customHeight="1"/>
     <row r="57" ht="14.25" customHeight="1"/>
     <row r="58" ht="14.25" customHeight="1"/>
@@ -17643,7 +17956,7 @@
     <row r="250" ht="14.25" customHeight="1"/>
     <row r="251" ht="14.25" customHeight="1"/>
     <row r="252" ht="14.25" customHeight="1"/>
-    <row r="253" ht="15.75" customHeight="1"/>
+    <row r="253" ht="14.25" customHeight="1"/>
     <row r="254" ht="15.75" customHeight="1"/>
     <row r="255" ht="15.75" customHeight="1"/>
     <row r="256" ht="15.75" customHeight="1"/>
@@ -18391,6 +18704,7 @@
     <row r="998" ht="15.75" customHeight="1"/>
     <row r="999" ht="15.75" customHeight="1"/>
     <row r="1000" ht="15.75" customHeight="1"/>
+    <row r="1001" ht="15.75" customHeight="1"/>
   </sheetData>
   <autoFilter ref="$A$1:$G$1"/>
   <printOptions/>
@@ -18426,7 +18740,7 @@
         <v>1</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>585</v>
+        <v>603</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>3</v>
@@ -18437,13 +18751,13 @@
     </row>
     <row r="2" ht="14.25" customHeight="1">
       <c r="A2" s="2" t="s">
-        <v>586</v>
+        <v>604</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>587</v>
+        <v>605</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>588</v>
+        <v>606</v>
       </c>
       <c r="E2" s="2">
         <v>1.0</v>
@@ -18454,13 +18768,13 @@
     </row>
     <row r="3" ht="14.25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>589</v>
+        <v>607</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>587</v>
+        <v>605</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>590</v>
+        <v>608</v>
       </c>
       <c r="E3" s="2">
         <v>1.0</v>
@@ -19488,924 +19802,924 @@
   </cols>
   <sheetData>
     <row r="1" ht="15.75" customHeight="1">
-      <c r="A1" s="6" t="s">
-        <v>591</v>
-      </c>
-      <c r="B1" s="6" t="s">
-        <v>592</v>
+      <c r="A1" s="5" t="s">
+        <v>609</v>
+      </c>
+      <c r="B1" s="5" t="s">
+        <v>610</v>
       </c>
     </row>
     <row r="2" ht="15.75" customHeight="1">
-      <c r="A2" s="7" t="s">
-        <v>593</v>
-      </c>
-      <c r="B2" s="7" t="s">
-        <v>594</v>
+      <c r="A2" s="6" t="s">
+        <v>611</v>
+      </c>
+      <c r="B2" s="6" t="s">
+        <v>612</v>
       </c>
     </row>
     <row r="3" ht="15.75" customHeight="1">
-      <c r="A3" s="7" t="s">
-        <v>595</v>
-      </c>
-      <c r="B3" s="7" t="s">
-        <v>596</v>
+      <c r="A3" s="6" t="s">
+        <v>613</v>
+      </c>
+      <c r="B3" s="6" t="s">
+        <v>614</v>
       </c>
     </row>
     <row r="4" ht="15.75" customHeight="1">
-      <c r="A4" s="7" t="s">
-        <v>597</v>
-      </c>
-      <c r="B4" s="7" t="s">
-        <v>598</v>
+      <c r="A4" s="6" t="s">
+        <v>615</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>616</v>
       </c>
     </row>
     <row r="5" ht="15.75" customHeight="1">
-      <c r="A5" s="7" t="s">
-        <v>599</v>
-      </c>
-      <c r="B5" s="7" t="s">
-        <v>600</v>
+      <c r="A5" s="6" t="s">
+        <v>617</v>
+      </c>
+      <c r="B5" s="6" t="s">
+        <v>618</v>
       </c>
     </row>
     <row r="6" ht="15.75" customHeight="1">
-      <c r="A6" s="7" t="s">
-        <v>210</v>
-      </c>
-      <c r="B6" s="7" t="s">
-        <v>601</v>
+      <c r="A6" s="6" t="s">
+        <v>214</v>
+      </c>
+      <c r="B6" s="6" t="s">
+        <v>619</v>
       </c>
     </row>
     <row r="7" ht="15.75" customHeight="1">
-      <c r="A7" s="7" t="s">
+      <c r="A7" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="B7" s="7" t="s">
-        <v>602</v>
+      <c r="B7" s="6" t="s">
+        <v>620</v>
       </c>
     </row>
     <row r="8" ht="15.75" customHeight="1">
-      <c r="A8" s="7" t="s">
-        <v>603</v>
-      </c>
-      <c r="B8" s="7" t="s">
-        <v>604</v>
+      <c r="A8" s="6" t="s">
+        <v>621</v>
+      </c>
+      <c r="B8" s="6" t="s">
+        <v>622</v>
       </c>
     </row>
     <row r="9" ht="15.75" customHeight="1">
-      <c r="A9" s="7" t="s">
-        <v>605</v>
-      </c>
-      <c r="B9" s="7" t="s">
-        <v>606</v>
+      <c r="A9" s="6" t="s">
+        <v>623</v>
+      </c>
+      <c r="B9" s="6" t="s">
+        <v>624</v>
       </c>
     </row>
     <row r="10" ht="15.75" customHeight="1">
-      <c r="A10" s="7" t="s">
-        <v>607</v>
-      </c>
-      <c r="B10" s="7" t="s">
-        <v>608</v>
+      <c r="A10" s="6" t="s">
+        <v>625</v>
+      </c>
+      <c r="B10" s="6" t="s">
+        <v>626</v>
       </c>
     </row>
     <row r="11" ht="14.25" customHeight="1">
-      <c r="A11" s="7"/>
-      <c r="B11" s="7"/>
+      <c r="A11" s="6"/>
+      <c r="B11" s="6"/>
     </row>
     <row r="12" ht="14.25" customHeight="1">
-      <c r="A12" s="7"/>
-      <c r="B12" s="7"/>
+      <c r="A12" s="6"/>
+      <c r="B12" s="6"/>
     </row>
     <row r="13" ht="14.25" customHeight="1">
-      <c r="A13" s="7"/>
-      <c r="B13" s="7"/>
+      <c r="A13" s="6"/>
+      <c r="B13" s="6"/>
     </row>
     <row r="14" ht="14.25" customHeight="1">
-      <c r="A14" s="7"/>
-      <c r="B14" s="7"/>
+      <c r="A14" s="6"/>
+      <c r="B14" s="6"/>
     </row>
     <row r="15" ht="14.25" customHeight="1">
-      <c r="A15" s="7"/>
-      <c r="B15" s="7"/>
+      <c r="A15" s="6"/>
+      <c r="B15" s="6"/>
     </row>
     <row r="16" ht="14.25" customHeight="1">
-      <c r="A16" s="7"/>
-      <c r="B16" s="7"/>
+      <c r="A16" s="6"/>
+      <c r="B16" s="6"/>
     </row>
     <row r="17" ht="14.25" customHeight="1">
-      <c r="A17" s="7"/>
-      <c r="B17" s="7"/>
+      <c r="A17" s="6"/>
+      <c r="B17" s="6"/>
     </row>
     <row r="18" ht="14.25" customHeight="1">
-      <c r="A18" s="7"/>
-      <c r="B18" s="7"/>
+      <c r="A18" s="6"/>
+      <c r="B18" s="6"/>
     </row>
     <row r="19" ht="14.25" customHeight="1">
-      <c r="A19" s="7"/>
-      <c r="B19" s="7"/>
+      <c r="A19" s="6"/>
+      <c r="B19" s="6"/>
     </row>
     <row r="20" ht="14.25" customHeight="1">
-      <c r="A20" s="7"/>
-      <c r="B20" s="7"/>
+      <c r="A20" s="6"/>
+      <c r="B20" s="6"/>
     </row>
     <row r="21" ht="14.25" customHeight="1">
-      <c r="A21" s="7"/>
-      <c r="B21" s="7"/>
+      <c r="A21" s="6"/>
+      <c r="B21" s="6"/>
     </row>
     <row r="22" ht="14.25" customHeight="1">
-      <c r="A22" s="7"/>
-      <c r="B22" s="7"/>
+      <c r="A22" s="6"/>
+      <c r="B22" s="6"/>
     </row>
     <row r="23" ht="14.25" customHeight="1">
-      <c r="A23" s="7"/>
-      <c r="B23" s="7"/>
+      <c r="A23" s="6"/>
+      <c r="B23" s="6"/>
     </row>
     <row r="24" ht="14.25" customHeight="1">
-      <c r="A24" s="7"/>
-      <c r="B24" s="7"/>
+      <c r="A24" s="6"/>
+      <c r="B24" s="6"/>
     </row>
     <row r="25" ht="14.25" customHeight="1">
-      <c r="A25" s="7"/>
-      <c r="B25" s="7"/>
+      <c r="A25" s="6"/>
+      <c r="B25" s="6"/>
     </row>
     <row r="26" ht="14.25" customHeight="1">
-      <c r="A26" s="7"/>
-      <c r="B26" s="7"/>
+      <c r="A26" s="6"/>
+      <c r="B26" s="6"/>
     </row>
     <row r="27" ht="14.25" customHeight="1">
-      <c r="A27" s="7"/>
-      <c r="B27" s="7"/>
+      <c r="A27" s="6"/>
+      <c r="B27" s="6"/>
     </row>
     <row r="28" ht="14.25" customHeight="1">
-      <c r="A28" s="7"/>
-      <c r="B28" s="7"/>
+      <c r="A28" s="6"/>
+      <c r="B28" s="6"/>
     </row>
     <row r="29" ht="14.25" customHeight="1">
-      <c r="A29" s="7"/>
-      <c r="B29" s="7"/>
+      <c r="A29" s="6"/>
+      <c r="B29" s="6"/>
     </row>
     <row r="30" ht="14.25" customHeight="1">
-      <c r="A30" s="7"/>
-      <c r="B30" s="7"/>
+      <c r="A30" s="6"/>
+      <c r="B30" s="6"/>
     </row>
     <row r="31" ht="14.25" customHeight="1">
-      <c r="A31" s="7"/>
-      <c r="B31" s="7"/>
+      <c r="A31" s="6"/>
+      <c r="B31" s="6"/>
     </row>
     <row r="32" ht="14.25" customHeight="1">
-      <c r="A32" s="7"/>
-      <c r="B32" s="7"/>
+      <c r="A32" s="6"/>
+      <c r="B32" s="6"/>
     </row>
     <row r="33" ht="14.25" customHeight="1">
-      <c r="A33" s="7"/>
-      <c r="B33" s="7"/>
+      <c r="A33" s="6"/>
+      <c r="B33" s="6"/>
     </row>
     <row r="34" ht="14.25" customHeight="1">
-      <c r="A34" s="7"/>
-      <c r="B34" s="7"/>
+      <c r="A34" s="6"/>
+      <c r="B34" s="6"/>
     </row>
     <row r="35" ht="14.25" customHeight="1">
-      <c r="A35" s="7"/>
-      <c r="B35" s="7"/>
+      <c r="A35" s="6"/>
+      <c r="B35" s="6"/>
     </row>
     <row r="36" ht="14.25" customHeight="1">
-      <c r="A36" s="7"/>
-      <c r="B36" s="7"/>
+      <c r="A36" s="6"/>
+      <c r="B36" s="6"/>
     </row>
     <row r="37" ht="14.25" customHeight="1">
-      <c r="A37" s="7"/>
-      <c r="B37" s="7"/>
+      <c r="A37" s="6"/>
+      <c r="B37" s="6"/>
     </row>
     <row r="38" ht="14.25" customHeight="1">
-      <c r="A38" s="7"/>
-      <c r="B38" s="7"/>
+      <c r="A38" s="6"/>
+      <c r="B38" s="6"/>
     </row>
     <row r="39" ht="14.25" customHeight="1">
-      <c r="A39" s="7"/>
-      <c r="B39" s="7"/>
+      <c r="A39" s="6"/>
+      <c r="B39" s="6"/>
     </row>
     <row r="40" ht="14.25" customHeight="1">
-      <c r="A40" s="7"/>
-      <c r="B40" s="7"/>
+      <c r="A40" s="6"/>
+      <c r="B40" s="6"/>
     </row>
     <row r="41" ht="14.25" customHeight="1">
-      <c r="A41" s="7"/>
-      <c r="B41" s="7"/>
+      <c r="A41" s="6"/>
+      <c r="B41" s="6"/>
     </row>
     <row r="42" ht="14.25" customHeight="1">
-      <c r="A42" s="7"/>
-      <c r="B42" s="7"/>
+      <c r="A42" s="6"/>
+      <c r="B42" s="6"/>
     </row>
     <row r="43" ht="14.25" customHeight="1">
-      <c r="A43" s="7"/>
-      <c r="B43" s="7"/>
+      <c r="A43" s="6"/>
+      <c r="B43" s="6"/>
     </row>
     <row r="44" ht="14.25" customHeight="1">
-      <c r="A44" s="7"/>
-      <c r="B44" s="7"/>
+      <c r="A44" s="6"/>
+      <c r="B44" s="6"/>
     </row>
     <row r="45" ht="14.25" customHeight="1">
-      <c r="A45" s="7"/>
-      <c r="B45" s="7"/>
+      <c r="A45" s="6"/>
+      <c r="B45" s="6"/>
     </row>
     <row r="46" ht="14.25" customHeight="1">
-      <c r="A46" s="7"/>
-      <c r="B46" s="7"/>
+      <c r="A46" s="6"/>
+      <c r="B46" s="6"/>
     </row>
     <row r="47" ht="14.25" customHeight="1">
-      <c r="A47" s="7"/>
-      <c r="B47" s="7"/>
+      <c r="A47" s="6"/>
+      <c r="B47" s="6"/>
     </row>
     <row r="48" ht="14.25" customHeight="1">
-      <c r="A48" s="7"/>
-      <c r="B48" s="7"/>
+      <c r="A48" s="6"/>
+      <c r="B48" s="6"/>
     </row>
     <row r="49" ht="14.25" customHeight="1">
-      <c r="A49" s="7"/>
-      <c r="B49" s="7"/>
+      <c r="A49" s="6"/>
+      <c r="B49" s="6"/>
     </row>
     <row r="50" ht="14.25" customHeight="1">
-      <c r="A50" s="7"/>
-      <c r="B50" s="7"/>
+      <c r="A50" s="6"/>
+      <c r="B50" s="6"/>
     </row>
     <row r="51" ht="14.25" customHeight="1">
-      <c r="A51" s="7"/>
-      <c r="B51" s="7"/>
+      <c r="A51" s="6"/>
+      <c r="B51" s="6"/>
     </row>
     <row r="52" ht="14.25" customHeight="1">
-      <c r="A52" s="7"/>
-      <c r="B52" s="7"/>
+      <c r="A52" s="6"/>
+      <c r="B52" s="6"/>
     </row>
     <row r="53" ht="14.25" customHeight="1">
-      <c r="A53" s="7"/>
-      <c r="B53" s="7"/>
+      <c r="A53" s="6"/>
+      <c r="B53" s="6"/>
     </row>
     <row r="54" ht="14.25" customHeight="1">
-      <c r="A54" s="7"/>
-      <c r="B54" s="7"/>
+      <c r="A54" s="6"/>
+      <c r="B54" s="6"/>
     </row>
     <row r="55" ht="14.25" customHeight="1">
-      <c r="A55" s="7"/>
-      <c r="B55" s="7"/>
+      <c r="A55" s="6"/>
+      <c r="B55" s="6"/>
     </row>
     <row r="56" ht="14.25" customHeight="1">
-      <c r="A56" s="7"/>
-      <c r="B56" s="7"/>
+      <c r="A56" s="6"/>
+      <c r="B56" s="6"/>
     </row>
     <row r="57" ht="14.25" customHeight="1">
-      <c r="A57" s="7"/>
-      <c r="B57" s="7"/>
+      <c r="A57" s="6"/>
+      <c r="B57" s="6"/>
     </row>
     <row r="58" ht="14.25" customHeight="1">
-      <c r="A58" s="7"/>
-      <c r="B58" s="7"/>
+      <c r="A58" s="6"/>
+      <c r="B58" s="6"/>
     </row>
     <row r="59" ht="14.25" customHeight="1">
-      <c r="A59" s="7"/>
-      <c r="B59" s="7"/>
+      <c r="A59" s="6"/>
+      <c r="B59" s="6"/>
     </row>
     <row r="60" ht="14.25" customHeight="1">
-      <c r="A60" s="7"/>
-      <c r="B60" s="7"/>
+      <c r="A60" s="6"/>
+      <c r="B60" s="6"/>
     </row>
     <row r="61" ht="14.25" customHeight="1">
-      <c r="A61" s="7"/>
-      <c r="B61" s="7"/>
+      <c r="A61" s="6"/>
+      <c r="B61" s="6"/>
     </row>
     <row r="62" ht="14.25" customHeight="1">
-      <c r="A62" s="7"/>
-      <c r="B62" s="7"/>
+      <c r="A62" s="6"/>
+      <c r="B62" s="6"/>
     </row>
     <row r="63" ht="14.25" customHeight="1">
-      <c r="A63" s="7"/>
-      <c r="B63" s="7"/>
+      <c r="A63" s="6"/>
+      <c r="B63" s="6"/>
     </row>
     <row r="64" ht="14.25" customHeight="1">
-      <c r="A64" s="7"/>
-      <c r="B64" s="7"/>
+      <c r="A64" s="6"/>
+      <c r="B64" s="6"/>
     </row>
     <row r="65" ht="14.25" customHeight="1">
-      <c r="A65" s="7"/>
-      <c r="B65" s="7"/>
+      <c r="A65" s="6"/>
+      <c r="B65" s="6"/>
     </row>
     <row r="66" ht="14.25" customHeight="1">
-      <c r="A66" s="7"/>
-      <c r="B66" s="7"/>
+      <c r="A66" s="6"/>
+      <c r="B66" s="6"/>
     </row>
     <row r="67" ht="14.25" customHeight="1">
-      <c r="A67" s="7"/>
-      <c r="B67" s="7"/>
+      <c r="A67" s="6"/>
+      <c r="B67" s="6"/>
     </row>
     <row r="68" ht="14.25" customHeight="1">
-      <c r="A68" s="7"/>
-      <c r="B68" s="7"/>
+      <c r="A68" s="6"/>
+      <c r="B68" s="6"/>
     </row>
     <row r="69" ht="14.25" customHeight="1">
-      <c r="A69" s="7"/>
-      <c r="B69" s="7"/>
+      <c r="A69" s="6"/>
+      <c r="B69" s="6"/>
     </row>
     <row r="70" ht="14.25" customHeight="1">
-      <c r="A70" s="7"/>
-      <c r="B70" s="7"/>
+      <c r="A70" s="6"/>
+      <c r="B70" s="6"/>
     </row>
     <row r="71" ht="14.25" customHeight="1">
-      <c r="A71" s="7"/>
-      <c r="B71" s="7"/>
+      <c r="A71" s="6"/>
+      <c r="B71" s="6"/>
     </row>
     <row r="72" ht="14.25" customHeight="1">
-      <c r="A72" s="7"/>
-      <c r="B72" s="7"/>
+      <c r="A72" s="6"/>
+      <c r="B72" s="6"/>
     </row>
     <row r="73" ht="14.25" customHeight="1">
-      <c r="A73" s="7"/>
-      <c r="B73" s="7"/>
+      <c r="A73" s="6"/>
+      <c r="B73" s="6"/>
     </row>
     <row r="74" ht="14.25" customHeight="1">
-      <c r="A74" s="7"/>
-      <c r="B74" s="7"/>
+      <c r="A74" s="6"/>
+      <c r="B74" s="6"/>
     </row>
     <row r="75" ht="14.25" customHeight="1">
-      <c r="A75" s="7"/>
-      <c r="B75" s="7"/>
+      <c r="A75" s="6"/>
+      <c r="B75" s="6"/>
     </row>
     <row r="76" ht="14.25" customHeight="1">
-      <c r="A76" s="7"/>
-      <c r="B76" s="7"/>
+      <c r="A76" s="6"/>
+      <c r="B76" s="6"/>
     </row>
     <row r="77" ht="14.25" customHeight="1">
-      <c r="A77" s="7"/>
-      <c r="B77" s="7"/>
+      <c r="A77" s="6"/>
+      <c r="B77" s="6"/>
     </row>
     <row r="78" ht="14.25" customHeight="1">
-      <c r="A78" s="7"/>
-      <c r="B78" s="7"/>
+      <c r="A78" s="6"/>
+      <c r="B78" s="6"/>
     </row>
     <row r="79" ht="14.25" customHeight="1">
-      <c r="A79" s="7"/>
-      <c r="B79" s="7"/>
+      <c r="A79" s="6"/>
+      <c r="B79" s="6"/>
     </row>
     <row r="80" ht="14.25" customHeight="1">
-      <c r="A80" s="7"/>
-      <c r="B80" s="7"/>
+      <c r="A80" s="6"/>
+      <c r="B80" s="6"/>
     </row>
     <row r="81" ht="14.25" customHeight="1">
-      <c r="A81" s="7"/>
-      <c r="B81" s="7"/>
+      <c r="A81" s="6"/>
+      <c r="B81" s="6"/>
     </row>
     <row r="82" ht="14.25" customHeight="1">
-      <c r="A82" s="7"/>
-      <c r="B82" s="7"/>
+      <c r="A82" s="6"/>
+      <c r="B82" s="6"/>
     </row>
     <row r="83" ht="14.25" customHeight="1">
-      <c r="A83" s="7"/>
-      <c r="B83" s="7"/>
+      <c r="A83" s="6"/>
+      <c r="B83" s="6"/>
     </row>
     <row r="84" ht="14.25" customHeight="1">
-      <c r="A84" s="7"/>
-      <c r="B84" s="7"/>
+      <c r="A84" s="6"/>
+      <c r="B84" s="6"/>
     </row>
     <row r="85" ht="14.25" customHeight="1">
-      <c r="A85" s="7"/>
-      <c r="B85" s="7"/>
+      <c r="A85" s="6"/>
+      <c r="B85" s="6"/>
     </row>
     <row r="86" ht="14.25" customHeight="1">
-      <c r="A86" s="7"/>
-      <c r="B86" s="7"/>
+      <c r="A86" s="6"/>
+      <c r="B86" s="6"/>
     </row>
     <row r="87" ht="14.25" customHeight="1">
-      <c r="A87" s="7"/>
-      <c r="B87" s="7"/>
+      <c r="A87" s="6"/>
+      <c r="B87" s="6"/>
     </row>
     <row r="88" ht="14.25" customHeight="1">
-      <c r="A88" s="7"/>
-      <c r="B88" s="7"/>
+      <c r="A88" s="6"/>
+      <c r="B88" s="6"/>
     </row>
     <row r="89" ht="14.25" customHeight="1">
-      <c r="A89" s="7"/>
-      <c r="B89" s="7"/>
+      <c r="A89" s="6"/>
+      <c r="B89" s="6"/>
     </row>
     <row r="90" ht="14.25" customHeight="1">
-      <c r="A90" s="7"/>
-      <c r="B90" s="7"/>
+      <c r="A90" s="6"/>
+      <c r="B90" s="6"/>
     </row>
     <row r="91" ht="14.25" customHeight="1">
-      <c r="A91" s="7"/>
-      <c r="B91" s="7"/>
+      <c r="A91" s="6"/>
+      <c r="B91" s="6"/>
     </row>
     <row r="92" ht="14.25" customHeight="1">
-      <c r="A92" s="7"/>
-      <c r="B92" s="7"/>
+      <c r="A92" s="6"/>
+      <c r="B92" s="6"/>
     </row>
     <row r="93" ht="14.25" customHeight="1">
-      <c r="A93" s="7"/>
-      <c r="B93" s="7"/>
+      <c r="A93" s="6"/>
+      <c r="B93" s="6"/>
     </row>
     <row r="94" ht="14.25" customHeight="1">
-      <c r="A94" s="7"/>
-      <c r="B94" s="7"/>
+      <c r="A94" s="6"/>
+      <c r="B94" s="6"/>
     </row>
     <row r="95" ht="14.25" customHeight="1">
-      <c r="A95" s="7"/>
-      <c r="B95" s="7"/>
+      <c r="A95" s="6"/>
+      <c r="B95" s="6"/>
     </row>
     <row r="96" ht="14.25" customHeight="1">
-      <c r="A96" s="7"/>
-      <c r="B96" s="7"/>
+      <c r="A96" s="6"/>
+      <c r="B96" s="6"/>
     </row>
     <row r="97" ht="14.25" customHeight="1">
-      <c r="A97" s="7"/>
-      <c r="B97" s="7"/>
+      <c r="A97" s="6"/>
+      <c r="B97" s="6"/>
     </row>
     <row r="98" ht="14.25" customHeight="1">
-      <c r="A98" s="7"/>
-      <c r="B98" s="7"/>
+      <c r="A98" s="6"/>
+      <c r="B98" s="6"/>
     </row>
     <row r="99" ht="14.25" customHeight="1">
-      <c r="A99" s="7"/>
-      <c r="B99" s="7"/>
+      <c r="A99" s="6"/>
+      <c r="B99" s="6"/>
     </row>
     <row r="100" ht="14.25" customHeight="1">
-      <c r="A100" s="7"/>
-      <c r="B100" s="7"/>
+      <c r="A100" s="6"/>
+      <c r="B100" s="6"/>
     </row>
     <row r="101" ht="14.25" customHeight="1">
-      <c r="A101" s="7"/>
-      <c r="B101" s="7"/>
+      <c r="A101" s="6"/>
+      <c r="B101" s="6"/>
     </row>
     <row r="102" ht="14.25" customHeight="1">
-      <c r="A102" s="7"/>
-      <c r="B102" s="7"/>
+      <c r="A102" s="6"/>
+      <c r="B102" s="6"/>
     </row>
     <row r="103" ht="14.25" customHeight="1">
-      <c r="A103" s="7"/>
-      <c r="B103" s="7"/>
+      <c r="A103" s="6"/>
+      <c r="B103" s="6"/>
     </row>
     <row r="104" ht="14.25" customHeight="1">
-      <c r="A104" s="7"/>
-      <c r="B104" s="7"/>
+      <c r="A104" s="6"/>
+      <c r="B104" s="6"/>
     </row>
     <row r="105" ht="14.25" customHeight="1">
-      <c r="A105" s="7"/>
-      <c r="B105" s="7"/>
+      <c r="A105" s="6"/>
+      <c r="B105" s="6"/>
     </row>
     <row r="106" ht="14.25" customHeight="1">
-      <c r="A106" s="7"/>
-      <c r="B106" s="7"/>
+      <c r="A106" s="6"/>
+      <c r="B106" s="6"/>
     </row>
     <row r="107" ht="14.25" customHeight="1">
-      <c r="A107" s="7"/>
-      <c r="B107" s="7"/>
+      <c r="A107" s="6"/>
+      <c r="B107" s="6"/>
     </row>
     <row r="108" ht="14.25" customHeight="1">
-      <c r="A108" s="7"/>
-      <c r="B108" s="7"/>
+      <c r="A108" s="6"/>
+      <c r="B108" s="6"/>
     </row>
     <row r="109" ht="14.25" customHeight="1">
-      <c r="A109" s="7"/>
-      <c r="B109" s="7"/>
+      <c r="A109" s="6"/>
+      <c r="B109" s="6"/>
     </row>
     <row r="110" ht="14.25" customHeight="1">
-      <c r="A110" s="7"/>
-      <c r="B110" s="7"/>
+      <c r="A110" s="6"/>
+      <c r="B110" s="6"/>
     </row>
     <row r="111" ht="14.25" customHeight="1">
-      <c r="A111" s="7"/>
-      <c r="B111" s="7"/>
+      <c r="A111" s="6"/>
+      <c r="B111" s="6"/>
     </row>
     <row r="112" ht="14.25" customHeight="1">
-      <c r="A112" s="7"/>
-      <c r="B112" s="7"/>
+      <c r="A112" s="6"/>
+      <c r="B112" s="6"/>
     </row>
     <row r="113" ht="14.25" customHeight="1">
-      <c r="A113" s="7"/>
-      <c r="B113" s="7"/>
+      <c r="A113" s="6"/>
+      <c r="B113" s="6"/>
     </row>
     <row r="114" ht="14.25" customHeight="1">
-      <c r="A114" s="7"/>
-      <c r="B114" s="7"/>
+      <c r="A114" s="6"/>
+      <c r="B114" s="6"/>
     </row>
     <row r="115" ht="14.25" customHeight="1">
-      <c r="A115" s="7"/>
-      <c r="B115" s="7"/>
+      <c r="A115" s="6"/>
+      <c r="B115" s="6"/>
     </row>
     <row r="116" ht="14.25" customHeight="1">
-      <c r="A116" s="7"/>
-      <c r="B116" s="7"/>
+      <c r="A116" s="6"/>
+      <c r="B116" s="6"/>
     </row>
     <row r="117" ht="14.25" customHeight="1">
-      <c r="A117" s="7"/>
-      <c r="B117" s="7"/>
+      <c r="A117" s="6"/>
+      <c r="B117" s="6"/>
     </row>
     <row r="118" ht="14.25" customHeight="1">
-      <c r="A118" s="7"/>
-      <c r="B118" s="7"/>
+      <c r="A118" s="6"/>
+      <c r="B118" s="6"/>
     </row>
     <row r="119" ht="14.25" customHeight="1">
-      <c r="A119" s="7"/>
-      <c r="B119" s="7"/>
+      <c r="A119" s="6"/>
+      <c r="B119" s="6"/>
     </row>
     <row r="120" ht="14.25" customHeight="1">
-      <c r="A120" s="7"/>
-      <c r="B120" s="7"/>
+      <c r="A120" s="6"/>
+      <c r="B120" s="6"/>
     </row>
     <row r="121" ht="14.25" customHeight="1">
-      <c r="A121" s="7"/>
-      <c r="B121" s="7"/>
+      <c r="A121" s="6"/>
+      <c r="B121" s="6"/>
     </row>
     <row r="122" ht="14.25" customHeight="1">
-      <c r="A122" s="7"/>
-      <c r="B122" s="7"/>
+      <c r="A122" s="6"/>
+      <c r="B122" s="6"/>
     </row>
     <row r="123" ht="14.25" customHeight="1">
-      <c r="A123" s="7"/>
-      <c r="B123" s="7"/>
+      <c r="A123" s="6"/>
+      <c r="B123" s="6"/>
     </row>
     <row r="124" ht="14.25" customHeight="1">
-      <c r="A124" s="7"/>
-      <c r="B124" s="7"/>
+      <c r="A124" s="6"/>
+      <c r="B124" s="6"/>
     </row>
     <row r="125" ht="14.25" customHeight="1">
-      <c r="A125" s="7"/>
-      <c r="B125" s="7"/>
+      <c r="A125" s="6"/>
+      <c r="B125" s="6"/>
     </row>
     <row r="126" ht="14.25" customHeight="1">
-      <c r="A126" s="7"/>
-      <c r="B126" s="7"/>
+      <c r="A126" s="6"/>
+      <c r="B126" s="6"/>
     </row>
     <row r="127" ht="14.25" customHeight="1">
-      <c r="A127" s="7"/>
-      <c r="B127" s="7"/>
+      <c r="A127" s="6"/>
+      <c r="B127" s="6"/>
     </row>
     <row r="128" ht="14.25" customHeight="1">
-      <c r="A128" s="7"/>
-      <c r="B128" s="7"/>
+      <c r="A128" s="6"/>
+      <c r="B128" s="6"/>
     </row>
     <row r="129" ht="14.25" customHeight="1">
-      <c r="A129" s="7"/>
-      <c r="B129" s="7"/>
+      <c r="A129" s="6"/>
+      <c r="B129" s="6"/>
     </row>
     <row r="130" ht="14.25" customHeight="1">
-      <c r="A130" s="7"/>
-      <c r="B130" s="7"/>
+      <c r="A130" s="6"/>
+      <c r="B130" s="6"/>
     </row>
     <row r="131" ht="14.25" customHeight="1">
-      <c r="A131" s="7"/>
-      <c r="B131" s="7"/>
+      <c r="A131" s="6"/>
+      <c r="B131" s="6"/>
     </row>
     <row r="132" ht="14.25" customHeight="1">
-      <c r="A132" s="7"/>
-      <c r="B132" s="7"/>
+      <c r="A132" s="6"/>
+      <c r="B132" s="6"/>
     </row>
     <row r="133" ht="14.25" customHeight="1">
-      <c r="A133" s="7"/>
-      <c r="B133" s="7"/>
+      <c r="A133" s="6"/>
+      <c r="B133" s="6"/>
     </row>
     <row r="134" ht="14.25" customHeight="1">
-      <c r="A134" s="7"/>
-      <c r="B134" s="7"/>
+      <c r="A134" s="6"/>
+      <c r="B134" s="6"/>
     </row>
     <row r="135" ht="14.25" customHeight="1">
-      <c r="A135" s="7"/>
-      <c r="B135" s="7"/>
+      <c r="A135" s="6"/>
+      <c r="B135" s="6"/>
     </row>
     <row r="136" ht="14.25" customHeight="1">
-      <c r="A136" s="7"/>
-      <c r="B136" s="7"/>
+      <c r="A136" s="6"/>
+      <c r="B136" s="6"/>
     </row>
     <row r="137" ht="14.25" customHeight="1">
-      <c r="A137" s="7"/>
-      <c r="B137" s="7"/>
+      <c r="A137" s="6"/>
+      <c r="B137" s="6"/>
     </row>
     <row r="138" ht="14.25" customHeight="1">
-      <c r="A138" s="7"/>
-      <c r="B138" s="7"/>
+      <c r="A138" s="6"/>
+      <c r="B138" s="6"/>
     </row>
     <row r="139" ht="14.25" customHeight="1">
-      <c r="A139" s="7"/>
-      <c r="B139" s="7"/>
+      <c r="A139" s="6"/>
+      <c r="B139" s="6"/>
     </row>
     <row r="140" ht="14.25" customHeight="1">
-      <c r="A140" s="7"/>
-      <c r="B140" s="7"/>
+      <c r="A140" s="6"/>
+      <c r="B140" s="6"/>
     </row>
     <row r="141" ht="14.25" customHeight="1">
-      <c r="A141" s="7"/>
-      <c r="B141" s="7"/>
+      <c r="A141" s="6"/>
+      <c r="B141" s="6"/>
     </row>
     <row r="142" ht="14.25" customHeight="1">
-      <c r="A142" s="7"/>
-      <c r="B142" s="7"/>
+      <c r="A142" s="6"/>
+      <c r="B142" s="6"/>
     </row>
     <row r="143" ht="14.25" customHeight="1">
-      <c r="A143" s="7"/>
-      <c r="B143" s="7"/>
+      <c r="A143" s="6"/>
+      <c r="B143" s="6"/>
     </row>
     <row r="144" ht="14.25" customHeight="1">
-      <c r="A144" s="7"/>
-      <c r="B144" s="7"/>
+      <c r="A144" s="6"/>
+      <c r="B144" s="6"/>
     </row>
     <row r="145" ht="14.25" customHeight="1">
-      <c r="A145" s="7"/>
-      <c r="B145" s="7"/>
+      <c r="A145" s="6"/>
+      <c r="B145" s="6"/>
     </row>
     <row r="146" ht="14.25" customHeight="1">
-      <c r="A146" s="7"/>
-      <c r="B146" s="7"/>
+      <c r="A146" s="6"/>
+      <c r="B146" s="6"/>
     </row>
     <row r="147" ht="14.25" customHeight="1">
-      <c r="A147" s="7"/>
-      <c r="B147" s="7"/>
+      <c r="A147" s="6"/>
+      <c r="B147" s="6"/>
     </row>
     <row r="148" ht="14.25" customHeight="1">
-      <c r="A148" s="7"/>
-      <c r="B148" s="7"/>
+      <c r="A148" s="6"/>
+      <c r="B148" s="6"/>
     </row>
     <row r="149" ht="14.25" customHeight="1">
-      <c r="A149" s="7"/>
-      <c r="B149" s="7"/>
+      <c r="A149" s="6"/>
+      <c r="B149" s="6"/>
     </row>
     <row r="150" ht="14.25" customHeight="1">
-      <c r="A150" s="7"/>
-      <c r="B150" s="7"/>
+      <c r="A150" s="6"/>
+      <c r="B150" s="6"/>
     </row>
     <row r="151" ht="14.25" customHeight="1">
-      <c r="A151" s="7"/>
-      <c r="B151" s="7"/>
+      <c r="A151" s="6"/>
+      <c r="B151" s="6"/>
     </row>
     <row r="152" ht="14.25" customHeight="1">
-      <c r="A152" s="7"/>
-      <c r="B152" s="7"/>
+      <c r="A152" s="6"/>
+      <c r="B152" s="6"/>
     </row>
     <row r="153" ht="14.25" customHeight="1">
-      <c r="A153" s="7"/>
-      <c r="B153" s="7"/>
+      <c r="A153" s="6"/>
+      <c r="B153" s="6"/>
     </row>
     <row r="154" ht="14.25" customHeight="1">
-      <c r="A154" s="7"/>
-      <c r="B154" s="7"/>
+      <c r="A154" s="6"/>
+      <c r="B154" s="6"/>
     </row>
     <row r="155" ht="14.25" customHeight="1">
-      <c r="A155" s="7"/>
-      <c r="B155" s="7"/>
+      <c r="A155" s="6"/>
+      <c r="B155" s="6"/>
     </row>
     <row r="156" ht="14.25" customHeight="1">
-      <c r="A156" s="7"/>
-      <c r="B156" s="7"/>
+      <c r="A156" s="6"/>
+      <c r="B156" s="6"/>
     </row>
     <row r="157" ht="14.25" customHeight="1">
-      <c r="A157" s="7"/>
-      <c r="B157" s="7"/>
+      <c r="A157" s="6"/>
+      <c r="B157" s="6"/>
     </row>
     <row r="158" ht="14.25" customHeight="1">
-      <c r="A158" s="7"/>
-      <c r="B158" s="7"/>
+      <c r="A158" s="6"/>
+      <c r="B158" s="6"/>
     </row>
     <row r="159" ht="14.25" customHeight="1">
-      <c r="A159" s="7"/>
-      <c r="B159" s="7"/>
+      <c r="A159" s="6"/>
+      <c r="B159" s="6"/>
     </row>
     <row r="160" ht="14.25" customHeight="1">
-      <c r="A160" s="7"/>
-      <c r="B160" s="7"/>
+      <c r="A160" s="6"/>
+      <c r="B160" s="6"/>
     </row>
     <row r="161" ht="14.25" customHeight="1">
-      <c r="A161" s="7"/>
-      <c r="B161" s="7"/>
+      <c r="A161" s="6"/>
+      <c r="B161" s="6"/>
     </row>
     <row r="162" ht="14.25" customHeight="1">
-      <c r="A162" s="7"/>
-      <c r="B162" s="7"/>
+      <c r="A162" s="6"/>
+      <c r="B162" s="6"/>
     </row>
     <row r="163" ht="14.25" customHeight="1">
-      <c r="A163" s="7"/>
-      <c r="B163" s="7"/>
+      <c r="A163" s="6"/>
+      <c r="B163" s="6"/>
     </row>
     <row r="164" ht="14.25" customHeight="1">
-      <c r="A164" s="7"/>
-      <c r="B164" s="7"/>
+      <c r="A164" s="6"/>
+      <c r="B164" s="6"/>
     </row>
     <row r="165" ht="14.25" customHeight="1">
-      <c r="A165" s="7"/>
-      <c r="B165" s="7"/>
+      <c r="A165" s="6"/>
+      <c r="B165" s="6"/>
     </row>
     <row r="166" ht="14.25" customHeight="1">
-      <c r="A166" s="7"/>
-      <c r="B166" s="7"/>
+      <c r="A166" s="6"/>
+      <c r="B166" s="6"/>
     </row>
     <row r="167" ht="14.25" customHeight="1">
-      <c r="A167" s="7"/>
-      <c r="B167" s="7"/>
+      <c r="A167" s="6"/>
+      <c r="B167" s="6"/>
     </row>
     <row r="168" ht="14.25" customHeight="1">
-      <c r="A168" s="7"/>
-      <c r="B168" s="7"/>
+      <c r="A168" s="6"/>
+      <c r="B168" s="6"/>
     </row>
     <row r="169" ht="14.25" customHeight="1">
-      <c r="A169" s="7"/>
-      <c r="B169" s="7"/>
+      <c r="A169" s="6"/>
+      <c r="B169" s="6"/>
     </row>
     <row r="170" ht="14.25" customHeight="1">
-      <c r="A170" s="7"/>
-      <c r="B170" s="7"/>
+      <c r="A170" s="6"/>
+      <c r="B170" s="6"/>
     </row>
     <row r="171" ht="14.25" customHeight="1">
-      <c r="A171" s="7"/>
-      <c r="B171" s="7"/>
+      <c r="A171" s="6"/>
+      <c r="B171" s="6"/>
     </row>
     <row r="172" ht="14.25" customHeight="1">
-      <c r="A172" s="7"/>
-      <c r="B172" s="7"/>
+      <c r="A172" s="6"/>
+      <c r="B172" s="6"/>
     </row>
     <row r="173" ht="14.25" customHeight="1">
-      <c r="A173" s="7"/>
-      <c r="B173" s="7"/>
+      <c r="A173" s="6"/>
+      <c r="B173" s="6"/>
     </row>
     <row r="174" ht="14.25" customHeight="1">
-      <c r="A174" s="7"/>
-      <c r="B174" s="7"/>
+      <c r="A174" s="6"/>
+      <c r="B174" s="6"/>
     </row>
     <row r="175" ht="14.25" customHeight="1">
-      <c r="A175" s="7"/>
-      <c r="B175" s="7"/>
+      <c r="A175" s="6"/>
+      <c r="B175" s="6"/>
     </row>
     <row r="176" ht="14.25" customHeight="1">
-      <c r="A176" s="7"/>
-      <c r="B176" s="7"/>
+      <c r="A176" s="6"/>
+      <c r="B176" s="6"/>
     </row>
     <row r="177" ht="14.25" customHeight="1">
-      <c r="A177" s="7"/>
-      <c r="B177" s="7"/>
+      <c r="A177" s="6"/>
+      <c r="B177" s="6"/>
     </row>
     <row r="178" ht="14.25" customHeight="1">
-      <c r="A178" s="7"/>
-      <c r="B178" s="7"/>
+      <c r="A178" s="6"/>
+      <c r="B178" s="6"/>
     </row>
     <row r="179" ht="14.25" customHeight="1">
-      <c r="A179" s="7"/>
-      <c r="B179" s="7"/>
+      <c r="A179" s="6"/>
+      <c r="B179" s="6"/>
     </row>
     <row r="180" ht="14.25" customHeight="1">
-      <c r="A180" s="7"/>
-      <c r="B180" s="7"/>
+      <c r="A180" s="6"/>
+      <c r="B180" s="6"/>
     </row>
     <row r="181" ht="14.25" customHeight="1">
-      <c r="A181" s="7"/>
-      <c r="B181" s="7"/>
+      <c r="A181" s="6"/>
+      <c r="B181" s="6"/>
     </row>
     <row r="182" ht="14.25" customHeight="1">
-      <c r="A182" s="7"/>
-      <c r="B182" s="7"/>
+      <c r="A182" s="6"/>
+      <c r="B182" s="6"/>
     </row>
     <row r="183" ht="14.25" customHeight="1">
-      <c r="A183" s="7"/>
-      <c r="B183" s="7"/>
+      <c r="A183" s="6"/>
+      <c r="B183" s="6"/>
     </row>
     <row r="184" ht="14.25" customHeight="1">
-      <c r="A184" s="7"/>
-      <c r="B184" s="7"/>
+      <c r="A184" s="6"/>
+      <c r="B184" s="6"/>
     </row>
     <row r="185" ht="14.25" customHeight="1">
-      <c r="A185" s="7"/>
-      <c r="B185" s="7"/>
+      <c r="A185" s="6"/>
+      <c r="B185" s="6"/>
     </row>
     <row r="186" ht="14.25" customHeight="1">
-      <c r="A186" s="7"/>
-      <c r="B186" s="7"/>
+      <c r="A186" s="6"/>
+      <c r="B186" s="6"/>
     </row>
     <row r="187" ht="14.25" customHeight="1">
-      <c r="A187" s="7"/>
-      <c r="B187" s="7"/>
+      <c r="A187" s="6"/>
+      <c r="B187" s="6"/>
     </row>
     <row r="188" ht="14.25" customHeight="1">
-      <c r="A188" s="7"/>
-      <c r="B188" s="7"/>
+      <c r="A188" s="6"/>
+      <c r="B188" s="6"/>
     </row>
     <row r="189" ht="14.25" customHeight="1">
-      <c r="A189" s="7"/>
-      <c r="B189" s="7"/>
+      <c r="A189" s="6"/>
+      <c r="B189" s="6"/>
     </row>
     <row r="190" ht="14.25" customHeight="1">
-      <c r="A190" s="7"/>
-      <c r="B190" s="7"/>
+      <c r="A190" s="6"/>
+      <c r="B190" s="6"/>
     </row>
     <row r="191" ht="14.25" customHeight="1">
-      <c r="A191" s="7"/>
-      <c r="B191" s="7"/>
+      <c r="A191" s="6"/>
+      <c r="B191" s="6"/>
     </row>
     <row r="192" ht="14.25" customHeight="1">
-      <c r="A192" s="7"/>
-      <c r="B192" s="7"/>
+      <c r="A192" s="6"/>
+      <c r="B192" s="6"/>
     </row>
     <row r="193" ht="14.25" customHeight="1">
-      <c r="A193" s="7"/>
-      <c r="B193" s="7"/>
+      <c r="A193" s="6"/>
+      <c r="B193" s="6"/>
     </row>
     <row r="194" ht="14.25" customHeight="1">
-      <c r="A194" s="7"/>
-      <c r="B194" s="7"/>
+      <c r="A194" s="6"/>
+      <c r="B194" s="6"/>
     </row>
     <row r="195" ht="14.25" customHeight="1">
-      <c r="A195" s="7"/>
-      <c r="B195" s="7"/>
+      <c r="A195" s="6"/>
+      <c r="B195" s="6"/>
     </row>
     <row r="196" ht="14.25" customHeight="1">
-      <c r="A196" s="7"/>
-      <c r="B196" s="7"/>
+      <c r="A196" s="6"/>
+      <c r="B196" s="6"/>
     </row>
     <row r="197" ht="14.25" customHeight="1">
-      <c r="A197" s="7"/>
-      <c r="B197" s="7"/>
+      <c r="A197" s="6"/>
+      <c r="B197" s="6"/>
     </row>
     <row r="198" ht="14.25" customHeight="1">
-      <c r="A198" s="7"/>
-      <c r="B198" s="7"/>
+      <c r="A198" s="6"/>
+      <c r="B198" s="6"/>
     </row>
     <row r="199" ht="14.25" customHeight="1">
-      <c r="A199" s="7"/>
-      <c r="B199" s="7"/>
+      <c r="A199" s="6"/>
+      <c r="B199" s="6"/>
     </row>
     <row r="200" ht="14.25" customHeight="1">
-      <c r="A200" s="7"/>
-      <c r="B200" s="7"/>
+      <c r="A200" s="6"/>
+      <c r="B200" s="6"/>
     </row>
     <row r="201" ht="14.25" customHeight="1">
-      <c r="A201" s="7"/>
-      <c r="B201" s="7"/>
+      <c r="A201" s="6"/>
+      <c r="B201" s="6"/>
     </row>
     <row r="202" ht="14.25" customHeight="1">
-      <c r="A202" s="7"/>
-      <c r="B202" s="7"/>
+      <c r="A202" s="6"/>
+      <c r="B202" s="6"/>
     </row>
     <row r="203" ht="14.25" customHeight="1">
-      <c r="A203" s="7"/>
-      <c r="B203" s="7"/>
+      <c r="A203" s="6"/>
+      <c r="B203" s="6"/>
     </row>
     <row r="204" ht="14.25" customHeight="1">
-      <c r="A204" s="7"/>
-      <c r="B204" s="7"/>
+      <c r="A204" s="6"/>
+      <c r="B204" s="6"/>
     </row>
     <row r="205" ht="14.25" customHeight="1">
-      <c r="A205" s="7"/>
-      <c r="B205" s="7"/>
+      <c r="A205" s="6"/>
+      <c r="B205" s="6"/>
     </row>
     <row r="206" ht="14.25" customHeight="1">
-      <c r="A206" s="7"/>
-      <c r="B206" s="7"/>
+      <c r="A206" s="6"/>
+      <c r="B206" s="6"/>
     </row>
     <row r="207" ht="14.25" customHeight="1">
-      <c r="A207" s="7"/>
-      <c r="B207" s="7"/>
+      <c r="A207" s="6"/>
+      <c r="B207" s="6"/>
     </row>
     <row r="208" ht="14.25" customHeight="1">
-      <c r="A208" s="7"/>
-      <c r="B208" s="7"/>
+      <c r="A208" s="6"/>
+      <c r="B208" s="6"/>
     </row>
     <row r="209" ht="14.25" customHeight="1">
-      <c r="A209" s="7"/>
-      <c r="B209" s="7"/>
+      <c r="A209" s="6"/>
+      <c r="B209" s="6"/>
     </row>
     <row r="210" ht="14.25" customHeight="1">
-      <c r="A210" s="7"/>
-      <c r="B210" s="7"/>
+      <c r="A210" s="6"/>
+      <c r="B210" s="6"/>
     </row>
     <row r="211" ht="14.25" customHeight="1">
-      <c r="A211" s="7"/>
-      <c r="B211" s="7"/>
+      <c r="A211" s="6"/>
+      <c r="B211" s="6"/>
     </row>
     <row r="212" ht="14.25" customHeight="1">
-      <c r="A212" s="7"/>
-      <c r="B212" s="7"/>
+      <c r="A212" s="6"/>
+      <c r="B212" s="6"/>
     </row>
     <row r="213" ht="14.25" customHeight="1">
-      <c r="A213" s="7"/>
-      <c r="B213" s="7"/>
+      <c r="A213" s="6"/>
+      <c r="B213" s="6"/>
     </row>
     <row r="214" ht="14.25" customHeight="1">
-      <c r="A214" s="7"/>
-      <c r="B214" s="7"/>
+      <c r="A214" s="6"/>
+      <c r="B214" s="6"/>
     </row>
     <row r="215" ht="14.25" customHeight="1">
-      <c r="A215" s="7"/>
-      <c r="B215" s="7"/>
+      <c r="A215" s="6"/>
+      <c r="B215" s="6"/>
     </row>
     <row r="216" ht="14.25" customHeight="1">
-      <c r="A216" s="7"/>
-      <c r="B216" s="7"/>
+      <c r="A216" s="6"/>
+      <c r="B216" s="6"/>
     </row>
     <row r="217" ht="14.25" customHeight="1">
-      <c r="A217" s="7"/>
-      <c r="B217" s="7"/>
+      <c r="A217" s="6"/>
+      <c r="B217" s="6"/>
     </row>
     <row r="218" ht="14.25" customHeight="1">
-      <c r="A218" s="7"/>
-      <c r="B218" s="7"/>
+      <c r="A218" s="6"/>
+      <c r="B218" s="6"/>
     </row>
     <row r="219" ht="14.25" customHeight="1">
-      <c r="A219" s="7"/>
-      <c r="B219" s="7"/>
+      <c r="A219" s="6"/>
+      <c r="B219" s="6"/>
     </row>
     <row r="220" ht="14.25" customHeight="1">
-      <c r="A220" s="7"/>
-      <c r="B220" s="7"/>
+      <c r="A220" s="6"/>
+      <c r="B220" s="6"/>
     </row>
     <row r="221" ht="15.75" customHeight="1"/>
     <row r="222" ht="15.75" customHeight="1"/>
